--- a/output/fixed/stress_test_summary.xlsx
+++ b/output/fixed/stress_test_summary.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="123" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="124" uniqueCount="115">
   <si>
     <t>qtr</t>
   </si>
@@ -117,15 +117,15 @@
     <t>NOBU</t>
   </si>
   <si>
+    <t>BBTN</t>
+  </si>
+  <si>
     <t>BABP</t>
   </si>
   <si>
     <t>BNII</t>
   </si>
   <si>
-    <t>BBTN</t>
-  </si>
-  <si>
     <t>BBNI</t>
   </si>
   <si>
@@ -156,24 +156,24 @@
     <t>BBRI</t>
   </si>
   <si>
+    <t>BNGA</t>
+  </si>
+  <si>
     <t>NISP</t>
   </si>
   <si>
-    <t>BNGA</t>
-  </si>
-  <si>
     <t>BSIM</t>
   </si>
   <si>
     <t>MEGA</t>
   </si>
   <si>
+    <t>BJTM</t>
+  </si>
+  <si>
     <t>SDRA</t>
   </si>
   <si>
-    <t>BJTM</t>
-  </si>
-  <si>
     <t>BBCA</t>
   </si>
   <si>
@@ -346,6 +346,9 @@
   </si>
   <si>
     <t>D_sbn</t>
+  </si>
+  <si>
+    <t>e_prop</t>
   </si>
   <si>
     <t>tax_rate</t>
@@ -538,49 +541,49 @@
         <v>45</v>
       </c>
       <c r="C3" s="1">
-        <v>22.482395172119141</v>
+        <v>22.48023796081543</v>
       </c>
       <c r="D3" s="1">
-        <v>22.393531799316406</v>
+        <v>22.391046524047852</v>
       </c>
       <c r="E3" s="1">
-        <v>22.30595588684082</v>
+        <v>22.302944183349609</v>
       </c>
       <c r="F3" s="1">
-        <v>21.309543609619141</v>
+        <v>21.307384490966797</v>
       </c>
       <c r="G3" s="1">
-        <v>21.220914840698242</v>
+        <v>21.218429565429688</v>
       </c>
       <c r="H3" s="1">
-        <v>21.132896423339844</v>
+        <v>21.129884719848633</v>
       </c>
       <c r="I3" s="1">
-        <v>2.2151889801025391</v>
+        <v>2.2514598369598389</v>
       </c>
       <c r="J3" s="1">
-        <v>2.2151889801025391</v>
+        <v>2.2514598369598389</v>
       </c>
       <c r="K3" s="1">
-        <v>2.2151889801025391</v>
+        <v>2.2514598369598389</v>
       </c>
       <c r="L3" s="1">
-        <v>0.49270701408386231</v>
+        <v>0.49013453722000122</v>
       </c>
       <c r="M3" s="1">
-        <v>0.44955036044120789</v>
+        <v>0.44660630822181702</v>
       </c>
       <c r="N3" s="1">
-        <v>0.39499717950820923</v>
+        <v>0.39149126410484314</v>
       </c>
       <c r="O3" s="1">
-        <v>0.24018634855747223</v>
+        <v>0.24511410295963287</v>
       </c>
       <c r="P3" s="1">
-        <v>0.28320330381393433</v>
+        <v>0.28883540630340576</v>
       </c>
       <c r="Q3" s="1">
-        <v>0.34726455807685852</v>
+        <v>0.35394558310508728</v>
       </c>
       <c r="R3" s="1">
         <v>-0.017740942537784576</v>
@@ -600,49 +603,49 @@
         <v>45</v>
       </c>
       <c r="C4" s="1">
-        <v>22.456111907958984</v>
+        <v>22.452136993408203</v>
       </c>
       <c r="D4" s="1">
-        <v>22.255199432373047</v>
+        <v>22.249353408813477</v>
       </c>
       <c r="E4" s="1">
-        <v>22.038839340209961</v>
+        <v>22.029691696166992</v>
       </c>
       <c r="F4" s="1">
-        <v>21.30640983581543</v>
+        <v>21.302433013916016</v>
       </c>
       <c r="G4" s="1">
-        <v>21.105731964111328</v>
+        <v>21.099885940551758</v>
       </c>
       <c r="H4" s="1">
-        <v>20.888069152832031</v>
+        <v>20.878921508789063</v>
       </c>
       <c r="I4" s="1">
-        <v>2.2083706855773926</v>
+        <v>2.2568924427032471</v>
       </c>
       <c r="J4" s="1">
-        <v>2.2079341411590576</v>
+        <v>2.2633206844329834</v>
       </c>
       <c r="K4" s="1">
-        <v>2.2072842121124268</v>
+        <v>2.2693188190460205</v>
       </c>
       <c r="L4" s="1">
-        <v>0.49565079808235168</v>
+        <v>0.49343514442443848</v>
       </c>
       <c r="M4" s="1">
-        <v>0.42031168937683105</v>
+        <v>0.41632750630378723</v>
       </c>
       <c r="N4" s="1">
-        <v>0.32351210713386536</v>
+        <v>0.31697571277618408</v>
       </c>
       <c r="O4" s="1">
-        <v>0.23178383708000183</v>
+        <v>0.23602797091007233</v>
       </c>
       <c r="P4" s="1">
-        <v>0.33846884965896607</v>
+        <v>0.34606754779815674</v>
       </c>
       <c r="Q4" s="1">
-        <v>0.46603944897651672</v>
+        <v>0.47820499539375305</v>
       </c>
       <c r="R4" s="1">
         <v>-0.010321144014596939</v>
@@ -662,49 +665,49 @@
         <v>45</v>
       </c>
       <c r="C5" s="1">
-        <v>22.470066070556641</v>
+        <v>22.464960098266602</v>
       </c>
       <c r="D5" s="1">
-        <v>22.106504440307617</v>
+        <v>22.088130950927734</v>
       </c>
       <c r="E5" s="1">
-        <v>21.714540481567383</v>
+        <v>21.66456413269043</v>
       </c>
       <c r="F5" s="1">
-        <v>21.342531204223633</v>
+        <v>21.337425231933594</v>
       </c>
       <c r="G5" s="1">
-        <v>20.979305267333984</v>
+        <v>20.960931777954102</v>
       </c>
       <c r="H5" s="1">
-        <v>20.584779739379883</v>
+        <v>20.534801483154297</v>
       </c>
       <c r="I5" s="1">
-        <v>2.2151401042938233</v>
+        <v>2.2835750579833984</v>
       </c>
       <c r="J5" s="1">
-        <v>2.2132468223571777</v>
+        <v>2.3756246566772461</v>
       </c>
       <c r="K5" s="1">
-        <v>2.3139948844909668</v>
+        <v>2.5675730705261231</v>
       </c>
       <c r="L5" s="1">
-        <v>0.51270288228988647</v>
+        <v>0.51126635074615479</v>
       </c>
       <c r="M5" s="1">
-        <v>0.39684149622917175</v>
+        <v>0.38248014450073242</v>
       </c>
       <c r="N5" s="1">
-        <v>0.24494832754135132</v>
+        <v>0.20377863943576813</v>
       </c>
       <c r="O5" s="1">
-        <v>0.21527276933193207</v>
+        <v>0.21802417933940887</v>
       </c>
       <c r="P5" s="1">
-        <v>0.38609185814857483</v>
+        <v>0.41330695152282715</v>
       </c>
       <c r="Q5" s="1">
-        <v>0.60734319686889649</v>
+        <v>0.68296492099761963</v>
       </c>
       <c r="R5" s="1">
         <v>-0.035828325897455215</v>
@@ -724,49 +727,49 @@
         <v>45</v>
       </c>
       <c r="C6" s="1">
-        <v>22.47239875793457</v>
+        <v>22.467874526977539</v>
       </c>
       <c r="D6" s="1">
-        <v>21.926902770996094</v>
+        <v>21.876472473144531</v>
       </c>
       <c r="E6" s="1">
-        <v>21.293201446533203</v>
+        <v>21.11314582824707</v>
       </c>
       <c r="F6" s="1">
-        <v>21.366863250732422</v>
+        <v>21.362339019775391</v>
       </c>
       <c r="G6" s="1">
-        <v>20.821121215820313</v>
+        <v>20.77069091796875</v>
       </c>
       <c r="H6" s="1">
-        <v>20.183219909667969</v>
+        <v>20.003164291381836</v>
       </c>
       <c r="I6" s="1">
-        <v>2.2128977775573731</v>
+        <v>2.2563803195953369</v>
       </c>
       <c r="J6" s="1">
-        <v>2.2744717597961426</v>
+        <v>2.569164514541626</v>
       </c>
       <c r="K6" s="1">
-        <v>2.4806675910949707</v>
+        <v>3.0078268051147461</v>
       </c>
       <c r="L6" s="1">
-        <v>0.51449078321456909</v>
+        <v>0.51506465673446655</v>
       </c>
       <c r="M6" s="1">
-        <v>0.35370251536369324</v>
+        <v>0.31969085335731506</v>
       </c>
       <c r="N6" s="1">
-        <v>0.13384121656417847</v>
+        <v>0.024486569687724113</v>
       </c>
       <c r="O6" s="1">
-        <v>0.20884057879447937</v>
+        <v>0.20774145424365997</v>
       </c>
       <c r="P6" s="1">
-        <v>0.46930152177810669</v>
+        <v>0.53251188993453979</v>
       </c>
       <c r="Q6" s="1">
-        <v>0.80430310964584351</v>
+        <v>0.99407404661178589</v>
       </c>
       <c r="R6" s="1">
         <v>-0.022434631362557411</v>
@@ -857,19 +860,19 @@
         <v>13.888044357299805</v>
       </c>
       <c r="E2" s="1">
-        <v>9.5464658737182617</v>
+        <v>9.478846549987793</v>
       </c>
       <c r="F2" s="1">
-        <v>4.6688957214355469</v>
+        <v>4.4121265411376953</v>
       </c>
       <c r="G2" s="1">
         <v>13.888044357299805</v>
       </c>
       <c r="H2" s="1">
-        <v>9.5464658737182617</v>
+        <v>9.478846549987793</v>
       </c>
       <c r="I2" s="1">
-        <v>4.6688957214355469</v>
+        <v>4.4121265411376953</v>
       </c>
       <c r="J2" s="1">
         <v>4.110689640045166</v>
@@ -884,10 +887,10 @@
         <v>10.843605041503906</v>
       </c>
       <c r="N2" s="1">
-        <v>16.957647323608399</v>
+        <v>17.43724250793457</v>
       </c>
       <c r="O2" s="1">
-        <v>24.327592849731445</v>
+        <v>26.141860961914063</v>
       </c>
       <c r="P2" s="1">
         <v>-6.1849474906921387</v>
@@ -913,19 +916,19 @@
         <v>14.748130798339844</v>
       </c>
       <c r="E3" s="1">
-        <v>10.18949031829834</v>
+        <v>10.113382339477539</v>
       </c>
       <c r="F3" s="1">
-        <v>5.1144413948059082</v>
+        <v>4.805572509765625</v>
       </c>
       <c r="G3" s="1">
         <v>14.441656112670898</v>
       </c>
       <c r="H3" s="1">
-        <v>10.18949031829834</v>
+        <v>10.113382339477539</v>
       </c>
       <c r="I3" s="1">
-        <v>5.1144413948059082</v>
+        <v>4.805572509765625</v>
       </c>
       <c r="J3" s="1">
         <v>2.7762997150421143</v>
@@ -940,10 +943,10 @@
         <v>0.87802988290786743</v>
       </c>
       <c r="N3" s="1">
-        <v>6.0766868591308594</v>
+        <v>6.6575255393981934</v>
       </c>
       <c r="O3" s="1">
-        <v>12.611120223999023</v>
+        <v>14.909927368164063</v>
       </c>
       <c r="P3" s="1">
         <v>-7.7250099182128906</v>
@@ -969,19 +972,19 @@
         <v>14.497843742370605</v>
       </c>
       <c r="E4" s="1">
-        <v>11.714064598083496</v>
+        <v>11.664794921875</v>
       </c>
       <c r="F4" s="1">
-        <v>8.6265029907226563</v>
+        <v>8.4240207672119141</v>
       </c>
       <c r="G4" s="1">
         <v>14.497843742370605</v>
       </c>
       <c r="H4" s="1">
-        <v>11.714064598083496</v>
+        <v>11.664794921875</v>
       </c>
       <c r="I4" s="1">
-        <v>8.6265029907226563</v>
+        <v>8.4240207672119141</v>
       </c>
       <c r="J4" s="1">
         <v>9.7105236053466797</v>
@@ -996,10 +999,10 @@
         <v>2.5965206623077393</v>
       </c>
       <c r="N4" s="1">
-        <v>15.81383228302002</v>
+        <v>16.127565383911133</v>
       </c>
       <c r="O4" s="1">
-        <v>31.083106994628906</v>
+        <v>32.367595672607422</v>
       </c>
       <c r="P4" s="1">
         <v>-1.1151782274246216</v>
@@ -1025,19 +1028,19 @@
         <v>10.247621536254883</v>
       </c>
       <c r="E5" s="1">
-        <v>9.7062091827392578</v>
+        <v>9.6573152542114258</v>
       </c>
       <c r="F5" s="1">
-        <v>8.8041276931762695</v>
+        <v>8.605682373046875</v>
       </c>
       <c r="G5" s="1">
         <v>10.247621536254883</v>
       </c>
       <c r="H5" s="1">
-        <v>9.7062091827392578</v>
+        <v>9.6573152542114258</v>
       </c>
       <c r="I5" s="1">
-        <v>8.8041276931762695</v>
+        <v>8.605682373046875</v>
       </c>
       <c r="J5" s="1">
         <v>4.0069994926452637</v>
@@ -1052,10 +1055,10 @@
         <v>2.3136627674102783</v>
       </c>
       <c r="N5" s="1">
-        <v>8.5943269729614258</v>
+        <v>9.0724105834960938</v>
       </c>
       <c r="O5" s="1">
-        <v>16.200885772705078</v>
+        <v>18.133941650390625</v>
       </c>
       <c r="P5" s="1">
         <v>0</v>
@@ -1081,19 +1084,19 @@
         <v>14.429388999938965</v>
       </c>
       <c r="E6" s="1">
-        <v>13.522500991821289</v>
+        <v>13.474980354309082</v>
       </c>
       <c r="F6" s="1">
-        <v>13.09816837310791</v>
+        <v>12.932558059692383</v>
       </c>
       <c r="G6" s="1">
         <v>14.429388999938965</v>
       </c>
       <c r="H6" s="1">
-        <v>13.522500991821289</v>
+        <v>13.474980354309082</v>
       </c>
       <c r="I6" s="1">
-        <v>13.09816837310791</v>
+        <v>12.932558059692383</v>
       </c>
       <c r="J6" s="1">
         <v>2.846287727355957</v>
@@ -1108,10 +1111,10 @@
         <v>0</v>
       </c>
       <c r="N6" s="1">
-        <v>4.9460520744323731</v>
+        <v>5.2408218383789063</v>
       </c>
       <c r="O6" s="1">
-        <v>10.862383842468262</v>
+        <v>11.885794639587402</v>
       </c>
       <c r="P6" s="1">
         <v>0</v>
@@ -1137,19 +1140,19 @@
         <v>18.56671142578125</v>
       </c>
       <c r="E7" s="1">
-        <v>16.375297546386719</v>
+        <v>16.348669052124023</v>
       </c>
       <c r="F7" s="1">
-        <v>13.580124855041504</v>
+        <v>13.318498611450195</v>
       </c>
       <c r="G7" s="1">
         <v>18.482387542724609</v>
       </c>
       <c r="H7" s="1">
-        <v>16.375297546386719</v>
+        <v>16.348669052124023</v>
       </c>
       <c r="I7" s="1">
-        <v>13.580124855041504</v>
+        <v>13.318498611450195</v>
       </c>
       <c r="J7" s="1">
         <v>5.2122688293457031</v>
@@ -1164,10 +1167,10 @@
         <v>6.620354175567627</v>
       </c>
       <c r="N7" s="1">
-        <v>12.654036521911621</v>
+        <v>13.04875659942627</v>
       </c>
       <c r="O7" s="1">
-        <v>20.014286041259766</v>
+        <v>21.520900726318359</v>
       </c>
       <c r="P7" s="1">
         <v>-2.8772175312042236</v>
@@ -1190,22 +1193,22 @@
         <v>23.036062240600586</v>
       </c>
       <c r="D8" s="1">
-        <v>24.01115608215332</v>
+        <v>24.004152297973633</v>
       </c>
       <c r="E8" s="1">
-        <v>18.947124481201172</v>
+        <v>18.891559600830078</v>
       </c>
       <c r="F8" s="1">
-        <v>13.849627494812012</v>
+        <v>13.708035469055176</v>
       </c>
       <c r="G8" s="1">
-        <v>23.211906433105469</v>
+        <v>23.208820343017578</v>
       </c>
       <c r="H8" s="1">
-        <v>18.947124481201172</v>
+        <v>18.891559600830078</v>
       </c>
       <c r="I8" s="1">
-        <v>13.849627494812012</v>
+        <v>13.708035469055176</v>
       </c>
       <c r="J8" s="1">
         <v>0.52955126762390137</v>
@@ -1217,13 +1220,13 @@
         <v>0</v>
       </c>
       <c r="M8" s="1">
-        <v>1.0166753530502319</v>
+        <v>1.1010450124740601</v>
       </c>
       <c r="N8" s="1">
-        <v>2.0204067230224609</v>
+        <v>2.6897656917572022</v>
       </c>
       <c r="O8" s="1">
-        <v>3.7451713085174561</v>
+        <v>5.4443087577819824</v>
       </c>
       <c r="P8" s="1">
         <v>-5.7517280578613281</v>
@@ -1240,55 +1243,55 @@
         <v>33</v>
       </c>
       <c r="B9" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9" s="1">
-        <v>20.894319534301758</v>
+        <v>20.045049667358399</v>
       </c>
       <c r="D9" s="1">
-        <v>20.008285522460938</v>
+        <v>19.551179885864258</v>
       </c>
       <c r="E9" s="1">
-        <v>18.314813613891602</v>
+        <v>18.36785888671875</v>
       </c>
       <c r="F9" s="1">
-        <v>16.08277702331543</v>
+        <v>15.645111083984375</v>
       </c>
       <c r="G9" s="1">
-        <v>20.008285522460938</v>
+        <v>19.551179885864258</v>
       </c>
       <c r="H9" s="1">
-        <v>18.314813613891602</v>
+        <v>18.36785888671875</v>
       </c>
       <c r="I9" s="1">
-        <v>16.08277702331543</v>
+        <v>15.645111083984375</v>
       </c>
       <c r="J9" s="1">
-        <v>3.036236047744751</v>
+        <v>2.9860866069793701</v>
       </c>
       <c r="K9" s="1">
-        <v>164.36265563964844</v>
+        <v>68.826248168945313</v>
       </c>
       <c r="L9" s="1">
         <v>0</v>
       </c>
       <c r="M9" s="1">
-        <v>0.21460218727588654</v>
+        <v>9.726811408996582</v>
       </c>
       <c r="N9" s="1">
-        <v>4.6277785301208496</v>
+        <v>20.176271438598633</v>
       </c>
       <c r="O9" s="1">
-        <v>9.8818511962890625</v>
+        <v>33.584583282470703</v>
       </c>
       <c r="P9" s="1">
-        <v>-1.6971728801727295</v>
+        <v>-0.71068477630615234</v>
       </c>
       <c r="Q9" s="1">
-        <v>5.2417135238647461</v>
+        <v>2.1949474811553955</v>
       </c>
       <c r="R9" s="1">
-        <v>12.063945770263672</v>
+        <v>5.051732063293457</v>
       </c>
     </row>
     <row r="10">
@@ -1296,55 +1299,55 @@
         <v>34</v>
       </c>
       <c r="B10" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" s="1">
-        <v>24.320249557495117</v>
+        <v>20.894319534301758</v>
       </c>
       <c r="D10" s="1">
-        <v>23.935552597045898</v>
+        <v>20.004081726074219</v>
       </c>
       <c r="E10" s="1">
-        <v>20.135768890380859</v>
+        <v>18.251867294311523</v>
       </c>
       <c r="F10" s="1">
-        <v>16.174459457397461</v>
+        <v>15.839443206787109</v>
       </c>
       <c r="G10" s="1">
-        <v>23.935552597045898</v>
+        <v>20.004081726074219</v>
       </c>
       <c r="H10" s="1">
-        <v>20.135768890380859</v>
+        <v>18.251867294311523</v>
       </c>
       <c r="I10" s="1">
-        <v>16.174459457397461</v>
+        <v>15.839443206787109</v>
       </c>
       <c r="J10" s="1">
-        <v>2.0872793197631836</v>
+        <v>3.036236047744751</v>
       </c>
       <c r="K10" s="1">
-        <v>372.96136474609375</v>
+        <v>164.36265563964844</v>
       </c>
       <c r="L10" s="1">
         <v>0</v>
       </c>
       <c r="M10" s="1">
-        <v>1.886405348777771</v>
+        <v>0.27044382691383362</v>
       </c>
       <c r="N10" s="1">
-        <v>4.9179363250732422</v>
+        <v>4.9997811317443848</v>
       </c>
       <c r="O10" s="1">
-        <v>8.7360248565673828</v>
+        <v>11.158867835998535</v>
       </c>
       <c r="P10" s="1">
-        <v>-3.8511176109313965</v>
+        <v>-1.6971728801727295</v>
       </c>
       <c r="Q10" s="1">
-        <v>11.8941650390625</v>
+        <v>5.2417135238647461</v>
       </c>
       <c r="R10" s="1">
-        <v>27.374744415283203</v>
+        <v>12.063945770263672</v>
       </c>
     </row>
     <row r="11">
@@ -1355,52 +1358,52 @@
         <v>3</v>
       </c>
       <c r="C11" s="1">
-        <v>20.045049667358399</v>
+        <v>24.320249557495117</v>
       </c>
       <c r="D11" s="1">
-        <v>19.564504623413086</v>
+        <v>23.929683685302734</v>
       </c>
       <c r="E11" s="1">
-        <v>18.561925888061523</v>
+        <v>20.089265823364258</v>
       </c>
       <c r="F11" s="1">
-        <v>16.244529724121094</v>
+        <v>15.897987365722656</v>
       </c>
       <c r="G11" s="1">
-        <v>19.564504623413086</v>
+        <v>23.929683685302734</v>
       </c>
       <c r="H11" s="1">
-        <v>18.561925888061523</v>
+        <v>20.089265823364258</v>
       </c>
       <c r="I11" s="1">
-        <v>16.244529724121094</v>
+        <v>15.897987365722656</v>
       </c>
       <c r="J11" s="1">
-        <v>2.9860866069793701</v>
+        <v>2.0872793197631836</v>
       </c>
       <c r="K11" s="1">
-        <v>68.826248168945313</v>
+        <v>372.96136474609375</v>
       </c>
       <c r="L11" s="1">
         <v>0</v>
       </c>
       <c r="M11" s="1">
-        <v>9.5423049926757813</v>
+        <v>1.9533945322036743</v>
       </c>
       <c r="N11" s="1">
-        <v>18.822689056396484</v>
+        <v>5.4485220909118652</v>
       </c>
       <c r="O11" s="1">
-        <v>30.305852890014649</v>
+        <v>10.022695541381836</v>
       </c>
       <c r="P11" s="1">
-        <v>-0.71068477630615234</v>
+        <v>-3.8511176109313965</v>
       </c>
       <c r="Q11" s="1">
-        <v>2.1949474811553955</v>
+        <v>11.8941650390625</v>
       </c>
       <c r="R11" s="1">
-        <v>5.051732063293457</v>
+        <v>27.374744415283203</v>
       </c>
     </row>
     <row r="12">
@@ -1414,22 +1417,22 @@
         <v>18.293428421020508</v>
       </c>
       <c r="D12" s="1">
-        <v>18.013042449951172</v>
+        <v>18.006549835205078</v>
       </c>
       <c r="E12" s="1">
-        <v>17.721504211425781</v>
+        <v>17.670412063598633</v>
       </c>
       <c r="F12" s="1">
-        <v>17.359096527099609</v>
+        <v>17.107669830322266</v>
       </c>
       <c r="G12" s="1">
-        <v>18.013042449951172</v>
+        <v>18.006549835205078</v>
       </c>
       <c r="H12" s="1">
-        <v>17.721504211425781</v>
+        <v>17.670412063598633</v>
       </c>
       <c r="I12" s="1">
-        <v>17.359096527099609</v>
+        <v>17.107669830322266</v>
       </c>
       <c r="J12" s="1">
         <v>1.9084329605102539</v>
@@ -1441,13 +1444,13 @@
         <v>0</v>
       </c>
       <c r="M12" s="1">
-        <v>3.6022477149963379</v>
+        <v>3.7006993293762207</v>
       </c>
       <c r="N12" s="1">
-        <v>7.3428926467895508</v>
+        <v>8.1179208755493164</v>
       </c>
       <c r="O12" s="1">
-        <v>12.154997825622559</v>
+        <v>14.03311824798584</v>
       </c>
       <c r="P12" s="1">
         <v>-0.20976652204990387</v>
@@ -1470,22 +1473,22 @@
         <v>17.884822845458984</v>
       </c>
       <c r="D13" s="1">
-        <v>18.434059143066406</v>
+        <v>18.427253723144531</v>
       </c>
       <c r="E13" s="1">
-        <v>18.069585800170899</v>
+        <v>18.015300750732422</v>
       </c>
       <c r="F13" s="1">
-        <v>17.68675422668457</v>
+        <v>17.554515838623047</v>
       </c>
       <c r="G13" s="1">
-        <v>18.01054573059082</v>
+        <v>18.00755500793457</v>
       </c>
       <c r="H13" s="1">
-        <v>17.956897735595703</v>
+        <v>17.953596115112305</v>
       </c>
       <c r="I13" s="1">
-        <v>17.68675422668457</v>
+        <v>17.554515838623047</v>
       </c>
       <c r="J13" s="1">
         <v>0.99057501554489136</v>
@@ -1497,13 +1500,13 @@
         <v>0</v>
       </c>
       <c r="M13" s="1">
-        <v>2.3144824504852295</v>
+        <v>2.4200980663299561</v>
       </c>
       <c r="N13" s="1">
-        <v>5.5058174133300781</v>
+        <v>6.348048210144043</v>
       </c>
       <c r="O13" s="1">
-        <v>9.7452125549316406</v>
+        <v>11.78919506072998</v>
       </c>
       <c r="P13" s="1">
         <v>-0.55528020858764648</v>
@@ -1529,19 +1532,19 @@
         <v>22.156579971313477</v>
       </c>
       <c r="E14" s="1">
-        <v>20.47514533996582</v>
+        <v>20.439937591552734</v>
       </c>
       <c r="F14" s="1">
-        <v>17.818458557128906</v>
+        <v>17.696060180664063</v>
       </c>
       <c r="G14" s="1">
         <v>22.156579971313477</v>
       </c>
       <c r="H14" s="1">
-        <v>20.47514533996582</v>
+        <v>20.439937591552734</v>
       </c>
       <c r="I14" s="1">
-        <v>17.818458557128906</v>
+        <v>17.696060180664063</v>
       </c>
       <c r="J14" s="1">
         <v>2.441215991973877</v>
@@ -1556,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="N14" s="1">
-        <v>2.2993264198303223</v>
+        <v>2.4255015850067139</v>
       </c>
       <c r="O14" s="1">
-        <v>5.0245575904846191</v>
+        <v>5.4615211486816406</v>
       </c>
       <c r="P14" s="1">
         <v>-1.0744326114654541</v>
@@ -1582,22 +1585,22 @@
         <v>23.573837280273438</v>
       </c>
       <c r="D15" s="1">
-        <v>22.545734405517578</v>
+        <v>22.538822174072266</v>
       </c>
       <c r="E15" s="1">
-        <v>20.757646560668945</v>
+        <v>20.631675720214844</v>
       </c>
       <c r="F15" s="1">
-        <v>18.056961059570313</v>
+        <v>17.741329193115234</v>
       </c>
       <c r="G15" s="1">
-        <v>22.545734405517578</v>
+        <v>22.538822174072266</v>
       </c>
       <c r="H15" s="1">
-        <v>20.757646560668945</v>
+        <v>20.631675720214844</v>
       </c>
       <c r="I15" s="1">
-        <v>18.056961059570313</v>
+        <v>17.741329193115234</v>
       </c>
       <c r="J15" s="1">
         <v>3.2154037952423096</v>
@@ -1609,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="M15" s="1">
-        <v>1.5760918855667114</v>
+        <v>1.6574674844741821</v>
       </c>
       <c r="N15" s="1">
-        <v>6.2093687057495117</v>
+        <v>6.8096075057983398</v>
       </c>
       <c r="O15" s="1">
-        <v>11.871732711791992</v>
+        <v>13.315217018127441</v>
       </c>
       <c r="P15" s="1">
         <v>-1.8186583518981934</v>
@@ -1638,22 +1641,22 @@
         <v>28.380533218383789</v>
       </c>
       <c r="D16" s="1">
-        <v>28.237459182739258</v>
+        <v>28.231882095336914</v>
       </c>
       <c r="E16" s="1">
-        <v>23.61994743347168</v>
+        <v>23.568092346191406</v>
       </c>
       <c r="F16" s="1">
-        <v>19.060783386230469</v>
+        <v>18.844953536987305</v>
       </c>
       <c r="G16" s="1">
-        <v>28.077304840087891</v>
+        <v>28.07227897644043</v>
       </c>
       <c r="H16" s="1">
-        <v>23.61994743347168</v>
+        <v>23.568092346191406</v>
       </c>
       <c r="I16" s="1">
-        <v>19.060783386230469</v>
+        <v>18.844953536987305</v>
       </c>
       <c r="J16" s="1">
         <v>0.76714533567428589</v>
@@ -1665,13 +1668,13 @@
         <v>0</v>
       </c>
       <c r="M16" s="1">
-        <v>14.080464363098145</v>
+        <v>14.135010719299316</v>
       </c>
       <c r="N16" s="1">
-        <v>15.93162727355957</v>
+        <v>16.438617706298828</v>
       </c>
       <c r="O16" s="1">
-        <v>18.393299102783203</v>
+        <v>19.643228530883789</v>
       </c>
       <c r="P16" s="1">
         <v>-4.1387767791748047</v>
@@ -1694,22 +1697,22 @@
         <v>20.405284881591797</v>
       </c>
       <c r="D17" s="1">
-        <v>20.543916702270508</v>
+        <v>20.536464691162109</v>
       </c>
       <c r="E17" s="1">
-        <v>20.002277374267578</v>
+        <v>19.937047958374023</v>
       </c>
       <c r="F17" s="1">
-        <v>19.255672454833984</v>
+        <v>18.929666519165039</v>
       </c>
       <c r="G17" s="1">
-        <v>20.418262481689453</v>
+        <v>20.41484260559082</v>
       </c>
       <c r="H17" s="1">
-        <v>20.002277374267578</v>
+        <v>19.937047958374023</v>
       </c>
       <c r="I17" s="1">
-        <v>19.255672454833984</v>
+        <v>18.929666519165039</v>
       </c>
       <c r="J17" s="1">
         <v>1.8116350173950195</v>
@@ -1721,13 +1724,13 @@
         <v>0</v>
       </c>
       <c r="M17" s="1">
-        <v>4.3545289039611816</v>
+        <v>4.4558606147766113</v>
       </c>
       <c r="N17" s="1">
-        <v>9.6535243988037109</v>
+        <v>10.540552139282227</v>
       </c>
       <c r="O17" s="1">
-        <v>16.298671722412109</v>
+        <v>18.472793579101563</v>
       </c>
       <c r="P17" s="1">
         <v>-0.51077693700790405</v>
@@ -1753,19 +1756,19 @@
         <v>22.591592788696289</v>
       </c>
       <c r="E18" s="1">
-        <v>21.206880569458008</v>
+        <v>21.193620681762695</v>
       </c>
       <c r="F18" s="1">
-        <v>19.402114868164063</v>
+        <v>19.281576156616211</v>
       </c>
       <c r="G18" s="1">
         <v>22.591592788696289</v>
       </c>
       <c r="H18" s="1">
-        <v>21.206880569458008</v>
+        <v>21.193620681762695</v>
       </c>
       <c r="I18" s="1">
-        <v>19.402114868164063</v>
+        <v>19.281576156616211</v>
       </c>
       <c r="J18" s="1">
         <v>2.153038501739502</v>
@@ -1780,10 +1783,10 @@
         <v>0</v>
       </c>
       <c r="N18" s="1">
-        <v>2.4982748031616211</v>
+        <v>2.6554343700408936</v>
       </c>
       <c r="O18" s="1">
-        <v>5.5129833221435547</v>
+        <v>6.0813584327697754</v>
       </c>
       <c r="P18" s="1">
         <v>-1.3891488313674927</v>
@@ -1809,19 +1812,19 @@
         <v>31.179271697998047</v>
       </c>
       <c r="E19" s="1">
-        <v>25.787624359130859</v>
+        <v>25.725887298583984</v>
       </c>
       <c r="F19" s="1">
-        <v>20.014373779296875</v>
+        <v>19.797641754150391</v>
       </c>
       <c r="G19" s="1">
         <v>31.179271697998047</v>
       </c>
       <c r="H19" s="1">
-        <v>25.787624359130859</v>
+        <v>25.725887298583984</v>
       </c>
       <c r="I19" s="1">
-        <v>20.014373779296875</v>
+        <v>19.797641754150391</v>
       </c>
       <c r="J19" s="1">
         <v>4.3763270378112793</v>
@@ -1836,10 +1839,10 @@
         <v>0</v>
       </c>
       <c r="N19" s="1">
-        <v>7.6835002899169922</v>
+        <v>7.8815255165100098</v>
       </c>
       <c r="O19" s="1">
-        <v>16.49116325378418</v>
+        <v>17.183755874633789</v>
       </c>
       <c r="P19" s="1">
         <v>-2.3791112899780273</v>
@@ -1862,22 +1865,22 @@
         <v>22.279584884643555</v>
       </c>
       <c r="D20" s="1">
-        <v>21.791997909545898</v>
+        <v>21.785884857177734</v>
       </c>
       <c r="E20" s="1">
-        <v>21.46629524230957</v>
+        <v>21.41783332824707</v>
       </c>
       <c r="F20" s="1">
-        <v>21.228683471679688</v>
+        <v>21.110713958740234</v>
       </c>
       <c r="G20" s="1">
-        <v>21.791997909545898</v>
+        <v>21.785884857177734</v>
       </c>
       <c r="H20" s="1">
-        <v>21.46629524230957</v>
+        <v>21.41783332824707</v>
       </c>
       <c r="I20" s="1">
-        <v>21.228683471679688</v>
+        <v>21.110713958740234</v>
       </c>
       <c r="J20" s="1">
         <v>1.231325626373291</v>
@@ -1889,13 +1892,13 @@
         <v>0</v>
       </c>
       <c r="M20" s="1">
-        <v>11.357086181640625</v>
+        <v>11.433267593383789</v>
       </c>
       <c r="N20" s="1">
-        <v>13.719327926635742</v>
+        <v>14.322908401489258</v>
       </c>
       <c r="O20" s="1">
-        <v>16.826021194458008</v>
+        <v>18.289754867553711</v>
       </c>
       <c r="P20" s="1">
         <v>-0.19765809178352356</v>
@@ -1921,19 +1924,19 @@
         <v>22.169673919677734</v>
       </c>
       <c r="E21" s="1">
-        <v>21.816368103027344</v>
+        <v>21.786811828613281</v>
       </c>
       <c r="F21" s="1">
-        <v>21.496490478515625</v>
+        <v>21.377309799194336</v>
       </c>
       <c r="G21" s="1">
         <v>21.65791130065918</v>
       </c>
       <c r="H21" s="1">
-        <v>21.608291625976563</v>
+        <v>21.607963562011719</v>
       </c>
       <c r="I21" s="1">
-        <v>21.496490478515625</v>
+        <v>21.377309799194336</v>
       </c>
       <c r="J21" s="1">
         <v>2.8153021335601807</v>
@@ -1948,10 +1951,10 @@
         <v>8.5872840881347656</v>
       </c>
       <c r="N21" s="1">
-        <v>11.868636131286621</v>
+        <v>12.250298500061035</v>
       </c>
       <c r="O21" s="1">
-        <v>15.984721183776855</v>
+        <v>17.517854690551758</v>
       </c>
       <c r="P21" s="1">
         <v>-0.18233299255371094</v>
@@ -1971,52 +1974,52 @@
         <v>3</v>
       </c>
       <c r="C22" s="1">
-        <v>23.088916778564453</v>
+        <v>23.519998550415039</v>
       </c>
       <c r="D22" s="1">
-        <v>22.741777420043945</v>
+        <v>23.194978713989258</v>
       </c>
       <c r="E22" s="1">
-        <v>22.494880676269531</v>
+        <v>22.658670425415039</v>
       </c>
       <c r="F22" s="1">
-        <v>22.173809051513672</v>
+        <v>21.965524673461914</v>
       </c>
       <c r="G22" s="1">
-        <v>22.741777420043945</v>
+        <v>23.194978713989258</v>
       </c>
       <c r="H22" s="1">
-        <v>22.494880676269531</v>
+        <v>22.658670425415039</v>
       </c>
       <c r="I22" s="1">
-        <v>22.173809051513672</v>
+        <v>21.965524673461914</v>
       </c>
       <c r="J22" s="1">
-        <v>1.8331828117370605</v>
+        <v>1.8094415664672852</v>
       </c>
       <c r="K22" s="1">
-        <v>18.29620361328125</v>
+        <v>58.85650634765625</v>
       </c>
       <c r="L22" s="1">
         <v>0</v>
       </c>
       <c r="M22" s="1">
-        <v>0.56653892993927002</v>
+        <v>4.300234317779541</v>
       </c>
       <c r="N22" s="1">
-        <v>2.7199757099151611</v>
+        <v>7.8137989044189453</v>
       </c>
       <c r="O22" s="1">
-        <v>5.5696587562561035</v>
+        <v>12.455674171447754</v>
       </c>
       <c r="P22" s="1">
-        <v>-0.18892258405685425</v>
+        <v>-0.60773938894271851</v>
       </c>
       <c r="Q22" s="1">
-        <v>0.58348685503005981</v>
+        <v>1.8770014047622681</v>
       </c>
       <c r="R22" s="1">
-        <v>1.3429108858108521</v>
+        <v>4.3199691772460938</v>
       </c>
     </row>
     <row r="23">
@@ -2027,52 +2030,52 @@
         <v>3</v>
       </c>
       <c r="C23" s="1">
-        <v>23.519998550415039</v>
+        <v>23.088916778564453</v>
       </c>
       <c r="D23" s="1">
-        <v>23.201093673706055</v>
+        <v>22.736440658569336</v>
       </c>
       <c r="E23" s="1">
-        <v>22.707242965698242</v>
+        <v>22.453287124633789</v>
       </c>
       <c r="F23" s="1">
-        <v>22.192785263061523</v>
+        <v>22.068267822265625</v>
       </c>
       <c r="G23" s="1">
-        <v>23.201093673706055</v>
+        <v>22.736440658569336</v>
       </c>
       <c r="H23" s="1">
-        <v>22.707242965698242</v>
+        <v>22.453287124633789</v>
       </c>
       <c r="I23" s="1">
-        <v>22.192785263061523</v>
+        <v>22.068267822265625</v>
       </c>
       <c r="J23" s="1">
-        <v>1.8094415664672852</v>
+        <v>1.8331828117370605</v>
       </c>
       <c r="K23" s="1">
-        <v>58.85650634765625</v>
+        <v>18.29620361328125</v>
       </c>
       <c r="L23" s="1">
         <v>0</v>
       </c>
       <c r="M23" s="1">
-        <v>4.228083610534668</v>
+        <v>0.63065856695175171</v>
       </c>
       <c r="N23" s="1">
-        <v>7.2407383918762207</v>
+        <v>3.2198450565338135</v>
       </c>
       <c r="O23" s="1">
-        <v>11.065567016601563</v>
+        <v>6.8332977294921875</v>
       </c>
       <c r="P23" s="1">
-        <v>-0.60773938894271851</v>
+        <v>-0.18892258405685425</v>
       </c>
       <c r="Q23" s="1">
-        <v>1.8770014047622681</v>
+        <v>0.58348685503005981</v>
       </c>
       <c r="R23" s="1">
-        <v>4.3199691772460938</v>
+        <v>1.3429108858108521</v>
       </c>
     </row>
     <row r="24">
@@ -2089,19 +2092,19 @@
         <v>26.339178085327149</v>
       </c>
       <c r="E24" s="1">
-        <v>25.159797668457031</v>
+        <v>25.13648796081543</v>
       </c>
       <c r="F24" s="1">
-        <v>23.141826629638672</v>
+        <v>23.060474395751953</v>
       </c>
       <c r="G24" s="1">
         <v>26.339178085327149</v>
       </c>
       <c r="H24" s="1">
-        <v>25.159797668457031</v>
+        <v>25.13648796081543</v>
       </c>
       <c r="I24" s="1">
-        <v>23.141826629638672</v>
+        <v>23.060474395751953</v>
       </c>
       <c r="J24" s="1">
         <v>1.4881768226623535</v>
@@ -2116,10 +2119,10 @@
         <v>0</v>
       </c>
       <c r="N24" s="1">
-        <v>1.4879814386367798</v>
+        <v>1.5750131607055664</v>
       </c>
       <c r="O24" s="1">
-        <v>3.2515439987182617</v>
+        <v>3.5541348457336426</v>
       </c>
       <c r="P24" s="1">
         <v>-0.86902743577957153</v>
@@ -2142,22 +2145,22 @@
         <v>25.033319473266602</v>
       </c>
       <c r="D25" s="1">
-        <v>25.223421096801758</v>
+        <v>25.217960357666016</v>
       </c>
       <c r="E25" s="1">
-        <v>25.059413909912109</v>
+        <v>25.020689010620117</v>
       </c>
       <c r="F25" s="1">
-        <v>24.857988357543945</v>
+        <v>24.761962890625</v>
       </c>
       <c r="G25" s="1">
-        <v>25.066194534301758</v>
+        <v>25.063941955566406</v>
       </c>
       <c r="H25" s="1">
-        <v>25.04096794128418</v>
+        <v>25.020689010620117</v>
       </c>
       <c r="I25" s="1">
-        <v>24.857988357543945</v>
+        <v>24.761962890625</v>
       </c>
       <c r="J25" s="1">
         <v>1.5383285284042358</v>
@@ -2169,13 +2172,13 @@
         <v>0</v>
       </c>
       <c r="M25" s="1">
-        <v>1.9665745496749878</v>
+        <v>2.0270929336547852</v>
       </c>
       <c r="N25" s="1">
-        <v>3.525313138961792</v>
+        <v>3.9545767307281494</v>
       </c>
       <c r="O25" s="1">
-        <v>5.6365466117858887</v>
+        <v>6.6969466209411621</v>
       </c>
       <c r="P25" s="1">
         <v>-0.11669077724218369</v>
@@ -2195,52 +2198,52 @@
         <v>2</v>
       </c>
       <c r="C26" s="1">
-        <v>32.023998260498047</v>
+        <v>27.585422515869141</v>
       </c>
       <c r="D26" s="1">
-        <v>30.280115127563477</v>
+        <v>26.890453338623047</v>
       </c>
       <c r="E26" s="1">
-        <v>27.872150421142578</v>
+        <v>26.2244873046875</v>
       </c>
       <c r="F26" s="1">
-        <v>25.274126052856445</v>
+        <v>24.914407730102539</v>
       </c>
       <c r="G26" s="1">
-        <v>30.280115127563477</v>
+        <v>26.890453338623047</v>
       </c>
       <c r="H26" s="1">
-        <v>27.872150421142578</v>
+        <v>26.2244873046875</v>
       </c>
       <c r="I26" s="1">
-        <v>25.274126052856445</v>
+        <v>24.914407730102539</v>
       </c>
       <c r="J26" s="1">
-        <v>5.4320864677429199</v>
+        <v>3.7642781734466553</v>
       </c>
       <c r="K26" s="1">
-        <v>143.84133911132813</v>
+        <v>8.1391191482543945</v>
       </c>
       <c r="L26" s="1">
         <v>0</v>
       </c>
       <c r="M26" s="1">
-        <v>2.8480558395385742</v>
+        <v>9.6281051635742188</v>
       </c>
       <c r="N26" s="1">
-        <v>6.083439826965332</v>
+        <v>15.586196899414063</v>
       </c>
       <c r="O26" s="1">
-        <v>10.041783332824707</v>
+        <v>23.184902191162109</v>
       </c>
       <c r="P26" s="1">
-        <v>-1.4852741956710816</v>
+        <v>-0.084042765200138092</v>
       </c>
       <c r="Q26" s="1">
-        <v>4.5872650146484375</v>
+        <v>0.25956583023071289</v>
       </c>
       <c r="R26" s="1">
-        <v>10.557712554931641</v>
+        <v>0.59739774465560913</v>
       </c>
     </row>
     <row r="27">
@@ -2251,52 +2254,52 @@
         <v>2</v>
       </c>
       <c r="C27" s="1">
-        <v>27.585422515869141</v>
+        <v>32.023998260498047</v>
       </c>
       <c r="D27" s="1">
-        <v>26.896343231201172</v>
+        <v>30.280115127563477</v>
       </c>
       <c r="E27" s="1">
-        <v>26.285453796386719</v>
+        <v>27.809898376464844</v>
       </c>
       <c r="F27" s="1">
-        <v>25.313243865966797</v>
+        <v>25.037725448608399</v>
       </c>
       <c r="G27" s="1">
-        <v>26.896343231201172</v>
+        <v>30.280115127563477</v>
       </c>
       <c r="H27" s="1">
-        <v>26.285453796386719</v>
+        <v>27.809898376464844</v>
       </c>
       <c r="I27" s="1">
-        <v>25.313243865966797</v>
+        <v>25.037725448608399</v>
       </c>
       <c r="J27" s="1">
-        <v>3.7642781734466553</v>
+        <v>5.4320864677429199</v>
       </c>
       <c r="K27" s="1">
-        <v>8.1391191482543945</v>
+        <v>143.84133911132813</v>
       </c>
       <c r="L27" s="1">
         <v>0</v>
       </c>
       <c r="M27" s="1">
-        <v>9.5688142776489258</v>
+        <v>2.8480558395385742</v>
       </c>
       <c r="N27" s="1">
-        <v>14.972907066345215</v>
+        <v>6.3015122413635254</v>
       </c>
       <c r="O27" s="1">
-        <v>21.562625885009766</v>
+        <v>10.83763313293457</v>
       </c>
       <c r="P27" s="1">
-        <v>-0.084042765200138092</v>
+        <v>-1.4852741956710816</v>
       </c>
       <c r="Q27" s="1">
-        <v>0.25956583023071289</v>
+        <v>4.5872650146484375</v>
       </c>
       <c r="R27" s="1">
-        <v>0.59739774465560913</v>
+        <v>10.557712554931641</v>
       </c>
     </row>
     <row r="28">
@@ -2310,22 +2313,22 @@
         <v>27.39015007019043</v>
       </c>
       <c r="D28" s="1">
-        <v>27.75529670715332</v>
+        <v>27.750946044921875</v>
       </c>
       <c r="E28" s="1">
-        <v>27.560453414916992</v>
+        <v>27.517244338989258</v>
       </c>
       <c r="F28" s="1">
-        <v>27.317119598388672</v>
+        <v>27.199169158935547</v>
       </c>
       <c r="G28" s="1">
-        <v>27.468576431274414</v>
+        <v>27.465757369995117</v>
       </c>
       <c r="H28" s="1">
-        <v>27.440326690673828</v>
+        <v>27.437219619750977</v>
       </c>
       <c r="I28" s="1">
-        <v>27.317119598388672</v>
+        <v>27.199169158935547</v>
       </c>
       <c r="J28" s="1">
         <v>1.7580658197402954</v>
@@ -2337,13 +2340,13 @@
         <v>0</v>
       </c>
       <c r="M28" s="1">
-        <v>1.5349183082580566</v>
+        <v>1.5790036916732788</v>
       </c>
       <c r="N28" s="1">
-        <v>3.3422143459320068</v>
+        <v>3.7799456119537354</v>
       </c>
       <c r="O28" s="1">
-        <v>5.7616691589355469</v>
+        <v>6.9521279335021973</v>
       </c>
       <c r="P28" s="1">
         <v>-0.092668108642101288</v>
@@ -2366,22 +2369,22 @@
         <v>30.68280029296875</v>
       </c>
       <c r="D29" s="1">
-        <v>28.576875686645508</v>
+        <v>28.572391510009766</v>
       </c>
       <c r="E29" s="1">
-        <v>28.363227844238281</v>
+        <v>28.274940490722656</v>
       </c>
       <c r="F29" s="1">
-        <v>28.223073959350586</v>
+        <v>27.924131393432617</v>
       </c>
       <c r="G29" s="1">
-        <v>28.576875686645508</v>
+        <v>28.572391510009766</v>
       </c>
       <c r="H29" s="1">
-        <v>28.363227844238281</v>
+        <v>28.274940490722656</v>
       </c>
       <c r="I29" s="1">
-        <v>28.223073959350586</v>
+        <v>27.924131393432617</v>
       </c>
       <c r="J29" s="1">
         <v>1.2923356294631958</v>
@@ -2393,13 +2396,13 @@
         <v>0</v>
       </c>
       <c r="M29" s="1">
-        <v>11.83489990234375</v>
+        <v>11.875471115112305</v>
       </c>
       <c r="N29" s="1">
-        <v>12.999580383300781</v>
+        <v>13.389826774597168</v>
       </c>
       <c r="O29" s="1">
-        <v>14.639804840087891</v>
+        <v>15.733658790588379</v>
       </c>
       <c r="P29" s="1">
         <v>-0.051728162914514542</v>
@@ -2425,19 +2428,19 @@
         <v>31.089242935180664</v>
       </c>
       <c r="E30" s="1">
-        <v>30.461736679077148</v>
+        <v>30.429536819458008</v>
       </c>
       <c r="F30" s="1">
-        <v>29.693563461303711</v>
+        <v>29.554224014282227</v>
       </c>
       <c r="G30" s="1">
         <v>31.089242935180664</v>
       </c>
       <c r="H30" s="1">
-        <v>30.461736679077148</v>
+        <v>30.429536819458008</v>
       </c>
       <c r="I30" s="1">
-        <v>29.693563461303711</v>
+        <v>29.554224014282227</v>
       </c>
       <c r="J30" s="1">
         <v>2.8590431213378906</v>
@@ -2452,10 +2455,10 @@
         <v>0</v>
       </c>
       <c r="N30" s="1">
-        <v>2.2548892498016358</v>
+        <v>2.3855111598968506</v>
       </c>
       <c r="O30" s="1">
-        <v>4.9491491317749024</v>
+        <v>5.4051594734191895</v>
       </c>
       <c r="P30" s="1">
         <v>-0.25040501356124878</v>
@@ -2478,22 +2481,22 @@
         <v>32.963825225830078</v>
       </c>
       <c r="D31" s="1">
-        <v>31.668182373046875</v>
+        <v>31.662092208862305</v>
       </c>
       <c r="E31" s="1">
-        <v>31.427616119384766</v>
+        <v>31.379671096801758</v>
       </c>
       <c r="F31" s="1">
-        <v>31.196176528930664</v>
+        <v>31.071037292480469</v>
       </c>
       <c r="G31" s="1">
-        <v>31.668182373046875</v>
+        <v>31.662092208862305</v>
       </c>
       <c r="H31" s="1">
-        <v>31.427616119384766</v>
+        <v>31.379671096801758</v>
       </c>
       <c r="I31" s="1">
-        <v>31.196176528930664</v>
+        <v>31.071037292480469</v>
       </c>
       <c r="J31" s="1">
         <v>1.812983512878418</v>
@@ -2505,13 +2508,13 @@
         <v>0</v>
       </c>
       <c r="M31" s="1">
-        <v>2.8071432113647461</v>
+        <v>2.8584282398223877</v>
       </c>
       <c r="N31" s="1">
-        <v>4.6662836074829102</v>
+        <v>5.069890022277832</v>
       </c>
       <c r="O31" s="1">
-        <v>7.0708847045898438</v>
+        <v>8.0489082336425781</v>
       </c>
       <c r="P31" s="1">
         <v>-0.026917701587080956</v>
@@ -2534,22 +2537,22 @@
         <v>40.793071746826172</v>
       </c>
       <c r="D32" s="1">
-        <v>35.480319976806641</v>
+        <v>35.465656280517578</v>
       </c>
       <c r="E32" s="1">
-        <v>34.314289093017578</v>
+        <v>34.198135375976563</v>
       </c>
       <c r="F32" s="1">
-        <v>32.936508178710938</v>
+        <v>32.653774261474609</v>
       </c>
       <c r="G32" s="1">
-        <v>35.480319976806641</v>
+        <v>35.465656280517578</v>
       </c>
       <c r="H32" s="1">
-        <v>34.314289093017578</v>
+        <v>34.198135375976563</v>
       </c>
       <c r="I32" s="1">
-        <v>32.936508178710938</v>
+        <v>32.653774261474609</v>
       </c>
       <c r="J32" s="1">
         <v>2.0582499504089356</v>
@@ -2561,13 +2564,13 @@
         <v>0</v>
       </c>
       <c r="M32" s="1">
-        <v>5.0781726837158203</v>
+        <v>5.1170773506164551</v>
       </c>
       <c r="N32" s="1">
-        <v>6.9046788215637207</v>
+        <v>7.2128152847290039</v>
       </c>
       <c r="O32" s="1">
-        <v>9.1859331130981445</v>
+        <v>9.93316650390625</v>
       </c>
       <c r="P32" s="1">
         <v>-0.33560475707054138</v>
@@ -2593,19 +2596,19 @@
         <v>35.453342437744141</v>
       </c>
       <c r="E33" s="1">
-        <v>34.484260559082031</v>
+        <v>34.447845458984375</v>
       </c>
       <c r="F33" s="1">
-        <v>33.378635406494141</v>
+        <v>33.086063385009766</v>
       </c>
       <c r="G33" s="1">
         <v>35.453342437744141</v>
       </c>
       <c r="H33" s="1">
-        <v>34.484260559082031</v>
+        <v>34.447845458984375</v>
       </c>
       <c r="I33" s="1">
-        <v>33.378635406494141</v>
+        <v>33.086063385009766</v>
       </c>
       <c r="J33" s="1">
         <v>3.0391237735748291</v>
@@ -2620,10 +2623,10 @@
         <v>58.534774780273438</v>
       </c>
       <c r="N33" s="1">
-        <v>61.014320373535156</v>
+        <v>61.288604736328125</v>
       </c>
       <c r="O33" s="1">
-        <v>63.990016937255859</v>
+        <v>64.9110107421875</v>
       </c>
       <c r="P33" s="1">
         <v>-0.67763090133666992</v>
@@ -2646,22 +2649,22 @@
         <v>35.928680419921875</v>
       </c>
       <c r="D34" s="1">
-        <v>34.159664154052734</v>
+        <v>34.155544281005859</v>
       </c>
       <c r="E34" s="1">
-        <v>33.823104858398438</v>
+        <v>33.781227111816406</v>
       </c>
       <c r="F34" s="1">
-        <v>33.493305206298828</v>
+        <v>33.267333984375</v>
       </c>
       <c r="G34" s="1">
-        <v>34.159664154052734</v>
+        <v>34.155544281005859</v>
       </c>
       <c r="H34" s="1">
-        <v>33.823104858398438</v>
+        <v>33.781227111816406</v>
       </c>
       <c r="I34" s="1">
-        <v>33.493305206298828</v>
+        <v>33.267333984375</v>
       </c>
       <c r="J34" s="1">
         <v>2.6939806938171387</v>
@@ -2673,13 +2676,13 @@
         <v>0</v>
       </c>
       <c r="M34" s="1">
-        <v>1.1708558797836304</v>
+        <v>1.2026726007461548</v>
       </c>
       <c r="N34" s="1">
-        <v>3.1933732032775879</v>
+        <v>3.5168149471282959</v>
       </c>
       <c r="O34" s="1">
-        <v>5.7451448440551758</v>
+        <v>6.5942554473876953</v>
       </c>
       <c r="P34" s="1">
         <v>-0.10902998596429825</v>
@@ -2705,19 +2708,19 @@
         <v>37.019683837890625</v>
       </c>
       <c r="E35" s="1">
-        <v>36.224609375</v>
+        <v>36.211704254150391</v>
       </c>
       <c r="F35" s="1">
-        <v>35.426914215087891</v>
+        <v>35.316864013671875</v>
       </c>
       <c r="G35" s="1">
         <v>37.019683837890625</v>
       </c>
       <c r="H35" s="1">
-        <v>36.224609375</v>
+        <v>36.211704254150391</v>
       </c>
       <c r="I35" s="1">
-        <v>35.426914215087891</v>
+        <v>35.316864013671875</v>
       </c>
       <c r="J35" s="1">
         <v>0.32150024175643921</v>
@@ -2732,10 +2735,10 @@
         <v>0</v>
       </c>
       <c r="N35" s="1">
-        <v>0.55549782514572144</v>
+        <v>0.64686918258666992</v>
       </c>
       <c r="O35" s="1">
-        <v>1.2887394428253174</v>
+        <v>1.606741189956665</v>
       </c>
       <c r="P35" s="1">
         <v>-0.71462589502334595</v>
@@ -2758,22 +2761,22 @@
         <v>41.467826843261719</v>
       </c>
       <c r="D36" s="1">
-        <v>39.880455017089844</v>
+        <v>39.873363494873047</v>
       </c>
       <c r="E36" s="1">
-        <v>37.95947265625</v>
+        <v>37.903785705566406</v>
       </c>
       <c r="F36" s="1">
-        <v>36.209774017333984</v>
+        <v>35.984672546386719</v>
       </c>
       <c r="G36" s="1">
-        <v>39.880455017089844</v>
+        <v>39.873363494873047</v>
       </c>
       <c r="H36" s="1">
-        <v>37.95947265625</v>
+        <v>37.903785705566406</v>
       </c>
       <c r="I36" s="1">
-        <v>36.209774017333984</v>
+        <v>35.984672546386719</v>
       </c>
       <c r="J36" s="1">
         <v>1.9415525197982788</v>
@@ -2785,13 +2788,13 @@
         <v>0</v>
       </c>
       <c r="M36" s="1">
-        <v>3.7111058235168457</v>
+        <v>3.7585716247558594</v>
       </c>
       <c r="N36" s="1">
-        <v>5.6354866027832031</v>
+        <v>6.0081357955932617</v>
       </c>
       <c r="O36" s="1">
-        <v>8.0837497711181641</v>
+        <v>8.9865150451660156</v>
       </c>
       <c r="P36" s="1">
         <v>-1.0365113019943237</v>
@@ -2817,19 +2820,19 @@
         <v>44.509128570556641</v>
       </c>
       <c r="E37" s="1">
-        <v>43.311183929443359</v>
+        <v>43.228977203369141</v>
       </c>
       <c r="F37" s="1">
-        <v>42.661033630371094</v>
+        <v>42.305355072021484</v>
       </c>
       <c r="G37" s="1">
         <v>44.509128570556641</v>
       </c>
       <c r="H37" s="1">
-        <v>43.311183929443359</v>
+        <v>43.228977203369141</v>
       </c>
       <c r="I37" s="1">
-        <v>42.661033630371094</v>
+        <v>42.305355072021484</v>
       </c>
       <c r="J37" s="1">
         <v>2.3083720207214355</v>
@@ -2844,10 +2847,10 @@
         <v>3.545093297958374</v>
       </c>
       <c r="N37" s="1">
-        <v>4.6756172180175781</v>
+        <v>4.8601541519165039</v>
       </c>
       <c r="O37" s="1">
-        <v>6.1680617332458496</v>
+        <v>6.963435173034668</v>
       </c>
       <c r="P37" s="1">
         <v>-0.32900702953338623</v>
@@ -2873,19 +2876,19 @@
         <v>45.018539428710938</v>
       </c>
       <c r="E38" s="1">
-        <v>43.792015075683594</v>
+        <v>43.774166107177734</v>
       </c>
       <c r="F38" s="1">
-        <v>42.692123413085938</v>
+        <v>42.630062103271484</v>
       </c>
       <c r="G38" s="1">
         <v>45.018539428710938</v>
       </c>
       <c r="H38" s="1">
-        <v>43.792015075683594</v>
+        <v>43.774166107177734</v>
       </c>
       <c r="I38" s="1">
-        <v>42.692123413085938</v>
+        <v>42.630062103271484</v>
       </c>
       <c r="J38" s="1">
         <v>1.9545148611068726</v>
@@ -2900,10 +2903,10 @@
         <v>0</v>
       </c>
       <c r="N38" s="1">
-        <v>1.0386511087417603</v>
+        <v>1.1433122158050537</v>
       </c>
       <c r="O38" s="1">
-        <v>2.3390898704528809</v>
+        <v>2.7016241550445557</v>
       </c>
       <c r="P38" s="1">
         <v>-0.59221667051315308</v>
@@ -2926,22 +2929,22 @@
         <v>50.226909637451172</v>
       </c>
       <c r="D39" s="1">
-        <v>48.690204620361328</v>
+        <v>48.685070037841797</v>
       </c>
       <c r="E39" s="1">
-        <v>47.494228363037109</v>
+        <v>47.454208374023438</v>
       </c>
       <c r="F39" s="1">
-        <v>46.193824768066406</v>
+        <v>46.032520294189453</v>
       </c>
       <c r="G39" s="1">
-        <v>48.690204620361328</v>
+        <v>48.685070037841797</v>
       </c>
       <c r="H39" s="1">
-        <v>47.494228363037109</v>
+        <v>47.454208374023438</v>
       </c>
       <c r="I39" s="1">
-        <v>46.193824768066406</v>
+        <v>46.032520294189453</v>
       </c>
       <c r="J39" s="1">
         <v>2.9923243522644043</v>
@@ -2953,13 +2956,13 @@
         <v>0</v>
       </c>
       <c r="M39" s="1">
-        <v>24.959156036376953</v>
+        <v>24.987585067749024</v>
       </c>
       <c r="N39" s="1">
-        <v>26.886796951293945</v>
+        <v>27.107892990112305</v>
       </c>
       <c r="O39" s="1">
-        <v>29.166629791259766</v>
+        <v>29.701688766479492</v>
       </c>
       <c r="P39" s="1">
         <v>-0.68098533153533936</v>
@@ -2985,19 +2988,19 @@
         <v>48.631397247314453</v>
       </c>
       <c r="E40" s="1">
-        <v>47.967216491699219</v>
+        <v>47.910167694091797</v>
       </c>
       <c r="F40" s="1">
-        <v>47.486343383789063</v>
+        <v>47.287372589111328</v>
       </c>
       <c r="G40" s="1">
         <v>48.631397247314453</v>
       </c>
       <c r="H40" s="1">
-        <v>47.967216491699219</v>
+        <v>47.910167694091797</v>
       </c>
       <c r="I40" s="1">
-        <v>47.486343383789063</v>
+        <v>47.287372589111328</v>
       </c>
       <c r="J40" s="1">
         <v>1.8385132551193237</v>
@@ -3012,10 +3015,10 @@
         <v>0</v>
       </c>
       <c r="N40" s="1">
-        <v>1.1640799045562744</v>
+        <v>1.2787305116653442</v>
       </c>
       <c r="O40" s="1">
-        <v>2.6173231601715088</v>
+        <v>3.0157017707824707</v>
       </c>
       <c r="P40" s="1">
         <v>-0.0324648916721344</v>
@@ -3038,22 +3041,22 @@
         <v>58.708145141601563</v>
       </c>
       <c r="D41" s="1">
-        <v>57.507640838623047</v>
+        <v>57.504615783691406</v>
       </c>
       <c r="E41" s="1">
-        <v>56.684478759765625</v>
+        <v>56.657455444335938</v>
       </c>
       <c r="F41" s="1">
-        <v>56.196338653564453</v>
+        <v>56.126174926757813</v>
       </c>
       <c r="G41" s="1">
-        <v>57.507640838623047</v>
+        <v>57.504615783691406</v>
       </c>
       <c r="H41" s="1">
-        <v>56.684478759765625</v>
+        <v>56.657455444335938</v>
       </c>
       <c r="I41" s="1">
-        <v>56.196338653564453</v>
+        <v>56.126174926757813</v>
       </c>
       <c r="J41" s="1">
         <v>2.3428640365600586</v>
@@ -3065,13 +3068,13 @@
         <v>0</v>
       </c>
       <c r="M41" s="1">
-        <v>8.4840059280395508</v>
+        <v>8.4982700347900391</v>
       </c>
       <c r="N41" s="1">
-        <v>9.2457857131958008</v>
+        <v>9.3735275268554688</v>
       </c>
       <c r="O41" s="1">
-        <v>10.204293251037598</v>
+        <v>10.534675598144531</v>
       </c>
       <c r="P41" s="1">
         <v>-0.41630640625953674</v>
@@ -3097,19 +3100,19 @@
         <v>65.240455627441406</v>
       </c>
       <c r="E42" s="1">
-        <v>63.330852508544922</v>
+        <v>63.288158416748047</v>
       </c>
       <c r="F42" s="1">
-        <v>61.488574981689453</v>
+        <v>61.339290618896484</v>
       </c>
       <c r="G42" s="1">
         <v>65.240455627441406</v>
       </c>
       <c r="H42" s="1">
-        <v>63.330852508544922</v>
+        <v>63.288158416748047</v>
       </c>
       <c r="I42" s="1">
-        <v>61.488574981689453</v>
+        <v>61.339290618896484</v>
       </c>
       <c r="J42" s="1">
         <v>1.9380583763122559</v>
@@ -3124,10 +3127,10 @@
         <v>0</v>
       </c>
       <c r="N42" s="1">
-        <v>0.85684746503829956</v>
+        <v>0.92144167423248291</v>
       </c>
       <c r="O42" s="1">
-        <v>1.8977710008621216</v>
+        <v>2.1227529048919678</v>
       </c>
       <c r="P42" s="1">
         <v>-0.50616496801376343</v>
@@ -3153,19 +3156,19 @@
         <v>68.602897644042969</v>
       </c>
       <c r="E43" s="1">
-        <v>65.280075073242188</v>
+        <v>65.258232116699219</v>
       </c>
       <c r="F43" s="1">
-        <v>62.027027130126953</v>
+        <v>61.8663330078125</v>
       </c>
       <c r="G43" s="1">
         <v>68.602897644042969</v>
       </c>
       <c r="H43" s="1">
-        <v>65.280075073242188</v>
+        <v>65.258232116699219</v>
       </c>
       <c r="I43" s="1">
-        <v>62.027027130126953</v>
+        <v>61.8663330078125</v>
       </c>
       <c r="J43" s="1">
         <v>1.1138042211532593</v>
@@ -3180,10 +3183,10 @@
         <v>0</v>
       </c>
       <c r="N43" s="1">
-        <v>1.0246307849884033</v>
+        <v>1.1088933944702149</v>
       </c>
       <c r="O43" s="1">
-        <v>2.2709286212921143</v>
+        <v>2.5635077953338623</v>
       </c>
       <c r="P43" s="1">
         <v>-1.2609143257141113</v>
@@ -3206,22 +3209,22 @@
         <v>66.349037170410156</v>
       </c>
       <c r="D44" s="1">
-        <v>64.5833740234375</v>
+        <v>64.582122802734375</v>
       </c>
       <c r="E44" s="1">
-        <v>64.433799743652344</v>
+        <v>64.402755737304688</v>
       </c>
       <c r="F44" s="1">
-        <v>64.574012756347656</v>
+        <v>64.479019165039063</v>
       </c>
       <c r="G44" s="1">
-        <v>64.5833740234375</v>
+        <v>64.582122802734375</v>
       </c>
       <c r="H44" s="1">
-        <v>64.433799743652344</v>
+        <v>64.402755737304688</v>
       </c>
       <c r="I44" s="1">
-        <v>64.574012756347656</v>
+        <v>64.479019165039063</v>
       </c>
       <c r="J44" s="1">
         <v>1.7335447072982788</v>
@@ -3233,13 +3236,13 @@
         <v>0</v>
       </c>
       <c r="M44" s="1">
-        <v>4.5300745964050293</v>
+        <v>4.535308837890625</v>
       </c>
       <c r="N44" s="1">
-        <v>5.0965065956115723</v>
+        <v>5.2263469696044922</v>
       </c>
       <c r="O44" s="1">
-        <v>5.8530597686767578</v>
+        <v>6.2488408088684082</v>
       </c>
       <c r="P44" s="1">
         <v>-0.0028829965740442276</v>
@@ -3265,19 +3268,19 @@
         <v>80.810401916503906</v>
       </c>
       <c r="E45" s="1">
-        <v>77.941421508789063</v>
+        <v>77.886856079101563</v>
       </c>
       <c r="F45" s="1">
-        <v>75.006149291992188</v>
+        <v>74.815383911132813</v>
       </c>
       <c r="G45" s="1">
         <v>80.810401916503906</v>
       </c>
       <c r="H45" s="1">
-        <v>77.941421508789063</v>
+        <v>77.886856079101563</v>
       </c>
       <c r="I45" s="1">
-        <v>75.006149291992188</v>
+        <v>74.815383911132813</v>
       </c>
       <c r="J45" s="1">
         <v>5.2754936218261719</v>
@@ -3292,10 +3295,10 @@
         <v>0</v>
       </c>
       <c r="N45" s="1">
-        <v>1.7976731061935425</v>
+        <v>1.8663080930709839</v>
       </c>
       <c r="O45" s="1">
-        <v>3.9028975963592529</v>
+        <v>4.1398692131042481</v>
       </c>
       <c r="P45" s="1">
         <v>-0.52598530054092407</v>
@@ -3321,19 +3324,19 @@
         <v>87.971038818359375</v>
       </c>
       <c r="E46" s="1">
-        <v>83.627113342285156</v>
+        <v>83.589035034179688</v>
       </c>
       <c r="F46" s="1">
-        <v>79.631591796875</v>
+        <v>79.499229431152344</v>
       </c>
       <c r="G46" s="1">
         <v>87.971038818359375</v>
       </c>
       <c r="H46" s="1">
-        <v>83.627113342285156</v>
+        <v>83.589035034179688</v>
       </c>
       <c r="I46" s="1">
-        <v>79.631591796875</v>
+        <v>79.499229431152344</v>
       </c>
       <c r="J46" s="1">
         <v>8.960113525390625</v>
@@ -3348,10 +3351,10 @@
         <v>31.12401008605957</v>
       </c>
       <c r="N46" s="1">
-        <v>34.343841552734375</v>
+        <v>34.461418151855469</v>
       </c>
       <c r="O46" s="1">
-        <v>38.023200988769531</v>
+        <v>38.421321868896484</v>
       </c>
       <c r="P46" s="1">
         <v>-1.037487268447876</v>
@@ -3427,28 +3430,28 @@
         <v>22.513217926025391</v>
       </c>
       <c r="C2" s="1">
-        <v>22.47239875793457</v>
+        <v>22.467874526977539</v>
       </c>
       <c r="D2" s="1">
         <v>21.316532135009769</v>
       </c>
       <c r="E2" s="1">
-        <v>21.366863250732418</v>
+        <v>21.362339019775391</v>
       </c>
       <c r="F2" s="1">
         <v>2.1007614135742192</v>
       </c>
       <c r="G2" s="1">
-        <v>2.2128977775573731</v>
+        <v>2.2563803195953369</v>
       </c>
       <c r="H2" s="1">
-        <v>4.6867044426616298</v>
+        <v>4.7423748593956638</v>
       </c>
       <c r="I2" s="1">
         <v>-0.45406845331923512</v>
       </c>
       <c r="J2" s="1">
-        <v>15.781349745552131</v>
+        <v>15.737912059494811</v>
       </c>
       <c r="K2" s="1">
         <v>100</v>
@@ -3474,31 +3477,31 @@
         <v>22.513217926025391</v>
       </c>
       <c r="C3" s="1">
-        <v>21.92690277099609</v>
+        <v>21.876472473144531</v>
       </c>
       <c r="D3" s="1">
         <v>21.316532135009769</v>
       </c>
       <c r="E3" s="1">
-        <v>20.821121215820309</v>
+        <v>20.77069091796875</v>
       </c>
       <c r="F3" s="1">
         <v>2.1007614135742192</v>
       </c>
       <c r="G3" s="1">
-        <v>2.274471759796143</v>
+        <v>2.569164514541626</v>
       </c>
       <c r="H3" s="1">
-        <v>7.7666765488880154</v>
+        <v>8.3193932085161375</v>
       </c>
       <c r="I3" s="1">
         <v>1.402389134764527</v>
       </c>
       <c r="J3" s="1">
-        <v>12.6600265354535</v>
+        <v>12.219223784927109</v>
       </c>
       <c r="K3" s="1">
-        <v>84.705212252270854</v>
+        <v>85.574773377498957</v>
       </c>
       <c r="L3" s="1">
         <v>0</v>
@@ -3521,31 +3524,31 @@
         <v>22.513217926025391</v>
       </c>
       <c r="C4" s="1">
-        <v>21.2932014465332</v>
+        <v>21.11314582824707</v>
       </c>
       <c r="D4" s="1">
         <v>21.316532135009769</v>
       </c>
       <c r="E4" s="1">
-        <v>20.183219909667969</v>
+        <v>20.00316429138184</v>
       </c>
       <c r="F4" s="1">
         <v>2.1007614135742192</v>
       </c>
       <c r="G4" s="1">
-        <v>2.4806675910949712</v>
+        <v>3.0078268051147461</v>
       </c>
       <c r="H4" s="1">
-        <v>11.70280876770113</v>
+        <v>13.217937112132621</v>
       </c>
       <c r="I4" s="1">
         <v>3.227636489499754</v>
       </c>
       <c r="J4" s="1">
-        <v>8.5107499904632356</v>
+        <v>7.2310853376423898</v>
       </c>
       <c r="K4" s="1">
-        <v>78.3821819517199</v>
+        <v>80.373828437462464</v>
       </c>
       <c r="L4" s="1">
         <v>2</v>
@@ -3566,7 +3569,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3574,7 +3577,7 @@
         <v>103</v>
       </c>
       <c r="B1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2">
@@ -3630,7 +3633,7 @@
         <v>110</v>
       </c>
       <c r="B8" s="1">
-        <v>0.22</v>
+        <v>-0.42899999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -3638,7 +3641,7 @@
         <v>111</v>
       </c>
       <c r="B9" s="1">
-        <v>265</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="10">
@@ -3646,6 +3649,14 @@
         <v>112</v>
       </c>
       <c r="B10" s="1">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>113</v>
+      </c>
+      <c r="B11" s="1">
         <v>4</v>
       </c>
     </row>

--- a/output/fixed/stress_test_summary.xlsx
+++ b/output/fixed/stress_test_summary.xlsx
@@ -173,22 +173,25 @@
     <t>MAYA</t>
   </si>
   <si>
+    <t>BJBR</t>
+  </si>
+  <si>
+    <t>NOBU</t>
+  </si>
+  <si>
     <t>PNBS</t>
   </si>
   <si>
-    <t>BJBR</t>
-  </si>
-  <si>
-    <t>NOBU</t>
-  </si>
-  <si>
     <t>BBTN</t>
   </si>
   <si>
+    <t>BNII</t>
+  </si>
+  <si>
     <t>BABP</t>
   </si>
   <si>
-    <t>BNII</t>
+    <t>INPC</t>
   </si>
   <si>
     <t>BBNI</t>
@@ -197,9 +200,6 @@
     <t>BMRI</t>
   </si>
   <si>
-    <t>INPC</t>
-  </si>
-  <si>
     <t>BVIC</t>
   </si>
   <si>
@@ -266,10 +266,10 @@
     <t>DNAR</t>
   </si>
   <si>
+    <t>BBMD</t>
+  </si>
+  <si>
     <t>BMAS</t>
-  </si>
-  <si>
-    <t>BBMD</t>
   </si>
   <si>
     <t>BBYB</t>
@@ -576,7 +576,7 @@
         <v>22.391046524047852</v>
       </c>
       <c r="E3" s="1">
-        <v>22.302944183349609</v>
+        <v>22.293838500976563</v>
       </c>
       <c r="F3" s="1">
         <v>21.307384490966797</v>
@@ -585,7 +585,7 @@
         <v>21.218429565429688</v>
       </c>
       <c r="H3" s="1">
-        <v>21.129884719848633</v>
+        <v>21.120779037475586</v>
       </c>
       <c r="I3" s="1">
         <v>2.2514598369598389</v>
@@ -603,7 +603,7 @@
         <v>0.44660630822181702</v>
       </c>
       <c r="N3" s="1">
-        <v>0.39149126410484314</v>
+        <v>0.38729450106620789</v>
       </c>
       <c r="O3" s="1">
         <v>0.24511410295963287</v>
@@ -621,7 +621,7 @@
         <v>0.061033107340335846</v>
       </c>
       <c r="T3" s="1">
-        <v>0.13901908695697784</v>
+        <v>0.1478293240070343</v>
       </c>
     </row>
     <row r="4">
@@ -635,55 +635,55 @@
         <v>22.452136993408203</v>
       </c>
       <c r="D4" s="1">
-        <v>22.249353408813477</v>
+        <v>22.229488372802734</v>
       </c>
       <c r="E4" s="1">
-        <v>22.029691696166992</v>
+        <v>21.997781753540039</v>
       </c>
       <c r="F4" s="1">
         <v>21.302433013916016</v>
       </c>
       <c r="G4" s="1">
-        <v>21.099885940551758</v>
+        <v>21.080020904541016</v>
       </c>
       <c r="H4" s="1">
-        <v>20.878921508789063</v>
+        <v>20.847011566162109</v>
       </c>
       <c r="I4" s="1">
         <v>2.2568924427032471</v>
       </c>
       <c r="J4" s="1">
-        <v>2.2633206844329834</v>
+        <v>2.2962322235107422</v>
       </c>
       <c r="K4" s="1">
-        <v>2.2693188190460205</v>
+        <v>2.3654963970184326</v>
       </c>
       <c r="L4" s="1">
         <v>0.49343514442443848</v>
       </c>
       <c r="M4" s="1">
-        <v>0.41632750630378723</v>
+        <v>0.40555211901664734</v>
       </c>
       <c r="N4" s="1">
-        <v>0.31697571277618408</v>
+        <v>0.29874759912490845</v>
       </c>
       <c r="O4" s="1">
         <v>0.23602797091007233</v>
       </c>
       <c r="P4" s="1">
-        <v>0.34606754779815674</v>
+        <v>0.35105428099632263</v>
       </c>
       <c r="Q4" s="1">
-        <v>0.47820499539375305</v>
+        <v>0.50026637315750122</v>
       </c>
       <c r="R4" s="1">
         <v>-0.010321144014596939</v>
       </c>
       <c r="S4" s="1">
-        <v>0.069598972797393799</v>
+        <v>0.086796216666698456</v>
       </c>
       <c r="T4" s="1">
-        <v>0.16210523247718811</v>
+        <v>0.17133872210979462</v>
       </c>
     </row>
     <row r="5">
@@ -697,55 +697,55 @@
         <v>22.464960098266602</v>
       </c>
       <c r="D5" s="1">
-        <v>22.088130950927734</v>
+        <v>22.036989212036133</v>
       </c>
       <c r="E5" s="1">
-        <v>21.66456413269043</v>
+        <v>21.601100921630859</v>
       </c>
       <c r="F5" s="1">
         <v>21.337425231933594</v>
       </c>
       <c r="G5" s="1">
-        <v>20.960931777954102</v>
+        <v>20.9097900390625</v>
       </c>
       <c r="H5" s="1">
-        <v>20.534801483154297</v>
+        <v>20.471340179443359</v>
       </c>
       <c r="I5" s="1">
         <v>2.2835750579833984</v>
       </c>
       <c r="J5" s="1">
-        <v>2.3756246566772461</v>
+        <v>2.4736855030059814</v>
       </c>
       <c r="K5" s="1">
-        <v>2.5675730705261231</v>
+        <v>2.6947524547576904</v>
       </c>
       <c r="L5" s="1">
         <v>0.51126635074615479</v>
       </c>
       <c r="M5" s="1">
-        <v>0.38248014450073242</v>
+        <v>0.35996437072753906</v>
       </c>
       <c r="N5" s="1">
-        <v>0.20377863943576813</v>
+        <v>0.17696189880371094</v>
       </c>
       <c r="O5" s="1">
         <v>0.21802417933940887</v>
       </c>
       <c r="P5" s="1">
-        <v>0.41330695152282715</v>
+        <v>0.43295383453369141</v>
       </c>
       <c r="Q5" s="1">
-        <v>0.68296492099761963</v>
+        <v>0.7168194055557251</v>
       </c>
       <c r="R5" s="1">
         <v>-0.035828325897455215</v>
       </c>
       <c r="S5" s="1">
-        <v>0.068838827311992645</v>
+        <v>0.086036205291748047</v>
       </c>
       <c r="T5" s="1">
-        <v>0.15926928818225861</v>
+        <v>0.16850250959396362</v>
       </c>
     </row>
     <row r="6">
@@ -759,55 +759,55 @@
         <v>22.467874526977539</v>
       </c>
       <c r="D6" s="1">
-        <v>21.876472473144531</v>
+        <v>21.802417755126953</v>
       </c>
       <c r="E6" s="1">
-        <v>21.11314582824707</v>
+        <v>21.034475326538086</v>
       </c>
       <c r="F6" s="1">
         <v>21.362339019775391</v>
       </c>
       <c r="G6" s="1">
-        <v>20.77069091796875</v>
+        <v>20.696636199951172</v>
       </c>
       <c r="H6" s="1">
-        <v>20.003164291381836</v>
+        <v>19.924493789672852</v>
       </c>
       <c r="I6" s="1">
         <v>2.2563803195953369</v>
       </c>
       <c r="J6" s="1">
-        <v>2.569164514541626</v>
+        <v>2.6670103073120117</v>
       </c>
       <c r="K6" s="1">
-        <v>3.0078268051147461</v>
+        <v>3.0794107913970947</v>
       </c>
       <c r="L6" s="1">
         <v>0.51506465673446655</v>
       </c>
       <c r="M6" s="1">
-        <v>0.31969085335731506</v>
+        <v>0.2992621660232544</v>
       </c>
       <c r="N6" s="1">
-        <v>0.024486569687724113</v>
+        <v>0.01218987163156271</v>
       </c>
       <c r="O6" s="1">
         <v>0.20774145424365997</v>
       </c>
       <c r="P6" s="1">
-        <v>0.53251188993453979</v>
+        <v>0.54956901073455811</v>
       </c>
       <c r="Q6" s="1">
-        <v>0.99407404661178589</v>
+        <v>1.0034915208816528</v>
       </c>
       <c r="R6" s="1">
         <v>-0.022434631362557411</v>
       </c>
       <c r="S6" s="1">
-        <v>0.068105123937129974</v>
+        <v>0.076492264866828918</v>
       </c>
       <c r="T6" s="1">
-        <v>0.15661917626857758</v>
+        <v>0.15704241394996643</v>
       </c>
     </row>
   </sheetData>
@@ -912,7 +912,7 @@
         <v>19.46058464050293</v>
       </c>
       <c r="F3" s="1">
-        <v>19.410577774047852</v>
+        <v>19.406673431396484</v>
       </c>
       <c r="G3" s="1">
         <v>18.374439239501953</v>
@@ -921,7 +921,7 @@
         <v>18.323020935058594</v>
       </c>
       <c r="I3" s="1">
-        <v>18.272584915161133</v>
+        <v>18.268680572509766</v>
       </c>
       <c r="J3" s="1">
         <v>2.1771860122680664</v>
@@ -947,28 +947,28 @@
         <v>19.584810256958008</v>
       </c>
       <c r="E4" s="1">
-        <v>19.455909729003906</v>
+        <v>19.44561767578125</v>
       </c>
       <c r="F4" s="1">
-        <v>19.316364288330078</v>
+        <v>19.294939041137695</v>
       </c>
       <c r="G4" s="1">
         <v>18.469474792480469</v>
       </c>
       <c r="H4" s="1">
-        <v>18.340805053710938</v>
+        <v>18.330513000488281</v>
       </c>
       <c r="I4" s="1">
-        <v>18.199995040893555</v>
+        <v>18.178569793701172</v>
       </c>
       <c r="J4" s="1">
         <v>2.211719274520874</v>
       </c>
       <c r="K4" s="1">
-        <v>2.2181477546691895</v>
+        <v>2.2510590553283692</v>
       </c>
       <c r="L4" s="1">
-        <v>2.2241458892822266</v>
+        <v>2.3203232288360596</v>
       </c>
     </row>
     <row r="5">
@@ -985,28 +985,28 @@
         <v>19.684576034545898</v>
       </c>
       <c r="E5" s="1">
-        <v>19.429523468017578</v>
+        <v>19.398456573486328</v>
       </c>
       <c r="F5" s="1">
-        <v>19.128240585327149</v>
+        <v>19.082208633422852</v>
       </c>
       <c r="G5" s="1">
         <v>18.590747833251953</v>
       </c>
       <c r="H5" s="1">
-        <v>18.336019515991211</v>
+        <v>18.304952621459961</v>
       </c>
       <c r="I5" s="1">
-        <v>18.032251358032227</v>
+        <v>17.98621940612793</v>
       </c>
       <c r="J5" s="1">
         <v>2.2579970359802246</v>
       </c>
       <c r="K5" s="1">
-        <v>2.3500466346740723</v>
+        <v>2.4481074810028076</v>
       </c>
       <c r="L5" s="1">
-        <v>2.5419950485229492</v>
+        <v>2.6691744327545166</v>
       </c>
     </row>
     <row r="6">
@@ -1023,28 +1023,28 @@
         <v>19.780158996582031</v>
       </c>
       <c r="E6" s="1">
-        <v>19.347400665283203</v>
+        <v>19.300323486328125</v>
       </c>
       <c r="F6" s="1">
-        <v>18.745532989501953</v>
+        <v>18.685705184936524</v>
       </c>
       <c r="G6" s="1">
         <v>18.707670211791992</v>
       </c>
       <c r="H6" s="1">
-        <v>18.274675369262695</v>
+        <v>18.227598190307617</v>
       </c>
       <c r="I6" s="1">
-        <v>17.668733596801758</v>
+        <v>17.608905792236328</v>
       </c>
       <c r="J6" s="1">
         <v>2.2439966201782227</v>
       </c>
       <c r="K6" s="1">
-        <v>2.5567808151245117</v>
+        <v>2.6546263694763184</v>
       </c>
       <c r="L6" s="1">
-        <v>2.9954431056976318</v>
+        <v>3.0670268535614014</v>
       </c>
     </row>
     <row r="7">
@@ -1102,7 +1102,7 @@
         <v>26.439062118530273</v>
       </c>
       <c r="F8" s="1">
-        <v>26.298336029052734</v>
+        <v>26.282045364379883</v>
       </c>
       <c r="G8" s="1">
         <v>25.358829498291016</v>
@@ -1111,7 +1111,7 @@
         <v>25.218021392822266</v>
       </c>
       <c r="I8" s="1">
-        <v>25.076833724975586</v>
+        <v>25.060543060302734</v>
       </c>
       <c r="J8" s="1">
         <v>2.371265172958374</v>
@@ -1137,28 +1137,28 @@
         <v>26.412939071655274</v>
       </c>
       <c r="E9" s="1">
-        <v>26.10809326171875</v>
+        <v>26.075006484985352</v>
       </c>
       <c r="F9" s="1">
-        <v>25.777765274047852</v>
+        <v>25.73137092590332</v>
       </c>
       <c r="G9" s="1">
         <v>25.21575927734375</v>
       </c>
       <c r="H9" s="1">
-        <v>24.911159515380859</v>
+        <v>24.878072738647461</v>
       </c>
       <c r="I9" s="1">
-        <v>24.579475402832031</v>
+        <v>24.5330810546875</v>
       </c>
       <c r="J9" s="1">
         <v>2.3297574520111084</v>
       </c>
       <c r="K9" s="1">
-        <v>2.3361854553222656</v>
+        <v>2.3690972328186035</v>
       </c>
       <c r="L9" s="1">
-        <v>2.3421838283538818</v>
+        <v>2.4383611679077149</v>
       </c>
     </row>
     <row r="10">
@@ -1175,28 +1175,28 @@
         <v>26.305662155151367</v>
       </c>
       <c r="E10" s="1">
-        <v>25.760616302490234</v>
+        <v>25.681747436523438</v>
       </c>
       <c r="F10" s="1">
-        <v>25.168132781982422</v>
+        <v>25.080593109130859</v>
       </c>
       <c r="G10" s="1">
         <v>25.131568908691406</v>
       </c>
       <c r="H10" s="1">
-        <v>24.586870193481445</v>
+        <v>24.508001327514649</v>
       </c>
       <c r="I10" s="1">
-        <v>23.991718292236328</v>
+        <v>23.904178619384766</v>
       </c>
       <c r="J10" s="1">
         <v>2.3248331546783447</v>
       </c>
       <c r="K10" s="1">
-        <v>2.4168825149536133</v>
+        <v>2.5149433612823486</v>
       </c>
       <c r="L10" s="1">
-        <v>2.6088309288024902</v>
+        <v>2.7360103130340576</v>
       </c>
     </row>
     <row r="11">
@@ -1213,28 +1213,28 @@
         <v>26.180570602416992</v>
       </c>
       <c r="E11" s="1">
-        <v>25.370023727416992</v>
+        <v>25.258701324462891</v>
       </c>
       <c r="F11" s="1">
-        <v>24.383663177490234</v>
+        <v>24.278963088989258</v>
       </c>
       <c r="G11" s="1">
         <v>25.029382705688477</v>
       </c>
       <c r="H11" s="1">
-        <v>24.21858024597168</v>
+        <v>24.107257843017578</v>
       </c>
       <c r="I11" s="1">
-        <v>23.227846145629883</v>
+        <v>23.123146057128906</v>
       </c>
       <c r="J11" s="1">
         <v>2.2763557434082031</v>
       </c>
       <c r="K11" s="1">
-        <v>2.5891399383544922</v>
+        <v>2.6869857311248779</v>
       </c>
       <c r="L11" s="1">
-        <v>3.0278022289276123</v>
+        <v>3.0993859767913818</v>
       </c>
     </row>
     <row r="12">
@@ -1292,7 +1292,7 @@
         <v>33.188522338867188</v>
       </c>
       <c r="F13" s="1">
-        <v>32.758235931396484</v>
+        <v>32.710655212402344</v>
       </c>
       <c r="G13" s="1">
         <v>32.291416168212891</v>
@@ -1301,7 +1301,7 @@
         <v>31.864368438720703</v>
       </c>
       <c r="I13" s="1">
-        <v>31.433582305908203</v>
+        <v>31.38599967956543</v>
       </c>
       <c r="J13" s="1">
         <v>2.7423791885375977</v>
@@ -1327,28 +1327,28 @@
         <v>33.032821655273438</v>
       </c>
       <c r="E14" s="1">
-        <v>32.138225555419922</v>
+        <v>32.043247222900391</v>
       </c>
       <c r="F14" s="1">
-        <v>31.144685745239258</v>
+        <v>31.032325744628906</v>
       </c>
       <c r="G14" s="1">
         <v>31.734540939331055</v>
       </c>
       <c r="H14" s="1">
-        <v>30.8402099609375</v>
+        <v>30.745235443115234</v>
       </c>
       <c r="I14" s="1">
-        <v>29.84520149230957</v>
+        <v>29.732839584350586</v>
       </c>
       <c r="J14" s="1">
         <v>2.7874999046325684</v>
       </c>
       <c r="K14" s="1">
-        <v>2.7939281463623047</v>
+        <v>2.8268396854400635</v>
       </c>
       <c r="L14" s="1">
-        <v>2.7999265193939209</v>
+        <v>2.8961038589477539</v>
       </c>
     </row>
     <row r="15">
@@ -1365,28 +1365,28 @@
         <v>32.609352111816406</v>
       </c>
       <c r="E15" s="1">
-        <v>31.066181182861328</v>
+        <v>30.859432220458984</v>
       </c>
       <c r="F15" s="1">
-        <v>29.407241821289063</v>
+        <v>29.208240509033203</v>
       </c>
       <c r="G15" s="1">
         <v>31.33610725402832</v>
       </c>
       <c r="H15" s="1">
-        <v>29.793313980102539</v>
+        <v>29.586563110351563</v>
       </c>
       <c r="I15" s="1">
-        <v>28.131479263305664</v>
+        <v>27.932479858398438</v>
       </c>
       <c r="J15" s="1">
         <v>2.8409068584442139</v>
       </c>
       <c r="K15" s="1">
-        <v>2.9329562187194824</v>
+        <v>3.0310170650482178</v>
       </c>
       <c r="L15" s="1">
-        <v>3.1249046325683594</v>
+        <v>3.2520840167999268</v>
       </c>
     </row>
     <row r="16">
@@ -1403,28 +1403,28 @@
         <v>32.125572204589844</v>
       </c>
       <c r="E16" s="1">
-        <v>29.928842544555664</v>
+        <v>29.654911041259766</v>
       </c>
       <c r="F16" s="1">
-        <v>27.439643859863281</v>
+        <v>27.210954666137695</v>
       </c>
       <c r="G16" s="1">
         <v>30.877168655395508</v>
       </c>
       <c r="H16" s="1">
-        <v>28.680160522460938</v>
+        <v>28.406229019165039</v>
       </c>
       <c r="I16" s="1">
-        <v>26.186220169067383</v>
+        <v>25.957530975341797</v>
       </c>
       <c r="J16" s="1">
         <v>2.8317065238952637</v>
       </c>
       <c r="K16" s="1">
-        <v>3.1444909572601318</v>
+        <v>3.2423365116119385</v>
       </c>
       <c r="L16" s="1">
-        <v>3.5831530094146729</v>
+        <v>3.6547367572784424</v>
       </c>
     </row>
     <row r="17">
@@ -1482,7 +1482,7 @@
         <v>20.384086608886719</v>
       </c>
       <c r="F18" s="1">
-        <v>20.077203750610352</v>
+        <v>20.045055389404297</v>
       </c>
       <c r="G18" s="1">
         <v>19.133279800415039</v>
@@ -1491,7 +1491,7 @@
         <v>18.865400314331055</v>
       </c>
       <c r="I18" s="1">
-        <v>18.557943344116211</v>
+        <v>18.525794982910156</v>
       </c>
       <c r="J18" s="1">
         <v>4.2995457649230957</v>
@@ -1517,28 +1517,28 @@
         <v>20.388492584228516</v>
       </c>
       <c r="E19" s="1">
-        <v>19.7984619140625</v>
+        <v>19.736696243286133</v>
       </c>
       <c r="F19" s="1">
-        <v>19.080802917480469</v>
+        <v>18.996833801269531</v>
       </c>
       <c r="G19" s="1">
         <v>18.899482727050781</v>
       </c>
       <c r="H19" s="1">
-        <v>18.309759140014649</v>
+        <v>18.247993469238281</v>
       </c>
       <c r="I19" s="1">
-        <v>17.590410232543945</v>
+        <v>17.506443023681641</v>
       </c>
       <c r="J19" s="1">
         <v>3.9411468505859375</v>
       </c>
       <c r="K19" s="1">
-        <v>3.9475748538970947</v>
+        <v>3.9804863929748535</v>
       </c>
       <c r="L19" s="1">
-        <v>3.9535732269287109</v>
+        <v>4.0497503280639648</v>
       </c>
     </row>
     <row r="20">
@@ -1555,28 +1555,28 @@
         <v>20.212512969970703</v>
       </c>
       <c r="E20" s="1">
-        <v>19.163366317749024</v>
+        <v>19.022176742553711</v>
       </c>
       <c r="F20" s="1">
-        <v>17.888872146606445</v>
+        <v>17.727632522583008</v>
       </c>
       <c r="G20" s="1">
         <v>18.752216339111328</v>
       </c>
       <c r="H20" s="1">
-        <v>17.703502655029297</v>
+        <v>17.562314987182617</v>
       </c>
       <c r="I20" s="1">
-        <v>16.425689697265625</v>
+        <v>16.264450073242188</v>
       </c>
       <c r="J20" s="1">
         <v>3.7228443622589111</v>
       </c>
       <c r="K20" s="1">
-        <v>3.8148937225341797</v>
+        <v>3.9129548072814942</v>
       </c>
       <c r="L20" s="1">
-        <v>4.0068426132202149</v>
+        <v>4.1340217590332031</v>
       </c>
     </row>
     <row r="21">
@@ -1593,28 +1593,28 @@
         <v>20.007083892822266</v>
       </c>
       <c r="E21" s="1">
-        <v>18.452011108398438</v>
+        <v>18.247068405151367</v>
       </c>
       <c r="F21" s="1">
-        <v>16.368619918823242</v>
+        <v>16.172700881958008</v>
       </c>
       <c r="G21" s="1">
         <v>18.575279235839844</v>
       </c>
       <c r="H21" s="1">
-        <v>17.019886016845703</v>
+        <v>16.814945220947266</v>
       </c>
       <c r="I21" s="1">
-        <v>14.931056976318359</v>
+        <v>14.735137939453125</v>
       </c>
       <c r="J21" s="1">
         <v>3.5306894779205322</v>
       </c>
       <c r="K21" s="1">
-        <v>3.8434736728668213</v>
+        <v>3.941319465637207</v>
       </c>
       <c r="L21" s="1">
-        <v>4.2821364402770996</v>
+        <v>4.3537197113037109</v>
       </c>
     </row>
     <row r="22">
@@ -1672,7 +1672,7 @@
         <v>24.884799957275391</v>
       </c>
       <c r="F23" s="1">
-        <v>24.778722763061523</v>
+        <v>24.76805305480957</v>
       </c>
       <c r="G23" s="1">
         <v>23.741832733154297</v>
@@ -1681,7 +1681,7 @@
         <v>23.630859375</v>
       </c>
       <c r="I23" s="1">
-        <v>23.524309158325195</v>
+        <v>23.513639450073242</v>
       </c>
       <c r="J23" s="1">
         <v>2.2925693988800049</v>
@@ -1707,28 +1707,28 @@
         <v>24.80644416809082</v>
       </c>
       <c r="E24" s="1">
-        <v>24.557720184326172</v>
+        <v>24.533811569213867</v>
       </c>
       <c r="F24" s="1">
-        <v>24.281103134155274</v>
+        <v>24.240409851074219</v>
       </c>
       <c r="G24" s="1">
         <v>23.577005386352539</v>
       </c>
       <c r="H24" s="1">
-        <v>23.328535079956055</v>
+        <v>23.30462646484375</v>
       </c>
       <c r="I24" s="1">
-        <v>23.05052375793457</v>
+        <v>23.009830474853516</v>
       </c>
       <c r="J24" s="1">
         <v>2.3896985054016113</v>
       </c>
       <c r="K24" s="1">
-        <v>2.3961267471313477</v>
+        <v>2.4290382862091065</v>
       </c>
       <c r="L24" s="1">
-        <v>2.4021251201629639</v>
+        <v>2.4983024597167969</v>
       </c>
     </row>
     <row r="25">
@@ -1745,28 +1745,28 @@
         <v>24.671808242797852</v>
       </c>
       <c r="E25" s="1">
-        <v>24.213138580322266</v>
+        <v>24.150112152099609</v>
       </c>
       <c r="F25" s="1">
-        <v>23.65843391418457</v>
+        <v>23.579900741577149</v>
       </c>
       <c r="G25" s="1">
         <v>23.46607780456543</v>
       </c>
       <c r="H25" s="1">
-        <v>23.00776481628418</v>
+        <v>22.944740295410156</v>
       </c>
       <c r="I25" s="1">
-        <v>22.450321197509766</v>
+        <v>22.371788024902344</v>
       </c>
       <c r="J25" s="1">
         <v>2.4781250953674317</v>
       </c>
       <c r="K25" s="1">
-        <v>2.5701744556427002</v>
+        <v>2.6682353019714355</v>
       </c>
       <c r="L25" s="1">
-        <v>2.7621231079101563</v>
+        <v>2.8893022537231445</v>
       </c>
     </row>
     <row r="26">
@@ -1783,28 +1783,28 @@
         <v>24.526863098144531</v>
       </c>
       <c r="E26" s="1">
-        <v>23.796562194824219</v>
+        <v>23.711071014404297</v>
       </c>
       <c r="F26" s="1">
-        <v>22.766939163208008</v>
+        <v>22.672828674316406</v>
       </c>
       <c r="G26" s="1">
         <v>23.344655990600586</v>
       </c>
       <c r="H26" s="1">
-        <v>22.614093780517578</v>
+        <v>22.528600692749024</v>
       </c>
       <c r="I26" s="1">
-        <v>21.579978942871094</v>
+        <v>21.485868453979492</v>
       </c>
       <c r="J26" s="1">
         <v>2.4925050735473633</v>
       </c>
       <c r="K26" s="1">
-        <v>2.8052895069122314</v>
+        <v>2.9031350612640381</v>
       </c>
       <c r="L26" s="1">
-        <v>3.2439517974853516</v>
+        <v>3.315535306930542</v>
       </c>
     </row>
     <row r="27">
@@ -1862,7 +1862,7 @@
         <v>21.043485641479492</v>
       </c>
       <c r="F28" s="1">
-        <v>21.003360748291016</v>
+        <v>20.99932861328125</v>
       </c>
       <c r="G28" s="1">
         <v>19.987415313720703</v>
@@ -1871,7 +1871,7 @@
         <v>19.943765640258789</v>
       </c>
       <c r="I28" s="1">
-        <v>19.903226852416992</v>
+        <v>19.899194717407227</v>
       </c>
       <c r="J28" s="1">
         <v>2.0186595916748047</v>
@@ -1897,28 +1897,28 @@
         <v>21.174201965332031</v>
       </c>
       <c r="E29" s="1">
-        <v>21.066535949707031</v>
+        <v>21.056634902954102</v>
       </c>
       <c r="F29" s="1">
-        <v>20.961719512939453</v>
+        <v>20.942834854125977</v>
       </c>
       <c r="G29" s="1">
         <v>20.095972061157227</v>
       </c>
       <c r="H29" s="1">
-        <v>19.988529205322266</v>
+        <v>19.978628158569336</v>
       </c>
       <c r="I29" s="1">
-        <v>19.882490158081055</v>
+        <v>19.863603591918945</v>
       </c>
       <c r="J29" s="1">
         <v>2.0205113887786865</v>
       </c>
       <c r="K29" s="1">
-        <v>2.0269396305084229</v>
+        <v>2.0598511695861817</v>
       </c>
       <c r="L29" s="1">
-        <v>2.0329380035400391</v>
+        <v>2.1291153430938721</v>
       </c>
     </row>
     <row r="30">
@@ -1935,28 +1935,28 @@
         <v>21.285316467285156</v>
       </c>
       <c r="E30" s="1">
-        <v>21.0723876953125</v>
+        <v>21.043506622314453</v>
       </c>
       <c r="F30" s="1">
-        <v>20.852521896362305</v>
+        <v>20.812095642089844</v>
       </c>
       <c r="G30" s="1">
         <v>20.227878570556641</v>
       </c>
       <c r="H30" s="1">
-        <v>20.015264511108399</v>
+        <v>19.986381530761719</v>
       </c>
       <c r="I30" s="1">
-        <v>19.792993545532227</v>
+        <v>19.752567291259766</v>
       </c>
       <c r="J30" s="1">
         <v>2.0447831153869629</v>
       </c>
       <c r="K30" s="1">
-        <v>2.1368324756622314</v>
+        <v>2.2348935604095459</v>
       </c>
       <c r="L30" s="1">
-        <v>2.3287811279296875</v>
+        <v>2.4559605121612549</v>
       </c>
     </row>
     <row r="31">
@@ -1973,28 +1973,28 @@
         <v>21.391513824462891</v>
       </c>
       <c r="E31" s="1">
-        <v>21.03917121887207</v>
+        <v>20.993791580200195</v>
       </c>
       <c r="F31" s="1">
-        <v>20.604049682617188</v>
+        <v>20.551307678222656</v>
       </c>
       <c r="G31" s="1">
         <v>20.354705810546875</v>
       </c>
       <c r="H31" s="1">
-        <v>20.002134323120117</v>
+        <v>19.956754684448242</v>
       </c>
       <c r="I31" s="1">
-        <v>19.563074111938477</v>
+        <v>19.510330200195313</v>
       </c>
       <c r="J31" s="1">
         <v>2.0159649848937988</v>
       </c>
       <c r="K31" s="1">
-        <v>2.3287491798400879</v>
+        <v>2.4265949726104736</v>
       </c>
       <c r="L31" s="1">
-        <v>2.767411470413208</v>
+        <v>2.8389952182769775</v>
       </c>
     </row>
   </sheetData>
@@ -2102,28 +2102,28 @@
         <v>19.437982559204102</v>
       </c>
       <c r="E3" s="1">
-        <v>19.347400665283203</v>
+        <v>19.300323486328125</v>
       </c>
       <c r="F3" s="1">
-        <v>19.347400665283203</v>
+        <v>19.300323486328125</v>
       </c>
       <c r="G3" s="1">
-        <v>18.274675369262695</v>
+        <v>18.227598190307617</v>
       </c>
       <c r="H3" s="1">
         <v>1.9832693338394165</v>
       </c>
       <c r="I3" s="1">
-        <v>2.5567808151245117</v>
+        <v>2.6546263694763184</v>
       </c>
       <c r="J3" s="1">
-        <v>9.8354682922363281</v>
+        <v>10.113280296325684</v>
       </c>
       <c r="K3" s="1">
-        <v>1.0846986770629883</v>
+        <v>1.2589941024780274</v>
       </c>
       <c r="L3" s="1">
-        <v>15.838034629821777</v>
+        <v>15.406893730163574</v>
       </c>
       <c r="M3" s="1">
         <v>0</v>
@@ -2143,28 +2143,28 @@
         <v>19.437982559204102</v>
       </c>
       <c r="E4" s="1">
-        <v>18.745532989501953</v>
+        <v>18.685705184936524</v>
       </c>
       <c r="F4" s="1">
-        <v>18.745532989501953</v>
+        <v>18.685705184936524</v>
       </c>
       <c r="G4" s="1">
-        <v>17.668733596801758</v>
+        <v>17.608905792236328</v>
       </c>
       <c r="H4" s="1">
         <v>1.9832693338394165</v>
       </c>
       <c r="I4" s="1">
-        <v>2.9954431056976318</v>
+        <v>3.0670268535614014</v>
       </c>
       <c r="J4" s="1">
-        <v>15.837949752807617</v>
+        <v>16.265968322753906</v>
       </c>
       <c r="K4" s="1">
-        <v>2.4964632987976074</v>
+        <v>2.6075263023376465</v>
       </c>
       <c r="L4" s="1">
-        <v>9.8339824676513672</v>
+        <v>9.3232507705688477</v>
       </c>
       <c r="M4" s="1">
         <v>0</v>
@@ -2225,28 +2225,28 @@
         <v>26.761215209960938</v>
       </c>
       <c r="E6" s="1">
-        <v>25.370023727416992</v>
+        <v>25.258701324462891</v>
       </c>
       <c r="F6" s="1">
-        <v>25.370023727416992</v>
+        <v>25.258701324462891</v>
       </c>
       <c r="G6" s="1">
-        <v>24.21858024597168</v>
+        <v>24.107257843017578</v>
       </c>
       <c r="H6" s="1">
         <v>2.2902781963348389</v>
       </c>
       <c r="I6" s="1">
-        <v>2.5891399383544922</v>
+        <v>2.6869857311248779</v>
       </c>
       <c r="J6" s="1">
-        <v>6.798243522644043</v>
+        <v>6.9636702537536621</v>
       </c>
       <c r="K6" s="1">
-        <v>1.7211430072784424</v>
+        <v>1.9977059364318848</v>
       </c>
       <c r="L6" s="1">
-        <v>8.5882997512817383</v>
+        <v>8.1672878265380859</v>
       </c>
       <c r="M6" s="1">
         <v>0</v>
@@ -2266,28 +2266,28 @@
         <v>26.761215209960938</v>
       </c>
       <c r="E7" s="1">
-        <v>24.383663177490234</v>
+        <v>24.278963088989258</v>
       </c>
       <c r="F7" s="1">
-        <v>24.383663177490234</v>
+        <v>24.278963088989258</v>
       </c>
       <c r="G7" s="1">
-        <v>23.227846145629883</v>
+        <v>23.123146057128906</v>
       </c>
       <c r="H7" s="1">
         <v>2.2902781963348389</v>
       </c>
       <c r="I7" s="1">
-        <v>3.0278022289276123</v>
+        <v>3.0993859767913818</v>
       </c>
       <c r="J7" s="1">
-        <v>10.589154243469238</v>
+        <v>10.847822189331055</v>
       </c>
       <c r="K7" s="1">
-        <v>3.9612569808959961</v>
+        <v>4.1374859809875488</v>
       </c>
       <c r="L7" s="1">
-        <v>4.6194758415222168</v>
+        <v>4.1639304161071777</v>
       </c>
       <c r="M7" s="1">
         <v>2</v>
@@ -2348,28 +2348,28 @@
         <v>34.186836242675781</v>
       </c>
       <c r="E9" s="1">
-        <v>29.928842544555664</v>
+        <v>29.654911041259766</v>
       </c>
       <c r="F9" s="1">
-        <v>29.928842544555664</v>
+        <v>29.654911041259766</v>
       </c>
       <c r="G9" s="1">
-        <v>28.680160522460938</v>
+        <v>28.406229019165039</v>
       </c>
       <c r="H9" s="1">
         <v>2.5327386856079102</v>
       </c>
       <c r="I9" s="1">
-        <v>3.1444909572601318</v>
+        <v>3.2423365116119385</v>
       </c>
       <c r="J9" s="1">
-        <v>8.1773147583007813</v>
+        <v>8.2835941314697266</v>
       </c>
       <c r="K9" s="1">
-        <v>4.2830290794372559</v>
+        <v>4.9712505340576172</v>
       </c>
       <c r="L9" s="1">
-        <v>0.10986289381980896</v>
+        <v>-0.23081494867801666</v>
       </c>
       <c r="M9" s="1">
         <v>0</v>
@@ -2389,28 +2389,28 @@
         <v>34.186836242675781</v>
       </c>
       <c r="E10" s="1">
-        <v>27.439643859863281</v>
+        <v>27.210954666137695</v>
       </c>
       <c r="F10" s="1">
-        <v>27.439643859863281</v>
+        <v>27.210954666137695</v>
       </c>
       <c r="G10" s="1">
-        <v>26.186220169067383</v>
+        <v>25.957530975341797</v>
       </c>
       <c r="H10" s="1">
         <v>2.5327386856079102</v>
       </c>
       <c r="I10" s="1">
-        <v>3.5831530094146729</v>
+        <v>3.6547367572784424</v>
       </c>
       <c r="J10" s="1">
-        <v>11.434160232543945</v>
+        <v>11.606899261474609</v>
       </c>
       <c r="K10" s="1">
-        <v>9.8575077056884766</v>
+        <v>10.296050071716309</v>
       </c>
       <c r="L10" s="1">
-        <v>-3.6611461639404297</v>
+        <v>-4.0364260673522949</v>
       </c>
       <c r="M10" s="1">
         <v>2</v>
@@ -2471,28 +2471,28 @@
         <v>20.997871398925781</v>
       </c>
       <c r="E12" s="1">
-        <v>18.452011108398438</v>
+        <v>18.247068405151367</v>
       </c>
       <c r="F12" s="1">
-        <v>18.452011108398438</v>
+        <v>18.247068405151367</v>
       </c>
       <c r="G12" s="1">
-        <v>17.019886016845703</v>
+        <v>16.814945220947266</v>
       </c>
       <c r="H12" s="1">
         <v>4.6891798973083496</v>
       </c>
       <c r="I12" s="1">
-        <v>3.8434736728668213</v>
+        <v>3.941319465637207</v>
       </c>
       <c r="J12" s="1">
-        <v>11.400674819946289</v>
+        <v>11.547447204589844</v>
       </c>
       <c r="K12" s="1">
-        <v>3.6954507827758789</v>
+        <v>4.2892565727233887</v>
       </c>
       <c r="L12" s="1">
-        <v>-0.4444388747215271</v>
+        <v>-1.1354372501373291</v>
       </c>
       <c r="M12" s="1">
         <v>0</v>
@@ -2512,28 +2512,28 @@
         <v>20.997871398925781</v>
       </c>
       <c r="E13" s="1">
-        <v>16.368619918823242</v>
+        <v>16.172700881958008</v>
       </c>
       <c r="F13" s="1">
-        <v>16.368619918823242</v>
+        <v>16.172700881958008</v>
       </c>
       <c r="G13" s="1">
-        <v>14.931056976318359</v>
+        <v>14.735137939453125</v>
       </c>
       <c r="H13" s="1">
         <v>4.6891798973083496</v>
       </c>
       <c r="I13" s="1">
-        <v>4.2821364402770996</v>
+        <v>4.3537197113037109</v>
       </c>
       <c r="J13" s="1">
-        <v>18.428886413574219</v>
+        <v>18.68934440612793</v>
       </c>
       <c r="K13" s="1">
-        <v>8.5051794052124023</v>
+        <v>8.8835592269897461</v>
       </c>
       <c r="L13" s="1">
-        <v>-8.677311897277832</v>
+        <v>-9.407923698425293</v>
       </c>
       <c r="M13" s="1">
         <v>0</v>
@@ -2594,28 +2594,28 @@
         <v>25.186426162719727</v>
       </c>
       <c r="E15" s="1">
-        <v>23.796562194824219</v>
+        <v>23.711071014404297</v>
       </c>
       <c r="F15" s="1">
-        <v>23.796562194824219</v>
+        <v>23.711071014404297</v>
       </c>
       <c r="G15" s="1">
-        <v>22.614093780517578</v>
+        <v>22.528600692749024</v>
       </c>
       <c r="H15" s="1">
         <v>2.0056905746459961</v>
       </c>
       <c r="I15" s="1">
-        <v>2.8052895069122314</v>
+        <v>2.9031350612640381</v>
       </c>
       <c r="J15" s="1">
-        <v>8.9136447906494141</v>
+        <v>9.1533021926879883</v>
       </c>
       <c r="K15" s="1">
-        <v>1.6336649656295776</v>
+        <v>1.8961714506149292</v>
       </c>
       <c r="L15" s="1">
-        <v>6.6298255920410156</v>
+        <v>6.2514395713806152</v>
       </c>
       <c r="M15" s="1">
         <v>0</v>
@@ -2635,28 +2635,28 @@
         <v>25.186426162719727</v>
       </c>
       <c r="E16" s="1">
-        <v>22.766939163208008</v>
+        <v>22.672828674316406</v>
       </c>
       <c r="F16" s="1">
-        <v>22.766939163208008</v>
+        <v>22.672828674316406</v>
       </c>
       <c r="G16" s="1">
-        <v>21.579978942871094</v>
+        <v>21.485868453979492</v>
       </c>
       <c r="H16" s="1">
         <v>2.0056905746459961</v>
       </c>
       <c r="I16" s="1">
-        <v>3.2439517974853516</v>
+        <v>3.315535306930542</v>
       </c>
       <c r="J16" s="1">
-        <v>13.781820297241211</v>
+        <v>14.143301010131836</v>
       </c>
       <c r="K16" s="1">
-        <v>3.7599241733551025</v>
+        <v>3.9271962642669678</v>
       </c>
       <c r="L16" s="1">
-        <v>1.5667103528976441</v>
+        <v>1.1138797998428345</v>
       </c>
       <c r="M16" s="1">
         <v>0</v>
@@ -2717,28 +2717,28 @@
         <v>21.000280380249024</v>
       </c>
       <c r="E18" s="1">
-        <v>21.03917121887207</v>
+        <v>20.993791580200195</v>
       </c>
       <c r="F18" s="1">
-        <v>21.03917121887207</v>
+        <v>20.993791580200195</v>
       </c>
       <c r="G18" s="1">
-        <v>20.002134323120117</v>
+        <v>19.956754684448242</v>
       </c>
       <c r="H18" s="1">
         <v>1.8732786178588867</v>
       </c>
       <c r="I18" s="1">
-        <v>2.3287491798400879</v>
+        <v>2.4265949726104736</v>
       </c>
       <c r="J18" s="1">
-        <v>7.7659258842468262</v>
+        <v>7.9979352951049805</v>
       </c>
       <c r="K18" s="1">
-        <v>0.80292439460754395</v>
+        <v>0.93194276094436646</v>
       </c>
       <c r="L18" s="1">
-        <v>17.082620620727539</v>
+        <v>16.653467178344727</v>
       </c>
       <c r="M18" s="1">
         <v>0</v>
@@ -2758,28 +2758,28 @@
         <v>21.000280380249024</v>
       </c>
       <c r="E19" s="1">
-        <v>20.604049682617188</v>
+        <v>20.551307678222656</v>
       </c>
       <c r="F19" s="1">
-        <v>20.604049682617188</v>
+        <v>20.551307678222656</v>
       </c>
       <c r="G19" s="1">
-        <v>19.563074111938477</v>
+        <v>19.510330200195313</v>
       </c>
       <c r="H19" s="1">
         <v>1.8732786178588867</v>
       </c>
       <c r="I19" s="1">
-        <v>2.767411470413208</v>
+        <v>2.8389952182769775</v>
       </c>
       <c r="J19" s="1">
-        <v>12.622594833374023</v>
+        <v>12.982355117797852</v>
       </c>
       <c r="K19" s="1">
-        <v>1.847952127456665</v>
+        <v>1.930164098739624</v>
       </c>
       <c r="L19" s="1">
-        <v>12.332840919494629</v>
+        <v>11.850432395935059</v>
       </c>
       <c r="M19" s="1">
         <v>0</v>
@@ -2870,19 +2870,19 @@
         <v>13.888044357299805</v>
       </c>
       <c r="F2" s="1">
-        <v>9.478846549987793</v>
+        <v>8.6816396713256836</v>
       </c>
       <c r="G2" s="1">
-        <v>4.4121265411376953</v>
+        <v>3.8106439113616943</v>
       </c>
       <c r="H2" s="1">
         <v>13.888044357299805</v>
       </c>
       <c r="I2" s="1">
-        <v>9.478846549987793</v>
+        <v>8.6816396713256836</v>
       </c>
       <c r="J2" s="1">
-        <v>4.4121265411376953</v>
+        <v>3.8106439113616943</v>
       </c>
       <c r="K2" s="1">
         <v>4.110689640045166</v>
@@ -2897,19 +2897,19 @@
         <v>10.843605041503906</v>
       </c>
       <c r="O2" s="1">
-        <v>17.43724250793457</v>
+        <v>17.693269729614258</v>
       </c>
       <c r="P2" s="1">
-        <v>26.141860961914063</v>
+        <v>26.435676574707031</v>
       </c>
       <c r="Q2" s="1">
         <v>-6.1849474906921387</v>
       </c>
       <c r="R2" s="1">
-        <v>19.102193832397461</v>
+        <v>22.171640396118164</v>
       </c>
       <c r="S2" s="1">
-        <v>43.964218139648438</v>
+        <v>45.920097351074219</v>
       </c>
     </row>
     <row r="3">
@@ -2929,19 +2929,19 @@
         <v>14.748130798339844</v>
       </c>
       <c r="F3" s="1">
-        <v>10.113382339477539</v>
+        <v>9.4476251602172852</v>
       </c>
       <c r="G3" s="1">
-        <v>4.805572509765625</v>
+        <v>4.3274130821228027</v>
       </c>
       <c r="H3" s="1">
         <v>14.441656112670898</v>
       </c>
       <c r="I3" s="1">
-        <v>10.113382339477539</v>
+        <v>9.4476251602172852</v>
       </c>
       <c r="J3" s="1">
-        <v>4.805572509765625</v>
+        <v>4.3274130821228027</v>
       </c>
       <c r="K3" s="1">
         <v>2.7762997150421143</v>
@@ -2956,19 +2956,19 @@
         <v>0.87802988290786743</v>
       </c>
       <c r="O3" s="1">
-        <v>6.6575255393981934</v>
+        <v>6.9954714775085449</v>
       </c>
       <c r="P3" s="1">
-        <v>14.909927368164063</v>
+        <v>15.29775333404541</v>
       </c>
       <c r="Q3" s="1">
         <v>-7.7250099182128906</v>
       </c>
       <c r="R3" s="1">
-        <v>23.858671188354492</v>
+        <v>27.692415237426758</v>
       </c>
       <c r="S3" s="1">
-        <v>54.911373138427734</v>
+        <v>57.354278564453125</v>
       </c>
     </row>
     <row r="4">
@@ -2988,19 +2988,19 @@
         <v>14.497843742370605</v>
       </c>
       <c r="F4" s="1">
-        <v>11.664794921875</v>
+        <v>11.539224624633789</v>
       </c>
       <c r="G4" s="1">
-        <v>8.4240207672119141</v>
+        <v>8.3162174224853516</v>
       </c>
       <c r="H4" s="1">
         <v>14.497843742370605</v>
       </c>
       <c r="I4" s="1">
-        <v>11.664794921875</v>
+        <v>11.539224624633789</v>
       </c>
       <c r="J4" s="1">
-        <v>8.4240207672119141</v>
+        <v>8.3162174224853516</v>
       </c>
       <c r="K4" s="1">
         <v>9.7105236053466797</v>
@@ -3015,19 +3015,19 @@
         <v>2.5965206623077393</v>
       </c>
       <c r="O4" s="1">
-        <v>16.127565383911133</v>
+        <v>16.253034591674805</v>
       </c>
       <c r="P4" s="1">
-        <v>32.367595672607422</v>
+        <v>32.595130920410156</v>
       </c>
       <c r="Q4" s="1">
         <v>-1.1151782274246216</v>
       </c>
       <c r="R4" s="1">
-        <v>3.4442245960235596</v>
+        <v>3.9976620674133301</v>
       </c>
       <c r="S4" s="1">
-        <v>7.9269757270812988</v>
+        <v>8.279632568359375</v>
       </c>
     </row>
     <row r="5">
@@ -3047,19 +3047,19 @@
         <v>10.247621536254883</v>
       </c>
       <c r="F5" s="1">
-        <v>9.6573152542114258</v>
+        <v>9.4931135177612305</v>
       </c>
       <c r="G5" s="1">
-        <v>8.605682373046875</v>
+        <v>8.4442501068115234</v>
       </c>
       <c r="H5" s="1">
         <v>10.247621536254883</v>
       </c>
       <c r="I5" s="1">
-        <v>9.6573152542114258</v>
+        <v>9.4931135177612305</v>
       </c>
       <c r="J5" s="1">
-        <v>8.605682373046875</v>
+        <v>8.4442501068115234</v>
       </c>
       <c r="K5" s="1">
         <v>4.0069994926452637</v>
@@ -3074,10 +3074,10 @@
         <v>2.3136627674102783</v>
       </c>
       <c r="O5" s="1">
-        <v>9.0724105834960938</v>
+        <v>9.2388086318969727</v>
       </c>
       <c r="P5" s="1">
-        <v>18.133941650390625</v>
+        <v>18.470314025878906</v>
       </c>
       <c r="Q5" s="1">
         <v>0</v>
@@ -3094,58 +3094,58 @@
         <v>51</v>
       </c>
       <c r="B6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1">
         <v>0</v>
       </c>
       <c r="D6" s="1">
-        <v>17.446327209472656</v>
+        <v>18.721660614013672</v>
       </c>
       <c r="E6" s="1">
-        <v>14.429388999938965</v>
+        <v>18.56671142578125</v>
       </c>
       <c r="F6" s="1">
-        <v>13.474980354309082</v>
+        <v>16.098915100097656</v>
       </c>
       <c r="G6" s="1">
-        <v>12.932558059692383</v>
+        <v>13.063480377197266</v>
       </c>
       <c r="H6" s="1">
-        <v>14.429388999938965</v>
+        <v>18.482387542724609</v>
       </c>
       <c r="I6" s="1">
-        <v>13.474980354309082</v>
+        <v>16.098915100097656</v>
       </c>
       <c r="J6" s="1">
-        <v>12.932558059692383</v>
+        <v>13.063480377197266</v>
       </c>
       <c r="K6" s="1">
-        <v>2.846287727355957</v>
+        <v>5.2122688293457031</v>
       </c>
       <c r="L6" s="1">
-        <v>0</v>
+        <v>278.64407348632813</v>
       </c>
       <c r="M6" s="1">
         <v>0</v>
       </c>
       <c r="N6" s="1">
-        <v>0</v>
+        <v>6.620354175567627</v>
       </c>
       <c r="O6" s="1">
-        <v>5.2408218383789063</v>
+        <v>13.207352638244629</v>
       </c>
       <c r="P6" s="1">
-        <v>11.885794639587402</v>
+        <v>21.808509826660156</v>
       </c>
       <c r="Q6" s="1">
-        <v>0</v>
+        <v>-2.8772175312042236</v>
       </c>
       <c r="R6" s="1">
-        <v>0</v>
+        <v>10.314175605773926</v>
       </c>
       <c r="S6" s="1">
-        <v>0</v>
+        <v>21.361883163452148</v>
       </c>
     </row>
     <row r="7">
@@ -3153,58 +3153,58 @@
         <v>52</v>
       </c>
       <c r="B7" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="1">
         <v>0</v>
       </c>
       <c r="D7" s="1">
-        <v>18.721660614013672</v>
+        <v>23.036062240600586</v>
       </c>
       <c r="E7" s="1">
-        <v>18.56671142578125</v>
+        <v>24.004152297973633</v>
       </c>
       <c r="F7" s="1">
-        <v>16.348669052124023</v>
+        <v>18.183055877685547</v>
       </c>
       <c r="G7" s="1">
-        <v>13.318498611450195</v>
+        <v>13.215836524963379</v>
       </c>
       <c r="H7" s="1">
-        <v>18.482387542724609</v>
+        <v>23.208820343017578</v>
       </c>
       <c r="I7" s="1">
-        <v>16.348669052124023</v>
+        <v>18.183055877685547</v>
       </c>
       <c r="J7" s="1">
-        <v>13.318498611450195</v>
+        <v>13.215836524963379</v>
       </c>
       <c r="K7" s="1">
-        <v>5.2122688293457031</v>
+        <v>0.52955126762390137</v>
       </c>
       <c r="L7" s="1">
-        <v>278.64407348632813</v>
+        <v>557.02593994140625</v>
       </c>
       <c r="M7" s="1">
         <v>0</v>
       </c>
       <c r="N7" s="1">
-        <v>6.620354175567627</v>
+        <v>1.1010450124740601</v>
       </c>
       <c r="O7" s="1">
-        <v>13.04875659942627</v>
+        <v>2.9763128757476807</v>
       </c>
       <c r="P7" s="1">
-        <v>21.520900726318359</v>
+        <v>5.8891878128051758</v>
       </c>
       <c r="Q7" s="1">
-        <v>-2.8772175312042236</v>
+        <v>-5.7517280578613281</v>
       </c>
       <c r="R7" s="1">
-        <v>8.8862791061401367</v>
+        <v>20.618646621704102</v>
       </c>
       <c r="S7" s="1">
-        <v>20.452011108398438</v>
+        <v>42.703670501708984</v>
       </c>
     </row>
     <row r="8">
@@ -3218,52 +3218,52 @@
         <v>0</v>
       </c>
       <c r="D8" s="1">
-        <v>23.036062240600586</v>
+        <v>17.446327209472656</v>
       </c>
       <c r="E8" s="1">
-        <v>24.004152297973633</v>
+        <v>14.429388999938965</v>
       </c>
       <c r="F8" s="1">
-        <v>18.891559600830078</v>
+        <v>13.902769088745117</v>
       </c>
       <c r="G8" s="1">
-        <v>13.708035469055176</v>
+        <v>13.27243709564209</v>
       </c>
       <c r="H8" s="1">
-        <v>23.208820343017578</v>
+        <v>14.429388999938965</v>
       </c>
       <c r="I8" s="1">
-        <v>18.891559600830078</v>
+        <v>13.902769088745117</v>
       </c>
       <c r="J8" s="1">
-        <v>13.708035469055176</v>
+        <v>13.27243709564209</v>
       </c>
       <c r="K8" s="1">
-        <v>0.52955126762390137</v>
+        <v>2.846287727355957</v>
       </c>
       <c r="L8" s="1">
-        <v>557.02593994140625</v>
+        <v>0</v>
       </c>
       <c r="M8" s="1">
         <v>0</v>
       </c>
       <c r="N8" s="1">
-        <v>1.1010450124740601</v>
+        <v>0</v>
       </c>
       <c r="O8" s="1">
-        <v>2.6897656917572022</v>
+        <v>5.3617038726806641</v>
       </c>
       <c r="P8" s="1">
-        <v>5.4443087577819824</v>
+        <v>12.168533325195313</v>
       </c>
       <c r="Q8" s="1">
-        <v>-5.7517280578613281</v>
+        <v>0</v>
       </c>
       <c r="R8" s="1">
-        <v>17.764196395874023</v>
+        <v>0</v>
       </c>
       <c r="S8" s="1">
-        <v>40.884780883789063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3283,19 +3283,19 @@
         <v>19.551179885864258</v>
       </c>
       <c r="F9" s="1">
-        <v>18.36785888671875</v>
+        <v>18.182851791381836</v>
       </c>
       <c r="G9" s="1">
-        <v>15.645111083984375</v>
+        <v>15.419641494750977</v>
       </c>
       <c r="H9" s="1">
         <v>19.551179885864258</v>
       </c>
       <c r="I9" s="1">
-        <v>18.36785888671875</v>
+        <v>18.182851791381836</v>
       </c>
       <c r="J9" s="1">
-        <v>15.645111083984375</v>
+        <v>15.419641494750977</v>
       </c>
       <c r="K9" s="1">
         <v>2.9860866069793701</v>
@@ -3310,19 +3310,19 @@
         <v>9.726811408996582</v>
       </c>
       <c r="O9" s="1">
-        <v>20.176271438598633</v>
+        <v>20.723474502563477</v>
       </c>
       <c r="P9" s="1">
-        <v>33.584583282470703</v>
+        <v>34.404457092285156</v>
       </c>
       <c r="Q9" s="1">
         <v>-0.71068477630615234</v>
       </c>
       <c r="R9" s="1">
-        <v>2.1949474811553955</v>
+        <v>2.5476441383361817</v>
       </c>
       <c r="S9" s="1">
-        <v>5.051732063293457</v>
+        <v>5.2764739990234375</v>
       </c>
     </row>
     <row r="10">
@@ -3330,58 +3330,58 @@
         <v>55</v>
       </c>
       <c r="B10" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" s="1">
         <v>0</v>
       </c>
       <c r="D10" s="1">
-        <v>20.894319534301758</v>
+        <v>24.320249557495117</v>
       </c>
       <c r="E10" s="1">
-        <v>20.004081726074219</v>
+        <v>23.929683685302734</v>
       </c>
       <c r="F10" s="1">
-        <v>18.251867294311523</v>
+        <v>19.645267486572266</v>
       </c>
       <c r="G10" s="1">
-        <v>15.839443206787109</v>
+        <v>15.574652671813965</v>
       </c>
       <c r="H10" s="1">
-        <v>20.004081726074219</v>
+        <v>23.929683685302734</v>
       </c>
       <c r="I10" s="1">
-        <v>18.251867294311523</v>
+        <v>19.645267486572266</v>
       </c>
       <c r="J10" s="1">
-        <v>15.839443206787109</v>
+        <v>15.574652671813965</v>
       </c>
       <c r="K10" s="1">
-        <v>3.036236047744751</v>
+        <v>2.0872793197631836</v>
       </c>
       <c r="L10" s="1">
-        <v>164.36265563964844</v>
+        <v>372.96136474609375</v>
       </c>
       <c r="M10" s="1">
         <v>0</v>
       </c>
       <c r="N10" s="1">
-        <v>0.27044382691383362</v>
+        <v>1.9533945322036743</v>
       </c>
       <c r="O10" s="1">
-        <v>4.9997811317443848</v>
+        <v>5.6636600494384766</v>
       </c>
       <c r="P10" s="1">
-        <v>11.158867835998535</v>
+        <v>10.345035552978516</v>
       </c>
       <c r="Q10" s="1">
-        <v>-1.6971728801727295</v>
+        <v>-3.8511176109313965</v>
       </c>
       <c r="R10" s="1">
-        <v>5.2417135238647461</v>
+        <v>13.805386543273926</v>
       </c>
       <c r="S10" s="1">
-        <v>12.063945770263672</v>
+        <v>28.592596054077149</v>
       </c>
     </row>
     <row r="11">
@@ -3389,58 +3389,58 @@
         <v>56</v>
       </c>
       <c r="B11" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" s="1">
         <v>0</v>
       </c>
       <c r="D11" s="1">
-        <v>24.320249557495117</v>
+        <v>20.894319534301758</v>
       </c>
       <c r="E11" s="1">
-        <v>23.929683685302734</v>
+        <v>20.004081726074219</v>
       </c>
       <c r="F11" s="1">
-        <v>20.089265823364258</v>
+        <v>18.003952026367188</v>
       </c>
       <c r="G11" s="1">
-        <v>15.897987365722656</v>
+        <v>15.629270553588867</v>
       </c>
       <c r="H11" s="1">
-        <v>23.929683685302734</v>
+        <v>20.004081726074219</v>
       </c>
       <c r="I11" s="1">
-        <v>20.089265823364258</v>
+        <v>18.003952026367188</v>
       </c>
       <c r="J11" s="1">
-        <v>15.897987365722656</v>
+        <v>15.629270553588867</v>
       </c>
       <c r="K11" s="1">
-        <v>2.0872793197631836</v>
+        <v>3.036236047744751</v>
       </c>
       <c r="L11" s="1">
-        <v>372.96136474609375</v>
+        <v>164.36265563964844</v>
       </c>
       <c r="M11" s="1">
         <v>0</v>
       </c>
       <c r="N11" s="1">
-        <v>1.9533945322036743</v>
+        <v>0.27044382691383362</v>
       </c>
       <c r="O11" s="1">
-        <v>5.4485220909118652</v>
+        <v>5.2119674682617188</v>
       </c>
       <c r="P11" s="1">
-        <v>10.022695541381836</v>
+        <v>11.476786613464355</v>
       </c>
       <c r="Q11" s="1">
-        <v>-3.8511176109313965</v>
+        <v>-1.6971728801727295</v>
       </c>
       <c r="R11" s="1">
-        <v>11.8941650390625</v>
+        <v>6.0839815139770508</v>
       </c>
       <c r="S11" s="1">
-        <v>27.374744415283203</v>
+        <v>12.600648880004883</v>
       </c>
     </row>
     <row r="12">
@@ -3448,58 +3448,58 @@
         <v>57</v>
       </c>
       <c r="B12" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="1">
-        <v>18.293428421020508</v>
+        <v>30.1993408203125</v>
       </c>
       <c r="E12" s="1">
-        <v>18.006549835205078</v>
+        <v>22.156579971313477</v>
       </c>
       <c r="F12" s="1">
-        <v>17.670412063598633</v>
+        <v>19.55424690246582</v>
       </c>
       <c r="G12" s="1">
-        <v>17.107669830322266</v>
+        <v>16.944234848022461</v>
       </c>
       <c r="H12" s="1">
-        <v>18.006549835205078</v>
+        <v>22.156579971313477</v>
       </c>
       <c r="I12" s="1">
-        <v>17.670412063598633</v>
+        <v>19.55424690246582</v>
       </c>
       <c r="J12" s="1">
-        <v>17.107669830322266</v>
+        <v>16.944234848022461</v>
       </c>
       <c r="K12" s="1">
-        <v>1.9084329605102539</v>
+        <v>2.441215991973877</v>
       </c>
       <c r="L12" s="1">
-        <v>20.314830780029297</v>
+        <v>104.05338287353516</v>
       </c>
       <c r="M12" s="1">
         <v>0</v>
       </c>
       <c r="N12" s="1">
-        <v>3.7006993293762207</v>
+        <v>0</v>
       </c>
       <c r="O12" s="1">
-        <v>8.1179208755493164</v>
+        <v>2.4769191741943359</v>
       </c>
       <c r="P12" s="1">
-        <v>14.03311824798584</v>
+        <v>5.5817866325378418</v>
       </c>
       <c r="Q12" s="1">
-        <v>-0.20976652204990387</v>
+        <v>-1.0744326114654541</v>
       </c>
       <c r="R12" s="1">
-        <v>0.64786326885223389</v>
+        <v>3.851597785949707</v>
       </c>
       <c r="S12" s="1">
-        <v>1.491074800491333</v>
+        <v>7.9771161079406738</v>
       </c>
     </row>
     <row r="13">
@@ -3513,52 +3513,52 @@
         <v>1</v>
       </c>
       <c r="D13" s="1">
-        <v>17.884822845458984</v>
+        <v>18.293428421020508</v>
       </c>
       <c r="E13" s="1">
-        <v>18.427253723144531</v>
+        <v>18.006549835205078</v>
       </c>
       <c r="F13" s="1">
-        <v>18.015300750732422</v>
+        <v>17.609222412109375</v>
       </c>
       <c r="G13" s="1">
-        <v>17.554515838623047</v>
+        <v>17.021293640136719</v>
       </c>
       <c r="H13" s="1">
-        <v>18.00755500793457</v>
+        <v>18.006549835205078</v>
       </c>
       <c r="I13" s="1">
-        <v>17.953596115112305</v>
+        <v>17.609222412109375</v>
       </c>
       <c r="J13" s="1">
-        <v>17.554515838623047</v>
+        <v>17.021293640136719</v>
       </c>
       <c r="K13" s="1">
-        <v>0.99057501554489136</v>
+        <v>1.9084329605102539</v>
       </c>
       <c r="L13" s="1">
-        <v>53.776096343994141</v>
+        <v>20.314830780029297</v>
       </c>
       <c r="M13" s="1">
         <v>0</v>
       </c>
       <c r="N13" s="1">
-        <v>2.4200980663299561</v>
+        <v>3.7006993293762207</v>
       </c>
       <c r="O13" s="1">
-        <v>6.348048210144043</v>
+        <v>8.4315853118896484</v>
       </c>
       <c r="P13" s="1">
-        <v>11.78919506072998</v>
+        <v>14.503084182739258</v>
       </c>
       <c r="Q13" s="1">
-        <v>-0.55528020858764648</v>
+        <v>-0.20976652204990387</v>
       </c>
       <c r="R13" s="1">
-        <v>1.7149811983108521</v>
+        <v>0.75196552276611328</v>
       </c>
       <c r="S13" s="1">
-        <v>3.9470758438110352</v>
+        <v>1.5574100017547607</v>
       </c>
     </row>
     <row r="14">
@@ -3566,58 +3566,58 @@
         <v>59</v>
       </c>
       <c r="B14" s="1">
+        <v>4</v>
+      </c>
+      <c r="C14" s="1">
         <v>1</v>
       </c>
-      <c r="C14" s="1">
-        <v>0</v>
-      </c>
       <c r="D14" s="1">
-        <v>30.1993408203125</v>
+        <v>17.884822845458984</v>
       </c>
       <c r="E14" s="1">
-        <v>22.156579971313477</v>
+        <v>18.427253723144531</v>
       </c>
       <c r="F14" s="1">
-        <v>20.439937591552734</v>
+        <v>17.963834762573242</v>
       </c>
       <c r="G14" s="1">
-        <v>17.696060180664063</v>
+        <v>17.500455856323242</v>
       </c>
       <c r="H14" s="1">
-        <v>22.156579971313477</v>
+        <v>18.00755500793457</v>
       </c>
       <c r="I14" s="1">
-        <v>20.439937591552734</v>
+        <v>17.953596115112305</v>
       </c>
       <c r="J14" s="1">
-        <v>17.696060180664063</v>
+        <v>17.500455856323242</v>
       </c>
       <c r="K14" s="1">
-        <v>2.441215991973877</v>
+        <v>0.99057501554489136</v>
       </c>
       <c r="L14" s="1">
-        <v>104.05338287353516</v>
+        <v>53.776096343994141</v>
       </c>
       <c r="M14" s="1">
         <v>0</v>
       </c>
       <c r="N14" s="1">
-        <v>0</v>
+        <v>2.4200980663299561</v>
       </c>
       <c r="O14" s="1">
-        <v>2.4255015850067139</v>
+        <v>6.6902384757995606</v>
       </c>
       <c r="P14" s="1">
-        <v>5.4615211486816406</v>
+        <v>12.301900863647461</v>
       </c>
       <c r="Q14" s="1">
-        <v>-1.0744326114654541</v>
+        <v>-0.55528020858764648</v>
       </c>
       <c r="R14" s="1">
-        <v>3.3183817863464356</v>
+        <v>1.9905540943145752</v>
       </c>
       <c r="S14" s="1">
-        <v>7.6373448371887207</v>
+        <v>4.1226739883422852</v>
       </c>
     </row>
     <row r="15">
@@ -3637,19 +3637,19 @@
         <v>22.538822174072266</v>
       </c>
       <c r="F15" s="1">
-        <v>20.631675720214844</v>
+        <v>20.3890380859375</v>
       </c>
       <c r="G15" s="1">
-        <v>17.741329193115234</v>
+        <v>17.542583465576172</v>
       </c>
       <c r="H15" s="1">
         <v>22.538822174072266</v>
       </c>
       <c r="I15" s="1">
-        <v>20.631675720214844</v>
+        <v>20.3890380859375</v>
       </c>
       <c r="J15" s="1">
-        <v>17.741329193115234</v>
+        <v>17.542583465576172</v>
       </c>
       <c r="K15" s="1">
         <v>3.2154037952423096</v>
@@ -3664,19 +3664,19 @@
         <v>1.6574674844741821</v>
       </c>
       <c r="O15" s="1">
-        <v>6.8096075057983398</v>
+        <v>7.0478076934814453</v>
       </c>
       <c r="P15" s="1">
-        <v>13.315217018127441</v>
+        <v>13.672114372253418</v>
       </c>
       <c r="Q15" s="1">
         <v>-1.8186583518981934</v>
       </c>
       <c r="R15" s="1">
-        <v>5.6169209480285645</v>
+        <v>6.5194787979125977</v>
       </c>
       <c r="S15" s="1">
-        <v>12.927495002746582</v>
+        <v>13.502614974975586</v>
       </c>
     </row>
     <row r="16">
@@ -3696,19 +3696,19 @@
         <v>28.231882095336914</v>
       </c>
       <c r="F16" s="1">
-        <v>23.568092346191406</v>
+        <v>22.99627685546875</v>
       </c>
       <c r="G16" s="1">
-        <v>18.844953536987305</v>
+        <v>18.445953369140625</v>
       </c>
       <c r="H16" s="1">
         <v>28.07227897644043</v>
       </c>
       <c r="I16" s="1">
-        <v>23.568092346191406</v>
+        <v>22.99627685546875</v>
       </c>
       <c r="J16" s="1">
-        <v>18.844953536987305</v>
+        <v>18.445953369140625</v>
       </c>
       <c r="K16" s="1">
         <v>0.76714533567428589</v>
@@ -3723,19 +3723,19 @@
         <v>14.135010719299316</v>
       </c>
       <c r="O16" s="1">
-        <v>16.438617706298828</v>
+        <v>16.652961730957031</v>
       </c>
       <c r="P16" s="1">
-        <v>19.643228530883789</v>
+        <v>19.964380264282227</v>
       </c>
       <c r="Q16" s="1">
         <v>-4.1387767791748047</v>
       </c>
       <c r="R16" s="1">
-        <v>12.782600402832031</v>
+        <v>14.836581230163574</v>
       </c>
       <c r="S16" s="1">
-        <v>29.419500350952148</v>
+        <v>30.72831916809082</v>
       </c>
     </row>
     <row r="17">
@@ -3755,19 +3755,19 @@
         <v>20.536464691162109</v>
       </c>
       <c r="F17" s="1">
-        <v>19.937047958374023</v>
+        <v>19.826375961303711</v>
       </c>
       <c r="G17" s="1">
-        <v>18.929666519165039</v>
+        <v>18.777742385864258</v>
       </c>
       <c r="H17" s="1">
         <v>20.41484260559082</v>
       </c>
       <c r="I17" s="1">
-        <v>19.937047958374023</v>
+        <v>19.826375961303711</v>
       </c>
       <c r="J17" s="1">
-        <v>18.929666519165039</v>
+        <v>18.777742385864258</v>
       </c>
       <c r="K17" s="1">
         <v>1.8116350173950195</v>
@@ -3782,19 +3782,19 @@
         <v>4.4558606147766113</v>
       </c>
       <c r="O17" s="1">
-        <v>10.540552139282227</v>
+        <v>10.910123825073242</v>
       </c>
       <c r="P17" s="1">
-        <v>18.472793579101563</v>
+        <v>19.026525497436524</v>
       </c>
       <c r="Q17" s="1">
         <v>-0.51077693700790405</v>
       </c>
       <c r="R17" s="1">
-        <v>1.5775330066680908</v>
+        <v>1.8310197591781616</v>
       </c>
       <c r="S17" s="1">
-        <v>3.630734920501709</v>
+        <v>3.7922592163085938</v>
       </c>
     </row>
     <row r="18">
@@ -3814,19 +3814,19 @@
         <v>22.591592788696289</v>
       </c>
       <c r="F18" s="1">
-        <v>21.193620681762695</v>
+        <v>20.840599060058594</v>
       </c>
       <c r="G18" s="1">
-        <v>19.281576156616211</v>
+        <v>18.80284309387207</v>
       </c>
       <c r="H18" s="1">
         <v>22.591592788696289</v>
       </c>
       <c r="I18" s="1">
-        <v>21.193620681762695</v>
+        <v>20.840599060058594</v>
       </c>
       <c r="J18" s="1">
-        <v>19.281576156616211</v>
+        <v>18.80284309387207</v>
       </c>
       <c r="K18" s="1">
         <v>2.153038501739502</v>
@@ -3841,19 +3841,19 @@
         <v>0</v>
       </c>
       <c r="O18" s="1">
-        <v>2.6554343700408936</v>
+        <v>2.7266736030578613</v>
       </c>
       <c r="P18" s="1">
-        <v>6.0813584327697754</v>
+        <v>6.24798583984375</v>
       </c>
       <c r="Q18" s="1">
         <v>-1.3891488313674927</v>
       </c>
       <c r="R18" s="1">
-        <v>4.2903828620910645</v>
+        <v>4.9797854423522949</v>
       </c>
       <c r="S18" s="1">
-        <v>9.8744316101074219</v>
+        <v>10.313726425170898</v>
       </c>
     </row>
     <row r="19">
@@ -3873,19 +3873,19 @@
         <v>31.179271697998047</v>
       </c>
       <c r="F19" s="1">
-        <v>25.725887298583984</v>
+        <v>25.216320037841797</v>
       </c>
       <c r="G19" s="1">
-        <v>19.797641754150391</v>
+        <v>19.401891708374023</v>
       </c>
       <c r="H19" s="1">
         <v>31.179271697998047</v>
       </c>
       <c r="I19" s="1">
-        <v>25.725887298583984</v>
+        <v>25.216320037841797</v>
       </c>
       <c r="J19" s="1">
-        <v>19.797641754150391</v>
+        <v>19.401891708374023</v>
       </c>
       <c r="K19" s="1">
         <v>4.3763270378112793</v>
@@ -3900,19 +3900,19 @@
         <v>0</v>
       </c>
       <c r="O19" s="1">
-        <v>7.8815255165100098</v>
+        <v>7.9642710685729981</v>
       </c>
       <c r="P19" s="1">
-        <v>17.183755874633789</v>
+        <v>17.377296447753906</v>
       </c>
       <c r="Q19" s="1">
         <v>-2.3791112899780273</v>
       </c>
       <c r="R19" s="1">
-        <v>7.3478784561157227</v>
+        <v>8.5285768508911133</v>
       </c>
       <c r="S19" s="1">
-        <v>16.911340713500977</v>
+        <v>17.663694381713867</v>
       </c>
     </row>
     <row r="20">
@@ -3932,19 +3932,19 @@
         <v>21.785884857177734</v>
       </c>
       <c r="F20" s="1">
-        <v>21.41783332824707</v>
+        <v>21.439346313476563</v>
       </c>
       <c r="G20" s="1">
-        <v>21.110713958740234</v>
+        <v>21.120079040527344</v>
       </c>
       <c r="H20" s="1">
         <v>21.785884857177734</v>
       </c>
       <c r="I20" s="1">
-        <v>21.41783332824707</v>
+        <v>21.439346313476563</v>
       </c>
       <c r="J20" s="1">
-        <v>21.110713958740234</v>
+        <v>21.120079040527344</v>
       </c>
       <c r="K20" s="1">
         <v>1.231325626373291</v>
@@ -3959,19 +3959,19 @@
         <v>11.433267593383789</v>
       </c>
       <c r="O20" s="1">
-        <v>14.322908401489258</v>
+        <v>14.56766414642334</v>
       </c>
       <c r="P20" s="1">
-        <v>18.289754867553711</v>
+        <v>18.656475067138672</v>
       </c>
       <c r="Q20" s="1">
         <v>-0.19765809178352356</v>
       </c>
       <c r="R20" s="1">
-        <v>0.61046642065048218</v>
+        <v>0.70855957269668579</v>
       </c>
       <c r="S20" s="1">
-        <v>1.4050049781799317</v>
+        <v>1.4675110578536987</v>
       </c>
     </row>
     <row r="21">
@@ -3991,10 +3991,10 @@
         <v>22.169673919677734</v>
       </c>
       <c r="F21" s="1">
-        <v>21.786811828613281</v>
+        <v>21.782459259033203</v>
       </c>
       <c r="G21" s="1">
-        <v>21.377309799194336</v>
+        <v>21.366090774536133</v>
       </c>
       <c r="H21" s="1">
         <v>21.65791130065918</v>
@@ -4003,7 +4003,7 @@
         <v>21.607963562011719</v>
       </c>
       <c r="J21" s="1">
-        <v>21.377309799194336</v>
+        <v>21.366090774536133</v>
       </c>
       <c r="K21" s="1">
         <v>2.8153021335601807</v>
@@ -4018,19 +4018,19 @@
         <v>8.5872840881347656</v>
       </c>
       <c r="O21" s="1">
-        <v>12.250298500061035</v>
+        <v>12.405588150024414</v>
       </c>
       <c r="P21" s="1">
-        <v>17.517854690551758</v>
+        <v>17.781841278076172</v>
       </c>
       <c r="Q21" s="1">
         <v>-0.18233299255371094</v>
       </c>
       <c r="R21" s="1">
-        <v>0.56313502788543701</v>
+        <v>0.65362268686294556</v>
       </c>
       <c r="S21" s="1">
-        <v>1.2960704565048218</v>
+        <v>1.3537302017211914</v>
       </c>
     </row>
     <row r="22">
@@ -4050,19 +4050,19 @@
         <v>23.194978713989258</v>
       </c>
       <c r="F22" s="1">
-        <v>22.658670425415039</v>
+        <v>22.58497428894043</v>
       </c>
       <c r="G22" s="1">
-        <v>21.965524673461914</v>
+        <v>21.878816604614258</v>
       </c>
       <c r="H22" s="1">
         <v>23.194978713989258</v>
       </c>
       <c r="I22" s="1">
-        <v>22.658670425415039</v>
+        <v>22.58497428894043</v>
       </c>
       <c r="J22" s="1">
-        <v>21.965524673461914</v>
+        <v>21.878816604614258</v>
       </c>
       <c r="K22" s="1">
         <v>1.8094415664672852</v>
@@ -4077,19 +4077,19 @@
         <v>4.300234317779541</v>
       </c>
       <c r="O22" s="1">
-        <v>7.8137989044189453</v>
+        <v>8.0463485717773438</v>
       </c>
       <c r="P22" s="1">
-        <v>12.455674171447754</v>
+        <v>12.804105758666992</v>
       </c>
       <c r="Q22" s="1">
         <v>-0.60773938894271851</v>
       </c>
       <c r="R22" s="1">
-        <v>1.8770014047622681</v>
+        <v>2.1786086559295654</v>
       </c>
       <c r="S22" s="1">
-        <v>4.3199691772460938</v>
+        <v>4.5121569633483887</v>
       </c>
     </row>
     <row r="23">
@@ -4109,19 +4109,19 @@
         <v>22.736440658569336</v>
       </c>
       <c r="F23" s="1">
-        <v>22.453287124633789</v>
+        <v>22.354040145874023</v>
       </c>
       <c r="G23" s="1">
-        <v>22.068267822265625</v>
+        <v>21.973073959350586</v>
       </c>
       <c r="H23" s="1">
         <v>22.736440658569336</v>
       </c>
       <c r="I23" s="1">
-        <v>22.453287124633789</v>
+        <v>22.354040145874023</v>
       </c>
       <c r="J23" s="1">
-        <v>22.068267822265625</v>
+        <v>21.973073959350586</v>
       </c>
       <c r="K23" s="1">
         <v>1.8331828117370605</v>
@@ -4136,19 +4136,19 @@
         <v>0.63065856695175171</v>
       </c>
       <c r="O23" s="1">
-        <v>3.2198450565338135</v>
+        <v>3.425438404083252</v>
       </c>
       <c r="P23" s="1">
-        <v>6.8332977294921875</v>
+        <v>7.1544723510742188</v>
       </c>
       <c r="Q23" s="1">
         <v>-0.18892258405685425</v>
       </c>
       <c r="R23" s="1">
-        <v>0.58348685503005981</v>
+        <v>0.67724478244781494</v>
       </c>
       <c r="S23" s="1">
-        <v>1.3429108858108521</v>
+        <v>1.4026545286178589</v>
       </c>
     </row>
     <row r="24">
@@ -4168,19 +4168,19 @@
         <v>26.339178085327149</v>
       </c>
       <c r="F24" s="1">
-        <v>25.13648796081543</v>
+        <v>24.355611801147461</v>
       </c>
       <c r="G24" s="1">
-        <v>23.060474395751953</v>
+        <v>22.398670196533203</v>
       </c>
       <c r="H24" s="1">
         <v>26.339178085327149</v>
       </c>
       <c r="I24" s="1">
-        <v>25.13648796081543</v>
+        <v>24.355611801147461</v>
       </c>
       <c r="J24" s="1">
-        <v>23.060474395751953</v>
+        <v>22.398670196533203</v>
       </c>
       <c r="K24" s="1">
         <v>1.4881768226623535</v>
@@ -4195,19 +4195,19 @@
         <v>0</v>
       </c>
       <c r="O24" s="1">
-        <v>1.5750131607055664</v>
+        <v>1.6108368635177612</v>
       </c>
       <c r="P24" s="1">
-        <v>3.5541348457336426</v>
+        <v>3.6379258632659912</v>
       </c>
       <c r="Q24" s="1">
         <v>-0.86902743577957153</v>
       </c>
       <c r="R24" s="1">
-        <v>2.6839890480041504</v>
+        <v>3.115267276763916</v>
       </c>
       <c r="S24" s="1">
-        <v>6.1772732734680176</v>
+        <v>6.4520883560180664</v>
       </c>
     </row>
     <row r="25">
@@ -4227,19 +4227,19 @@
         <v>25.217960357666016</v>
       </c>
       <c r="F25" s="1">
-        <v>25.020689010620117</v>
+        <v>24.944515228271484</v>
       </c>
       <c r="G25" s="1">
-        <v>24.761962890625</v>
+        <v>24.687053680419922</v>
       </c>
       <c r="H25" s="1">
         <v>25.063941955566406</v>
       </c>
       <c r="I25" s="1">
-        <v>25.020689010620117</v>
+        <v>24.944515228271484</v>
       </c>
       <c r="J25" s="1">
-        <v>24.761962890625</v>
+        <v>24.687053680419922</v>
       </c>
       <c r="K25" s="1">
         <v>1.5383285284042358</v>
@@ -4254,19 +4254,19 @@
         <v>2.0270929336547852</v>
       </c>
       <c r="O25" s="1">
-        <v>3.9545767307281494</v>
+        <v>4.1341357231140137</v>
       </c>
       <c r="P25" s="1">
-        <v>6.6969466209411621</v>
+        <v>6.965980052947998</v>
       </c>
       <c r="Q25" s="1">
         <v>-0.11669077724218369</v>
       </c>
       <c r="R25" s="1">
-        <v>0.36039909720420838</v>
+        <v>0.41831004619598389</v>
       </c>
       <c r="S25" s="1">
-        <v>0.82946836948394775</v>
+        <v>0.86636990308761597</v>
       </c>
     </row>
     <row r="26">
@@ -4286,19 +4286,19 @@
         <v>26.890453338623047</v>
       </c>
       <c r="F26" s="1">
-        <v>26.2244873046875</v>
+        <v>26.161117553710938</v>
       </c>
       <c r="G26" s="1">
-        <v>24.914407730102539</v>
+        <v>24.777814865112305</v>
       </c>
       <c r="H26" s="1">
         <v>26.890453338623047</v>
       </c>
       <c r="I26" s="1">
-        <v>26.2244873046875</v>
+        <v>26.161117553710938</v>
       </c>
       <c r="J26" s="1">
-        <v>24.914407730102539</v>
+        <v>24.777814865112305</v>
       </c>
       <c r="K26" s="1">
         <v>3.7642781734466553</v>
@@ -4313,19 +4313,19 @@
         <v>9.6281051635742188</v>
       </c>
       <c r="O26" s="1">
-        <v>15.586196899414063</v>
+        <v>15.810348510742188</v>
       </c>
       <c r="P26" s="1">
-        <v>23.184902191162109</v>
+        <v>23.557899475097656</v>
       </c>
       <c r="Q26" s="1">
         <v>-0.084042765200138092</v>
       </c>
       <c r="R26" s="1">
-        <v>0.25956583023071289</v>
+        <v>0.30127432942390442</v>
       </c>
       <c r="S26" s="1">
-        <v>0.59739774465560913</v>
+        <v>0.62397491931915283</v>
       </c>
     </row>
     <row r="27">
@@ -4345,19 +4345,19 @@
         <v>30.280115127563477</v>
       </c>
       <c r="F27" s="1">
-        <v>27.809898376464844</v>
+        <v>27.771562576293945</v>
       </c>
       <c r="G27" s="1">
-        <v>25.037725448608399</v>
+        <v>25.049161911010742</v>
       </c>
       <c r="H27" s="1">
         <v>30.280115127563477</v>
       </c>
       <c r="I27" s="1">
-        <v>27.809898376464844</v>
+        <v>27.771562576293945</v>
       </c>
       <c r="J27" s="1">
-        <v>25.037725448608399</v>
+        <v>25.049161911010742</v>
       </c>
       <c r="K27" s="1">
         <v>5.4320864677429199</v>
@@ -4372,19 +4372,19 @@
         <v>2.8480558395385742</v>
       </c>
       <c r="O27" s="1">
-        <v>6.3015122413635254</v>
+        <v>6.3876533508300781</v>
       </c>
       <c r="P27" s="1">
-        <v>10.83763313293457</v>
+        <v>10.993846893310547</v>
       </c>
       <c r="Q27" s="1">
         <v>-1.4852741956710816</v>
       </c>
       <c r="R27" s="1">
-        <v>4.5872650146484375</v>
+        <v>5.3243727684020996</v>
       </c>
       <c r="S27" s="1">
-        <v>10.557712554931641</v>
+        <v>11.027406692504883</v>
       </c>
     </row>
     <row r="28">
@@ -4404,19 +4404,19 @@
         <v>27.750946044921875</v>
       </c>
       <c r="F28" s="1">
-        <v>27.517244338989258</v>
+        <v>27.435285568237305</v>
       </c>
       <c r="G28" s="1">
-        <v>27.199169158935547</v>
+        <v>27.118268966674805</v>
       </c>
       <c r="H28" s="1">
         <v>27.465757369995117</v>
       </c>
       <c r="I28" s="1">
-        <v>27.437219619750977</v>
+        <v>27.435285568237305</v>
       </c>
       <c r="J28" s="1">
-        <v>27.199169158935547</v>
+        <v>27.118268966674805</v>
       </c>
       <c r="K28" s="1">
         <v>1.7580658197402954</v>
@@ -4431,19 +4431,19 @@
         <v>1.5790036916732788</v>
       </c>
       <c r="O28" s="1">
-        <v>3.7799456119537354</v>
+        <v>3.9432468414306641</v>
       </c>
       <c r="P28" s="1">
-        <v>6.9521279335021973</v>
+        <v>7.206110954284668</v>
       </c>
       <c r="Q28" s="1">
         <v>-0.092668108642101288</v>
       </c>
       <c r="R28" s="1">
-        <v>0.28620520234107971</v>
+        <v>0.33219426870346069</v>
       </c>
       <c r="S28" s="1">
-        <v>0.65870893001556396</v>
+        <v>0.68801367282867432</v>
       </c>
     </row>
     <row r="29">
@@ -4463,19 +4463,19 @@
         <v>28.572391510009766</v>
       </c>
       <c r="F29" s="1">
-        <v>28.274940490722656</v>
+        <v>28.379671096801758</v>
       </c>
       <c r="G29" s="1">
-        <v>27.924131393432617</v>
+        <v>28.011348724365234</v>
       </c>
       <c r="H29" s="1">
         <v>28.572391510009766</v>
       </c>
       <c r="I29" s="1">
-        <v>28.274940490722656</v>
+        <v>28.379671096801758</v>
       </c>
       <c r="J29" s="1">
-        <v>27.924131393432617</v>
+        <v>28.011348724365234</v>
       </c>
       <c r="K29" s="1">
         <v>1.2923356294631958</v>
@@ -4490,19 +4490,19 @@
         <v>11.875471115112305</v>
       </c>
       <c r="O29" s="1">
-        <v>13.389826774597168</v>
+        <v>13.539841651916504</v>
       </c>
       <c r="P29" s="1">
-        <v>15.733658790588379</v>
+        <v>15.949491500854492</v>
       </c>
       <c r="Q29" s="1">
         <v>-0.051728162914514542</v>
       </c>
       <c r="R29" s="1">
-        <v>0.15976226329803467</v>
+        <v>0.1854337751865387</v>
       </c>
       <c r="S29" s="1">
-        <v>0.36769720911979675</v>
+        <v>0.38405537605285645</v>
       </c>
     </row>
     <row r="30">
@@ -4522,19 +4522,19 @@
         <v>31.089242935180664</v>
       </c>
       <c r="F30" s="1">
-        <v>30.429536819458008</v>
+        <v>30.447328567504883</v>
       </c>
       <c r="G30" s="1">
-        <v>29.554224014282227</v>
+        <v>29.571104049682617</v>
       </c>
       <c r="H30" s="1">
         <v>31.089242935180664</v>
       </c>
       <c r="I30" s="1">
-        <v>30.429536819458008</v>
+        <v>30.447328567504883</v>
       </c>
       <c r="J30" s="1">
-        <v>29.554224014282227</v>
+        <v>29.571104049682617</v>
       </c>
       <c r="K30" s="1">
         <v>2.8590431213378906</v>
@@ -4549,19 +4549,19 @@
         <v>0</v>
       </c>
       <c r="O30" s="1">
-        <v>2.3855111598968506</v>
+        <v>2.4398257732391357</v>
       </c>
       <c r="P30" s="1">
-        <v>5.4051594734191895</v>
+        <v>5.532200813293457</v>
       </c>
       <c r="Q30" s="1">
         <v>-0.25040501356124878</v>
       </c>
       <c r="R30" s="1">
-        <v>0.77337509393692017</v>
+        <v>0.89764535427093506</v>
       </c>
       <c r="S30" s="1">
-        <v>1.7799438238143921</v>
+        <v>1.8591302633285523</v>
       </c>
     </row>
     <row r="31">
@@ -4581,19 +4581,19 @@
         <v>31.662092208862305</v>
       </c>
       <c r="F31" s="1">
-        <v>31.379671096801758</v>
+        <v>31.330020904541016</v>
       </c>
       <c r="G31" s="1">
-        <v>31.071037292480469</v>
+        <v>30.998691558837891</v>
       </c>
       <c r="H31" s="1">
         <v>31.662092208862305</v>
       </c>
       <c r="I31" s="1">
-        <v>31.379671096801758</v>
+        <v>31.330020904541016</v>
       </c>
       <c r="J31" s="1">
-        <v>31.071037292480469</v>
+        <v>30.998691558837891</v>
       </c>
       <c r="K31" s="1">
         <v>1.812983512878418</v>
@@ -4608,19 +4608,19 @@
         <v>2.8584282398223877</v>
       </c>
       <c r="O31" s="1">
-        <v>5.069890022277832</v>
+        <v>5.2332205772399902</v>
       </c>
       <c r="P31" s="1">
-        <v>8.0489082336425781</v>
+        <v>8.2936267852783203</v>
       </c>
       <c r="Q31" s="1">
         <v>-0.026917701587080956</v>
       </c>
       <c r="R31" s="1">
-        <v>0.083135239779949188</v>
+        <v>0.096493877470493317</v>
       </c>
       <c r="S31" s="1">
-        <v>0.19133801758289337</v>
+        <v>0.19985027611255646</v>
       </c>
     </row>
     <row r="32">
@@ -4640,19 +4640,19 @@
         <v>35.465656280517578</v>
       </c>
       <c r="F32" s="1">
-        <v>34.198135375976563</v>
+        <v>33.9617919921875</v>
       </c>
       <c r="G32" s="1">
-        <v>32.653774261474609</v>
+        <v>32.433746337890625</v>
       </c>
       <c r="H32" s="1">
         <v>35.465656280517578</v>
       </c>
       <c r="I32" s="1">
-        <v>34.198135375976563</v>
+        <v>33.9617919921875</v>
       </c>
       <c r="J32" s="1">
-        <v>32.653774261474609</v>
+        <v>32.433746337890625</v>
       </c>
       <c r="K32" s="1">
         <v>2.0582499504089356</v>
@@ -4667,19 +4667,19 @@
         <v>5.1170773506164551</v>
       </c>
       <c r="O32" s="1">
-        <v>7.2128152847290039</v>
+        <v>7.3377618789672852</v>
       </c>
       <c r="P32" s="1">
-        <v>9.93316650390625</v>
+        <v>10.12037467956543</v>
       </c>
       <c r="Q32" s="1">
         <v>-0.33560475707054138</v>
       </c>
       <c r="R32" s="1">
-        <v>1.0365142822265625</v>
+        <v>1.2030673027038574</v>
       </c>
       <c r="S32" s="1">
-        <v>2.3855657577514649</v>
+        <v>2.4916951656341553</v>
       </c>
     </row>
     <row r="33">
@@ -4699,19 +4699,19 @@
         <v>35.453342437744141</v>
       </c>
       <c r="F33" s="1">
-        <v>34.447845458984375</v>
+        <v>34.323963165283203</v>
       </c>
       <c r="G33" s="1">
-        <v>33.086063385009766</v>
+        <v>32.934234619140625</v>
       </c>
       <c r="H33" s="1">
         <v>35.453342437744141</v>
       </c>
       <c r="I33" s="1">
-        <v>34.447845458984375</v>
+        <v>34.323963165283203</v>
       </c>
       <c r="J33" s="1">
-        <v>33.086063385009766</v>
+        <v>32.934234619140625</v>
       </c>
       <c r="K33" s="1">
         <v>3.0391237735748291</v>
@@ -4726,19 +4726,19 @@
         <v>58.534774780273438</v>
       </c>
       <c r="O33" s="1">
-        <v>61.288604736328125</v>
+        <v>61.424823760986328</v>
       </c>
       <c r="P33" s="1">
-        <v>64.9110107421875</v>
+        <v>65.067344665527344</v>
       </c>
       <c r="Q33" s="1">
         <v>-0.67763090133666992</v>
       </c>
       <c r="R33" s="1">
-        <v>2.0928611755371094</v>
+        <v>2.4291539192199707</v>
       </c>
       <c r="S33" s="1">
-        <v>4.8167767524719238</v>
+        <v>5.0310659408569336</v>
       </c>
     </row>
     <row r="34">
@@ -4758,19 +4758,19 @@
         <v>34.155544281005859</v>
       </c>
       <c r="F34" s="1">
-        <v>33.781227111816406</v>
+        <v>33.766056060791016</v>
       </c>
       <c r="G34" s="1">
-        <v>33.267333984375</v>
+        <v>33.243087768554688</v>
       </c>
       <c r="H34" s="1">
         <v>34.155544281005859</v>
       </c>
       <c r="I34" s="1">
-        <v>33.781227111816406</v>
+        <v>33.766056060791016</v>
       </c>
       <c r="J34" s="1">
-        <v>33.267333984375</v>
+        <v>33.243087768554688</v>
       </c>
       <c r="K34" s="1">
         <v>2.6939806938171387</v>
@@ -4785,19 +4785,19 @@
         <v>1.2026726007461548</v>
       </c>
       <c r="O34" s="1">
-        <v>3.5168149471282959</v>
+        <v>3.6356034278869629</v>
       </c>
       <c r="P34" s="1">
-        <v>6.5942554473876953</v>
+        <v>6.7904548645019531</v>
       </c>
       <c r="Q34" s="1">
         <v>-0.10902998596429825</v>
       </c>
       <c r="R34" s="1">
-        <v>0.33673885464668274</v>
+        <v>0.39084795117378235</v>
       </c>
       <c r="S34" s="1">
-        <v>0.7750135064125061</v>
+        <v>0.80949240922927857</v>
       </c>
     </row>
     <row r="35">
@@ -4817,19 +4817,19 @@
         <v>37.019683837890625</v>
       </c>
       <c r="F35" s="1">
-        <v>36.211704254150391</v>
+        <v>36.075309753417969</v>
       </c>
       <c r="G35" s="1">
-        <v>35.316864013671875</v>
+        <v>35.148616790771484</v>
       </c>
       <c r="H35" s="1">
         <v>37.019683837890625</v>
       </c>
       <c r="I35" s="1">
-        <v>36.211704254150391</v>
+        <v>36.075309753417969</v>
       </c>
       <c r="J35" s="1">
-        <v>35.316864013671875</v>
+        <v>35.148616790771484</v>
       </c>
       <c r="K35" s="1">
         <v>0.32150024175643921</v>
@@ -4844,19 +4844,19 @@
         <v>0</v>
       </c>
       <c r="O35" s="1">
-        <v>0.64686918258666992</v>
+        <v>0.68457144498825073</v>
       </c>
       <c r="P35" s="1">
-        <v>1.606741189956665</v>
+        <v>1.6949261426925659</v>
       </c>
       <c r="Q35" s="1">
         <v>-0.71462589502334595</v>
       </c>
       <c r="R35" s="1">
-        <v>2.2071199417114258</v>
+        <v>2.561772346496582</v>
       </c>
       <c r="S35" s="1">
-        <v>5.0797462463378906</v>
+        <v>5.3057351112365723</v>
       </c>
     </row>
     <row r="36">
@@ -4876,19 +4876,19 @@
         <v>39.873363494873047</v>
       </c>
       <c r="F36" s="1">
-        <v>37.903785705566406</v>
+        <v>37.75830078125</v>
       </c>
       <c r="G36" s="1">
-        <v>35.984672546386719</v>
+        <v>35.916431427001953</v>
       </c>
       <c r="H36" s="1">
         <v>39.873363494873047</v>
       </c>
       <c r="I36" s="1">
-        <v>37.903785705566406</v>
+        <v>37.75830078125</v>
       </c>
       <c r="J36" s="1">
-        <v>35.984672546386719</v>
+        <v>35.916431427001953</v>
       </c>
       <c r="K36" s="1">
         <v>1.9415525197982788</v>
@@ -4903,19 +4903,19 @@
         <v>3.7585716247558594</v>
       </c>
       <c r="O36" s="1">
-        <v>6.0081357955932617</v>
+        <v>6.158841609954834</v>
       </c>
       <c r="P36" s="1">
-        <v>8.9865150451660156</v>
+        <v>9.2123174667358399</v>
       </c>
       <c r="Q36" s="1">
         <v>-1.0365113019943237</v>
       </c>
       <c r="R36" s="1">
-        <v>3.2012622356414795</v>
+        <v>3.7156591415405274</v>
       </c>
       <c r="S36" s="1">
-        <v>7.3677916526794434</v>
+        <v>7.6955704689025879</v>
       </c>
     </row>
     <row r="37">
@@ -4929,52 +4929,52 @@
         <v>0</v>
       </c>
       <c r="D37" s="1">
-        <v>48.211658477783203</v>
+        <v>47.321636199951172</v>
       </c>
       <c r="E37" s="1">
-        <v>44.509128570556641</v>
+        <v>45.018539428710938</v>
       </c>
       <c r="F37" s="1">
-        <v>43.228977203369141</v>
+        <v>43.641483306884766</v>
       </c>
       <c r="G37" s="1">
-        <v>42.305355072021484</v>
+        <v>42.533458709716797</v>
       </c>
       <c r="H37" s="1">
-        <v>44.509128570556641</v>
+        <v>45.018539428710938</v>
       </c>
       <c r="I37" s="1">
-        <v>43.228977203369141</v>
+        <v>43.641483306884766</v>
       </c>
       <c r="J37" s="1">
-        <v>42.305355072021484</v>
+        <v>42.533458709716797</v>
       </c>
       <c r="K37" s="1">
-        <v>2.3083720207214355</v>
+        <v>1.9545148611068726</v>
       </c>
       <c r="L37" s="1">
-        <v>31.862676620483398</v>
+        <v>57.353202819824219</v>
       </c>
       <c r="M37" s="1">
         <v>0</v>
       </c>
       <c r="N37" s="1">
-        <v>3.545093297958374</v>
+        <v>0</v>
       </c>
       <c r="O37" s="1">
-        <v>4.8601541519165039</v>
+        <v>1.1859802007675171</v>
       </c>
       <c r="P37" s="1">
-        <v>6.963435173034668</v>
+        <v>2.8014233112335205</v>
       </c>
       <c r="Q37" s="1">
-        <v>-0.32900702953338623</v>
+        <v>-0.59221667051315308</v>
       </c>
       <c r="R37" s="1">
-        <v>1.0161373615264893</v>
+        <v>2.1229629516601563</v>
       </c>
       <c r="S37" s="1">
-        <v>2.3386671543121338</v>
+        <v>4.3969082832336426</v>
       </c>
     </row>
     <row r="38">
@@ -4988,52 +4988,52 @@
         <v>0</v>
       </c>
       <c r="D38" s="1">
-        <v>47.321636199951172</v>
+        <v>48.211658477783203</v>
       </c>
       <c r="E38" s="1">
-        <v>45.018539428710938</v>
+        <v>44.509128570556641</v>
       </c>
       <c r="F38" s="1">
-        <v>43.774166107177734</v>
+        <v>43.544685363769531</v>
       </c>
       <c r="G38" s="1">
-        <v>42.630062103271484</v>
+        <v>42.551666259765625</v>
       </c>
       <c r="H38" s="1">
-        <v>45.018539428710938</v>
+        <v>44.509128570556641</v>
       </c>
       <c r="I38" s="1">
-        <v>43.774166107177734</v>
+        <v>43.544685363769531</v>
       </c>
       <c r="J38" s="1">
-        <v>42.630062103271484</v>
+        <v>42.551666259765625</v>
       </c>
       <c r="K38" s="1">
-        <v>1.9545148611068726</v>
+        <v>2.3083720207214355</v>
       </c>
       <c r="L38" s="1">
-        <v>57.353202819824219</v>
+        <v>31.862676620483398</v>
       </c>
       <c r="M38" s="1">
         <v>0</v>
       </c>
       <c r="N38" s="1">
-        <v>0</v>
+        <v>3.545093297958374</v>
       </c>
       <c r="O38" s="1">
-        <v>1.1433122158050537</v>
+        <v>4.9259381294250488</v>
       </c>
       <c r="P38" s="1">
-        <v>2.7016241550445557</v>
+        <v>7.1140284538269043</v>
       </c>
       <c r="Q38" s="1">
-        <v>-0.59221667051315308</v>
+        <v>-0.32900702953338623</v>
       </c>
       <c r="R38" s="1">
-        <v>1.8290594816207886</v>
+        <v>1.1794159412384033</v>
       </c>
       <c r="S38" s="1">
-        <v>4.2096295356750488</v>
+        <v>2.4427101612091065</v>
       </c>
     </row>
     <row r="39">
@@ -5053,19 +5053,19 @@
         <v>48.685070037841797</v>
       </c>
       <c r="F39" s="1">
-        <v>47.454208374023438</v>
+        <v>47.172443389892578</v>
       </c>
       <c r="G39" s="1">
-        <v>46.032520294189453</v>
+        <v>45.725273132324219</v>
       </c>
       <c r="H39" s="1">
         <v>48.685070037841797</v>
       </c>
       <c r="I39" s="1">
-        <v>47.454208374023438</v>
+        <v>47.172443389892578</v>
       </c>
       <c r="J39" s="1">
-        <v>46.032520294189453</v>
+        <v>45.725273132324219</v>
       </c>
       <c r="K39" s="1">
         <v>2.9923243522644043</v>
@@ -5080,19 +5080,19 @@
         <v>24.987585067749024</v>
       </c>
       <c r="O39" s="1">
-        <v>27.107892990112305</v>
+        <v>27.197084426879883</v>
       </c>
       <c r="P39" s="1">
-        <v>29.701688766479492</v>
+        <v>29.835329055786133</v>
       </c>
       <c r="Q39" s="1">
         <v>-0.68098533153533936</v>
       </c>
       <c r="R39" s="1">
-        <v>2.1032211780548096</v>
+        <v>2.4411787986755371</v>
       </c>
       <c r="S39" s="1">
-        <v>4.8406205177307129</v>
+        <v>5.0559706687927246</v>
       </c>
     </row>
     <row r="40">
@@ -5112,19 +5112,19 @@
         <v>48.631397247314453</v>
       </c>
       <c r="F40" s="1">
-        <v>47.910167694091797</v>
+        <v>47.996326446533203</v>
       </c>
       <c r="G40" s="1">
-        <v>47.287372589111328</v>
+        <v>47.328617095947266</v>
       </c>
       <c r="H40" s="1">
         <v>48.631397247314453</v>
       </c>
       <c r="I40" s="1">
-        <v>47.910167694091797</v>
+        <v>47.996326446533203</v>
       </c>
       <c r="J40" s="1">
-        <v>47.287372589111328</v>
+        <v>47.328617095947266</v>
       </c>
       <c r="K40" s="1">
         <v>1.8385132551193237</v>
@@ -5139,19 +5139,19 @@
         <v>0</v>
       </c>
       <c r="O40" s="1">
-        <v>1.2787305116653442</v>
+        <v>1.3258427381515503</v>
       </c>
       <c r="P40" s="1">
-        <v>3.0157017707824707</v>
+        <v>3.125896692276001</v>
       </c>
       <c r="Q40" s="1">
         <v>-0.0324648916721344</v>
       </c>
       <c r="R40" s="1">
-        <v>0.10026773065328598</v>
+        <v>0.11637930572032928</v>
       </c>
       <c r="S40" s="1">
-        <v>0.23076890408992767</v>
+        <v>0.24103538691997528</v>
       </c>
     </row>
     <row r="41">
@@ -5171,19 +5171,19 @@
         <v>57.504615783691406</v>
       </c>
       <c r="F41" s="1">
-        <v>56.657455444335938</v>
+        <v>56.701080322265625</v>
       </c>
       <c r="G41" s="1">
-        <v>56.126174926757813</v>
+        <v>56.172615051269531</v>
       </c>
       <c r="H41" s="1">
         <v>57.504615783691406</v>
       </c>
       <c r="I41" s="1">
-        <v>56.657455444335938</v>
+        <v>56.701080322265625</v>
       </c>
       <c r="J41" s="1">
-        <v>56.126174926757813</v>
+        <v>56.172615051269531</v>
       </c>
       <c r="K41" s="1">
         <v>2.3428640365600586</v>
@@ -5198,19 +5198,19 @@
         <v>8.4982700347900391</v>
       </c>
       <c r="O41" s="1">
-        <v>9.3735275268554688</v>
+        <v>9.4306840896606445</v>
       </c>
       <c r="P41" s="1">
-        <v>10.534675598144531</v>
+        <v>10.623865127563477</v>
       </c>
       <c r="Q41" s="1">
         <v>-0.41630640625953674</v>
       </c>
       <c r="R41" s="1">
-        <v>1.2857609987258911</v>
+        <v>1.4923642873764038</v>
       </c>
       <c r="S41" s="1">
-        <v>2.9592137336730957</v>
+        <v>3.0908637046813965</v>
       </c>
     </row>
     <row r="42">
@@ -5230,19 +5230,19 @@
         <v>65.240455627441406</v>
       </c>
       <c r="F42" s="1">
-        <v>63.288158416748047</v>
+        <v>63.063045501708984</v>
       </c>
       <c r="G42" s="1">
-        <v>61.339290618896484</v>
+        <v>61.155933380126953</v>
       </c>
       <c r="H42" s="1">
         <v>65.240455627441406</v>
       </c>
       <c r="I42" s="1">
-        <v>63.288158416748047</v>
+        <v>63.063045501708984</v>
       </c>
       <c r="J42" s="1">
-        <v>61.339290618896484</v>
+        <v>61.155933380126953</v>
       </c>
       <c r="K42" s="1">
         <v>1.9380583763122559</v>
@@ -5257,19 +5257,19 @@
         <v>0</v>
       </c>
       <c r="O42" s="1">
-        <v>0.92144167423248291</v>
+        <v>0.94814598560333252</v>
       </c>
       <c r="P42" s="1">
-        <v>2.1227529048919678</v>
+        <v>2.1852138042449951</v>
       </c>
       <c r="Q42" s="1">
         <v>-0.50616496801376343</v>
       </c>
       <c r="R42" s="1">
-        <v>1.5632890462875366</v>
+        <v>1.8144869804382324</v>
       </c>
       <c r="S42" s="1">
-        <v>3.5979518890380859</v>
+        <v>3.7580180168151855</v>
       </c>
     </row>
     <row r="43">
@@ -5289,19 +5289,19 @@
         <v>68.602897644042969</v>
       </c>
       <c r="F43" s="1">
-        <v>65.258232116699219</v>
+        <v>64.815093994140625</v>
       </c>
       <c r="G43" s="1">
-        <v>61.8663330078125</v>
+        <v>61.514823913574219</v>
       </c>
       <c r="H43" s="1">
         <v>68.602897644042969</v>
       </c>
       <c r="I43" s="1">
-        <v>65.258232116699219</v>
+        <v>64.815093994140625</v>
       </c>
       <c r="J43" s="1">
-        <v>61.8663330078125</v>
+        <v>61.514823913574219</v>
       </c>
       <c r="K43" s="1">
         <v>1.1138042211532593</v>
@@ -5316,19 +5316,19 @@
         <v>0</v>
       </c>
       <c r="O43" s="1">
-        <v>1.1088933944702149</v>
+        <v>1.1434602737426758</v>
       </c>
       <c r="P43" s="1">
-        <v>2.5635077953338623</v>
+        <v>2.6443591117858887</v>
       </c>
       <c r="Q43" s="1">
         <v>-1.2609143257141113</v>
       </c>
       <c r="R43" s="1">
-        <v>3.8943307399749756</v>
+        <v>4.5200934410095215</v>
       </c>
       <c r="S43" s="1">
-        <v>8.9629058837890625</v>
+        <v>9.3616495132446289</v>
       </c>
     </row>
     <row r="44">
@@ -5348,19 +5348,19 @@
         <v>64.582122802734375</v>
       </c>
       <c r="F44" s="1">
-        <v>64.402755737304688</v>
+        <v>64.475189208984375</v>
       </c>
       <c r="G44" s="1">
-        <v>64.479019165039063</v>
+        <v>64.535690307617188</v>
       </c>
       <c r="H44" s="1">
         <v>64.582122802734375</v>
       </c>
       <c r="I44" s="1">
-        <v>64.402755737304688</v>
+        <v>64.475189208984375</v>
       </c>
       <c r="J44" s="1">
-        <v>64.479019165039063</v>
+        <v>64.535690307617188</v>
       </c>
       <c r="K44" s="1">
         <v>1.7335447072982788</v>
@@ -5375,19 +5375,19 @@
         <v>4.535308837890625</v>
       </c>
       <c r="O44" s="1">
-        <v>5.2263469696044922</v>
+        <v>5.2819509506225586</v>
       </c>
       <c r="P44" s="1">
-        <v>6.2488408088684082</v>
+        <v>6.3214783668518067</v>
       </c>
       <c r="Q44" s="1">
         <v>-0.0028829965740442276</v>
       </c>
       <c r="R44" s="1">
-        <v>0.0089041274040937424</v>
+        <v>0.010334892198443413</v>
       </c>
       <c r="S44" s="1">
-        <v>0.020493090152740479</v>
+        <v>0.02140478789806366</v>
       </c>
     </row>
     <row r="45">
@@ -5407,19 +5407,19 @@
         <v>80.810401916503906</v>
       </c>
       <c r="F45" s="1">
-        <v>77.886856079101563</v>
+        <v>77.790985107421875</v>
       </c>
       <c r="G45" s="1">
-        <v>74.815383911132813</v>
+        <v>74.746261596679688</v>
       </c>
       <c r="H45" s="1">
         <v>80.810401916503906</v>
       </c>
       <c r="I45" s="1">
-        <v>77.886856079101563</v>
+        <v>77.790985107421875</v>
       </c>
       <c r="J45" s="1">
-        <v>74.815383911132813</v>
+        <v>74.746261596679688</v>
       </c>
       <c r="K45" s="1">
         <v>5.2754936218261719</v>
@@ -5434,19 +5434,19 @@
         <v>0</v>
       </c>
       <c r="O45" s="1">
-        <v>1.8663080930709839</v>
+        <v>1.8940582275390625</v>
       </c>
       <c r="P45" s="1">
-        <v>4.1398692131042481</v>
+        <v>4.2047758102416992</v>
       </c>
       <c r="Q45" s="1">
         <v>-0.52598530054092407</v>
       </c>
       <c r="R45" s="1">
-        <v>1.6245042085647583</v>
+        <v>1.8855386972427368</v>
       </c>
       <c r="S45" s="1">
-        <v>3.7388401031494141</v>
+        <v>3.9051744937896729</v>
       </c>
     </row>
     <row r="46">
@@ -5466,19 +5466,19 @@
         <v>87.971038818359375</v>
       </c>
       <c r="F46" s="1">
-        <v>83.589035034179688</v>
+        <v>83.315071105957031</v>
       </c>
       <c r="G46" s="1">
-        <v>79.499229431152344</v>
+        <v>79.349342346191406</v>
       </c>
       <c r="H46" s="1">
         <v>87.971038818359375</v>
       </c>
       <c r="I46" s="1">
-        <v>83.589035034179688</v>
+        <v>83.315071105957031</v>
       </c>
       <c r="J46" s="1">
-        <v>79.499229431152344</v>
+        <v>79.349342346191406</v>
       </c>
       <c r="K46" s="1">
         <v>8.960113525390625</v>
@@ -5493,19 +5493,19 @@
         <v>31.12401008605957</v>
       </c>
       <c r="O46" s="1">
-        <v>34.461418151855469</v>
+        <v>34.519184112548828</v>
       </c>
       <c r="P46" s="1">
-        <v>38.421321868896484</v>
+        <v>38.48760986328125</v>
       </c>
       <c r="Q46" s="1">
         <v>-1.037487268447876</v>
       </c>
       <c r="R46" s="1">
-        <v>3.2042765617370605</v>
+        <v>3.7191579341888428</v>
       </c>
       <c r="S46" s="1">
-        <v>7.3747296333312988</v>
+        <v>7.7028179168701172</v>
       </c>
     </row>
   </sheetData>
@@ -5619,31 +5619,31 @@
         <v>22.513217926025391</v>
       </c>
       <c r="C3" s="1">
-        <v>21.876472473144531</v>
+        <v>21.80241775512695</v>
       </c>
       <c r="D3" s="1">
         <v>21.316532135009769</v>
       </c>
       <c r="E3" s="1">
-        <v>20.77069091796875</v>
+        <v>20.696636199951168</v>
       </c>
       <c r="F3" s="1">
         <v>2.1007614135742192</v>
       </c>
       <c r="G3" s="1">
-        <v>2.569164514541626</v>
+        <v>2.6670103073120122</v>
       </c>
       <c r="H3" s="1">
-        <v>8.3193932085161375</v>
+        <v>8.5411063419639959</v>
       </c>
       <c r="I3" s="1">
-        <v>1.402389134764527</v>
+        <v>1.6277328804753139</v>
       </c>
       <c r="J3" s="1">
-        <v>12.219223784927109</v>
+        <v>11.7931389740451</v>
       </c>
       <c r="K3" s="1">
-        <v>85.574773377498957</v>
+        <v>83.992933265348143</v>
       </c>
       <c r="L3" s="1">
         <v>0</v>
@@ -5666,31 +5666,31 @@
         <v>22.513217926025391</v>
       </c>
       <c r="C4" s="1">
-        <v>21.11314582824707</v>
+        <v>21.03447532653809</v>
       </c>
       <c r="D4" s="1">
         <v>21.316532135009769</v>
       </c>
       <c r="E4" s="1">
-        <v>20.00316429138184</v>
+        <v>19.924493789672852</v>
       </c>
       <c r="F4" s="1">
         <v>2.1007614135742192</v>
       </c>
       <c r="G4" s="1">
-        <v>3.0078268051147461</v>
+        <v>3.0794107913970952</v>
       </c>
       <c r="H4" s="1">
-        <v>13.217937112132621</v>
+        <v>13.561421608018341</v>
       </c>
       <c r="I4" s="1">
-        <v>3.227636489499754</v>
+        <v>3.371228042897124</v>
       </c>
       <c r="J4" s="1">
-        <v>7.2310853376423898</v>
+        <v>6.7479009260389136</v>
       </c>
       <c r="K4" s="1">
-        <v>80.373828437462464</v>
+        <v>80.090369124746758</v>
       </c>
       <c r="L4" s="1">
         <v>2</v>

--- a/output/fixed/stress_test_summary.xlsx
+++ b/output/fixed/stress_test_summary.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="246" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="247" uniqueCount="125">
   <si>
     <t>qtr</t>
   </si>
@@ -228,6 +228,9 @@
   </si>
   <si>
     <t>BSIM</t>
+  </si>
+  <si>
+    <t>MCOR</t>
   </si>
   <si>
     <t>MEGA</t>
@@ -505,61 +508,61 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2" s="1">
-        <v>22.513217926025391</v>
+        <v>22.532503128051758</v>
       </c>
       <c r="D2" s="1">
-        <v>22.513217926025391</v>
+        <v>22.532503128051758</v>
       </c>
       <c r="E2" s="1">
-        <v>22.513217926025391</v>
+        <v>22.532503128051758</v>
       </c>
       <c r="F2" s="1">
-        <v>21.316532135009766</v>
+        <v>21.336328506469727</v>
       </c>
       <c r="G2" s="1">
-        <v>21.316532135009766</v>
+        <v>21.336328506469727</v>
       </c>
       <c r="H2" s="1">
-        <v>21.316532135009766</v>
+        <v>21.336328506469727</v>
       </c>
       <c r="I2" s="1">
-        <v>2.1007614135742188</v>
+        <v>2.0984182357788086</v>
       </c>
       <c r="J2" s="1">
-        <v>2.1007614135742188</v>
+        <v>2.0984182357788086</v>
       </c>
       <c r="K2" s="1">
-        <v>2.1007614135742188</v>
+        <v>2.0984182357788086</v>
       </c>
       <c r="L2" s="1">
-        <v>0.51663017272949219</v>
+        <v>0.51564747095108032</v>
       </c>
       <c r="M2" s="1">
-        <v>0.51663017272949219</v>
+        <v>0.51564747095108032</v>
       </c>
       <c r="N2" s="1">
-        <v>0.51663017272949219</v>
+        <v>0.51564747095108032</v>
       </c>
       <c r="O2" s="1">
-        <v>0.21526722609996796</v>
+        <v>0.21444690227508545</v>
       </c>
       <c r="P2" s="1">
-        <v>0.21526722609996796</v>
+        <v>0.21444690227508545</v>
       </c>
       <c r="Q2" s="1">
-        <v>0.21526722609996796</v>
+        <v>0.21444690227508545</v>
       </c>
       <c r="R2" s="1">
-        <v>0.0853252112865448</v>
+        <v>0.086249701678752899</v>
       </c>
       <c r="S2" s="1">
-        <v>0.0853252112865448</v>
+        <v>0.086249701678752899</v>
       </c>
       <c r="T2" s="1">
-        <v>0.0853252112865448</v>
+        <v>0.086249701678752899</v>
       </c>
     </row>
     <row r="3">
@@ -567,61 +570,61 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3" s="1">
-        <v>22.48023796081543</v>
+        <v>22.498384475708008</v>
       </c>
       <c r="D3" s="1">
-        <v>22.391046524047852</v>
+        <v>22.408557891845703</v>
       </c>
       <c r="E3" s="1">
-        <v>22.293838500976563</v>
+        <v>22.310403823852539</v>
       </c>
       <c r="F3" s="1">
-        <v>21.307384490966797</v>
+        <v>21.326032638549805</v>
       </c>
       <c r="G3" s="1">
-        <v>21.218429565429688</v>
+        <v>21.236438751220703</v>
       </c>
       <c r="H3" s="1">
-        <v>21.120779037475586</v>
+        <v>21.137842178344727</v>
       </c>
       <c r="I3" s="1">
-        <v>2.2514598369598389</v>
+        <v>2.2504801750183105</v>
       </c>
       <c r="J3" s="1">
-        <v>2.2514598369598389</v>
+        <v>2.2504801750183105</v>
       </c>
       <c r="K3" s="1">
-        <v>2.2514598369598389</v>
+        <v>2.2504801750183105</v>
       </c>
       <c r="L3" s="1">
-        <v>0.49013453722000122</v>
+        <v>0.48911944031715393</v>
       </c>
       <c r="M3" s="1">
-        <v>0.44660630822181702</v>
+        <v>0.44537994265556335</v>
       </c>
       <c r="N3" s="1">
-        <v>0.38729450106620789</v>
+        <v>0.38578882813453674</v>
       </c>
       <c r="O3" s="1">
-        <v>0.24511410295963287</v>
+        <v>0.24474991858005524</v>
       </c>
       <c r="P3" s="1">
-        <v>0.28883540630340576</v>
+        <v>0.28845217823982239</v>
       </c>
       <c r="Q3" s="1">
-        <v>0.35394558310508728</v>
+        <v>0.35353401303291321</v>
       </c>
       <c r="R3" s="1">
-        <v>-0.017740942537784576</v>
+        <v>-0.017933163791894913</v>
       </c>
       <c r="S3" s="1">
-        <v>0.061033107340335846</v>
+        <v>0.061694394797086716</v>
       </c>
       <c r="T3" s="1">
-        <v>0.1478293240070343</v>
+        <v>0.14943104982376099</v>
       </c>
     </row>
     <row r="4">
@@ -629,61 +632,61 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C4" s="1">
-        <v>22.452136993408203</v>
+        <v>22.469232559204102</v>
       </c>
       <c r="D4" s="1">
-        <v>22.229488372802734</v>
+        <v>22.245197296142578</v>
       </c>
       <c r="E4" s="1">
-        <v>21.997781753540039</v>
+        <v>22.011495590209961</v>
       </c>
       <c r="F4" s="1">
-        <v>21.302433013916016</v>
+        <v>21.32002067565918</v>
       </c>
       <c r="G4" s="1">
-        <v>21.080020904541016</v>
+        <v>21.096221923828125</v>
       </c>
       <c r="H4" s="1">
-        <v>20.847011566162109</v>
+        <v>20.861215591430664</v>
       </c>
       <c r="I4" s="1">
-        <v>2.2568924427032471</v>
+        <v>2.2543222904205322</v>
       </c>
       <c r="J4" s="1">
-        <v>2.2962322235107422</v>
+        <v>2.2931809425354004</v>
       </c>
       <c r="K4" s="1">
-        <v>2.3654963970184326</v>
+        <v>2.3612267971038818</v>
       </c>
       <c r="L4" s="1">
-        <v>0.49343514442443848</v>
+        <v>0.4925592839717865</v>
       </c>
       <c r="M4" s="1">
-        <v>0.40555211901664734</v>
+        <v>0.40450090169906616</v>
       </c>
       <c r="N4" s="1">
-        <v>0.29874759912490845</v>
+        <v>0.29760658740997314</v>
       </c>
       <c r="O4" s="1">
-        <v>0.23602797091007233</v>
+        <v>0.2353503555059433</v>
       </c>
       <c r="P4" s="1">
-        <v>0.35105428099632263</v>
+        <v>0.35017648339271546</v>
       </c>
       <c r="Q4" s="1">
-        <v>0.50026637315750122</v>
+        <v>0.49887070059776306</v>
       </c>
       <c r="R4" s="1">
-        <v>-0.010321144014596939</v>
+        <v>-0.010432972572743893</v>
       </c>
       <c r="S4" s="1">
-        <v>0.086796216666698456</v>
+        <v>0.087736643850803375</v>
       </c>
       <c r="T4" s="1">
-        <v>0.17133872210979462</v>
+        <v>0.17319515347480774</v>
       </c>
     </row>
     <row r="5">
@@ -691,61 +694,61 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C5" s="1">
-        <v>22.464960098266602</v>
+        <v>22.481237411499024</v>
       </c>
       <c r="D5" s="1">
-        <v>22.036989212036133</v>
+        <v>22.051111221313477</v>
       </c>
       <c r="E5" s="1">
-        <v>21.601100921630859</v>
+        <v>21.61274528503418</v>
       </c>
       <c r="F5" s="1">
-        <v>21.337425231933594</v>
+        <v>21.354185104370117</v>
       </c>
       <c r="G5" s="1">
-        <v>20.9097900390625</v>
+        <v>20.924392700195313</v>
       </c>
       <c r="H5" s="1">
-        <v>20.471340179443359</v>
+        <v>20.483465194702148</v>
       </c>
       <c r="I5" s="1">
-        <v>2.2835750579833984</v>
+        <v>2.2808027267456055</v>
       </c>
       <c r="J5" s="1">
-        <v>2.4736855030059814</v>
+        <v>2.4686329364776611</v>
       </c>
       <c r="K5" s="1">
-        <v>2.6947524547576904</v>
+        <v>2.6856958866119385</v>
       </c>
       <c r="L5" s="1">
-        <v>0.51126635074615479</v>
+        <v>0.51045423746109009</v>
       </c>
       <c r="M5" s="1">
-        <v>0.35996437072753906</v>
+        <v>0.35918039083480835</v>
       </c>
       <c r="N5" s="1">
-        <v>0.17696189880371094</v>
+        <v>0.17670455574989319</v>
       </c>
       <c r="O5" s="1">
-        <v>0.21802417933940887</v>
+        <v>0.2173498272895813</v>
       </c>
       <c r="P5" s="1">
-        <v>0.43295383453369141</v>
+        <v>0.43155106902122498</v>
       </c>
       <c r="Q5" s="1">
-        <v>0.7168194055557251</v>
+        <v>0.7137485146522522</v>
       </c>
       <c r="R5" s="1">
-        <v>-0.035828325897455215</v>
+        <v>-0.036216519773006439</v>
       </c>
       <c r="S5" s="1">
-        <v>0.086036205291748047</v>
+        <v>0.086968399584293365</v>
       </c>
       <c r="T5" s="1">
-        <v>0.16850250959396362</v>
+        <v>0.17032821476459503</v>
       </c>
     </row>
     <row r="6">
@@ -753,61 +756,61 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C6" s="1">
-        <v>22.467874526977539</v>
+        <v>22.48326301574707</v>
       </c>
       <c r="D6" s="1">
-        <v>21.802417755126953</v>
+        <v>21.815752029418945</v>
       </c>
       <c r="E6" s="1">
-        <v>21.034475326538086</v>
+        <v>21.047142028808594</v>
       </c>
       <c r="F6" s="1">
-        <v>21.362339019775391</v>
+        <v>21.378198623657227</v>
       </c>
       <c r="G6" s="1">
-        <v>20.696636199951172</v>
+        <v>20.710443496704102</v>
       </c>
       <c r="H6" s="1">
-        <v>19.924493789672852</v>
+        <v>19.937633514404297</v>
       </c>
       <c r="I6" s="1">
-        <v>2.2563803195953369</v>
+        <v>2.2517673969268799</v>
       </c>
       <c r="J6" s="1">
-        <v>2.6670103073120117</v>
+        <v>2.6560423374176025</v>
       </c>
       <c r="K6" s="1">
-        <v>3.0794107913970947</v>
+        <v>3.0604684352874756</v>
       </c>
       <c r="L6" s="1">
-        <v>0.51506465673446655</v>
+        <v>0.51425039768218994</v>
       </c>
       <c r="M6" s="1">
-        <v>0.2992621660232544</v>
+        <v>0.29935985803604126</v>
       </c>
       <c r="N6" s="1">
-        <v>0.01218987163156271</v>
+        <v>0.014345861040055752</v>
       </c>
       <c r="O6" s="1">
-        <v>0.20774145424365997</v>
+        <v>0.20698535442352295</v>
       </c>
       <c r="P6" s="1">
-        <v>0.54956901073455811</v>
+        <v>0.54651373624801636</v>
       </c>
       <c r="Q6" s="1">
-        <v>1.0034915208816528</v>
+        <v>0.9963497519493103</v>
       </c>
       <c r="R6" s="1">
-        <v>-0.022434631362557411</v>
+        <v>-0.0226777084171772</v>
       </c>
       <c r="S6" s="1">
-        <v>0.076492264866828918</v>
+        <v>0.077321052551269531</v>
       </c>
       <c r="T6" s="1">
-        <v>0.15704241394996643</v>
+        <v>0.15874394774436951</v>
       </c>
     </row>
   </sheetData>
@@ -906,31 +909,31 @@
         <v>5</v>
       </c>
       <c r="D3" s="1">
-        <v>19.512229919433594</v>
+        <v>19.512197494506836</v>
       </c>
       <c r="E3" s="1">
-        <v>19.46058464050293</v>
+        <v>19.460554122924805</v>
       </c>
       <c r="F3" s="1">
-        <v>19.406673431396484</v>
+        <v>19.406646728515625</v>
       </c>
       <c r="G3" s="1">
-        <v>18.374439239501953</v>
+        <v>18.374406814575195</v>
       </c>
       <c r="H3" s="1">
-        <v>18.323020935058594</v>
+        <v>18.322990417480469</v>
       </c>
       <c r="I3" s="1">
-        <v>18.268680572509766</v>
+        <v>18.268653869628906</v>
       </c>
       <c r="J3" s="1">
-        <v>2.1771860122680664</v>
+        <v>2.1769814491271973</v>
       </c>
       <c r="K3" s="1">
-        <v>2.1771860122680664</v>
+        <v>2.1769814491271973</v>
       </c>
       <c r="L3" s="1">
-        <v>2.1771862506866455</v>
+        <v>2.1769814491271973</v>
       </c>
     </row>
     <row r="4">
@@ -944,31 +947,31 @@
         <v>5</v>
       </c>
       <c r="D4" s="1">
-        <v>19.584810256958008</v>
+        <v>19.584991455078125</v>
       </c>
       <c r="E4" s="1">
-        <v>19.44561767578125</v>
+        <v>19.445896148681641</v>
       </c>
       <c r="F4" s="1">
-        <v>19.294939041137695</v>
+        <v>19.295503616333008</v>
       </c>
       <c r="G4" s="1">
-        <v>18.469474792480469</v>
+        <v>18.469655990600586</v>
       </c>
       <c r="H4" s="1">
-        <v>18.330513000488281</v>
+        <v>18.330791473388672</v>
       </c>
       <c r="I4" s="1">
-        <v>18.178569793701172</v>
+        <v>18.179134368896484</v>
       </c>
       <c r="J4" s="1">
-        <v>2.211719274520874</v>
+        <v>2.208909273147583</v>
       </c>
       <c r="K4" s="1">
-        <v>2.2510590553283692</v>
+        <v>2.2477679252624512</v>
       </c>
       <c r="L4" s="1">
-        <v>2.3203232288360596</v>
+        <v>2.3158137798309326</v>
       </c>
     </row>
     <row r="5">
@@ -982,31 +985,31 @@
         <v>5</v>
       </c>
       <c r="D5" s="1">
-        <v>19.684576034545898</v>
+        <v>19.684902191162109</v>
       </c>
       <c r="E5" s="1">
-        <v>19.398456573486328</v>
+        <v>19.399332046508789</v>
       </c>
       <c r="F5" s="1">
-        <v>19.082208633422852</v>
+        <v>19.084421157836914</v>
       </c>
       <c r="G5" s="1">
-        <v>18.590747833251953</v>
+        <v>18.591075897216797</v>
       </c>
       <c r="H5" s="1">
-        <v>18.304952621459961</v>
+        <v>18.305830001831055</v>
       </c>
       <c r="I5" s="1">
-        <v>17.98621940612793</v>
+        <v>17.988431930541992</v>
       </c>
       <c r="J5" s="1">
-        <v>2.2579970359802246</v>
+        <v>2.254328727722168</v>
       </c>
       <c r="K5" s="1">
-        <v>2.4481074810028076</v>
+        <v>2.4421586990356445</v>
       </c>
       <c r="L5" s="1">
-        <v>2.6691744327545166</v>
+        <v>2.659221887588501</v>
       </c>
     </row>
     <row r="6">
@@ -1020,31 +1023,31 @@
         <v>5</v>
       </c>
       <c r="D6" s="1">
-        <v>19.780158996582031</v>
+        <v>19.780633926391602</v>
       </c>
       <c r="E6" s="1">
-        <v>19.300323486328125</v>
+        <v>19.302658081054688</v>
       </c>
       <c r="F6" s="1">
-        <v>18.685705184936524</v>
+        <v>18.692916870117188</v>
       </c>
       <c r="G6" s="1">
-        <v>18.707670211791992</v>
+        <v>18.708147048950195</v>
       </c>
       <c r="H6" s="1">
-        <v>18.227598190307617</v>
+        <v>18.229934692382813</v>
       </c>
       <c r="I6" s="1">
-        <v>17.608905792236328</v>
+        <v>17.616117477416992</v>
       </c>
       <c r="J6" s="1">
-        <v>2.2439966201782227</v>
+        <v>2.2380642890930176</v>
       </c>
       <c r="K6" s="1">
-        <v>2.6546263694763184</v>
+        <v>2.6423392295837402</v>
       </c>
       <c r="L6" s="1">
-        <v>3.0670268535614014</v>
+        <v>3.0467653274536133</v>
       </c>
     </row>
     <row r="7">
@@ -1055,34 +1058,34 @@
         <v>1</v>
       </c>
       <c r="C7" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D7" s="1">
-        <v>26.761215209960938</v>
+        <v>26.774463653564453</v>
       </c>
       <c r="E7" s="1">
-        <v>26.761215209960938</v>
+        <v>26.774463653564453</v>
       </c>
       <c r="F7" s="1">
-        <v>26.761215209960938</v>
+        <v>26.774463653564453</v>
       </c>
       <c r="G7" s="1">
-        <v>25.515111923217773</v>
+        <v>25.529949188232422</v>
       </c>
       <c r="H7" s="1">
-        <v>25.515111923217773</v>
+        <v>25.529949188232422</v>
       </c>
       <c r="I7" s="1">
-        <v>25.515111923217773</v>
+        <v>25.529949188232422</v>
       </c>
       <c r="J7" s="1">
-        <v>2.2902781963348389</v>
+        <v>2.2826457023620605</v>
       </c>
       <c r="K7" s="1">
-        <v>2.2902781963348389</v>
+        <v>2.2826457023620605</v>
       </c>
       <c r="L7" s="1">
-        <v>2.2902781963348389</v>
+        <v>2.2826457023620605</v>
       </c>
     </row>
     <row r="8">
@@ -1093,34 +1096,34 @@
         <v>2</v>
       </c>
       <c r="C8" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D8" s="1">
-        <v>26.580114364624023</v>
+        <v>26.591842651367188</v>
       </c>
       <c r="E8" s="1">
-        <v>26.439062118530273</v>
+        <v>26.449670791625977</v>
       </c>
       <c r="F8" s="1">
-        <v>26.282045364379883</v>
+        <v>26.290864944458008</v>
       </c>
       <c r="G8" s="1">
-        <v>25.358829498291016</v>
+        <v>25.372116088867188</v>
       </c>
       <c r="H8" s="1">
-        <v>25.218021392822266</v>
+        <v>25.230188369750977</v>
       </c>
       <c r="I8" s="1">
-        <v>25.060543060302734</v>
+        <v>25.070920944213867</v>
       </c>
       <c r="J8" s="1">
-        <v>2.371265172958374</v>
+        <v>2.3680710792541504</v>
       </c>
       <c r="K8" s="1">
-        <v>2.3712649345397949</v>
+        <v>2.3680710792541504</v>
       </c>
       <c r="L8" s="1">
-        <v>2.3712649345397949</v>
+        <v>2.3680710792541504</v>
       </c>
     </row>
     <row r="9">
@@ -1131,34 +1134,34 @@
         <v>3</v>
       </c>
       <c r="C9" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D9" s="1">
-        <v>26.412939071655274</v>
+        <v>26.422945022583008</v>
       </c>
       <c r="E9" s="1">
-        <v>26.075006484985352</v>
+        <v>26.082473754882813</v>
       </c>
       <c r="F9" s="1">
-        <v>25.73137092590332</v>
+        <v>25.734569549560547</v>
       </c>
       <c r="G9" s="1">
-        <v>25.21575927734375</v>
+        <v>25.227291107177734</v>
       </c>
       <c r="H9" s="1">
-        <v>24.878072738647461</v>
+        <v>24.887065887451172</v>
       </c>
       <c r="I9" s="1">
-        <v>24.5330810546875</v>
+        <v>24.537805557250977</v>
       </c>
       <c r="J9" s="1">
-        <v>2.3297574520111084</v>
+        <v>2.3269786834716797</v>
       </c>
       <c r="K9" s="1">
-        <v>2.3690972328186035</v>
+        <v>2.3658373355865479</v>
       </c>
       <c r="L9" s="1">
-        <v>2.4383611679077149</v>
+        <v>2.4338831901550293</v>
       </c>
     </row>
     <row r="10">
@@ -1169,34 +1172,34 @@
         <v>4</v>
       </c>
       <c r="C10" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D10" s="1">
-        <v>26.305662155151367</v>
+        <v>26.314443588256836</v>
       </c>
       <c r="E10" s="1">
-        <v>25.681747436523438</v>
+        <v>25.686161041259766</v>
       </c>
       <c r="F10" s="1">
-        <v>25.080593109130859</v>
+        <v>25.078563690185547</v>
       </c>
       <c r="G10" s="1">
-        <v>25.131568908691406</v>
+        <v>25.141845703125</v>
       </c>
       <c r="H10" s="1">
-        <v>24.508001327514649</v>
+        <v>24.513910293579102</v>
       </c>
       <c r="I10" s="1">
-        <v>23.904178619384766</v>
+        <v>23.903648376464844</v>
       </c>
       <c r="J10" s="1">
-        <v>2.3248331546783447</v>
+        <v>2.3231587409973145</v>
       </c>
       <c r="K10" s="1">
-        <v>2.5149433612823486</v>
+        <v>2.510988712310791</v>
       </c>
       <c r="L10" s="1">
-        <v>2.7360103130340576</v>
+        <v>2.7280516624450684</v>
       </c>
     </row>
     <row r="11">
@@ -1207,34 +1210,34 @@
         <v>5</v>
       </c>
       <c r="C11" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D11" s="1">
-        <v>26.180570602416992</v>
+        <v>26.188018798828125</v>
       </c>
       <c r="E11" s="1">
-        <v>25.258701324462891</v>
+        <v>25.260692596435547</v>
       </c>
       <c r="F11" s="1">
-        <v>24.278963088989258</v>
+        <v>24.274307250976563</v>
       </c>
       <c r="G11" s="1">
-        <v>25.029382705688477</v>
+        <v>25.038297653198242</v>
       </c>
       <c r="H11" s="1">
-        <v>24.107257843017578</v>
+        <v>24.1107177734375</v>
       </c>
       <c r="I11" s="1">
-        <v>23.123146057128906</v>
+        <v>23.119962692260742</v>
       </c>
       <c r="J11" s="1">
-        <v>2.2763557434082031</v>
+        <v>2.273690938949585</v>
       </c>
       <c r="K11" s="1">
-        <v>2.6869857311248779</v>
+        <v>2.6779658794403076</v>
       </c>
       <c r="L11" s="1">
-        <v>3.0993859767913818</v>
+        <v>3.0823919773101807</v>
       </c>
     </row>
     <row r="12">
@@ -1245,34 +1248,34 @@
         <v>1</v>
       </c>
       <c r="C12" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D12" s="1">
-        <v>34.186836242675781</v>
+        <v>33.739055633544922</v>
       </c>
       <c r="E12" s="1">
-        <v>34.186836242675781</v>
+        <v>33.739055633544922</v>
       </c>
       <c r="F12" s="1">
-        <v>34.186836242675781</v>
+        <v>33.739055633544922</v>
       </c>
       <c r="G12" s="1">
-        <v>32.835498809814453</v>
+        <v>32.412342071533203</v>
       </c>
       <c r="H12" s="1">
-        <v>32.835498809814453</v>
+        <v>32.412342071533203</v>
       </c>
       <c r="I12" s="1">
-        <v>32.835498809814453</v>
+        <v>32.412342071533203</v>
       </c>
       <c r="J12" s="1">
-        <v>2.5327386856079102</v>
+        <v>2.4324369430541992</v>
       </c>
       <c r="K12" s="1">
-        <v>2.5327386856079102</v>
+        <v>2.4324369430541992</v>
       </c>
       <c r="L12" s="1">
-        <v>2.5327386856079102</v>
+        <v>2.4324369430541992</v>
       </c>
     </row>
     <row r="13">
@@ -1283,34 +1286,34 @@
         <v>2</v>
       </c>
       <c r="C13" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D13" s="1">
-        <v>33.615833282470703</v>
+        <v>33.182823181152344</v>
       </c>
       <c r="E13" s="1">
-        <v>33.188522338867188</v>
+        <v>32.766506195068359</v>
       </c>
       <c r="F13" s="1">
-        <v>32.710655212402344</v>
+        <v>32.295276641845703</v>
       </c>
       <c r="G13" s="1">
-        <v>32.291416168212891</v>
+        <v>31.882535934448242</v>
       </c>
       <c r="H13" s="1">
-        <v>31.864368438720703</v>
+        <v>31.46647834777832</v>
       </c>
       <c r="I13" s="1">
-        <v>31.38599967956543</v>
+        <v>30.994758605957031</v>
       </c>
       <c r="J13" s="1">
-        <v>2.7423791885375977</v>
+        <v>2.6759073734283447</v>
       </c>
       <c r="K13" s="1">
-        <v>2.7423791885375977</v>
+        <v>2.6759073734283447</v>
       </c>
       <c r="L13" s="1">
-        <v>2.7423791885375977</v>
+        <v>2.6759073734283447</v>
       </c>
     </row>
     <row r="14">
@@ -1321,34 +1324,34 @@
         <v>3</v>
       </c>
       <c r="C14" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D14" s="1">
-        <v>33.032821655273438</v>
+        <v>32.614086151123047</v>
       </c>
       <c r="E14" s="1">
-        <v>32.043247222900391</v>
+        <v>31.648738861083984</v>
       </c>
       <c r="F14" s="1">
-        <v>31.032325744628906</v>
+        <v>30.643526077270508</v>
       </c>
       <c r="G14" s="1">
-        <v>31.734540939331055</v>
+        <v>31.339462280273438</v>
       </c>
       <c r="H14" s="1">
-        <v>30.745235443115234</v>
+        <v>30.374378204345703</v>
       </c>
       <c r="I14" s="1">
-        <v>29.732839584350586</v>
+        <v>29.367719650268555</v>
       </c>
       <c r="J14" s="1">
-        <v>2.7874999046325684</v>
+        <v>2.7413887977600098</v>
       </c>
       <c r="K14" s="1">
-        <v>2.8268396854400635</v>
+        <v>2.7802474498748779</v>
       </c>
       <c r="L14" s="1">
-        <v>2.8961038589477539</v>
+        <v>2.8482930660247803</v>
       </c>
     </row>
     <row r="15">
@@ -1359,34 +1362,34 @@
         <v>4</v>
       </c>
       <c r="C15" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D15" s="1">
-        <v>32.609352111816406</v>
+        <v>32.202350616455078</v>
       </c>
       <c r="E15" s="1">
-        <v>30.859432220458984</v>
+        <v>30.492002487182617</v>
       </c>
       <c r="F15" s="1">
-        <v>29.208240509033203</v>
+        <v>28.844316482543945</v>
       </c>
       <c r="G15" s="1">
-        <v>31.33610725402832</v>
+        <v>30.952304840087891</v>
       </c>
       <c r="H15" s="1">
-        <v>29.586563110351563</v>
+        <v>29.242330551147461</v>
       </c>
       <c r="I15" s="1">
-        <v>27.932479858398438</v>
+        <v>27.591802597045898</v>
       </c>
       <c r="J15" s="1">
-        <v>2.8409068584442139</v>
+        <v>2.8094339370727539</v>
       </c>
       <c r="K15" s="1">
-        <v>3.0310170650482178</v>
+        <v>2.9972641468048096</v>
       </c>
       <c r="L15" s="1">
-        <v>3.2520840167999268</v>
+        <v>3.2143270969390869</v>
       </c>
     </row>
     <row r="16">
@@ -1397,34 +1400,34 @@
         <v>5</v>
       </c>
       <c r="C16" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D16" s="1">
-        <v>32.125572204589844</v>
+        <v>31.73249626159668</v>
       </c>
       <c r="E16" s="1">
-        <v>29.654911041259766</v>
+        <v>29.312572479248047</v>
       </c>
       <c r="F16" s="1">
-        <v>27.210954666137695</v>
+        <v>26.87030029296875</v>
       </c>
       <c r="G16" s="1">
-        <v>30.877168655395508</v>
+        <v>30.506839752197266</v>
       </c>
       <c r="H16" s="1">
-        <v>28.406229019165039</v>
+        <v>28.086645126342774</v>
       </c>
       <c r="I16" s="1">
-        <v>25.957530975341797</v>
+        <v>25.639717102050781</v>
       </c>
       <c r="J16" s="1">
-        <v>2.8317065238952637</v>
+        <v>2.8084266185760498</v>
       </c>
       <c r="K16" s="1">
-        <v>3.2423365116119385</v>
+        <v>3.2127015590667725</v>
       </c>
       <c r="L16" s="1">
-        <v>3.6547367572784424</v>
+        <v>3.6171276569366455</v>
       </c>
     </row>
     <row r="17">
@@ -1476,31 +1479,31 @@
         <v>8</v>
       </c>
       <c r="D18" s="1">
-        <v>20.652267456054688</v>
+        <v>20.652599334716797</v>
       </c>
       <c r="E18" s="1">
-        <v>20.384086608886719</v>
+        <v>20.384426116943359</v>
       </c>
       <c r="F18" s="1">
-        <v>20.045055389404297</v>
+        <v>20.045492172241211</v>
       </c>
       <c r="G18" s="1">
-        <v>19.133279800415039</v>
+        <v>19.133609771728516</v>
       </c>
       <c r="H18" s="1">
-        <v>18.865400314331055</v>
+        <v>18.865739822387695</v>
       </c>
       <c r="I18" s="1">
-        <v>18.525794982910156</v>
+        <v>18.526233673095703</v>
       </c>
       <c r="J18" s="1">
-        <v>4.2995457649230957</v>
+        <v>4.3011026382446289</v>
       </c>
       <c r="K18" s="1">
-        <v>4.2995457649230957</v>
+        <v>4.3011026382446289</v>
       </c>
       <c r="L18" s="1">
-        <v>4.2995457649230957</v>
+        <v>4.3011026382446289</v>
       </c>
     </row>
     <row r="19">
@@ -1514,31 +1517,31 @@
         <v>8</v>
       </c>
       <c r="D19" s="1">
-        <v>20.388492584228516</v>
+        <v>20.388845443725586</v>
       </c>
       <c r="E19" s="1">
-        <v>19.736696243286133</v>
+        <v>19.737102508544922</v>
       </c>
       <c r="F19" s="1">
-        <v>18.996833801269531</v>
+        <v>18.99751091003418</v>
       </c>
       <c r="G19" s="1">
-        <v>18.899482727050781</v>
+        <v>18.899835586547852</v>
       </c>
       <c r="H19" s="1">
-        <v>18.247993469238281</v>
+        <v>18.24839973449707</v>
       </c>
       <c r="I19" s="1">
-        <v>17.506443023681641</v>
+        <v>17.507118225097656</v>
       </c>
       <c r="J19" s="1">
-        <v>3.9411468505859375</v>
+        <v>3.9407155513763428</v>
       </c>
       <c r="K19" s="1">
-        <v>3.9804863929748535</v>
+        <v>3.9795742034912109</v>
       </c>
       <c r="L19" s="1">
-        <v>4.0497503280639648</v>
+        <v>4.0476198196411133</v>
       </c>
     </row>
     <row r="20">
@@ -1552,31 +1555,31 @@
         <v>8</v>
       </c>
       <c r="D20" s="1">
-        <v>20.212512969970703</v>
+        <v>20.212871551513672</v>
       </c>
       <c r="E20" s="1">
-        <v>19.022176742553711</v>
+        <v>19.022928237915039</v>
       </c>
       <c r="F20" s="1">
-        <v>17.727632522583008</v>
+        <v>17.730104446411133</v>
       </c>
       <c r="G20" s="1">
-        <v>18.752216339111328</v>
+        <v>18.752574920654297</v>
       </c>
       <c r="H20" s="1">
-        <v>17.562314987182617</v>
+        <v>17.563064575195313</v>
       </c>
       <c r="I20" s="1">
-        <v>16.264450073242188</v>
+        <v>16.266921997070313</v>
       </c>
       <c r="J20" s="1">
-        <v>3.7228443622589111</v>
+        <v>3.7215871810913086</v>
       </c>
       <c r="K20" s="1">
-        <v>3.9129548072814942</v>
+        <v>3.9094173908233643</v>
       </c>
       <c r="L20" s="1">
-        <v>4.1340217590332031</v>
+        <v>4.1264801025390625</v>
       </c>
     </row>
     <row r="21">
@@ -1590,31 +1593,31 @@
         <v>8</v>
       </c>
       <c r="D21" s="1">
-        <v>20.007083892822266</v>
+        <v>20.007450103759766</v>
       </c>
       <c r="E21" s="1">
-        <v>18.247068405151367</v>
+        <v>18.249076843261719</v>
       </c>
       <c r="F21" s="1">
-        <v>16.172700881958008</v>
+        <v>16.181604385375977</v>
       </c>
       <c r="G21" s="1">
-        <v>18.575279235839844</v>
+        <v>18.575643539428711</v>
       </c>
       <c r="H21" s="1">
-        <v>16.814945220947266</v>
+        <v>16.816951751708984</v>
       </c>
       <c r="I21" s="1">
-        <v>14.735137939453125</v>
+        <v>14.744041442871094</v>
       </c>
       <c r="J21" s="1">
-        <v>3.5306894779205322</v>
+        <v>3.5269320011138916</v>
       </c>
       <c r="K21" s="1">
-        <v>3.941319465637207</v>
+        <v>3.9312069416046143</v>
       </c>
       <c r="L21" s="1">
-        <v>4.3537197113037109</v>
+        <v>4.3356328010559082</v>
       </c>
     </row>
     <row r="22">
@@ -1666,31 +1669,31 @@
         <v>10</v>
       </c>
       <c r="D23" s="1">
-        <v>24.996023178100586</v>
+        <v>24.995981216430664</v>
       </c>
       <c r="E23" s="1">
-        <v>24.884799957275391</v>
+        <v>24.884761810302734</v>
       </c>
       <c r="F23" s="1">
-        <v>24.76805305480957</v>
+        <v>24.768022537231445</v>
       </c>
       <c r="G23" s="1">
-        <v>23.741832733154297</v>
+        <v>23.741788864135742</v>
       </c>
       <c r="H23" s="1">
-        <v>23.630859375</v>
+        <v>23.630821228027344</v>
       </c>
       <c r="I23" s="1">
-        <v>23.513639450073242</v>
+        <v>23.513608932495117</v>
       </c>
       <c r="J23" s="1">
-        <v>2.2925693988800049</v>
+        <v>2.2920432090759277</v>
       </c>
       <c r="K23" s="1">
-        <v>2.2925693988800049</v>
+        <v>2.2920432090759277</v>
       </c>
       <c r="L23" s="1">
-        <v>2.2925693988800049</v>
+        <v>2.2920432090759277</v>
       </c>
     </row>
     <row r="24">
@@ -1704,31 +1707,31 @@
         <v>10</v>
       </c>
       <c r="D24" s="1">
-        <v>24.80644416809082</v>
+        <v>24.806625366210938</v>
       </c>
       <c r="E24" s="1">
-        <v>24.533811569213867</v>
+        <v>24.534149169921875</v>
       </c>
       <c r="F24" s="1">
-        <v>24.240409851074219</v>
+        <v>24.241203308105469</v>
       </c>
       <c r="G24" s="1">
-        <v>23.577005386352539</v>
+        <v>23.577186584472656</v>
       </c>
       <c r="H24" s="1">
-        <v>23.30462646484375</v>
+        <v>23.304964065551758</v>
       </c>
       <c r="I24" s="1">
-        <v>23.009830474853516</v>
+        <v>23.010625839233398</v>
       </c>
       <c r="J24" s="1">
-        <v>2.3896985054016113</v>
+        <v>2.3864409923553467</v>
       </c>
       <c r="K24" s="1">
-        <v>2.4290382862091065</v>
+        <v>2.4252998828887939</v>
       </c>
       <c r="L24" s="1">
-        <v>2.4983024597167969</v>
+        <v>2.4933454990386963</v>
       </c>
     </row>
     <row r="25">
@@ -1742,31 +1745,31 @@
         <v>10</v>
       </c>
       <c r="D25" s="1">
-        <v>24.671808242797852</v>
+        <v>24.672149658203125</v>
       </c>
       <c r="E25" s="1">
-        <v>24.150112152099609</v>
+        <v>24.151182174682617</v>
       </c>
       <c r="F25" s="1">
-        <v>23.579900741577149</v>
+        <v>23.583185195922852</v>
       </c>
       <c r="G25" s="1">
-        <v>23.46607780456543</v>
+        <v>23.466421127319336</v>
       </c>
       <c r="H25" s="1">
-        <v>22.944740295410156</v>
+        <v>22.945808410644531</v>
       </c>
       <c r="I25" s="1">
-        <v>22.371788024902344</v>
+        <v>22.375072479248047</v>
       </c>
       <c r="J25" s="1">
-        <v>2.4781250953674317</v>
+        <v>2.4739854335784912</v>
       </c>
       <c r="K25" s="1">
-        <v>2.6682353019714355</v>
+        <v>2.6618156433105469</v>
       </c>
       <c r="L25" s="1">
-        <v>2.8893022537231445</v>
+        <v>2.8788785934448242</v>
       </c>
     </row>
     <row r="26">
@@ -1780,31 +1783,31 @@
         <v>10</v>
       </c>
       <c r="D26" s="1">
-        <v>24.526863098144531</v>
+        <v>24.52734375</v>
       </c>
       <c r="E26" s="1">
-        <v>23.711071014404297</v>
+        <v>23.7139892578125</v>
       </c>
       <c r="F26" s="1">
-        <v>22.672828674316406</v>
+        <v>22.683252334594727</v>
       </c>
       <c r="G26" s="1">
-        <v>23.344655990600586</v>
+        <v>23.345138549804688</v>
       </c>
       <c r="H26" s="1">
-        <v>22.528600692749024</v>
+        <v>22.531518936157227</v>
       </c>
       <c r="I26" s="1">
-        <v>21.485868453979492</v>
+        <v>21.496292114257813</v>
       </c>
       <c r="J26" s="1">
-        <v>2.4925050735473633</v>
+        <v>2.4861268997192383</v>
       </c>
       <c r="K26" s="1">
-        <v>2.9031350612640381</v>
+        <v>2.89040207862854</v>
       </c>
       <c r="L26" s="1">
-        <v>3.315535306930542</v>
+        <v>3.294827938079834</v>
       </c>
     </row>
     <row r="27">
@@ -1856,31 +1859,31 @@
         <v>4</v>
       </c>
       <c r="D28" s="1">
-        <v>21.08735466003418</v>
+        <v>21.087326049804688</v>
       </c>
       <c r="E28" s="1">
-        <v>21.043485641479492</v>
+        <v>21.04345703125</v>
       </c>
       <c r="F28" s="1">
-        <v>20.99932861328125</v>
+        <v>20.999301910400391</v>
       </c>
       <c r="G28" s="1">
-        <v>19.987415313720703</v>
+        <v>19.987386703491211</v>
       </c>
       <c r="H28" s="1">
-        <v>19.943765640258789</v>
+        <v>19.94373893737793</v>
       </c>
       <c r="I28" s="1">
-        <v>19.899194717407227</v>
+        <v>19.899166107177734</v>
       </c>
       <c r="J28" s="1">
-        <v>2.0186595916748047</v>
+        <v>2.0186150074005127</v>
       </c>
       <c r="K28" s="1">
-        <v>2.0186595916748047</v>
+        <v>2.0186150074005127</v>
       </c>
       <c r="L28" s="1">
-        <v>2.0186595916748047</v>
+        <v>2.0186150074005127</v>
       </c>
     </row>
     <row r="29">
@@ -1894,31 +1897,31 @@
         <v>4</v>
       </c>
       <c r="D29" s="1">
-        <v>21.174201965332031</v>
+        <v>21.174322128295898</v>
       </c>
       <c r="E29" s="1">
-        <v>21.056634902954102</v>
+        <v>21.056835174560547</v>
       </c>
       <c r="F29" s="1">
-        <v>20.942834854125977</v>
+        <v>20.943269729614258</v>
       </c>
       <c r="G29" s="1">
-        <v>20.095972061157227</v>
+        <v>20.096092224121094</v>
       </c>
       <c r="H29" s="1">
-        <v>19.978628158569336</v>
+        <v>19.978828430175781</v>
       </c>
       <c r="I29" s="1">
-        <v>19.863603591918945</v>
+        <v>19.864038467407227</v>
       </c>
       <c r="J29" s="1">
-        <v>2.0205113887786865</v>
+        <v>2.0179219245910645</v>
       </c>
       <c r="K29" s="1">
-        <v>2.0598511695861817</v>
+        <v>2.0567805767059326</v>
       </c>
       <c r="L29" s="1">
-        <v>2.1291153430938721</v>
+        <v>2.1248264312744141</v>
       </c>
     </row>
     <row r="30">
@@ -1932,31 +1935,31 @@
         <v>4</v>
       </c>
       <c r="D30" s="1">
-        <v>21.285316467285156</v>
+        <v>21.285539627075195</v>
       </c>
       <c r="E30" s="1">
-        <v>21.043506622314453</v>
+        <v>21.044162750244141</v>
       </c>
       <c r="F30" s="1">
-        <v>20.812095642089844</v>
+        <v>20.813749313354492</v>
       </c>
       <c r="G30" s="1">
-        <v>20.227878570556641</v>
+        <v>20.22810173034668</v>
       </c>
       <c r="H30" s="1">
-        <v>19.986381530761719</v>
+        <v>19.987037658691406</v>
       </c>
       <c r="I30" s="1">
-        <v>19.752567291259766</v>
+        <v>19.754220962524414</v>
       </c>
       <c r="J30" s="1">
-        <v>2.0447831153869629</v>
+        <v>2.041344165802002</v>
       </c>
       <c r="K30" s="1">
-        <v>2.2348935604095459</v>
+        <v>2.2291743755340576</v>
       </c>
       <c r="L30" s="1">
-        <v>2.4559605121612549</v>
+        <v>2.446237325668335</v>
       </c>
     </row>
     <row r="31">
@@ -1970,31 +1973,31 @@
         <v>4</v>
       </c>
       <c r="D31" s="1">
-        <v>21.391513824462891</v>
+        <v>21.391849517822266</v>
       </c>
       <c r="E31" s="1">
-        <v>20.993791580200195</v>
+        <v>20.995651245117188</v>
       </c>
       <c r="F31" s="1">
-        <v>20.551307678222656</v>
+        <v>20.556858062744141</v>
       </c>
       <c r="G31" s="1">
-        <v>20.354705810546875</v>
+        <v>20.355043411254883</v>
       </c>
       <c r="H31" s="1">
-        <v>19.956754684448242</v>
+        <v>19.958614349365234</v>
       </c>
       <c r="I31" s="1">
-        <v>19.510330200195313</v>
+        <v>19.515880584716797</v>
       </c>
       <c r="J31" s="1">
-        <v>2.0159649848937988</v>
+        <v>2.0102465152740479</v>
       </c>
       <c r="K31" s="1">
-        <v>2.4265949726104736</v>
+        <v>2.4145216941833496</v>
       </c>
       <c r="L31" s="1">
-        <v>2.8389952182769775</v>
+        <v>2.8189475536346436</v>
       </c>
     </row>
   </sheetData>
@@ -2061,28 +2064,28 @@
         <v>19.437982559204102</v>
       </c>
       <c r="E2" s="1">
-        <v>19.780158996582031</v>
+        <v>19.780633926391602</v>
       </c>
       <c r="F2" s="1">
-        <v>19.512229919433594</v>
+        <v>19.512197494506836</v>
       </c>
       <c r="G2" s="1">
-        <v>18.707670211791992</v>
+        <v>18.708147048950195</v>
       </c>
       <c r="H2" s="1">
         <v>1.9832693338394165</v>
       </c>
       <c r="I2" s="1">
-        <v>2.2439966201782227</v>
+        <v>2.2380642890930176</v>
       </c>
       <c r="J2" s="1">
-        <v>5.4672207832336426</v>
+        <v>5.4604249000549317</v>
       </c>
       <c r="K2" s="1">
         <v>-0.351205974817276</v>
       </c>
       <c r="L2" s="1">
-        <v>20.200071334838867</v>
+        <v>20.205373764038086</v>
       </c>
       <c r="M2" s="1">
         <v>0</v>
@@ -2102,28 +2105,28 @@
         <v>19.437982559204102</v>
       </c>
       <c r="E3" s="1">
-        <v>19.300323486328125</v>
+        <v>19.302658081054688</v>
       </c>
       <c r="F3" s="1">
-        <v>19.300323486328125</v>
+        <v>19.302658081054688</v>
       </c>
       <c r="G3" s="1">
-        <v>18.227598190307617</v>
+        <v>18.229934692382813</v>
       </c>
       <c r="H3" s="1">
         <v>1.9832693338394165</v>
       </c>
       <c r="I3" s="1">
-        <v>2.6546263694763184</v>
+        <v>2.6423392295837402</v>
       </c>
       <c r="J3" s="1">
-        <v>10.113280296325684</v>
+        <v>10.083325386047363</v>
       </c>
       <c r="K3" s="1">
         <v>1.2589941024780274</v>
       </c>
       <c r="L3" s="1">
-        <v>15.406893730163574</v>
+        <v>15.430734634399414</v>
       </c>
       <c r="M3" s="1">
         <v>0</v>
@@ -2143,28 +2146,28 @@
         <v>19.437982559204102</v>
       </c>
       <c r="E4" s="1">
-        <v>18.685705184936524</v>
+        <v>18.692916870117188</v>
       </c>
       <c r="F4" s="1">
-        <v>18.685705184936524</v>
+        <v>18.692916870117188</v>
       </c>
       <c r="G4" s="1">
-        <v>17.608905792236328</v>
+        <v>17.616117477416992</v>
       </c>
       <c r="H4" s="1">
         <v>1.9832693338394165</v>
       </c>
       <c r="I4" s="1">
-        <v>3.0670268535614014</v>
+        <v>3.0467653274536133</v>
       </c>
       <c r="J4" s="1">
-        <v>16.265968322753906</v>
+        <v>16.194080352783203</v>
       </c>
       <c r="K4" s="1">
         <v>2.6075263023376465</v>
       </c>
       <c r="L4" s="1">
-        <v>9.3232507705688477</v>
+        <v>9.3836345672607422</v>
       </c>
       <c r="M4" s="1">
         <v>0</v>
@@ -2178,34 +2181,34 @@
         <v>33</v>
       </c>
       <c r="C5" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D5" s="1">
-        <v>26.761215209960938</v>
+        <v>26.774463653564453</v>
       </c>
       <c r="E5" s="1">
-        <v>26.180570602416992</v>
+        <v>26.188018798828125</v>
       </c>
       <c r="F5" s="1">
-        <v>26.180570602416992</v>
+        <v>26.188018798828125</v>
       </c>
       <c r="G5" s="1">
-        <v>25.029382705688477</v>
+        <v>25.038297653198242</v>
       </c>
       <c r="H5" s="1">
-        <v>2.2902781963348389</v>
+        <v>2.2826457023620605</v>
       </c>
       <c r="I5" s="1">
-        <v>2.2763557434082031</v>
+        <v>2.273690938949585</v>
       </c>
       <c r="J5" s="1">
-        <v>4.0151028633117676</v>
+        <v>3.9928374290466309</v>
       </c>
       <c r="K5" s="1">
-        <v>-0.55727523565292358</v>
+        <v>-0.56537854671478272</v>
       </c>
       <c r="L5" s="1">
-        <v>11.26081657409668</v>
+        <v>11.207788467407227</v>
       </c>
       <c r="M5" s="1">
         <v>0</v>
@@ -2219,34 +2222,34 @@
         <v>34</v>
       </c>
       <c r="C6" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" s="1">
-        <v>26.761215209960938</v>
+        <v>26.774463653564453</v>
       </c>
       <c r="E6" s="1">
-        <v>25.258701324462891</v>
+        <v>25.260692596435547</v>
       </c>
       <c r="F6" s="1">
-        <v>25.258701324462891</v>
+        <v>25.260692596435547</v>
       </c>
       <c r="G6" s="1">
-        <v>24.107257843017578</v>
+        <v>24.1107177734375</v>
       </c>
       <c r="H6" s="1">
-        <v>2.2902781963348389</v>
+        <v>2.2826457023620605</v>
       </c>
       <c r="I6" s="1">
-        <v>2.6869857311248779</v>
+        <v>2.6779658794403076</v>
       </c>
       <c r="J6" s="1">
-        <v>6.9636702537536621</v>
+        <v>6.9294953346252442</v>
       </c>
       <c r="K6" s="1">
-        <v>1.9977059364318848</v>
+        <v>2.0267543792724609</v>
       </c>
       <c r="L6" s="1">
-        <v>8.1672878265380859</v>
+        <v>8.1054286956787109</v>
       </c>
       <c r="M6" s="1">
         <v>0</v>
@@ -2260,34 +2263,34 @@
         <v>35</v>
       </c>
       <c r="C7" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D7" s="1">
-        <v>26.761215209960938</v>
+        <v>26.774463653564453</v>
       </c>
       <c r="E7" s="1">
-        <v>24.278963088989258</v>
+        <v>24.274307250976563</v>
       </c>
       <c r="F7" s="1">
-        <v>24.278963088989258</v>
+        <v>24.274307250976563</v>
       </c>
       <c r="G7" s="1">
-        <v>23.123146057128906</v>
+        <v>23.119962692260742</v>
       </c>
       <c r="H7" s="1">
-        <v>2.2902781963348389</v>
+        <v>2.2826457023620605</v>
       </c>
       <c r="I7" s="1">
-        <v>3.0993859767913818</v>
+        <v>3.0823919773101807</v>
       </c>
       <c r="J7" s="1">
-        <v>10.847822189331055</v>
+        <v>10.788318634033203</v>
       </c>
       <c r="K7" s="1">
-        <v>4.1374859809875488</v>
+        <v>4.1976490020751953</v>
       </c>
       <c r="L7" s="1">
-        <v>4.1639304161071777</v>
+        <v>4.1022982597351074</v>
       </c>
       <c r="M7" s="1">
         <v>2</v>
@@ -2301,34 +2304,34 @@
         <v>33</v>
       </c>
       <c r="C8" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" s="1">
-        <v>34.186836242675781</v>
+        <v>33.739055633544922</v>
       </c>
       <c r="E8" s="1">
-        <v>32.125572204589844</v>
+        <v>31.73249626159668</v>
       </c>
       <c r="F8" s="1">
-        <v>32.125572204589844</v>
+        <v>31.73249626159668</v>
       </c>
       <c r="G8" s="1">
-        <v>30.877168655395508</v>
+        <v>30.506839752197266</v>
       </c>
       <c r="H8" s="1">
-        <v>2.5327386856079102</v>
+        <v>2.4324369430541992</v>
       </c>
       <c r="I8" s="1">
-        <v>2.8317065238952637</v>
+        <v>2.8084266185760498</v>
       </c>
       <c r="J8" s="1">
-        <v>5.7125906944274902</v>
+        <v>5.4335556030273438</v>
       </c>
       <c r="K8" s="1">
-        <v>-1.386768102645874</v>
+        <v>-1.3978339433670044</v>
       </c>
       <c r="L8" s="1">
-        <v>2.7136828899383545</v>
+        <v>2.8361277580261231</v>
       </c>
       <c r="M8" s="1">
         <v>0</v>
@@ -2342,34 +2345,34 @@
         <v>34</v>
       </c>
       <c r="C9" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D9" s="1">
-        <v>34.186836242675781</v>
+        <v>33.739055633544922</v>
       </c>
       <c r="E9" s="1">
-        <v>29.654911041259766</v>
+        <v>29.312572479248047</v>
       </c>
       <c r="F9" s="1">
-        <v>29.654911041259766</v>
+        <v>29.312572479248047</v>
       </c>
       <c r="G9" s="1">
-        <v>28.406229019165039</v>
+        <v>28.086645126342774</v>
       </c>
       <c r="H9" s="1">
-        <v>2.5327386856079102</v>
+        <v>2.4324369430541992</v>
       </c>
       <c r="I9" s="1">
-        <v>3.2423365116119385</v>
+        <v>3.2127015590667725</v>
       </c>
       <c r="J9" s="1">
-        <v>8.2835941314697266</v>
+        <v>8.0391464233398438</v>
       </c>
       <c r="K9" s="1">
-        <v>4.9712505340576172</v>
+        <v>5.0109190940856934</v>
       </c>
       <c r="L9" s="1">
-        <v>-0.23081494867801666</v>
+        <v>-0.2759544849395752</v>
       </c>
       <c r="M9" s="1">
         <v>0</v>
@@ -2383,34 +2386,34 @@
         <v>35</v>
       </c>
       <c r="C10" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D10" s="1">
-        <v>34.186836242675781</v>
+        <v>33.739055633544922</v>
       </c>
       <c r="E10" s="1">
-        <v>27.210954666137695</v>
+        <v>26.87030029296875</v>
       </c>
       <c r="F10" s="1">
-        <v>27.210954666137695</v>
+        <v>26.87030029296875</v>
       </c>
       <c r="G10" s="1">
-        <v>25.957530975341797</v>
+        <v>25.639717102050781</v>
       </c>
       <c r="H10" s="1">
-        <v>2.5327386856079102</v>
+        <v>2.4324369430541992</v>
       </c>
       <c r="I10" s="1">
-        <v>3.6547367572784424</v>
+        <v>3.6171276569366455</v>
       </c>
       <c r="J10" s="1">
-        <v>11.606899261474609</v>
+        <v>11.396491050720215</v>
       </c>
       <c r="K10" s="1">
-        <v>10.296050071716309</v>
+        <v>10.378209114074707</v>
       </c>
       <c r="L10" s="1">
-        <v>-4.0364260673522949</v>
+        <v>-4.2748856544494629</v>
       </c>
       <c r="M10" s="1">
         <v>2</v>
@@ -2430,28 +2433,28 @@
         <v>20.997871398925781</v>
       </c>
       <c r="E11" s="1">
-        <v>20.007083892822266</v>
+        <v>20.007450103759766</v>
       </c>
       <c r="F11" s="1">
-        <v>20.007083892822266</v>
+        <v>20.007450103759766</v>
       </c>
       <c r="G11" s="1">
-        <v>18.575279235839844</v>
+        <v>18.575643539428711</v>
       </c>
       <c r="H11" s="1">
         <v>4.6891798973083496</v>
       </c>
       <c r="I11" s="1">
-        <v>3.5306894779205322</v>
+        <v>3.5269320011138916</v>
       </c>
       <c r="J11" s="1">
-        <v>5.9443149566650391</v>
+        <v>5.9410257339477539</v>
       </c>
       <c r="K11" s="1">
         <v>-1.1965206861495972</v>
       </c>
       <c r="L11" s="1">
-        <v>5.2910242080688477</v>
+        <v>5.2938055992126465</v>
       </c>
       <c r="M11" s="1">
         <v>0</v>
@@ -2471,28 +2474,28 @@
         <v>20.997871398925781</v>
       </c>
       <c r="E12" s="1">
-        <v>18.247068405151367</v>
+        <v>18.249076843261719</v>
       </c>
       <c r="F12" s="1">
-        <v>18.247068405151367</v>
+        <v>18.249076843261719</v>
       </c>
       <c r="G12" s="1">
-        <v>16.814945220947266</v>
+        <v>16.816951751708984</v>
       </c>
       <c r="H12" s="1">
         <v>4.6891798973083496</v>
       </c>
       <c r="I12" s="1">
-        <v>3.941319465637207</v>
+        <v>3.9312069416046143</v>
       </c>
       <c r="J12" s="1">
-        <v>11.547447204589844</v>
+        <v>11.531002998352051</v>
       </c>
       <c r="K12" s="1">
         <v>4.2892565727233887</v>
       </c>
       <c r="L12" s="1">
-        <v>-1.1354372501373291</v>
+        <v>-1.1211901903152466</v>
       </c>
       <c r="M12" s="1">
         <v>0</v>
@@ -2512,28 +2515,28 @@
         <v>20.997871398925781</v>
       </c>
       <c r="E13" s="1">
-        <v>16.172700881958008</v>
+        <v>16.181604385375977</v>
       </c>
       <c r="F13" s="1">
-        <v>16.172700881958008</v>
+        <v>16.181604385375977</v>
       </c>
       <c r="G13" s="1">
-        <v>14.735137939453125</v>
+        <v>14.744041442871094</v>
       </c>
       <c r="H13" s="1">
         <v>4.6891798973083496</v>
       </c>
       <c r="I13" s="1">
-        <v>4.3537197113037109</v>
+        <v>4.3356328010559082</v>
       </c>
       <c r="J13" s="1">
-        <v>18.68934440612793</v>
+        <v>18.640840530395508</v>
       </c>
       <c r="K13" s="1">
         <v>8.8835592269897461</v>
       </c>
       <c r="L13" s="1">
-        <v>-9.407923698425293</v>
+        <v>-9.3604249954223633</v>
       </c>
       <c r="M13" s="1">
         <v>0</v>
@@ -2553,28 +2556,28 @@
         <v>25.186426162719727</v>
       </c>
       <c r="E14" s="1">
-        <v>24.526863098144531</v>
+        <v>24.52734375</v>
       </c>
       <c r="F14" s="1">
-        <v>24.526863098144531</v>
+        <v>24.52734375</v>
       </c>
       <c r="G14" s="1">
-        <v>23.344655990600586</v>
+        <v>23.345138549804688</v>
       </c>
       <c r="H14" s="1">
         <v>2.0056905746459961</v>
       </c>
       <c r="I14" s="1">
-        <v>2.4925050735473633</v>
+        <v>2.4861268997192383</v>
       </c>
       <c r="J14" s="1">
-        <v>5.2612800598144531</v>
+        <v>5.2559685707092285</v>
       </c>
       <c r="K14" s="1">
         <v>-0.52895146608352661</v>
       </c>
       <c r="L14" s="1">
-        <v>10.201906204223633</v>
+        <v>10.206048965454102</v>
       </c>
       <c r="M14" s="1">
         <v>0</v>
@@ -2594,28 +2597,28 @@
         <v>25.186426162719727</v>
       </c>
       <c r="E15" s="1">
-        <v>23.711071014404297</v>
+        <v>23.7139892578125</v>
       </c>
       <c r="F15" s="1">
-        <v>23.711071014404297</v>
+        <v>23.7139892578125</v>
       </c>
       <c r="G15" s="1">
-        <v>22.528600692749024</v>
+        <v>22.531518936157227</v>
       </c>
       <c r="H15" s="1">
         <v>2.0056905746459961</v>
       </c>
       <c r="I15" s="1">
-        <v>2.9031350612640381</v>
+        <v>2.89040207862854</v>
       </c>
       <c r="J15" s="1">
-        <v>9.1533021926879883</v>
+        <v>9.1292171478271484</v>
       </c>
       <c r="K15" s="1">
         <v>1.8961714506149292</v>
       </c>
       <c r="L15" s="1">
-        <v>6.2514395713806152</v>
+        <v>6.2713603973388672</v>
       </c>
       <c r="M15" s="1">
         <v>0</v>
@@ -2635,28 +2638,28 @@
         <v>25.186426162719727</v>
       </c>
       <c r="E16" s="1">
-        <v>22.672828674316406</v>
+        <v>22.683252334594727</v>
       </c>
       <c r="F16" s="1">
-        <v>22.672828674316406</v>
+        <v>22.683252334594727</v>
       </c>
       <c r="G16" s="1">
-        <v>21.485868453979492</v>
+        <v>21.496292114257813</v>
       </c>
       <c r="H16" s="1">
         <v>2.0056905746459961</v>
       </c>
       <c r="I16" s="1">
-        <v>3.315535306930542</v>
+        <v>3.294827938079834</v>
       </c>
       <c r="J16" s="1">
-        <v>14.143301010131836</v>
+        <v>14.085872650146484</v>
       </c>
       <c r="K16" s="1">
         <v>3.9271962642669678</v>
       </c>
       <c r="L16" s="1">
-        <v>1.1138797998428345</v>
+        <v>1.1666896343231201</v>
       </c>
       <c r="M16" s="1">
         <v>0</v>
@@ -2676,28 +2679,28 @@
         <v>21.000280380249024</v>
       </c>
       <c r="E17" s="1">
-        <v>21.391513824462891</v>
+        <v>21.391849517822266</v>
       </c>
       <c r="F17" s="1">
-        <v>21.08735466003418</v>
+        <v>21.087326049804688</v>
       </c>
       <c r="G17" s="1">
-        <v>20.354705810546875</v>
+        <v>20.355043411254883</v>
       </c>
       <c r="H17" s="1">
         <v>1.8732786178588867</v>
       </c>
       <c r="I17" s="1">
-        <v>2.0159649848937988</v>
+        <v>2.0102465152740479</v>
       </c>
       <c r="J17" s="1">
-        <v>4.3027715682983398</v>
+        <v>4.298314094543457</v>
       </c>
       <c r="K17" s="1">
         <v>-0.25997251272201538</v>
       </c>
       <c r="L17" s="1">
-        <v>20.445346832275391</v>
+        <v>20.448823928833008</v>
       </c>
       <c r="M17" s="1">
         <v>0</v>
@@ -2717,28 +2720,28 @@
         <v>21.000280380249024</v>
       </c>
       <c r="E18" s="1">
-        <v>20.993791580200195</v>
+        <v>20.995651245117188</v>
       </c>
       <c r="F18" s="1">
-        <v>20.993791580200195</v>
+        <v>20.995651245117188</v>
       </c>
       <c r="G18" s="1">
-        <v>19.956754684448242</v>
+        <v>19.958614349365234</v>
       </c>
       <c r="H18" s="1">
         <v>1.8732786178588867</v>
       </c>
       <c r="I18" s="1">
-        <v>2.4265949726104736</v>
+        <v>2.4145216941833496</v>
       </c>
       <c r="J18" s="1">
-        <v>7.9979352951049805</v>
+        <v>7.973358154296875</v>
       </c>
       <c r="K18" s="1">
         <v>0.93194276094436646</v>
       </c>
       <c r="L18" s="1">
-        <v>16.653467178344727</v>
+        <v>16.672637939453125</v>
       </c>
       <c r="M18" s="1">
         <v>0</v>
@@ -2758,28 +2761,28 @@
         <v>21.000280380249024</v>
       </c>
       <c r="E19" s="1">
-        <v>20.551307678222656</v>
+        <v>20.556858062744141</v>
       </c>
       <c r="F19" s="1">
-        <v>20.551307678222656</v>
+        <v>20.556858062744141</v>
       </c>
       <c r="G19" s="1">
-        <v>19.510330200195313</v>
+        <v>19.515880584716797</v>
       </c>
       <c r="H19" s="1">
         <v>1.8732786178588867</v>
       </c>
       <c r="I19" s="1">
-        <v>2.8389952182769775</v>
+        <v>2.8189475536346436</v>
       </c>
       <c r="J19" s="1">
-        <v>12.982355117797852</v>
+        <v>12.920832633972168</v>
       </c>
       <c r="K19" s="1">
         <v>1.930164098739624</v>
       </c>
       <c r="L19" s="1">
-        <v>11.850432395935059</v>
+        <v>11.900041580200195</v>
       </c>
       <c r="M19" s="1">
         <v>0</v>
@@ -2791,7 +2794,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S46"/>
+  <dimension ref="A1:S47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2799,58 +2802,58 @@
         <v>46</v>
       </c>
       <c r="B1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D1" t="s">
         <v>36</v>
       </c>
       <c r="E1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K1" t="s">
         <v>40</v>
       </c>
       <c r="L1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="S1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2">
@@ -2867,22 +2870,22 @@
         <v>15.258353233337402</v>
       </c>
       <c r="E2" s="1">
-        <v>13.888044357299805</v>
+        <v>13.888388633728027</v>
       </c>
       <c r="F2" s="1">
-        <v>8.6816396713256836</v>
+        <v>8.6847171783447266</v>
       </c>
       <c r="G2" s="1">
-        <v>3.8106439113616943</v>
+        <v>3.8185718059539795</v>
       </c>
       <c r="H2" s="1">
-        <v>13.888044357299805</v>
+        <v>13.888388633728027</v>
       </c>
       <c r="I2" s="1">
-        <v>8.6816396713256836</v>
+        <v>8.6847171783447266</v>
       </c>
       <c r="J2" s="1">
-        <v>3.8106439113616943</v>
+        <v>3.8185718059539795</v>
       </c>
       <c r="K2" s="1">
         <v>4.110689640045166</v>
@@ -2894,13 +2897,13 @@
         <v>0</v>
       </c>
       <c r="N2" s="1">
-        <v>10.843605041503906</v>
+        <v>10.841164588928223</v>
       </c>
       <c r="O2" s="1">
-        <v>17.693269729614258</v>
+        <v>17.671440124511719</v>
       </c>
       <c r="P2" s="1">
-        <v>26.435676574707031</v>
+        <v>26.379657745361328</v>
       </c>
       <c r="Q2" s="1">
         <v>-6.1849474906921387</v>
@@ -2929,19 +2932,19 @@
         <v>14.748130798339844</v>
       </c>
       <c r="F3" s="1">
-        <v>9.4476251602172852</v>
+        <v>9.4534473419189453</v>
       </c>
       <c r="G3" s="1">
-        <v>4.3274130821228027</v>
+        <v>4.341585636138916</v>
       </c>
       <c r="H3" s="1">
         <v>14.441656112670898</v>
       </c>
       <c r="I3" s="1">
-        <v>9.4476251602172852</v>
+        <v>9.4534473419189453</v>
       </c>
       <c r="J3" s="1">
-        <v>4.3274130821228027</v>
+        <v>4.341585636138916</v>
       </c>
       <c r="K3" s="1">
         <v>2.7762997150421143</v>
@@ -2956,10 +2959,10 @@
         <v>0.87802988290786743</v>
       </c>
       <c r="O3" s="1">
-        <v>6.9954714775085449</v>
+        <v>6.9505338668823242</v>
       </c>
       <c r="P3" s="1">
-        <v>15.29775333404541</v>
+        <v>15.192225456237793</v>
       </c>
       <c r="Q3" s="1">
         <v>-7.7250099182128906</v>
@@ -2985,22 +2988,22 @@
         <v>16.995023727416992</v>
       </c>
       <c r="E4" s="1">
-        <v>14.497843742370605</v>
+        <v>14.499282836914063</v>
       </c>
       <c r="F4" s="1">
-        <v>11.539224624633789</v>
+        <v>11.541708946228027</v>
       </c>
       <c r="G4" s="1">
-        <v>8.3162174224853516</v>
+        <v>8.3242111206054688</v>
       </c>
       <c r="H4" s="1">
-        <v>14.497843742370605</v>
+        <v>14.499282836914063</v>
       </c>
       <c r="I4" s="1">
-        <v>11.539224624633789</v>
+        <v>11.541708946228027</v>
       </c>
       <c r="J4" s="1">
-        <v>8.3162174224853516</v>
+        <v>8.3242111206054688</v>
       </c>
       <c r="K4" s="1">
         <v>9.7105236053466797</v>
@@ -3012,13 +3015,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="1">
-        <v>2.5965206623077393</v>
+        <v>2.5873517990112305</v>
       </c>
       <c r="O4" s="1">
-        <v>16.253034591674805</v>
+        <v>16.237209320068359</v>
       </c>
       <c r="P4" s="1">
-        <v>32.595130920410156</v>
+        <v>32.544410705566406</v>
       </c>
       <c r="Q4" s="1">
         <v>-1.1151782274246216</v>
@@ -3044,22 +3047,22 @@
         <v>11.067777633666992</v>
       </c>
       <c r="E5" s="1">
-        <v>10.247621536254883</v>
+        <v>10.247744560241699</v>
       </c>
       <c r="F5" s="1">
-        <v>9.4931135177612305</v>
+        <v>9.4956283569335938</v>
       </c>
       <c r="G5" s="1">
-        <v>8.4442501068115234</v>
+        <v>8.4508266448974609</v>
       </c>
       <c r="H5" s="1">
-        <v>10.247621536254883</v>
+        <v>10.247744560241699</v>
       </c>
       <c r="I5" s="1">
-        <v>9.4931135177612305</v>
+        <v>9.4956283569335938</v>
       </c>
       <c r="J5" s="1">
-        <v>8.4442501068115234</v>
+        <v>8.4508266448974609</v>
       </c>
       <c r="K5" s="1">
         <v>4.0069994926452637</v>
@@ -3071,13 +3074,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="1">
-        <v>2.3136627674102783</v>
+        <v>2.3124582767486572</v>
       </c>
       <c r="O5" s="1">
-        <v>9.2388086318969727</v>
+        <v>9.2142171859741211</v>
       </c>
       <c r="P5" s="1">
-        <v>18.470314025878906</v>
+        <v>18.406246185302734</v>
       </c>
       <c r="Q5" s="1">
         <v>0</v>
@@ -3103,22 +3106,22 @@
         <v>18.721660614013672</v>
       </c>
       <c r="E6" s="1">
-        <v>18.56671142578125</v>
+        <v>18.567167282104492</v>
       </c>
       <c r="F6" s="1">
-        <v>16.098915100097656</v>
+        <v>16.099763870239258</v>
       </c>
       <c r="G6" s="1">
-        <v>13.063480377197266</v>
+        <v>13.072973251342773</v>
       </c>
       <c r="H6" s="1">
-        <v>18.482387542724609</v>
+        <v>18.48286247253418</v>
       </c>
       <c r="I6" s="1">
-        <v>16.098915100097656</v>
+        <v>16.099763870239258</v>
       </c>
       <c r="J6" s="1">
-        <v>13.063480377197266</v>
+        <v>13.072973251342773</v>
       </c>
       <c r="K6" s="1">
         <v>5.2122688293457031</v>
@@ -3130,13 +3133,13 @@
         <v>0</v>
       </c>
       <c r="N6" s="1">
-        <v>6.620354175567627</v>
+        <v>6.6135783195495605</v>
       </c>
       <c r="O6" s="1">
-        <v>13.207352638244629</v>
+        <v>13.194785118103027</v>
       </c>
       <c r="P6" s="1">
-        <v>21.808509826660156</v>
+        <v>21.753849029541016</v>
       </c>
       <c r="Q6" s="1">
         <v>-2.8772175312042236</v>
@@ -3162,22 +3165,22 @@
         <v>23.036062240600586</v>
       </c>
       <c r="E7" s="1">
-        <v>24.004152297973633</v>
+        <v>24.004234313964844</v>
       </c>
       <c r="F7" s="1">
-        <v>18.183055877685547</v>
+        <v>18.185268402099609</v>
       </c>
       <c r="G7" s="1">
-        <v>13.215836524963379</v>
+        <v>13.221207618713379</v>
       </c>
       <c r="H7" s="1">
-        <v>23.208820343017578</v>
+        <v>23.208763122558594</v>
       </c>
       <c r="I7" s="1">
-        <v>18.183055877685547</v>
+        <v>18.185268402099609</v>
       </c>
       <c r="J7" s="1">
-        <v>13.215836524963379</v>
+        <v>13.221207618713379</v>
       </c>
       <c r="K7" s="1">
         <v>0.52955126762390137</v>
@@ -3189,13 +3192,13 @@
         <v>0</v>
       </c>
       <c r="N7" s="1">
-        <v>1.1010450124740601</v>
+        <v>1.100072979927063</v>
       </c>
       <c r="O7" s="1">
-        <v>2.9763128757476807</v>
+        <v>2.9496452808380127</v>
       </c>
       <c r="P7" s="1">
-        <v>5.8891878128051758</v>
+        <v>5.8247413635253906</v>
       </c>
       <c r="Q7" s="1">
         <v>-5.7517280578613281</v>
@@ -3224,19 +3227,19 @@
         <v>14.429388999938965</v>
       </c>
       <c r="F8" s="1">
-        <v>13.902769088745117</v>
+        <v>13.904655456542969</v>
       </c>
       <c r="G8" s="1">
-        <v>13.27243709564209</v>
+        <v>13.278882026672363</v>
       </c>
       <c r="H8" s="1">
         <v>14.429388999938965</v>
       </c>
       <c r="I8" s="1">
-        <v>13.902769088745117</v>
+        <v>13.904655456542969</v>
       </c>
       <c r="J8" s="1">
-        <v>13.27243709564209</v>
+        <v>13.278882026672363</v>
       </c>
       <c r="K8" s="1">
         <v>2.846287727355957</v>
@@ -3251,10 +3254,10 @@
         <v>0</v>
       </c>
       <c r="O8" s="1">
-        <v>5.3617038726806641</v>
+        <v>5.3499994277954102</v>
       </c>
       <c r="P8" s="1">
-        <v>12.168533325195313</v>
+        <v>12.128705024719238</v>
       </c>
       <c r="Q8" s="1">
         <v>0</v>
@@ -3280,22 +3283,22 @@
         <v>20.045049667358399</v>
       </c>
       <c r="E9" s="1">
-        <v>19.551179885864258</v>
+        <v>19.551990509033203</v>
       </c>
       <c r="F9" s="1">
-        <v>18.182851791381836</v>
+        <v>18.191621780395508</v>
       </c>
       <c r="G9" s="1">
-        <v>15.419641494750977</v>
+        <v>15.442683219909668</v>
       </c>
       <c r="H9" s="1">
-        <v>19.551179885864258</v>
+        <v>19.551990509033203</v>
       </c>
       <c r="I9" s="1">
-        <v>18.182851791381836</v>
+        <v>18.191621780395508</v>
       </c>
       <c r="J9" s="1">
-        <v>15.419641494750977</v>
+        <v>15.442683219909668</v>
       </c>
       <c r="K9" s="1">
         <v>2.9860866069793701</v>
@@ -3307,13 +3310,13 @@
         <v>0</v>
       </c>
       <c r="N9" s="1">
-        <v>9.726811408996582</v>
+        <v>9.7155628204345703</v>
       </c>
       <c r="O9" s="1">
-        <v>20.723474502563477</v>
+        <v>20.671564102172852</v>
       </c>
       <c r="P9" s="1">
-        <v>34.404457092285156</v>
+        <v>34.281124114990234</v>
       </c>
       <c r="Q9" s="1">
         <v>-0.71068477630615234</v>
@@ -3339,22 +3342,22 @@
         <v>24.320249557495117</v>
       </c>
       <c r="E10" s="1">
-        <v>23.929683685302734</v>
+        <v>23.930278778076172</v>
       </c>
       <c r="F10" s="1">
-        <v>19.645267486572266</v>
+        <v>19.647172927856445</v>
       </c>
       <c r="G10" s="1">
-        <v>15.574652671813965</v>
+        <v>15.585298538208008</v>
       </c>
       <c r="H10" s="1">
-        <v>23.929683685302734</v>
+        <v>23.930278778076172</v>
       </c>
       <c r="I10" s="1">
-        <v>19.645267486572266</v>
+        <v>19.647172927856445</v>
       </c>
       <c r="J10" s="1">
-        <v>15.574652671813965</v>
+        <v>15.585298538208008</v>
       </c>
       <c r="K10" s="1">
         <v>2.0872793197631836</v>
@@ -3366,13 +3369,13 @@
         <v>0</v>
       </c>
       <c r="N10" s="1">
-        <v>1.9533945322036743</v>
+        <v>1.9466069936752319</v>
       </c>
       <c r="O10" s="1">
-        <v>5.6636600494384766</v>
+        <v>5.6418848037719727</v>
       </c>
       <c r="P10" s="1">
-        <v>10.345035552978516</v>
+        <v>10.294215202331543</v>
       </c>
       <c r="Q10" s="1">
         <v>-3.8511176109313965</v>
@@ -3398,22 +3401,22 @@
         <v>20.894319534301758</v>
       </c>
       <c r="E11" s="1">
-        <v>20.004081726074219</v>
+        <v>20.004240036010742</v>
       </c>
       <c r="F11" s="1">
-        <v>18.003952026367188</v>
+        <v>18.007610321044922</v>
       </c>
       <c r="G11" s="1">
-        <v>15.629270553588867</v>
+        <v>15.638980865478516</v>
       </c>
       <c r="H11" s="1">
-        <v>20.004081726074219</v>
+        <v>20.004240036010742</v>
       </c>
       <c r="I11" s="1">
-        <v>18.003952026367188</v>
+        <v>18.007610321044922</v>
       </c>
       <c r="J11" s="1">
-        <v>15.629270553588867</v>
+        <v>15.638980865478516</v>
       </c>
       <c r="K11" s="1">
         <v>3.036236047744751</v>
@@ -3425,13 +3428,13 @@
         <v>0</v>
       </c>
       <c r="N11" s="1">
-        <v>0.27044382691383362</v>
+        <v>0.26833945512771606</v>
       </c>
       <c r="O11" s="1">
-        <v>5.2119674682617188</v>
+        <v>5.1909928321838379</v>
       </c>
       <c r="P11" s="1">
-        <v>11.476786613464355</v>
+        <v>11.427026748657227</v>
       </c>
       <c r="Q11" s="1">
         <v>-1.6971728801727295</v>
@@ -3460,19 +3463,19 @@
         <v>22.156579971313477</v>
       </c>
       <c r="F12" s="1">
-        <v>19.55424690246582</v>
+        <v>19.556190490722656</v>
       </c>
       <c r="G12" s="1">
-        <v>16.944234848022461</v>
+        <v>16.95014762878418</v>
       </c>
       <c r="H12" s="1">
         <v>22.156579971313477</v>
       </c>
       <c r="I12" s="1">
-        <v>19.55424690246582</v>
+        <v>19.556190490722656</v>
       </c>
       <c r="J12" s="1">
-        <v>16.944234848022461</v>
+        <v>16.95014762878418</v>
       </c>
       <c r="K12" s="1">
         <v>2.441215991973877</v>
@@ -3487,10 +3490,10 @@
         <v>0</v>
       </c>
       <c r="O12" s="1">
-        <v>2.4769191741943359</v>
+        <v>2.4699621200561523</v>
       </c>
       <c r="P12" s="1">
-        <v>5.5817866325378418</v>
+        <v>5.5606765747070313</v>
       </c>
       <c r="Q12" s="1">
         <v>-1.0744326114654541</v>
@@ -3516,22 +3519,22 @@
         <v>18.293428421020508</v>
       </c>
       <c r="E13" s="1">
-        <v>18.006549835205078</v>
+        <v>18.007177352905274</v>
       </c>
       <c r="F13" s="1">
-        <v>17.609222412109375</v>
+        <v>17.611238479614258</v>
       </c>
       <c r="G13" s="1">
-        <v>17.021293640136719</v>
+        <v>17.030733108520508</v>
       </c>
       <c r="H13" s="1">
-        <v>18.006549835205078</v>
+        <v>18.007177352905274</v>
       </c>
       <c r="I13" s="1">
-        <v>17.609222412109375</v>
+        <v>17.611238479614258</v>
       </c>
       <c r="J13" s="1">
-        <v>17.021293640136719</v>
+        <v>17.030733108520508</v>
       </c>
       <c r="K13" s="1">
         <v>1.9084329605102539</v>
@@ -3543,13 +3546,13 @@
         <v>0</v>
       </c>
       <c r="N13" s="1">
-        <v>3.7006993293762207</v>
+        <v>3.6911745071411133</v>
       </c>
       <c r="O13" s="1">
-        <v>8.4315853118896484</v>
+        <v>8.4010066986083984</v>
       </c>
       <c r="P13" s="1">
-        <v>14.503084182739258</v>
+        <v>14.431048393249512</v>
       </c>
       <c r="Q13" s="1">
         <v>-0.20976652204990387</v>
@@ -3575,22 +3578,22 @@
         <v>17.884822845458984</v>
       </c>
       <c r="E14" s="1">
-        <v>18.427253723144531</v>
+        <v>18.427993774414063</v>
       </c>
       <c r="F14" s="1">
-        <v>17.963834762573242</v>
+        <v>17.966167449951172</v>
       </c>
       <c r="G14" s="1">
-        <v>17.500455856323242</v>
+        <v>17.505853652954102</v>
       </c>
       <c r="H14" s="1">
-        <v>18.00755500793457</v>
+        <v>18.007511138916016</v>
       </c>
       <c r="I14" s="1">
-        <v>17.953596115112305</v>
+        <v>17.953563690185547</v>
       </c>
       <c r="J14" s="1">
-        <v>17.500455856323242</v>
+        <v>17.505853652954102</v>
       </c>
       <c r="K14" s="1">
         <v>0.99057501554489136</v>
@@ -3602,13 +3605,13 @@
         <v>0</v>
       </c>
       <c r="N14" s="1">
-        <v>2.4200980663299561</v>
+        <v>2.4085962772369385</v>
       </c>
       <c r="O14" s="1">
-        <v>6.6902384757995606</v>
+        <v>6.6539797782897949</v>
       </c>
       <c r="P14" s="1">
-        <v>12.301900863647461</v>
+        <v>12.218425750732422</v>
       </c>
       <c r="Q14" s="1">
         <v>-0.55528020858764648</v>
@@ -3634,22 +3637,22 @@
         <v>23.573837280273438</v>
       </c>
       <c r="E15" s="1">
-        <v>22.538822174072266</v>
+        <v>22.539394378662109</v>
       </c>
       <c r="F15" s="1">
-        <v>20.3890380859375</v>
+        <v>20.394044876098633</v>
       </c>
       <c r="G15" s="1">
-        <v>17.542583465576172</v>
+        <v>17.554388046264649</v>
       </c>
       <c r="H15" s="1">
-        <v>22.538822174072266</v>
+        <v>22.539394378662109</v>
       </c>
       <c r="I15" s="1">
-        <v>20.3890380859375</v>
+        <v>20.394044876098633</v>
       </c>
       <c r="J15" s="1">
-        <v>17.542583465576172</v>
+        <v>17.554388046264649</v>
       </c>
       <c r="K15" s="1">
         <v>3.2154037952423096</v>
@@ -3661,13 +3664,13 @@
         <v>0</v>
       </c>
       <c r="N15" s="1">
-        <v>1.6574674844741821</v>
+        <v>1.6507298946380615</v>
       </c>
       <c r="O15" s="1">
-        <v>7.0478076934814453</v>
+        <v>7.0251946449279785</v>
       </c>
       <c r="P15" s="1">
-        <v>13.672114372253418</v>
+        <v>13.618130683898926</v>
       </c>
       <c r="Q15" s="1">
         <v>-1.8186583518981934</v>
@@ -3693,22 +3696,22 @@
         <v>28.380533218383789</v>
       </c>
       <c r="E16" s="1">
-        <v>28.231882095336914</v>
+        <v>28.232702255249024</v>
       </c>
       <c r="F16" s="1">
-        <v>22.99627685546875</v>
+        <v>22.998754501342774</v>
       </c>
       <c r="G16" s="1">
-        <v>18.445953369140625</v>
+        <v>18.456802368164063</v>
       </c>
       <c r="H16" s="1">
-        <v>28.07227897644043</v>
+        <v>28.072620391845703</v>
       </c>
       <c r="I16" s="1">
-        <v>22.99627685546875</v>
+        <v>22.998754501342774</v>
       </c>
       <c r="J16" s="1">
-        <v>18.445953369140625</v>
+        <v>18.456802368164063</v>
       </c>
       <c r="K16" s="1">
         <v>0.76714533567428589</v>
@@ -3720,13 +3723,13 @@
         <v>0</v>
       </c>
       <c r="N16" s="1">
-        <v>14.135010719299316</v>
+        <v>14.127007484436035</v>
       </c>
       <c r="O16" s="1">
-        <v>16.652961730957031</v>
+        <v>16.628742218017578</v>
       </c>
       <c r="P16" s="1">
-        <v>19.964380264282227</v>
+        <v>19.909807205200195</v>
       </c>
       <c r="Q16" s="1">
         <v>-4.1387767791748047</v>
@@ -3752,22 +3755,22 @@
         <v>20.405284881591797</v>
       </c>
       <c r="E17" s="1">
-        <v>20.536464691162109</v>
+        <v>20.537343978881836</v>
       </c>
       <c r="F17" s="1">
-        <v>19.826375961303711</v>
+        <v>19.829217910766602</v>
       </c>
       <c r="G17" s="1">
-        <v>18.777742385864258</v>
+        <v>18.793422698974609</v>
       </c>
       <c r="H17" s="1">
-        <v>20.41484260559082</v>
+        <v>20.414770126342774</v>
       </c>
       <c r="I17" s="1">
-        <v>19.826375961303711</v>
+        <v>19.829217910766602</v>
       </c>
       <c r="J17" s="1">
-        <v>18.777742385864258</v>
+        <v>18.793422698974609</v>
       </c>
       <c r="K17" s="1">
         <v>1.8116350173950195</v>
@@ -3779,13 +3782,13 @@
         <v>0</v>
       </c>
       <c r="N17" s="1">
-        <v>4.4558606147766113</v>
+        <v>4.443941593170166</v>
       </c>
       <c r="O17" s="1">
-        <v>10.910123825073242</v>
+        <v>10.871476173400879</v>
       </c>
       <c r="P17" s="1">
-        <v>19.026525497436524</v>
+        <v>18.936885833740234</v>
       </c>
       <c r="Q17" s="1">
         <v>-0.51077693700790405</v>
@@ -3814,19 +3817,19 @@
         <v>22.591592788696289</v>
       </c>
       <c r="F18" s="1">
-        <v>20.840599060058594</v>
+        <v>20.841276168823242</v>
       </c>
       <c r="G18" s="1">
-        <v>18.80284309387207</v>
+        <v>18.808174133300781</v>
       </c>
       <c r="H18" s="1">
         <v>22.591592788696289</v>
       </c>
       <c r="I18" s="1">
-        <v>20.840599060058594</v>
+        <v>20.841276168823242</v>
       </c>
       <c r="J18" s="1">
-        <v>18.80284309387207</v>
+        <v>18.808174133300781</v>
       </c>
       <c r="K18" s="1">
         <v>2.153038501739502</v>
@@ -3841,10 +3844,10 @@
         <v>0</v>
       </c>
       <c r="O18" s="1">
-        <v>2.7266736030578613</v>
+        <v>2.7186367511749268</v>
       </c>
       <c r="P18" s="1">
-        <v>6.24798583984375</v>
+        <v>6.2221164703369141</v>
       </c>
       <c r="Q18" s="1">
         <v>-1.3891488313674927</v>
@@ -3873,19 +3876,19 @@
         <v>31.179271697998047</v>
       </c>
       <c r="F19" s="1">
-        <v>25.216320037841797</v>
+        <v>25.220613479614258</v>
       </c>
       <c r="G19" s="1">
-        <v>19.401891708374023</v>
+        <v>19.41423225402832</v>
       </c>
       <c r="H19" s="1">
         <v>31.179271697998047</v>
       </c>
       <c r="I19" s="1">
-        <v>25.216320037841797</v>
+        <v>25.220613479614258</v>
       </c>
       <c r="J19" s="1">
-        <v>19.401891708374023</v>
+        <v>19.41423225402832</v>
       </c>
       <c r="K19" s="1">
         <v>4.3763270378112793</v>
@@ -3900,10 +3903,10 @@
         <v>0</v>
       </c>
       <c r="O19" s="1">
-        <v>7.9642710685729981</v>
+        <v>7.950502872467041</v>
       </c>
       <c r="P19" s="1">
-        <v>17.377296447753906</v>
+        <v>17.337860107421875</v>
       </c>
       <c r="Q19" s="1">
         <v>-2.3791112899780273</v>
@@ -3929,22 +3932,22 @@
         <v>22.279584884643555</v>
       </c>
       <c r="E20" s="1">
-        <v>21.785884857177734</v>
+        <v>21.786508560180664</v>
       </c>
       <c r="F20" s="1">
-        <v>21.439346313476563</v>
+        <v>21.441341400146484</v>
       </c>
       <c r="G20" s="1">
-        <v>21.120079040527344</v>
+        <v>21.124746322631836</v>
       </c>
       <c r="H20" s="1">
-        <v>21.785884857177734</v>
+        <v>21.786508560180664</v>
       </c>
       <c r="I20" s="1">
-        <v>21.439346313476563</v>
+        <v>21.441341400146484</v>
       </c>
       <c r="J20" s="1">
-        <v>21.120079040527344</v>
+        <v>21.124746322631836</v>
       </c>
       <c r="K20" s="1">
         <v>1.231325626373291</v>
@@ -3956,13 +3959,13 @@
         <v>0</v>
       </c>
       <c r="N20" s="1">
-        <v>11.433267593383789</v>
+        <v>11.425483703613281</v>
       </c>
       <c r="O20" s="1">
-        <v>14.56766414642334</v>
+        <v>14.542804718017578</v>
       </c>
       <c r="P20" s="1">
-        <v>18.656475067138672</v>
+        <v>18.598545074462891</v>
       </c>
       <c r="Q20" s="1">
         <v>-0.19765809178352356</v>
@@ -3991,19 +3994,19 @@
         <v>22.169673919677734</v>
       </c>
       <c r="F21" s="1">
-        <v>21.782459259033203</v>
+        <v>21.784017562866211</v>
       </c>
       <c r="G21" s="1">
-        <v>21.366090774536133</v>
+        <v>21.370183944702148</v>
       </c>
       <c r="H21" s="1">
         <v>21.65791130065918</v>
       </c>
       <c r="I21" s="1">
-        <v>21.607963562011719</v>
+        <v>21.607955932617188</v>
       </c>
       <c r="J21" s="1">
-        <v>21.366090774536133</v>
+        <v>21.370183944702148</v>
       </c>
       <c r="K21" s="1">
         <v>2.8153021335601807</v>
@@ -4018,10 +4021,10 @@
         <v>8.5872840881347656</v>
       </c>
       <c r="O21" s="1">
-        <v>12.405588150024414</v>
+        <v>12.385482788085938</v>
       </c>
       <c r="P21" s="1">
-        <v>17.781841278076172</v>
+        <v>17.729238510131836</v>
       </c>
       <c r="Q21" s="1">
         <v>-0.18233299255371094</v>
@@ -4047,22 +4050,22 @@
         <v>23.519998550415039</v>
       </c>
       <c r="E22" s="1">
-        <v>23.194978713989258</v>
+        <v>23.195619583129883</v>
       </c>
       <c r="F22" s="1">
-        <v>22.58497428894043</v>
+        <v>22.587013244628906</v>
       </c>
       <c r="G22" s="1">
-        <v>21.878816604614258</v>
+        <v>21.888105392456055</v>
       </c>
       <c r="H22" s="1">
-        <v>23.194978713989258</v>
+        <v>23.195619583129883</v>
       </c>
       <c r="I22" s="1">
-        <v>22.58497428894043</v>
+        <v>22.587013244628906</v>
       </c>
       <c r="J22" s="1">
-        <v>21.878816604614258</v>
+        <v>21.888105392456055</v>
       </c>
       <c r="K22" s="1">
         <v>1.8094415664672852</v>
@@ -4074,13 +4077,13 @@
         <v>0</v>
       </c>
       <c r="N22" s="1">
-        <v>4.300234317779541</v>
+        <v>4.2926797866821289</v>
       </c>
       <c r="O22" s="1">
-        <v>8.0463485717773438</v>
+        <v>8.0223407745361328</v>
       </c>
       <c r="P22" s="1">
-        <v>12.804105758666992</v>
+        <v>12.748421669006348</v>
       </c>
       <c r="Q22" s="1">
         <v>-0.60773938894271851</v>
@@ -4106,22 +4109,22 @@
         <v>23.088916778564453</v>
       </c>
       <c r="E23" s="1">
-        <v>22.736440658569336</v>
+        <v>22.736509323120117</v>
       </c>
       <c r="F23" s="1">
-        <v>22.354040145874023</v>
+        <v>22.355678558349609</v>
       </c>
       <c r="G23" s="1">
-        <v>21.973073959350586</v>
+        <v>21.977024078369141</v>
       </c>
       <c r="H23" s="1">
-        <v>22.736440658569336</v>
+        <v>22.736509323120117</v>
       </c>
       <c r="I23" s="1">
-        <v>22.354040145874023</v>
+        <v>22.355678558349609</v>
       </c>
       <c r="J23" s="1">
-        <v>21.973073959350586</v>
+        <v>21.977024078369141</v>
       </c>
       <c r="K23" s="1">
         <v>1.8331828117370605</v>
@@ -4133,13 +4136,13 @@
         <v>0</v>
       </c>
       <c r="N23" s="1">
-        <v>0.63065856695175171</v>
+        <v>0.6298632025718689</v>
       </c>
       <c r="O23" s="1">
-        <v>3.425438404083252</v>
+        <v>3.4057650566101074</v>
       </c>
       <c r="P23" s="1">
-        <v>7.1544723510742188</v>
+        <v>7.1071696281433105</v>
       </c>
       <c r="Q23" s="1">
         <v>-0.18892258405685425</v>
@@ -4168,19 +4171,19 @@
         <v>26.339178085327149</v>
       </c>
       <c r="F24" s="1">
-        <v>24.355611801147461</v>
+        <v>24.357187271118164</v>
       </c>
       <c r="G24" s="1">
-        <v>22.398670196533203</v>
+        <v>22.403219223022461</v>
       </c>
       <c r="H24" s="1">
         <v>26.339178085327149</v>
       </c>
       <c r="I24" s="1">
-        <v>24.355611801147461</v>
+        <v>24.357187271118164</v>
       </c>
       <c r="J24" s="1">
-        <v>22.398670196533203</v>
+        <v>22.403219223022461</v>
       </c>
       <c r="K24" s="1">
         <v>1.4881768226623535</v>
@@ -4195,10 +4198,10 @@
         <v>0</v>
       </c>
       <c r="O24" s="1">
-        <v>1.6108368635177612</v>
+        <v>1.6049402952194214</v>
       </c>
       <c r="P24" s="1">
-        <v>3.6379258632659912</v>
+        <v>3.6210050582885742</v>
       </c>
       <c r="Q24" s="1">
         <v>-0.86902743577957153</v>
@@ -4215,58 +4218,58 @@
         <v>70</v>
       </c>
       <c r="B25" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C25" s="1">
         <v>0</v>
       </c>
       <c r="D25" s="1">
-        <v>25.033319473266602</v>
+        <v>28.494235992431641</v>
       </c>
       <c r="E25" s="1">
-        <v>25.217960357666016</v>
+        <v>27.126667022705078</v>
       </c>
       <c r="F25" s="1">
-        <v>24.944515228271484</v>
+        <v>25.271799087524414</v>
       </c>
       <c r="G25" s="1">
-        <v>24.687053680419922</v>
+        <v>22.784492492675781</v>
       </c>
       <c r="H25" s="1">
-        <v>25.063941955566406</v>
+        <v>27.126667022705078</v>
       </c>
       <c r="I25" s="1">
-        <v>24.944515228271484</v>
+        <v>25.271799087524414</v>
       </c>
       <c r="J25" s="1">
-        <v>24.687053680419922</v>
+        <v>22.784492492675781</v>
       </c>
       <c r="K25" s="1">
-        <v>1.5383285284042358</v>
+        <v>1.3515106439590454</v>
       </c>
       <c r="L25" s="1">
-        <v>11.300914764404297</v>
+        <v>150.43344116210938</v>
       </c>
       <c r="M25" s="1">
         <v>0</v>
       </c>
       <c r="N25" s="1">
-        <v>2.0270929336547852</v>
+        <v>1.5251953601837158</v>
       </c>
       <c r="O25" s="1">
-        <v>4.1341357231140137</v>
+        <v>4.7614107131958008</v>
       </c>
       <c r="P25" s="1">
-        <v>6.965980052947998</v>
+        <v>8.8604898452758789</v>
       </c>
       <c r="Q25" s="1">
-        <v>-0.11669077724218369</v>
+        <v>-1.5533427000045776</v>
       </c>
       <c r="R25" s="1">
-        <v>0.41831004619598389</v>
+        <v>5.5683836936950684</v>
       </c>
       <c r="S25" s="1">
-        <v>0.86636990308761597</v>
+        <v>11.532782554626465</v>
       </c>
     </row>
     <row r="26">
@@ -4274,58 +4277,58 @@
         <v>71</v>
       </c>
       <c r="B26" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C26" s="1">
         <v>0</v>
       </c>
       <c r="D26" s="1">
-        <v>27.585422515869141</v>
+        <v>25.033319473266602</v>
       </c>
       <c r="E26" s="1">
-        <v>26.890453338623047</v>
+        <v>25.218048095703125</v>
       </c>
       <c r="F26" s="1">
-        <v>26.161117553710938</v>
+        <v>24.946056365966797</v>
       </c>
       <c r="G26" s="1">
-        <v>24.777814865112305</v>
+        <v>24.690711975097656</v>
       </c>
       <c r="H26" s="1">
-        <v>26.890453338623047</v>
+        <v>25.06391716003418</v>
       </c>
       <c r="I26" s="1">
-        <v>26.161117553710938</v>
+        <v>24.946056365966797</v>
       </c>
       <c r="J26" s="1">
-        <v>24.777814865112305</v>
+        <v>24.690711975097656</v>
       </c>
       <c r="K26" s="1">
-        <v>3.7642781734466553</v>
+        <v>1.5383285284042358</v>
       </c>
       <c r="L26" s="1">
-        <v>8.1391191482543945</v>
+        <v>11.300914764404297</v>
       </c>
       <c r="M26" s="1">
         <v>0</v>
       </c>
       <c r="N26" s="1">
-        <v>9.6281051635742188</v>
+        <v>2.0261704921722412</v>
       </c>
       <c r="O26" s="1">
-        <v>15.810348510742188</v>
+        <v>4.117067813873291</v>
       </c>
       <c r="P26" s="1">
-        <v>23.557899475097656</v>
+        <v>6.925590991973877</v>
       </c>
       <c r="Q26" s="1">
-        <v>-0.084042765200138092</v>
+        <v>-0.11669077724218369</v>
       </c>
       <c r="R26" s="1">
-        <v>0.30127432942390442</v>
+        <v>0.41831004619598389</v>
       </c>
       <c r="S26" s="1">
-        <v>0.62397491931915283</v>
+        <v>0.86636990308761597</v>
       </c>
     </row>
     <row r="27">
@@ -4339,52 +4342,52 @@
         <v>0</v>
       </c>
       <c r="D27" s="1">
-        <v>32.023998260498047</v>
+        <v>27.585422515869141</v>
       </c>
       <c r="E27" s="1">
-        <v>30.280115127563477</v>
+        <v>26.890562057495117</v>
       </c>
       <c r="F27" s="1">
-        <v>27.771562576293945</v>
+        <v>26.163722991943359</v>
       </c>
       <c r="G27" s="1">
-        <v>25.049161911010742</v>
+        <v>24.794157028198242</v>
       </c>
       <c r="H27" s="1">
-        <v>30.280115127563477</v>
+        <v>26.890562057495117</v>
       </c>
       <c r="I27" s="1">
-        <v>27.771562576293945</v>
+        <v>26.163722991943359</v>
       </c>
       <c r="J27" s="1">
-        <v>25.049161911010742</v>
+        <v>24.794157028198242</v>
       </c>
       <c r="K27" s="1">
-        <v>5.4320864677429199</v>
+        <v>3.7642781734466553</v>
       </c>
       <c r="L27" s="1">
-        <v>143.84133911132813</v>
+        <v>8.1391191482543945</v>
       </c>
       <c r="M27" s="1">
         <v>0</v>
       </c>
       <c r="N27" s="1">
-        <v>2.8480558395385742</v>
+        <v>9.6269979476928711</v>
       </c>
       <c r="O27" s="1">
-        <v>6.3876533508300781</v>
+        <v>15.784145355224609</v>
       </c>
       <c r="P27" s="1">
-        <v>10.993846893310547</v>
+        <v>23.488571166992188</v>
       </c>
       <c r="Q27" s="1">
-        <v>-1.4852741956710816</v>
+        <v>-0.084042765200138092</v>
       </c>
       <c r="R27" s="1">
-        <v>5.3243727684020996</v>
+        <v>0.30127432942390442</v>
       </c>
       <c r="S27" s="1">
-        <v>11.027406692504883</v>
+        <v>0.62397491931915283</v>
       </c>
     </row>
     <row r="28">
@@ -4392,58 +4395,58 @@
         <v>73</v>
       </c>
       <c r="B28" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C28" s="1">
         <v>0</v>
       </c>
       <c r="D28" s="1">
-        <v>27.39015007019043</v>
+        <v>32.023998260498047</v>
       </c>
       <c r="E28" s="1">
-        <v>27.750946044921875</v>
+        <v>30.280406951904297</v>
       </c>
       <c r="F28" s="1">
-        <v>27.435285568237305</v>
+        <v>27.773284912109375</v>
       </c>
       <c r="G28" s="1">
-        <v>27.118268966674805</v>
+        <v>25.056312561035156</v>
       </c>
       <c r="H28" s="1">
-        <v>27.465757369995117</v>
+        <v>30.280406951904297</v>
       </c>
       <c r="I28" s="1">
-        <v>27.435285568237305</v>
+        <v>27.773284912109375</v>
       </c>
       <c r="J28" s="1">
-        <v>27.118268966674805</v>
+        <v>25.056312561035156</v>
       </c>
       <c r="K28" s="1">
-        <v>1.7580658197402954</v>
+        <v>5.4320864677429199</v>
       </c>
       <c r="L28" s="1">
-        <v>8.9744405746459961</v>
+        <v>143.84133911132813</v>
       </c>
       <c r="M28" s="1">
         <v>0</v>
       </c>
       <c r="N28" s="1">
-        <v>1.5790036916732788</v>
+        <v>2.8455393314361572</v>
       </c>
       <c r="O28" s="1">
-        <v>3.9432468414306641</v>
+        <v>6.3820791244506836</v>
       </c>
       <c r="P28" s="1">
-        <v>7.206110954284668</v>
+        <v>10.969767570495605</v>
       </c>
       <c r="Q28" s="1">
-        <v>-0.092668108642101288</v>
+        <v>-1.4852741956710816</v>
       </c>
       <c r="R28" s="1">
-        <v>0.33219426870346069</v>
+        <v>5.3243727684020996</v>
       </c>
       <c r="S28" s="1">
-        <v>0.68801367282867432</v>
+        <v>11.027406692504883</v>
       </c>
     </row>
     <row r="29">
@@ -4451,58 +4454,58 @@
         <v>74</v>
       </c>
       <c r="B29" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C29" s="1">
         <v>0</v>
       </c>
       <c r="D29" s="1">
-        <v>30.68280029296875</v>
+        <v>27.39015007019043</v>
       </c>
       <c r="E29" s="1">
-        <v>28.572391510009766</v>
+        <v>27.750909805297852</v>
       </c>
       <c r="F29" s="1">
-        <v>28.379671096801758</v>
+        <v>27.436735153198242</v>
       </c>
       <c r="G29" s="1">
-        <v>28.011348724365234</v>
+        <v>27.122634887695313</v>
       </c>
       <c r="H29" s="1">
-        <v>28.572391510009766</v>
+        <v>27.465723037719727</v>
       </c>
       <c r="I29" s="1">
-        <v>28.379671096801758</v>
+        <v>27.436735153198242</v>
       </c>
       <c r="J29" s="1">
-        <v>28.011348724365234</v>
+        <v>27.122634887695313</v>
       </c>
       <c r="K29" s="1">
-        <v>1.2923356294631958</v>
+        <v>1.7580658197402954</v>
       </c>
       <c r="L29" s="1">
-        <v>5.0096120834350586</v>
+        <v>8.9744405746459961</v>
       </c>
       <c r="M29" s="1">
         <v>0</v>
       </c>
       <c r="N29" s="1">
-        <v>11.875471115112305</v>
+        <v>1.5793594121932983</v>
       </c>
       <c r="O29" s="1">
-        <v>13.539841651916504</v>
+        <v>3.9285428524017334</v>
       </c>
       <c r="P29" s="1">
-        <v>15.949491500854492</v>
+        <v>7.162083625793457</v>
       </c>
       <c r="Q29" s="1">
-        <v>-0.051728162914514542</v>
+        <v>-0.092668108642101288</v>
       </c>
       <c r="R29" s="1">
-        <v>0.1854337751865387</v>
+        <v>0.33219426870346069</v>
       </c>
       <c r="S29" s="1">
-        <v>0.38405537605285645</v>
+        <v>0.68801367282867432</v>
       </c>
     </row>
     <row r="30">
@@ -4510,58 +4513,58 @@
         <v>75</v>
       </c>
       <c r="B30" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C30" s="1">
         <v>0</v>
       </c>
       <c r="D30" s="1">
-        <v>33.137016296386719</v>
+        <v>30.68280029296875</v>
       </c>
       <c r="E30" s="1">
-        <v>31.089242935180664</v>
+        <v>28.572349548339844</v>
       </c>
       <c r="F30" s="1">
-        <v>30.447328567504883</v>
+        <v>28.382940292358399</v>
       </c>
       <c r="G30" s="1">
-        <v>29.571104049682617</v>
+        <v>28.022138595581055</v>
       </c>
       <c r="H30" s="1">
-        <v>31.089242935180664</v>
+        <v>28.572349548339844</v>
       </c>
       <c r="I30" s="1">
-        <v>30.447328567504883</v>
+        <v>28.382940292358399</v>
       </c>
       <c r="J30" s="1">
-        <v>29.571104049682617</v>
+        <v>28.022138595581055</v>
       </c>
       <c r="K30" s="1">
-        <v>2.8590431213378906</v>
+        <v>1.2923356294631958</v>
       </c>
       <c r="L30" s="1">
-        <v>24.250465393066406</v>
+        <v>5.0096120834350586</v>
       </c>
       <c r="M30" s="1">
         <v>0</v>
       </c>
       <c r="N30" s="1">
-        <v>0</v>
+        <v>11.875863075256348</v>
       </c>
       <c r="O30" s="1">
-        <v>2.4398257732391357</v>
+        <v>13.526473045349121</v>
       </c>
       <c r="P30" s="1">
-        <v>5.532200813293457</v>
+        <v>15.909316062927246</v>
       </c>
       <c r="Q30" s="1">
-        <v>-0.25040501356124878</v>
+        <v>-0.051728162914514542</v>
       </c>
       <c r="R30" s="1">
-        <v>0.89764535427093506</v>
+        <v>0.1854337751865387</v>
       </c>
       <c r="S30" s="1">
-        <v>1.8591302633285523</v>
+        <v>0.38405537605285645</v>
       </c>
     </row>
     <row r="31">
@@ -4569,58 +4572,58 @@
         <v>76</v>
       </c>
       <c r="B31" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C31" s="1">
         <v>0</v>
       </c>
       <c r="D31" s="1">
-        <v>32.963825225830078</v>
+        <v>33.137016296386719</v>
       </c>
       <c r="E31" s="1">
-        <v>31.662092208862305</v>
+        <v>31.089242935180664</v>
       </c>
       <c r="F31" s="1">
-        <v>31.330020904541016</v>
+        <v>30.448698043823242</v>
       </c>
       <c r="G31" s="1">
-        <v>30.998691558837891</v>
+        <v>29.576528549194336</v>
       </c>
       <c r="H31" s="1">
-        <v>31.662092208862305</v>
+        <v>31.089242935180664</v>
       </c>
       <c r="I31" s="1">
-        <v>31.330020904541016</v>
+        <v>30.448698043823242</v>
       </c>
       <c r="J31" s="1">
-        <v>30.998691558837891</v>
+        <v>29.576528549194336</v>
       </c>
       <c r="K31" s="1">
-        <v>1.812983512878418</v>
+        <v>2.8590431213378906</v>
       </c>
       <c r="L31" s="1">
-        <v>2.6068441867828369</v>
+        <v>24.250465393066406</v>
       </c>
       <c r="M31" s="1">
         <v>0</v>
       </c>
       <c r="N31" s="1">
-        <v>2.8584282398223877</v>
+        <v>0</v>
       </c>
       <c r="O31" s="1">
-        <v>5.2332205772399902</v>
+        <v>2.4342901706695557</v>
       </c>
       <c r="P31" s="1">
-        <v>8.2936267852783203</v>
+        <v>5.5137238502502441</v>
       </c>
       <c r="Q31" s="1">
-        <v>-0.026917701587080956</v>
+        <v>-0.25040501356124878</v>
       </c>
       <c r="R31" s="1">
-        <v>0.096493877470493317</v>
+        <v>0.89764535427093506</v>
       </c>
       <c r="S31" s="1">
-        <v>0.19985027611255646</v>
+        <v>1.8591302633285523</v>
       </c>
     </row>
     <row r="32">
@@ -4628,58 +4631,58 @@
         <v>77</v>
       </c>
       <c r="B32" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" s="1">
         <v>0</v>
       </c>
       <c r="D32" s="1">
-        <v>40.793071746826172</v>
+        <v>32.963825225830078</v>
       </c>
       <c r="E32" s="1">
-        <v>35.465656280517578</v>
+        <v>31.662679672241211</v>
       </c>
       <c r="F32" s="1">
-        <v>33.9617919921875</v>
+        <v>31.331905364990234</v>
       </c>
       <c r="G32" s="1">
-        <v>32.433746337890625</v>
+        <v>31.007537841796875</v>
       </c>
       <c r="H32" s="1">
-        <v>35.465656280517578</v>
+        <v>31.662679672241211</v>
       </c>
       <c r="I32" s="1">
-        <v>33.9617919921875</v>
+        <v>31.331905364990234</v>
       </c>
       <c r="J32" s="1">
-        <v>32.433746337890625</v>
+        <v>31.007537841796875</v>
       </c>
       <c r="K32" s="1">
-        <v>2.0582499504089356</v>
+        <v>1.812983512878418</v>
       </c>
       <c r="L32" s="1">
-        <v>32.501632690429688</v>
+        <v>2.6068441867828369</v>
       </c>
       <c r="M32" s="1">
         <v>0</v>
       </c>
       <c r="N32" s="1">
-        <v>5.1170773506164551</v>
+        <v>2.8534793853759766</v>
       </c>
       <c r="O32" s="1">
-        <v>7.3377618789672852</v>
+        <v>5.2173285484313965</v>
       </c>
       <c r="P32" s="1">
-        <v>10.12037467956543</v>
+        <v>8.256169319152832</v>
       </c>
       <c r="Q32" s="1">
-        <v>-0.33560475707054138</v>
+        <v>-0.026917701587080956</v>
       </c>
       <c r="R32" s="1">
-        <v>1.2030673027038574</v>
+        <v>0.096493877470493317</v>
       </c>
       <c r="S32" s="1">
-        <v>2.4916951656341553</v>
+        <v>0.19985027611255646</v>
       </c>
     </row>
     <row r="33">
@@ -4693,52 +4696,52 @@
         <v>0</v>
       </c>
       <c r="D33" s="1">
-        <v>36.838943481445313</v>
+        <v>40.793071746826172</v>
       </c>
       <c r="E33" s="1">
-        <v>35.453342437744141</v>
+        <v>35.467098236083984</v>
       </c>
       <c r="F33" s="1">
-        <v>34.323963165283203</v>
+        <v>33.966518402099609</v>
       </c>
       <c r="G33" s="1">
-        <v>32.934234619140625</v>
+        <v>32.444877624511719</v>
       </c>
       <c r="H33" s="1">
-        <v>35.453342437744141</v>
+        <v>35.467098236083984</v>
       </c>
       <c r="I33" s="1">
-        <v>34.323963165283203</v>
+        <v>33.966518402099609</v>
       </c>
       <c r="J33" s="1">
-        <v>32.934234619140625</v>
+        <v>32.444877624511719</v>
       </c>
       <c r="K33" s="1">
-        <v>3.0391237735748291</v>
+        <v>2.0582499504089356</v>
       </c>
       <c r="L33" s="1">
-        <v>65.625144958496094</v>
+        <v>32.501632690429688</v>
       </c>
       <c r="M33" s="1">
         <v>0</v>
       </c>
       <c r="N33" s="1">
-        <v>58.534774780273438</v>
+        <v>5.1132559776306152</v>
       </c>
       <c r="O33" s="1">
-        <v>61.424823760986328</v>
+        <v>7.3252196311950684</v>
       </c>
       <c r="P33" s="1">
-        <v>65.067344665527344</v>
+        <v>10.090941429138184</v>
       </c>
       <c r="Q33" s="1">
-        <v>-0.67763090133666992</v>
+        <v>-0.33560475707054138</v>
       </c>
       <c r="R33" s="1">
-        <v>2.4291539192199707</v>
+        <v>1.2030673027038574</v>
       </c>
       <c r="S33" s="1">
-        <v>5.0310659408569336</v>
+        <v>2.4916951656341553</v>
       </c>
     </row>
     <row r="34">
@@ -4746,58 +4749,58 @@
         <v>79</v>
       </c>
       <c r="B34" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C34" s="1">
         <v>0</v>
       </c>
       <c r="D34" s="1">
-        <v>35.928680419921875</v>
+        <v>36.838943481445313</v>
       </c>
       <c r="E34" s="1">
-        <v>34.155544281005859</v>
+        <v>35.453342437744141</v>
       </c>
       <c r="F34" s="1">
-        <v>33.766056060791016</v>
+        <v>34.325752258300781</v>
       </c>
       <c r="G34" s="1">
-        <v>33.243087768554688</v>
+        <v>32.945659637451172</v>
       </c>
       <c r="H34" s="1">
-        <v>34.155544281005859</v>
+        <v>35.453342437744141</v>
       </c>
       <c r="I34" s="1">
-        <v>33.766056060791016</v>
+        <v>34.325752258300781</v>
       </c>
       <c r="J34" s="1">
-        <v>33.243087768554688</v>
+        <v>32.945659637451172</v>
       </c>
       <c r="K34" s="1">
-        <v>2.6939806938171387</v>
+        <v>3.0391237735748291</v>
       </c>
       <c r="L34" s="1">
-        <v>10.559006690979004</v>
+        <v>65.625144958496094</v>
       </c>
       <c r="M34" s="1">
         <v>0</v>
       </c>
       <c r="N34" s="1">
-        <v>1.2026726007461548</v>
+        <v>58.534774780273438</v>
       </c>
       <c r="O34" s="1">
-        <v>3.6356034278869629</v>
+        <v>61.411361694335938</v>
       </c>
       <c r="P34" s="1">
-        <v>6.7904548645019531</v>
+        <v>65.033004760742188</v>
       </c>
       <c r="Q34" s="1">
-        <v>-0.10902998596429825</v>
+        <v>-0.67763090133666992</v>
       </c>
       <c r="R34" s="1">
-        <v>0.39084795117378235</v>
+        <v>2.4291539192199707</v>
       </c>
       <c r="S34" s="1">
-        <v>0.80949240922927857</v>
+        <v>5.0310659408569336</v>
       </c>
     </row>
     <row r="35">
@@ -4805,58 +4808,58 @@
         <v>80</v>
       </c>
       <c r="B35" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C35" s="1">
         <v>0</v>
       </c>
       <c r="D35" s="1">
-        <v>39.194725036621094</v>
+        <v>35.928680419921875</v>
       </c>
       <c r="E35" s="1">
-        <v>37.019683837890625</v>
+        <v>34.155609130859375</v>
       </c>
       <c r="F35" s="1">
-        <v>36.075309753417969</v>
+        <v>33.768051147460938</v>
       </c>
       <c r="G35" s="1">
-        <v>35.148616790771484</v>
+        <v>33.252079010009766</v>
       </c>
       <c r="H35" s="1">
-        <v>37.019683837890625</v>
+        <v>34.155609130859375</v>
       </c>
       <c r="I35" s="1">
-        <v>36.075309753417969</v>
+        <v>33.768051147460938</v>
       </c>
       <c r="J35" s="1">
-        <v>35.148616790771484</v>
+        <v>33.252079010009766</v>
       </c>
       <c r="K35" s="1">
-        <v>0.32150024175643921</v>
+        <v>2.6939806938171387</v>
       </c>
       <c r="L35" s="1">
-        <v>69.207923889160156</v>
+        <v>10.559006690979004</v>
       </c>
       <c r="M35" s="1">
         <v>0</v>
       </c>
       <c r="N35" s="1">
-        <v>0</v>
+        <v>1.2021737098693848</v>
       </c>
       <c r="O35" s="1">
-        <v>0.68457144498825073</v>
+        <v>3.6201558113098145</v>
       </c>
       <c r="P35" s="1">
-        <v>1.6949261426925659</v>
+        <v>6.7551174163818359</v>
       </c>
       <c r="Q35" s="1">
-        <v>-0.71462589502334595</v>
+        <v>-0.10902998596429825</v>
       </c>
       <c r="R35" s="1">
-        <v>2.561772346496582</v>
+        <v>0.39084795117378235</v>
       </c>
       <c r="S35" s="1">
-        <v>5.3057351112365723</v>
+        <v>0.80949240922927857</v>
       </c>
     </row>
     <row r="36">
@@ -4870,52 +4873,52 @@
         <v>0</v>
       </c>
       <c r="D36" s="1">
-        <v>41.467826843261719</v>
+        <v>39.194725036621094</v>
       </c>
       <c r="E36" s="1">
-        <v>39.873363494873047</v>
+        <v>37.019683837890625</v>
       </c>
       <c r="F36" s="1">
-        <v>37.75830078125</v>
+        <v>36.075977325439453</v>
       </c>
       <c r="G36" s="1">
-        <v>35.916431427001953</v>
+        <v>35.153644561767578</v>
       </c>
       <c r="H36" s="1">
-        <v>39.873363494873047</v>
+        <v>37.019683837890625</v>
       </c>
       <c r="I36" s="1">
-        <v>37.75830078125</v>
+        <v>36.075977325439453</v>
       </c>
       <c r="J36" s="1">
-        <v>35.916431427001953</v>
+        <v>35.153644561767578</v>
       </c>
       <c r="K36" s="1">
-        <v>1.9415525197982788</v>
+        <v>0.32150024175643921</v>
       </c>
       <c r="L36" s="1">
-        <v>100.38091278076172</v>
+        <v>69.207923889160156</v>
       </c>
       <c r="M36" s="1">
         <v>0</v>
       </c>
       <c r="N36" s="1">
-        <v>3.7585716247558594</v>
+        <v>0</v>
       </c>
       <c r="O36" s="1">
-        <v>6.158841609954834</v>
+        <v>0.679859459400177</v>
       </c>
       <c r="P36" s="1">
-        <v>9.2123174667358399</v>
+        <v>1.6802687644958496</v>
       </c>
       <c r="Q36" s="1">
-        <v>-1.0365113019943237</v>
+        <v>-0.71462589502334595</v>
       </c>
       <c r="R36" s="1">
-        <v>3.7156591415405274</v>
+        <v>2.561772346496582</v>
       </c>
       <c r="S36" s="1">
-        <v>7.6955704689025879</v>
+        <v>5.3057351112365723</v>
       </c>
     </row>
     <row r="37">
@@ -4929,52 +4932,52 @@
         <v>0</v>
       </c>
       <c r="D37" s="1">
-        <v>47.321636199951172</v>
+        <v>41.467826843261719</v>
       </c>
       <c r="E37" s="1">
-        <v>45.018539428710938</v>
+        <v>39.873992919921875</v>
       </c>
       <c r="F37" s="1">
-        <v>43.641483306884766</v>
+        <v>37.760429382324219</v>
       </c>
       <c r="G37" s="1">
-        <v>42.533458709716797</v>
+        <v>35.926563262939453</v>
       </c>
       <c r="H37" s="1">
-        <v>45.018539428710938</v>
+        <v>39.873992919921875</v>
       </c>
       <c r="I37" s="1">
-        <v>43.641483306884766</v>
+        <v>37.760429382324219</v>
       </c>
       <c r="J37" s="1">
-        <v>42.533458709716797</v>
+        <v>35.926563262939453</v>
       </c>
       <c r="K37" s="1">
-        <v>1.9545148611068726</v>
+        <v>1.9415525197982788</v>
       </c>
       <c r="L37" s="1">
-        <v>57.353202819824219</v>
+        <v>100.38091278076172</v>
       </c>
       <c r="M37" s="1">
         <v>0</v>
       </c>
       <c r="N37" s="1">
-        <v>0</v>
+        <v>3.7543389797210693</v>
       </c>
       <c r="O37" s="1">
-        <v>1.1859802007675171</v>
+        <v>6.1446247100830078</v>
       </c>
       <c r="P37" s="1">
-        <v>2.8014233112335205</v>
+        <v>9.1783218383789063</v>
       </c>
       <c r="Q37" s="1">
-        <v>-0.59221667051315308</v>
+        <v>-1.0365113019943237</v>
       </c>
       <c r="R37" s="1">
-        <v>2.1229629516601563</v>
+        <v>3.7156591415405274</v>
       </c>
       <c r="S37" s="1">
-        <v>4.3969082832336426</v>
+        <v>7.6955704689025879</v>
       </c>
     </row>
     <row r="38">
@@ -4988,52 +4991,52 @@
         <v>0</v>
       </c>
       <c r="D38" s="1">
-        <v>48.211658477783203</v>
+        <v>47.321636199951172</v>
       </c>
       <c r="E38" s="1">
-        <v>44.509128570556641</v>
+        <v>45.018539428710938</v>
       </c>
       <c r="F38" s="1">
-        <v>43.544685363769531</v>
+        <v>43.642322540283203</v>
       </c>
       <c r="G38" s="1">
-        <v>42.551666259765625</v>
+        <v>42.536151885986328</v>
       </c>
       <c r="H38" s="1">
-        <v>44.509128570556641</v>
+        <v>45.018539428710938</v>
       </c>
       <c r="I38" s="1">
-        <v>43.544685363769531</v>
+        <v>43.642322540283203</v>
       </c>
       <c r="J38" s="1">
-        <v>42.551666259765625</v>
+        <v>42.536151885986328</v>
       </c>
       <c r="K38" s="1">
-        <v>2.3083720207214355</v>
+        <v>1.9545148611068726</v>
       </c>
       <c r="L38" s="1">
-        <v>31.862676620483398</v>
+        <v>57.353202819824219</v>
       </c>
       <c r="M38" s="1">
         <v>0</v>
       </c>
       <c r="N38" s="1">
-        <v>3.545093297958374</v>
+        <v>0</v>
       </c>
       <c r="O38" s="1">
-        <v>4.9259381294250488</v>
+        <v>1.1810562610626221</v>
       </c>
       <c r="P38" s="1">
-        <v>7.1140284538269043</v>
+        <v>2.7857098579406738</v>
       </c>
       <c r="Q38" s="1">
-        <v>-0.32900702953338623</v>
+        <v>-0.59221667051315308</v>
       </c>
       <c r="R38" s="1">
-        <v>1.1794159412384033</v>
+        <v>2.1229629516601563</v>
       </c>
       <c r="S38" s="1">
-        <v>2.4427101612091065</v>
+        <v>4.3969082832336426</v>
       </c>
     </row>
     <row r="39">
@@ -5047,52 +5050,52 @@
         <v>0</v>
       </c>
       <c r="D39" s="1">
-        <v>50.226909637451172</v>
+        <v>48.211658477783203</v>
       </c>
       <c r="E39" s="1">
-        <v>48.685070037841797</v>
+        <v>44.509128570556641</v>
       </c>
       <c r="F39" s="1">
-        <v>47.172443389892578</v>
+        <v>43.548534393310547</v>
       </c>
       <c r="G39" s="1">
-        <v>45.725273132324219</v>
+        <v>42.564781188964844</v>
       </c>
       <c r="H39" s="1">
-        <v>48.685070037841797</v>
+        <v>44.509128570556641</v>
       </c>
       <c r="I39" s="1">
-        <v>47.172443389892578</v>
+        <v>43.548534393310547</v>
       </c>
       <c r="J39" s="1">
-        <v>45.725273132324219</v>
+        <v>42.564781188964844</v>
       </c>
       <c r="K39" s="1">
-        <v>2.9923243522644043</v>
+        <v>2.3083720207214355</v>
       </c>
       <c r="L39" s="1">
-        <v>65.950004577636719</v>
+        <v>31.862676620483398</v>
       </c>
       <c r="M39" s="1">
         <v>0</v>
       </c>
       <c r="N39" s="1">
-        <v>24.987585067749024</v>
+        <v>3.545093297958374</v>
       </c>
       <c r="O39" s="1">
-        <v>27.197084426879883</v>
+        <v>4.9173016548156738</v>
       </c>
       <c r="P39" s="1">
-        <v>29.835329055786133</v>
+        <v>7.0847058296203613</v>
       </c>
       <c r="Q39" s="1">
-        <v>-0.68098533153533936</v>
+        <v>-0.32900702953338623</v>
       </c>
       <c r="R39" s="1">
-        <v>2.4411787986755371</v>
+        <v>1.1794159412384033</v>
       </c>
       <c r="S39" s="1">
-        <v>5.0559706687927246</v>
+        <v>2.4427101612091065</v>
       </c>
     </row>
     <row r="40">
@@ -5106,52 +5109,52 @@
         <v>0</v>
       </c>
       <c r="D40" s="1">
-        <v>53.848400115966797</v>
+        <v>50.226909637451172</v>
       </c>
       <c r="E40" s="1">
-        <v>48.631397247314453</v>
+        <v>48.685302734375</v>
       </c>
       <c r="F40" s="1">
-        <v>47.996326446533203</v>
+        <v>47.173667907714844</v>
       </c>
       <c r="G40" s="1">
-        <v>47.328617095947266</v>
+        <v>45.731891632080078</v>
       </c>
       <c r="H40" s="1">
-        <v>48.631397247314453</v>
+        <v>48.685302734375</v>
       </c>
       <c r="I40" s="1">
-        <v>47.996326446533203</v>
+        <v>47.173667907714844</v>
       </c>
       <c r="J40" s="1">
-        <v>47.328617095947266</v>
+        <v>45.731891632080078</v>
       </c>
       <c r="K40" s="1">
-        <v>1.8385132551193237</v>
+        <v>2.9923243522644043</v>
       </c>
       <c r="L40" s="1">
-        <v>3.1440615653991699</v>
+        <v>65.950004577636719</v>
       </c>
       <c r="M40" s="1">
         <v>0</v>
       </c>
       <c r="N40" s="1">
-        <v>0</v>
+        <v>24.986234664916992</v>
       </c>
       <c r="O40" s="1">
-        <v>1.3258427381515503</v>
+        <v>27.190309524536133</v>
       </c>
       <c r="P40" s="1">
-        <v>3.125896692276001</v>
+        <v>29.817365646362305</v>
       </c>
       <c r="Q40" s="1">
-        <v>-0.0324648916721344</v>
+        <v>-0.68098533153533936</v>
       </c>
       <c r="R40" s="1">
-        <v>0.11637930572032928</v>
+        <v>2.4411787986755371</v>
       </c>
       <c r="S40" s="1">
-        <v>0.24103538691997528</v>
+        <v>5.0559706687927246</v>
       </c>
     </row>
     <row r="41">
@@ -5159,58 +5162,58 @@
         <v>86</v>
       </c>
       <c r="B41" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" s="1">
         <v>0</v>
       </c>
       <c r="D41" s="1">
-        <v>58.708145141601563</v>
+        <v>53.848400115966797</v>
       </c>
       <c r="E41" s="1">
-        <v>57.504615783691406</v>
+        <v>48.631397247314453</v>
       </c>
       <c r="F41" s="1">
-        <v>56.701080322265625</v>
+        <v>47.9991455078125</v>
       </c>
       <c r="G41" s="1">
-        <v>56.172615051269531</v>
+        <v>47.337520599365234</v>
       </c>
       <c r="H41" s="1">
-        <v>57.504615783691406</v>
+        <v>48.631397247314453</v>
       </c>
       <c r="I41" s="1">
-        <v>56.701080322265625</v>
+        <v>47.9991455078125</v>
       </c>
       <c r="J41" s="1">
-        <v>56.172615051269531</v>
+        <v>47.337520599365234</v>
       </c>
       <c r="K41" s="1">
-        <v>2.3428640365600586</v>
+        <v>1.8385132551193237</v>
       </c>
       <c r="L41" s="1">
-        <v>40.317180633544922</v>
+        <v>3.1440615653991699</v>
       </c>
       <c r="M41" s="1">
         <v>0</v>
       </c>
       <c r="N41" s="1">
-        <v>8.4982700347900391</v>
+        <v>0</v>
       </c>
       <c r="O41" s="1">
-        <v>9.4306840896606445</v>
+        <v>1.3201804161071777</v>
       </c>
       <c r="P41" s="1">
-        <v>10.623865127563477</v>
+        <v>3.1080698966979981</v>
       </c>
       <c r="Q41" s="1">
-        <v>-0.41630640625953674</v>
+        <v>-0.0324648916721344</v>
       </c>
       <c r="R41" s="1">
-        <v>1.4923642873764038</v>
+        <v>0.11637930572032928</v>
       </c>
       <c r="S41" s="1">
-        <v>3.0908637046813965</v>
+        <v>0.24103538691997528</v>
       </c>
     </row>
     <row r="42">
@@ -5218,58 +5221,58 @@
         <v>87</v>
       </c>
       <c r="B42" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" s="1">
         <v>0</v>
       </c>
       <c r="D42" s="1">
-        <v>71.537399291992188</v>
+        <v>58.708145141601563</v>
       </c>
       <c r="E42" s="1">
-        <v>65.240455627441406</v>
+        <v>57.504634857177734</v>
       </c>
       <c r="F42" s="1">
-        <v>63.063045501708984</v>
+        <v>56.702167510986328</v>
       </c>
       <c r="G42" s="1">
-        <v>61.155933380126953</v>
+        <v>56.17529296875</v>
       </c>
       <c r="H42" s="1">
-        <v>65.240455627441406</v>
+        <v>57.504634857177734</v>
       </c>
       <c r="I42" s="1">
-        <v>63.063045501708984</v>
+        <v>56.702167510986328</v>
       </c>
       <c r="J42" s="1">
-        <v>61.155933380126953</v>
+        <v>56.17529296875</v>
       </c>
       <c r="K42" s="1">
-        <v>1.9380583763122559</v>
+        <v>2.3428640365600586</v>
       </c>
       <c r="L42" s="1">
-        <v>49.01953125</v>
+        <v>40.317180633544922</v>
       </c>
       <c r="M42" s="1">
         <v>0</v>
       </c>
       <c r="N42" s="1">
-        <v>0</v>
+        <v>8.4981727600097656</v>
       </c>
       <c r="O42" s="1">
-        <v>0.94814598560333252</v>
+        <v>9.4255790710449219</v>
       </c>
       <c r="P42" s="1">
-        <v>2.1852138042449951</v>
+        <v>10.611268997192383</v>
       </c>
       <c r="Q42" s="1">
-        <v>-0.50616496801376343</v>
+        <v>-0.41630640625953674</v>
       </c>
       <c r="R42" s="1">
-        <v>1.8144869804382324</v>
+        <v>1.4923642873764038</v>
       </c>
       <c r="S42" s="1">
-        <v>3.7580180168151855</v>
+        <v>3.0908637046813965</v>
       </c>
     </row>
     <row r="43">
@@ -5283,31 +5286,31 @@
         <v>0</v>
       </c>
       <c r="D43" s="1">
-        <v>71.927200317382813</v>
+        <v>71.537399291992188</v>
       </c>
       <c r="E43" s="1">
-        <v>68.602897644042969</v>
+        <v>65.240455627441406</v>
       </c>
       <c r="F43" s="1">
-        <v>64.815093994140625</v>
+        <v>63.065341949462891</v>
       </c>
       <c r="G43" s="1">
-        <v>61.514823913574219</v>
+        <v>61.162994384765625</v>
       </c>
       <c r="H43" s="1">
-        <v>68.602897644042969</v>
+        <v>65.240455627441406</v>
       </c>
       <c r="I43" s="1">
-        <v>64.815093994140625</v>
+        <v>63.065341949462891</v>
       </c>
       <c r="J43" s="1">
-        <v>61.514823913574219</v>
+        <v>61.162994384765625</v>
       </c>
       <c r="K43" s="1">
-        <v>1.1138042211532593</v>
+        <v>1.9380583763122559</v>
       </c>
       <c r="L43" s="1">
-        <v>122.11321258544922</v>
+        <v>49.01953125</v>
       </c>
       <c r="M43" s="1">
         <v>0</v>
@@ -5316,19 +5319,19 @@
         <v>0</v>
       </c>
       <c r="O43" s="1">
-        <v>1.1434602737426758</v>
+        <v>0.94468170404434204</v>
       </c>
       <c r="P43" s="1">
-        <v>2.6443591117858887</v>
+        <v>2.1745691299438477</v>
       </c>
       <c r="Q43" s="1">
-        <v>-1.2609143257141113</v>
+        <v>-0.50616496801376343</v>
       </c>
       <c r="R43" s="1">
-        <v>4.5200934410095215</v>
+        <v>1.8144869804382324</v>
       </c>
       <c r="S43" s="1">
-        <v>9.3616495132446289</v>
+        <v>3.7580180168151855</v>
       </c>
     </row>
     <row r="44">
@@ -5342,52 +5345,52 @@
         <v>0</v>
       </c>
       <c r="D44" s="1">
-        <v>66.349037170410156</v>
+        <v>71.927200317382813</v>
       </c>
       <c r="E44" s="1">
-        <v>64.582122802734375</v>
+        <v>68.602897644042969</v>
       </c>
       <c r="F44" s="1">
-        <v>64.475189208984375</v>
+        <v>64.81640625</v>
       </c>
       <c r="G44" s="1">
-        <v>64.535690307617188</v>
+        <v>61.522605895996094</v>
       </c>
       <c r="H44" s="1">
-        <v>64.582122802734375</v>
+        <v>68.602897644042969</v>
       </c>
       <c r="I44" s="1">
-        <v>64.475189208984375</v>
+        <v>64.81640625</v>
       </c>
       <c r="J44" s="1">
-        <v>64.535690307617188</v>
+        <v>61.522605895996094</v>
       </c>
       <c r="K44" s="1">
-        <v>1.7335447072982788</v>
+        <v>1.1138042211532593</v>
       </c>
       <c r="L44" s="1">
-        <v>0.27920371294021606</v>
+        <v>122.11321258544922</v>
       </c>
       <c r="M44" s="1">
         <v>0</v>
       </c>
       <c r="N44" s="1">
-        <v>4.535308837890625</v>
+        <v>0</v>
       </c>
       <c r="O44" s="1">
-        <v>5.2819509506225586</v>
+        <v>1.1383930444717407</v>
       </c>
       <c r="P44" s="1">
-        <v>6.3214783668518067</v>
+        <v>2.6293468475341797</v>
       </c>
       <c r="Q44" s="1">
-        <v>-0.0028829965740442276</v>
+        <v>-1.2609143257141113</v>
       </c>
       <c r="R44" s="1">
-        <v>0.010334892198443413</v>
+        <v>4.5200934410095215</v>
       </c>
       <c r="S44" s="1">
-        <v>0.02140478789806366</v>
+        <v>9.3616495132446289</v>
       </c>
     </row>
     <row r="45">
@@ -5401,52 +5404,52 @@
         <v>0</v>
       </c>
       <c r="D45" s="1">
-        <v>86.785316467285156</v>
+        <v>66.349037170410156</v>
       </c>
       <c r="E45" s="1">
-        <v>80.810401916503906</v>
+        <v>64.582183837890625</v>
       </c>
       <c r="F45" s="1">
-        <v>77.790985107421875</v>
+        <v>64.476692199707031</v>
       </c>
       <c r="G45" s="1">
-        <v>74.746261596679688</v>
+        <v>64.539825439453125</v>
       </c>
       <c r="H45" s="1">
-        <v>80.810401916503906</v>
+        <v>64.582183837890625</v>
       </c>
       <c r="I45" s="1">
-        <v>77.790985107421875</v>
+        <v>64.476692199707031</v>
       </c>
       <c r="J45" s="1">
-        <v>74.746261596679688</v>
+        <v>64.539825439453125</v>
       </c>
       <c r="K45" s="1">
-        <v>5.2754936218261719</v>
+        <v>1.7335447072982788</v>
       </c>
       <c r="L45" s="1">
-        <v>50.939029693603516</v>
+        <v>0.27920371294021606</v>
       </c>
       <c r="M45" s="1">
         <v>0</v>
       </c>
       <c r="N45" s="1">
-        <v>0</v>
+        <v>4.5350542068481445</v>
       </c>
       <c r="O45" s="1">
-        <v>1.8940582275390625</v>
+        <v>5.275667667388916</v>
       </c>
       <c r="P45" s="1">
-        <v>4.2047758102416992</v>
+        <v>6.3042812347412109</v>
       </c>
       <c r="Q45" s="1">
-        <v>-0.52598530054092407</v>
+        <v>-0.0028829965740442276</v>
       </c>
       <c r="R45" s="1">
-        <v>1.8855386972427368</v>
+        <v>0.010334892198443413</v>
       </c>
       <c r="S45" s="1">
-        <v>3.9051744937896729</v>
+        <v>0.02140478789806366</v>
       </c>
     </row>
     <row r="46">
@@ -5460,51 +5463,110 @@
         <v>0</v>
       </c>
       <c r="D46" s="1">
+        <v>86.785316467285156</v>
+      </c>
+      <c r="E46" s="1">
+        <v>80.810401916503906</v>
+      </c>
+      <c r="F46" s="1">
+        <v>77.793388366699219</v>
+      </c>
+      <c r="G46" s="1">
+        <v>74.754150390625</v>
+      </c>
+      <c r="H46" s="1">
+        <v>80.810401916503906</v>
+      </c>
+      <c r="I46" s="1">
+        <v>77.793388366699219</v>
+      </c>
+      <c r="J46" s="1">
+        <v>74.754150390625</v>
+      </c>
+      <c r="K46" s="1">
+        <v>5.2754936218261719</v>
+      </c>
+      <c r="L46" s="1">
+        <v>50.939029693603516</v>
+      </c>
+      <c r="M46" s="1">
+        <v>0</v>
+      </c>
+      <c r="N46" s="1">
+        <v>0</v>
+      </c>
+      <c r="O46" s="1">
+        <v>1.8910566568374634</v>
+      </c>
+      <c r="P46" s="1">
+        <v>4.194979190826416</v>
+      </c>
+      <c r="Q46" s="1">
+        <v>-0.52598530054092407</v>
+      </c>
+      <c r="R46" s="1">
+        <v>1.8855386972427368</v>
+      </c>
+      <c r="S46" s="1">
+        <v>3.9051744937896729</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>92</v>
+      </c>
+      <c r="B47" s="1">
+        <v>1</v>
+      </c>
+      <c r="C47" s="1">
+        <v>0</v>
+      </c>
+      <c r="D47" s="1">
         <v>89.858207702636719</v>
       </c>
-      <c r="E46" s="1">
-        <v>87.971038818359375</v>
-      </c>
-      <c r="F46" s="1">
-        <v>83.315071105957031</v>
-      </c>
-      <c r="G46" s="1">
-        <v>79.349342346191406</v>
-      </c>
-      <c r="H46" s="1">
-        <v>87.971038818359375</v>
-      </c>
-      <c r="I46" s="1">
-        <v>83.315071105957031</v>
-      </c>
-      <c r="J46" s="1">
-        <v>79.349342346191406</v>
-      </c>
-      <c r="K46" s="1">
+      <c r="E47" s="1">
+        <v>87.971145629882813</v>
+      </c>
+      <c r="F47" s="1">
+        <v>83.316246032714844</v>
+      </c>
+      <c r="G47" s="1">
+        <v>79.352760314941406</v>
+      </c>
+      <c r="H47" s="1">
+        <v>87.971145629882813</v>
+      </c>
+      <c r="I47" s="1">
+        <v>83.316246032714844</v>
+      </c>
+      <c r="J47" s="1">
+        <v>79.352760314941406</v>
+      </c>
+      <c r="K47" s="1">
         <v>8.960113525390625</v>
       </c>
-      <c r="L46" s="1">
+      <c r="L47" s="1">
         <v>100.47543334960938</v>
       </c>
-      <c r="M46" s="1">
-        <v>0</v>
-      </c>
-      <c r="N46" s="1">
-        <v>31.12401008605957</v>
-      </c>
-      <c r="O46" s="1">
-        <v>34.519184112548828</v>
-      </c>
-      <c r="P46" s="1">
-        <v>38.48760986328125</v>
-      </c>
-      <c r="Q46" s="1">
+      <c r="M47" s="1">
+        <v>0</v>
+      </c>
+      <c r="N47" s="1">
+        <v>31.123693466186523</v>
+      </c>
+      <c r="O47" s="1">
+        <v>34.515571594238281</v>
+      </c>
+      <c r="P47" s="1">
+        <v>38.477104187011719</v>
+      </c>
+      <c r="Q47" s="1">
         <v>-1.037487268447876</v>
       </c>
-      <c r="R46" s="1">
+      <c r="R47" s="1">
         <v>3.7191579341888428</v>
       </c>
-      <c r="S46" s="1">
+      <c r="S47" s="1">
         <v>7.7028179168701172</v>
       </c>
     </row>
@@ -5528,7 +5590,7 @@
         <v>37</v>
       </c>
       <c r="D1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E1" t="s">
         <v>39</v>
@@ -5549,16 +5611,16 @@
         <v>44</v>
       </c>
       <c r="K1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L1" t="s">
         <v>45</v>
       </c>
       <c r="M1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O1" t="s">
         <v>6</v>
@@ -5569,31 +5631,31 @@
         <v>33</v>
       </c>
       <c r="B2" s="1">
-        <v>22.513217926025391</v>
+        <v>22.532503128051761</v>
       </c>
       <c r="C2" s="1">
-        <v>22.467874526977539</v>
+        <v>22.48326301574707</v>
       </c>
       <c r="D2" s="1">
-        <v>21.316532135009769</v>
+        <v>21.33632850646973</v>
       </c>
       <c r="E2" s="1">
-        <v>21.362339019775391</v>
+        <v>21.37819862365723</v>
       </c>
       <c r="F2" s="1">
-        <v>2.1007614135742192</v>
+        <v>2.098418235778809</v>
       </c>
       <c r="G2" s="1">
-        <v>2.2563803195953369</v>
+        <v>2.2517673969268799</v>
       </c>
       <c r="H2" s="1">
-        <v>4.7423748593956638</v>
+        <v>4.7248601695613051</v>
       </c>
       <c r="I2" s="1">
-        <v>-0.45406845331923512</v>
+        <v>-0.45855069879978899</v>
       </c>
       <c r="J2" s="1">
-        <v>15.737912059494811</v>
+        <v>15.695722980486099</v>
       </c>
       <c r="K2" s="1">
         <v>100</v>
@@ -5608,7 +5670,7 @@
         <v>5</v>
       </c>
       <c r="O2" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
@@ -5616,34 +5678,34 @@
         <v>34</v>
       </c>
       <c r="B3" s="1">
-        <v>22.513217926025391</v>
+        <v>22.532503128051761</v>
       </c>
       <c r="C3" s="1">
-        <v>21.80241775512695</v>
+        <v>21.815752029418949</v>
       </c>
       <c r="D3" s="1">
-        <v>21.316532135009769</v>
+        <v>21.33632850646973</v>
       </c>
       <c r="E3" s="1">
-        <v>20.696636199951168</v>
+        <v>20.710443496704102</v>
       </c>
       <c r="F3" s="1">
-        <v>2.1007614135742192</v>
+        <v>2.098418235778809</v>
       </c>
       <c r="G3" s="1">
-        <v>2.6670103073120122</v>
+        <v>2.656042337417603</v>
       </c>
       <c r="H3" s="1">
-        <v>8.5411063419639959</v>
+        <v>8.5026045191464661</v>
       </c>
       <c r="I3" s="1">
-        <v>1.6277328804753139</v>
+        <v>1.6438007223960529</v>
       </c>
       <c r="J3" s="1">
-        <v>11.7931389740451</v>
+        <v>11.75924173093461</v>
       </c>
       <c r="K3" s="1">
-        <v>83.992933265348143</v>
+        <v>83.799181254205919</v>
       </c>
       <c r="L3" s="1">
         <v>0</v>
@@ -5655,7 +5717,7 @@
         <v>5</v>
       </c>
       <c r="O3" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
@@ -5663,34 +5725,34 @@
         <v>35</v>
       </c>
       <c r="B4" s="1">
-        <v>22.513217926025391</v>
+        <v>22.532503128051761</v>
       </c>
       <c r="C4" s="1">
-        <v>21.03447532653809</v>
+        <v>21.04714202880859</v>
       </c>
       <c r="D4" s="1">
-        <v>21.316532135009769</v>
+        <v>21.33632850646973</v>
       </c>
       <c r="E4" s="1">
-        <v>19.924493789672852</v>
+        <v>19.937633514404301</v>
       </c>
       <c r="F4" s="1">
-        <v>2.1007614135742192</v>
+        <v>2.098418235778809</v>
       </c>
       <c r="G4" s="1">
-        <v>3.0794107913970952</v>
+        <v>3.060468435287476</v>
       </c>
       <c r="H4" s="1">
-        <v>13.561421608018341</v>
+        <v>13.484676326366801</v>
       </c>
       <c r="I4" s="1">
-        <v>3.371228042897124</v>
+        <v>3.404506446363996</v>
       </c>
       <c r="J4" s="1">
-        <v>6.7479009260389136</v>
+        <v>6.7365932485337092</v>
       </c>
       <c r="K4" s="1">
-        <v>80.090369124746758</v>
+        <v>79.84208891468154</v>
       </c>
       <c r="L4" s="1">
         <v>2</v>
@@ -5702,7 +5764,7 @@
         <v>5</v>
       </c>
       <c r="O4" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -5716,15 +5778,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B2" s="1">
         <v>0.5</v>
@@ -5732,7 +5794,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B3" s="1">
         <v>0.050000000000000003</v>
@@ -5740,23 +5802,23 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B4" s="1">
-        <v>0.18825186946715719</v>
+        <v>0.18894011085868601</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B5" s="1">
-        <v>0.1176576282904908</v>
+        <v>0.1172495384343593</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B6" s="1">
         <v>0.36201603544677707</v>
@@ -5764,7 +5826,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B7" s="1">
         <v>5</v>
@@ -5772,7 +5834,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B8" s="1">
         <v>-0.42899999999999999</v>
@@ -5780,7 +5842,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B9" s="1">
         <v>0.22</v>
@@ -5788,7 +5850,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B10" s="1">
         <v>265</v>
@@ -5796,7 +5858,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B11" s="1">
         <v>4</v>

--- a/output/fixed/stress_test_summary.xlsx
+++ b/output/fixed/stress_test_summary.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="247" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="249" uniqueCount="127">
   <si>
     <t>qtr</t>
   </si>
@@ -167,39 +167,39 @@
     <t>BCIC</t>
   </si>
   <si>
+    <t>MAYA</t>
+  </si>
+  <si>
     <t>BBKP</t>
   </si>
   <si>
-    <t>MAYA</t>
+    <t>NOBU</t>
+  </si>
+  <si>
+    <t>PNBS</t>
   </si>
   <si>
     <t>BJBR</t>
   </si>
   <si>
-    <t>NOBU</t>
-  </si>
-  <si>
-    <t>PNBS</t>
+    <t>BNII</t>
+  </si>
+  <si>
+    <t>BABP</t>
   </si>
   <si>
     <t>BBTN</t>
   </si>
   <si>
-    <t>BNII</t>
-  </si>
-  <si>
-    <t>BABP</t>
+    <t>BBNI</t>
+  </si>
+  <si>
+    <t>BMRI</t>
   </si>
   <si>
     <t>INPC</t>
   </si>
   <si>
-    <t>BBNI</t>
-  </si>
-  <si>
-    <t>BMRI</t>
-  </si>
-  <si>
     <t>BVIC</t>
   </si>
   <si>
@@ -221,12 +221,12 @@
     <t>BBRI</t>
   </si>
   <si>
+    <t>NISP</t>
+  </si>
+  <si>
     <t>BNGA</t>
   </si>
   <si>
-    <t>NISP</t>
-  </si>
-  <si>
     <t>BSIM</t>
   </si>
   <si>
@@ -236,12 +236,12 @@
     <t>MEGA</t>
   </si>
   <si>
+    <t>SDRA</t>
+  </si>
+  <si>
     <t>BJTM</t>
   </si>
   <si>
-    <t>SDRA</t>
-  </si>
-  <si>
     <t>BBCA</t>
   </si>
   <si>
@@ -269,12 +269,12 @@
     <t>DNAR</t>
   </si>
   <si>
+    <t>BMAS</t>
+  </si>
+  <si>
     <t>BBMD</t>
   </si>
   <si>
-    <t>BMAS</t>
-  </si>
-  <si>
     <t>BBYB</t>
   </si>
   <si>
@@ -381,6 +381,12 @@
   </si>
   <si>
     <t>e_prop</t>
+  </si>
+  <si>
+    <t>beta_l</t>
+  </si>
+  <si>
+    <t>beta_d</t>
   </si>
   <si>
     <t>tax_rate</t>
@@ -576,19 +582,19 @@
         <v>22.498384475708008</v>
       </c>
       <c r="D3" s="1">
-        <v>22.408557891845703</v>
+        <v>22.417062759399414</v>
       </c>
       <c r="E3" s="1">
-        <v>22.310403823852539</v>
+        <v>22.316936492919922</v>
       </c>
       <c r="F3" s="1">
         <v>21.326032638549805</v>
       </c>
       <c r="G3" s="1">
-        <v>21.236438751220703</v>
+        <v>21.244945526123047</v>
       </c>
       <c r="H3" s="1">
-        <v>21.137842178344727</v>
+        <v>21.144376754760742</v>
       </c>
       <c r="I3" s="1">
         <v>2.2504801750183105</v>
@@ -603,19 +609,19 @@
         <v>0.48911944031715393</v>
       </c>
       <c r="M3" s="1">
-        <v>0.44537994265556335</v>
+        <v>0.45468792319297791</v>
       </c>
       <c r="N3" s="1">
-        <v>0.38578882813453674</v>
+        <v>0.39158865809440613</v>
       </c>
       <c r="O3" s="1">
         <v>0.24474991858005524</v>
       </c>
       <c r="P3" s="1">
-        <v>0.28845217823982239</v>
+        <v>0.27097126841545105</v>
       </c>
       <c r="Q3" s="1">
-        <v>0.35353401303291321</v>
+        <v>0.31002038717269897</v>
       </c>
       <c r="R3" s="1">
         <v>-0.017933163791894913</v>
@@ -638,19 +644,19 @@
         <v>22.469232559204102</v>
       </c>
       <c r="D4" s="1">
-        <v>22.245197296142578</v>
+        <v>22.259685516357422</v>
       </c>
       <c r="E4" s="1">
-        <v>22.011495590209961</v>
+        <v>22.022344589233398</v>
       </c>
       <c r="F4" s="1">
         <v>21.32002067565918</v>
       </c>
       <c r="G4" s="1">
-        <v>21.096221923828125</v>
+        <v>21.110710144042969</v>
       </c>
       <c r="H4" s="1">
-        <v>20.861215591430664</v>
+        <v>20.872064590454102</v>
       </c>
       <c r="I4" s="1">
         <v>2.2543222904205322</v>
@@ -665,19 +671,19 @@
         <v>0.4925592839717865</v>
       </c>
       <c r="M4" s="1">
-        <v>0.40450090169906616</v>
+        <v>0.41057136654853821</v>
       </c>
       <c r="N4" s="1">
-        <v>0.29760658740997314</v>
+        <v>0.29879981279373169</v>
       </c>
       <c r="O4" s="1">
         <v>0.2353503555059433</v>
       </c>
       <c r="P4" s="1">
-        <v>0.35017648339271546</v>
+        <v>0.30583718419075012</v>
       </c>
       <c r="Q4" s="1">
-        <v>0.49887070059776306</v>
+        <v>0.39858812093734741</v>
       </c>
       <c r="R4" s="1">
         <v>-0.010432972572743893</v>
@@ -697,22 +703,22 @@
         <v>46</v>
       </c>
       <c r="C5" s="1">
-        <v>22.481237411499024</v>
+        <v>22.496133804321289</v>
       </c>
       <c r="D5" s="1">
-        <v>22.051111221313477</v>
+        <v>22.073032379150391</v>
       </c>
       <c r="E5" s="1">
-        <v>21.61274528503418</v>
+        <v>21.635410308837891</v>
       </c>
       <c r="F5" s="1">
-        <v>21.354185104370117</v>
+        <v>21.369081497192383</v>
       </c>
       <c r="G5" s="1">
-        <v>20.924392700195313</v>
+        <v>20.946313858032227</v>
       </c>
       <c r="H5" s="1">
-        <v>20.483465194702148</v>
+        <v>20.506130218505859</v>
       </c>
       <c r="I5" s="1">
         <v>2.2808027267456055</v>
@@ -724,22 +730,22 @@
         <v>2.6856958866119385</v>
       </c>
       <c r="L5" s="1">
-        <v>0.51045423746109009</v>
+        <v>0.52787935733795166</v>
       </c>
       <c r="M5" s="1">
-        <v>0.35918039083480835</v>
+        <v>0.36503401398658752</v>
       </c>
       <c r="N5" s="1">
-        <v>0.17670455574989319</v>
+        <v>0.18356201052665711</v>
       </c>
       <c r="O5" s="1">
         <v>0.2173498272895813</v>
       </c>
       <c r="P5" s="1">
-        <v>0.43155106902122498</v>
+        <v>0.35526314377784729</v>
       </c>
       <c r="Q5" s="1">
-        <v>0.7137485146522522</v>
+        <v>0.53755128383636475</v>
       </c>
       <c r="R5" s="1">
         <v>-0.036216519773006439</v>
@@ -759,22 +765,22 @@
         <v>46</v>
       </c>
       <c r="C6" s="1">
-        <v>22.48326301574707</v>
+        <v>22.527645111083984</v>
       </c>
       <c r="D6" s="1">
-        <v>21.815752029418945</v>
+        <v>21.867099761962891</v>
       </c>
       <c r="E6" s="1">
-        <v>21.047142028808594</v>
+        <v>21.13709831237793</v>
       </c>
       <c r="F6" s="1">
-        <v>21.378198623657227</v>
+        <v>21.422582626342774</v>
       </c>
       <c r="G6" s="1">
-        <v>20.710443496704102</v>
+        <v>20.761791229248047</v>
       </c>
       <c r="H6" s="1">
-        <v>19.937633514404297</v>
+        <v>20.027591705322266</v>
       </c>
       <c r="I6" s="1">
         <v>2.2517673969268799</v>
@@ -786,22 +792,22 @@
         <v>3.0604684352874756</v>
       </c>
       <c r="L6" s="1">
-        <v>0.51425039768218994</v>
+        <v>0.54909712076187134</v>
       </c>
       <c r="M6" s="1">
-        <v>0.29935985803604126</v>
+        <v>0.32786744832992554</v>
       </c>
       <c r="N6" s="1">
-        <v>0.014345861040055752</v>
+        <v>0.062386922538280487</v>
       </c>
       <c r="O6" s="1">
         <v>0.20698535442352295</v>
       </c>
       <c r="P6" s="1">
-        <v>0.54651373624801636</v>
+        <v>0.42839813232421875</v>
       </c>
       <c r="Q6" s="1">
-        <v>0.9963497519493103</v>
+        <v>0.71863949298858643</v>
       </c>
       <c r="R6" s="1">
         <v>-0.0226777084171772</v>
@@ -912,19 +918,19 @@
         <v>19.512197494506836</v>
       </c>
       <c r="E3" s="1">
-        <v>19.460554122924805</v>
+        <v>19.468423843383789</v>
       </c>
       <c r="F3" s="1">
-        <v>19.406646728515625</v>
+        <v>19.410497665405274</v>
       </c>
       <c r="G3" s="1">
         <v>18.374406814575195</v>
       </c>
       <c r="H3" s="1">
-        <v>18.322990417480469</v>
+        <v>18.330860137939453</v>
       </c>
       <c r="I3" s="1">
-        <v>18.268653869628906</v>
+        <v>18.272504806518555</v>
       </c>
       <c r="J3" s="1">
         <v>2.1769814491271973</v>
@@ -950,19 +956,19 @@
         <v>19.584991455078125</v>
       </c>
       <c r="E4" s="1">
-        <v>19.445896148681641</v>
+        <v>19.458097457885742</v>
       </c>
       <c r="F4" s="1">
-        <v>19.295503616333008</v>
+        <v>19.300325393676758</v>
       </c>
       <c r="G4" s="1">
         <v>18.469655990600586</v>
       </c>
       <c r="H4" s="1">
-        <v>18.330791473388672</v>
+        <v>18.342994689941406</v>
       </c>
       <c r="I4" s="1">
-        <v>18.179134368896484</v>
+        <v>18.183956146240234</v>
       </c>
       <c r="J4" s="1">
         <v>2.208909273147583</v>
@@ -985,22 +991,22 @@
         <v>5</v>
       </c>
       <c r="D5" s="1">
-        <v>19.684902191162109</v>
+        <v>19.700643539428711</v>
       </c>
       <c r="E5" s="1">
-        <v>19.399332046508789</v>
+        <v>19.417373657226563</v>
       </c>
       <c r="F5" s="1">
-        <v>19.084421157836914</v>
+        <v>19.096343994140625</v>
       </c>
       <c r="G5" s="1">
-        <v>18.591075897216797</v>
+        <v>18.606815338134766</v>
       </c>
       <c r="H5" s="1">
-        <v>18.305830001831055</v>
+        <v>18.323871612548828</v>
       </c>
       <c r="I5" s="1">
-        <v>17.988431930541992</v>
+        <v>18.000354766845703</v>
       </c>
       <c r="J5" s="1">
         <v>2.254328727722168</v>
@@ -1023,22 +1029,22 @@
         <v>5</v>
       </c>
       <c r="D6" s="1">
-        <v>19.780633926391602</v>
+        <v>19.827547073364258</v>
       </c>
       <c r="E6" s="1">
-        <v>19.302658081054688</v>
+        <v>19.349361419677734</v>
       </c>
       <c r="F6" s="1">
-        <v>18.692916870117188</v>
+        <v>18.769155502319336</v>
       </c>
       <c r="G6" s="1">
-        <v>18.708147048950195</v>
+        <v>18.755060195922852</v>
       </c>
       <c r="H6" s="1">
-        <v>18.229934692382813</v>
+        <v>18.276636123657227</v>
       </c>
       <c r="I6" s="1">
-        <v>17.616117477416992</v>
+        <v>17.692358016967773</v>
       </c>
       <c r="J6" s="1">
         <v>2.2380642890930176</v>
@@ -1102,19 +1108,19 @@
         <v>26.591842651367188</v>
       </c>
       <c r="E8" s="1">
-        <v>26.449670791625977</v>
+        <v>26.459049224853516</v>
       </c>
       <c r="F8" s="1">
-        <v>26.290864944458008</v>
+        <v>26.301076889038086</v>
       </c>
       <c r="G8" s="1">
         <v>25.372116088867188</v>
       </c>
       <c r="H8" s="1">
-        <v>25.230188369750977</v>
+        <v>25.239564895629883</v>
       </c>
       <c r="I8" s="1">
-        <v>25.070920944213867</v>
+        <v>25.081132888793945</v>
       </c>
       <c r="J8" s="1">
         <v>2.3680710792541504</v>
@@ -1140,19 +1146,19 @@
         <v>26.422945022583008</v>
       </c>
       <c r="E9" s="1">
-        <v>26.082473754882813</v>
+        <v>26.100095748901367</v>
       </c>
       <c r="F9" s="1">
-        <v>25.734569549560547</v>
+        <v>25.753681182861328</v>
       </c>
       <c r="G9" s="1">
         <v>25.227291107177734</v>
       </c>
       <c r="H9" s="1">
-        <v>24.887065887451172</v>
+        <v>24.904687881469727</v>
       </c>
       <c r="I9" s="1">
-        <v>24.537805557250977</v>
+        <v>24.556917190551758</v>
       </c>
       <c r="J9" s="1">
         <v>2.3269786834716797</v>
@@ -1175,22 +1181,22 @@
         <v>41</v>
       </c>
       <c r="D10" s="1">
-        <v>26.314443588256836</v>
+        <v>26.328184127807617</v>
       </c>
       <c r="E10" s="1">
-        <v>25.686161041259766</v>
+        <v>25.713403701782227</v>
       </c>
       <c r="F10" s="1">
-        <v>25.078563690185547</v>
+        <v>25.115957260131836</v>
       </c>
       <c r="G10" s="1">
-        <v>25.141845703125</v>
+        <v>25.155586242675781</v>
       </c>
       <c r="H10" s="1">
-        <v>24.513910293579102</v>
+        <v>24.541152954101563</v>
       </c>
       <c r="I10" s="1">
-        <v>23.903648376464844</v>
+        <v>23.941041946411133</v>
       </c>
       <c r="J10" s="1">
         <v>2.3231587409973145</v>
@@ -1213,22 +1219,22 @@
         <v>41</v>
       </c>
       <c r="D11" s="1">
-        <v>26.188018798828125</v>
+        <v>26.228933334350586</v>
       </c>
       <c r="E11" s="1">
-        <v>25.260692596435547</v>
+        <v>25.318410873413086</v>
       </c>
       <c r="F11" s="1">
-        <v>24.274307250976563</v>
+        <v>24.38306999206543</v>
       </c>
       <c r="G11" s="1">
-        <v>25.038297653198242</v>
+        <v>25.079212188720703</v>
       </c>
       <c r="H11" s="1">
-        <v>24.1107177734375</v>
+        <v>24.168436050415039</v>
       </c>
       <c r="I11" s="1">
-        <v>23.119962692260742</v>
+        <v>23.228727340698242</v>
       </c>
       <c r="J11" s="1">
         <v>2.273690938949585</v>
@@ -1292,19 +1298,19 @@
         <v>33.182823181152344</v>
       </c>
       <c r="E13" s="1">
-        <v>32.766506195068359</v>
+        <v>32.778701782226563</v>
       </c>
       <c r="F13" s="1">
-        <v>32.295276641845703</v>
+        <v>32.309421539306641</v>
       </c>
       <c r="G13" s="1">
         <v>31.882535934448242</v>
       </c>
       <c r="H13" s="1">
-        <v>31.46647834777832</v>
+        <v>31.478673934936524</v>
       </c>
       <c r="I13" s="1">
-        <v>30.994758605957031</v>
+        <v>31.008905410766602</v>
       </c>
       <c r="J13" s="1">
         <v>2.6759073734283447</v>
@@ -1330,19 +1336,19 @@
         <v>32.614086151123047</v>
       </c>
       <c r="E14" s="1">
-        <v>31.648738861083984</v>
+        <v>31.67633056640625</v>
       </c>
       <c r="F14" s="1">
-        <v>30.643526077270508</v>
+        <v>30.678815841674805</v>
       </c>
       <c r="G14" s="1">
         <v>31.339462280273438</v>
       </c>
       <c r="H14" s="1">
-        <v>30.374378204345703</v>
+        <v>30.401969909667969</v>
       </c>
       <c r="I14" s="1">
-        <v>29.367719650268555</v>
+        <v>29.403009414672852</v>
       </c>
       <c r="J14" s="1">
         <v>2.7413887977600098</v>
@@ -1365,22 +1371,22 @@
         <v>24</v>
       </c>
       <c r="D15" s="1">
-        <v>32.202350616455078</v>
+        <v>32.220645904541016</v>
       </c>
       <c r="E15" s="1">
-        <v>30.492002487182617</v>
+        <v>30.542661666870117</v>
       </c>
       <c r="F15" s="1">
-        <v>28.844316482543945</v>
+        <v>28.926494598388672</v>
       </c>
       <c r="G15" s="1">
-        <v>30.952304840087891</v>
+        <v>30.970600128173828</v>
       </c>
       <c r="H15" s="1">
-        <v>29.242330551147461</v>
+        <v>29.292987823486328</v>
       </c>
       <c r="I15" s="1">
-        <v>27.591802597045898</v>
+        <v>27.673978805541992</v>
       </c>
       <c r="J15" s="1">
         <v>2.8094339370727539</v>
@@ -1403,22 +1409,22 @@
         <v>24</v>
       </c>
       <c r="D16" s="1">
-        <v>31.73249626159668</v>
+        <v>31.786628723144531</v>
       </c>
       <c r="E16" s="1">
-        <v>29.312572479248047</v>
+        <v>29.427352905273438</v>
       </c>
       <c r="F16" s="1">
-        <v>26.87030029296875</v>
+        <v>27.080663681030273</v>
       </c>
       <c r="G16" s="1">
-        <v>30.506839752197266</v>
+        <v>30.560972213745117</v>
       </c>
       <c r="H16" s="1">
-        <v>28.086645126342774</v>
+        <v>28.201423645019531</v>
       </c>
       <c r="I16" s="1">
-        <v>25.639717102050781</v>
+        <v>25.850080490112305</v>
       </c>
       <c r="J16" s="1">
         <v>2.8084266185760498</v>
@@ -1482,19 +1488,19 @@
         <v>20.652599334716797</v>
       </c>
       <c r="E18" s="1">
-        <v>20.384426116943359</v>
+        <v>20.409036636352539</v>
       </c>
       <c r="F18" s="1">
-        <v>20.045492172241211</v>
+        <v>20.094171524047852</v>
       </c>
       <c r="G18" s="1">
         <v>19.133609771728516</v>
       </c>
       <c r="H18" s="1">
-        <v>18.865739822387695</v>
+        <v>18.890350341796875</v>
       </c>
       <c r="I18" s="1">
-        <v>18.526233673095703</v>
+        <v>18.574911117553711</v>
       </c>
       <c r="J18" s="1">
         <v>4.3011026382446289</v>
@@ -1520,19 +1526,19 @@
         <v>20.388845443725586</v>
       </c>
       <c r="E19" s="1">
-        <v>19.737102508544922</v>
+        <v>19.795322418212891</v>
       </c>
       <c r="F19" s="1">
-        <v>18.99751091003418</v>
+        <v>19.117879867553711</v>
       </c>
       <c r="G19" s="1">
         <v>18.899835586547852</v>
       </c>
       <c r="H19" s="1">
-        <v>18.24839973449707</v>
+        <v>18.306619644165039</v>
       </c>
       <c r="I19" s="1">
-        <v>17.507118225097656</v>
+        <v>17.627487182617188</v>
       </c>
       <c r="J19" s="1">
         <v>3.9407155513763428</v>
@@ -1555,22 +1561,22 @@
         <v>8</v>
       </c>
       <c r="D20" s="1">
-        <v>20.212871551513672</v>
+        <v>20.228128433227539</v>
       </c>
       <c r="E20" s="1">
-        <v>19.022928237915039</v>
+        <v>19.126827239990234</v>
       </c>
       <c r="F20" s="1">
-        <v>17.730104446411133</v>
+        <v>17.967748641967773</v>
       </c>
       <c r="G20" s="1">
-        <v>18.752574920654297</v>
+        <v>18.767831802368164</v>
       </c>
       <c r="H20" s="1">
-        <v>17.563064575195313</v>
+        <v>17.666963577270508</v>
       </c>
       <c r="I20" s="1">
-        <v>16.266921997070313</v>
+        <v>16.504566192626953</v>
       </c>
       <c r="J20" s="1">
         <v>3.7215871810913086</v>
@@ -1593,22 +1599,22 @@
         <v>8</v>
       </c>
       <c r="D21" s="1">
-        <v>20.007450103759766</v>
+        <v>20.052921295166016</v>
       </c>
       <c r="E21" s="1">
-        <v>18.249076843261719</v>
+        <v>18.437797546386719</v>
       </c>
       <c r="F21" s="1">
-        <v>16.181604385375977</v>
+        <v>16.628829956054688</v>
       </c>
       <c r="G21" s="1">
-        <v>18.575643539428711</v>
+        <v>18.621114730834961</v>
       </c>
       <c r="H21" s="1">
-        <v>16.816951751708984</v>
+        <v>17.005672454833984</v>
       </c>
       <c r="I21" s="1">
-        <v>14.744041442871094</v>
+        <v>15.191267013549805</v>
       </c>
       <c r="J21" s="1">
         <v>3.5269320011138916</v>
@@ -1672,19 +1678,19 @@
         <v>24.995981216430664</v>
       </c>
       <c r="E23" s="1">
-        <v>24.884761810302734</v>
+        <v>24.892892837524414</v>
       </c>
       <c r="F23" s="1">
-        <v>24.768022537231445</v>
+        <v>24.772912979125977</v>
       </c>
       <c r="G23" s="1">
         <v>23.741788864135742</v>
       </c>
       <c r="H23" s="1">
-        <v>23.630821228027344</v>
+        <v>23.638952255249024</v>
       </c>
       <c r="I23" s="1">
-        <v>23.513608932495117</v>
+        <v>23.518499374389648</v>
       </c>
       <c r="J23" s="1">
         <v>2.2920432090759277</v>
@@ -1710,19 +1716,19 @@
         <v>24.806625366210938</v>
       </c>
       <c r="E24" s="1">
-        <v>24.534149169921875</v>
+        <v>24.548187255859375</v>
       </c>
       <c r="F24" s="1">
-        <v>24.241203308105469</v>
+        <v>24.252639770507813</v>
       </c>
       <c r="G24" s="1">
         <v>23.577186584472656</v>
       </c>
       <c r="H24" s="1">
-        <v>23.304964065551758</v>
+        <v>23.319002151489258</v>
       </c>
       <c r="I24" s="1">
-        <v>23.010625839233398</v>
+        <v>23.022062301635742</v>
       </c>
       <c r="J24" s="1">
         <v>2.3864409923553467</v>
@@ -1745,22 +1751,22 @@
         <v>10</v>
       </c>
       <c r="D25" s="1">
-        <v>24.672149658203125</v>
+        <v>24.687498092651367</v>
       </c>
       <c r="E25" s="1">
-        <v>24.151182174682617</v>
+        <v>24.177635192871094</v>
       </c>
       <c r="F25" s="1">
-        <v>23.583185195922852</v>
+        <v>23.611125946044922</v>
       </c>
       <c r="G25" s="1">
-        <v>23.466421127319336</v>
+        <v>23.481767654418945</v>
       </c>
       <c r="H25" s="1">
-        <v>22.945808410644531</v>
+        <v>22.972263336181641</v>
       </c>
       <c r="I25" s="1">
-        <v>22.375072479248047</v>
+        <v>22.403013229370117</v>
       </c>
       <c r="J25" s="1">
         <v>2.4739854335784912</v>
@@ -1783,22 +1789,22 @@
         <v>10</v>
       </c>
       <c r="D26" s="1">
-        <v>24.52734375</v>
+        <v>24.573089599609375</v>
       </c>
       <c r="E26" s="1">
-        <v>23.7139892578125</v>
+        <v>23.781251907348633</v>
       </c>
       <c r="F26" s="1">
-        <v>22.683252334594727</v>
+        <v>22.814777374267578</v>
       </c>
       <c r="G26" s="1">
-        <v>23.345138549804688</v>
+        <v>23.39088249206543</v>
       </c>
       <c r="H26" s="1">
-        <v>22.531518936157227</v>
+        <v>22.598781585693359</v>
       </c>
       <c r="I26" s="1">
-        <v>21.496292114257813</v>
+        <v>21.627817153930664</v>
       </c>
       <c r="J26" s="1">
         <v>2.4861268997192383</v>
@@ -1862,19 +1868,19 @@
         <v>21.087326049804688</v>
       </c>
       <c r="E28" s="1">
-        <v>21.04345703125</v>
+        <v>21.050283432006836</v>
       </c>
       <c r="F28" s="1">
-        <v>20.999301910400391</v>
+        <v>21.001811981201172</v>
       </c>
       <c r="G28" s="1">
         <v>19.987386703491211</v>
       </c>
       <c r="H28" s="1">
-        <v>19.94373893737793</v>
+        <v>19.950565338134766</v>
       </c>
       <c r="I28" s="1">
-        <v>19.899166107177734</v>
+        <v>19.901678085327149</v>
       </c>
       <c r="J28" s="1">
         <v>2.0186150074005127</v>
@@ -1900,19 +1906,19 @@
         <v>21.174322128295898</v>
       </c>
       <c r="E29" s="1">
-        <v>21.056835174560547</v>
+        <v>21.06635856628418</v>
       </c>
       <c r="F29" s="1">
-        <v>20.943269729614258</v>
+        <v>20.94157600402832</v>
       </c>
       <c r="G29" s="1">
         <v>20.096092224121094</v>
       </c>
       <c r="H29" s="1">
-        <v>19.978828430175781</v>
+        <v>19.988351821899414</v>
       </c>
       <c r="I29" s="1">
-        <v>19.864038467407227</v>
+        <v>19.862346649169922</v>
       </c>
       <c r="J29" s="1">
         <v>2.0179219245910645</v>
@@ -1935,22 +1941,22 @@
         <v>4</v>
       </c>
       <c r="D30" s="1">
-        <v>21.285539627075195</v>
+        <v>21.300020217895508</v>
       </c>
       <c r="E30" s="1">
-        <v>21.044162750244141</v>
+        <v>21.054529190063477</v>
       </c>
       <c r="F30" s="1">
-        <v>20.813749313354492</v>
+        <v>20.809549331665039</v>
       </c>
       <c r="G30" s="1">
-        <v>20.22810173034668</v>
+        <v>20.242584228515625</v>
       </c>
       <c r="H30" s="1">
-        <v>19.987037658691406</v>
+        <v>19.997406005859375</v>
       </c>
       <c r="I30" s="1">
-        <v>19.754220962524414</v>
+        <v>19.750022888183594</v>
       </c>
       <c r="J30" s="1">
         <v>2.041344165802002</v>
@@ -1973,22 +1979,22 @@
         <v>4</v>
       </c>
       <c r="D31" s="1">
-        <v>21.391849517822266</v>
+        <v>21.43501091003418</v>
       </c>
       <c r="E31" s="1">
-        <v>20.995651245117188</v>
+        <v>21.023605346679688</v>
       </c>
       <c r="F31" s="1">
-        <v>20.556858062744141</v>
+        <v>20.588703155517578</v>
       </c>
       <c r="G31" s="1">
-        <v>20.355043411254883</v>
+        <v>20.398204803466797</v>
       </c>
       <c r="H31" s="1">
-        <v>19.958614349365234</v>
+        <v>19.986568450927734</v>
       </c>
       <c r="I31" s="1">
-        <v>19.515880584716797</v>
+        <v>19.5477294921875</v>
       </c>
       <c r="J31" s="1">
         <v>2.0102465152740479</v>
@@ -2064,13 +2070,13 @@
         <v>19.437982559204102</v>
       </c>
       <c r="E2" s="1">
-        <v>19.780633926391602</v>
+        <v>19.827547073364258</v>
       </c>
       <c r="F2" s="1">
         <v>19.512197494506836</v>
       </c>
       <c r="G2" s="1">
-        <v>18.708147048950195</v>
+        <v>18.755060195922852</v>
       </c>
       <c r="H2" s="1">
         <v>1.9832693338394165</v>
@@ -2085,7 +2091,7 @@
         <v>-0.351205974817276</v>
       </c>
       <c r="L2" s="1">
-        <v>20.205373764038086</v>
+        <v>20.727863311767578</v>
       </c>
       <c r="M2" s="1">
         <v>0</v>
@@ -2105,13 +2111,13 @@
         <v>19.437982559204102</v>
       </c>
       <c r="E3" s="1">
-        <v>19.302658081054688</v>
+        <v>19.349361419677734</v>
       </c>
       <c r="F3" s="1">
-        <v>19.302658081054688</v>
+        <v>19.349361419677734</v>
       </c>
       <c r="G3" s="1">
-        <v>18.229934692382813</v>
+        <v>18.276636123657227</v>
       </c>
       <c r="H3" s="1">
         <v>1.9832693338394165</v>
@@ -2120,13 +2126,13 @@
         <v>2.6423392295837402</v>
       </c>
       <c r="J3" s="1">
-        <v>10.083325386047363</v>
+        <v>8.4268894195556641</v>
       </c>
       <c r="K3" s="1">
         <v>1.2589941024780274</v>
       </c>
       <c r="L3" s="1">
-        <v>15.430734634399414</v>
+        <v>15.876166343688965</v>
       </c>
       <c r="M3" s="1">
         <v>0</v>
@@ -2146,13 +2152,13 @@
         <v>19.437982559204102</v>
       </c>
       <c r="E4" s="1">
-        <v>18.692916870117188</v>
+        <v>18.769155502319336</v>
       </c>
       <c r="F4" s="1">
-        <v>18.692916870117188</v>
+        <v>18.769155502319336</v>
       </c>
       <c r="G4" s="1">
-        <v>17.616117477416992</v>
+        <v>17.692358016967773</v>
       </c>
       <c r="H4" s="1">
         <v>1.9832693338394165</v>
@@ -2161,13 +2167,13 @@
         <v>3.0467653274536133</v>
       </c>
       <c r="J4" s="1">
-        <v>16.194080352783203</v>
+        <v>12.337897300720215</v>
       </c>
       <c r="K4" s="1">
         <v>2.6075263023376465</v>
       </c>
       <c r="L4" s="1">
-        <v>9.3836345672607422</v>
+        <v>9.8902740478515625</v>
       </c>
       <c r="M4" s="1">
         <v>0</v>
@@ -2187,13 +2193,13 @@
         <v>26.774463653564453</v>
       </c>
       <c r="E5" s="1">
-        <v>26.188018798828125</v>
+        <v>26.228933334350586</v>
       </c>
       <c r="F5" s="1">
-        <v>26.188018798828125</v>
+        <v>26.228933334350586</v>
       </c>
       <c r="G5" s="1">
-        <v>25.038297653198242</v>
+        <v>25.079212188720703</v>
       </c>
       <c r="H5" s="1">
         <v>2.2826457023620605</v>
@@ -2208,7 +2214,7 @@
         <v>-0.56537854671478272</v>
       </c>
       <c r="L5" s="1">
-        <v>11.207788467407227</v>
+        <v>11.522054672241211</v>
       </c>
       <c r="M5" s="1">
         <v>0</v>
@@ -2228,13 +2234,13 @@
         <v>26.774463653564453</v>
       </c>
       <c r="E6" s="1">
-        <v>25.260692596435547</v>
+        <v>25.318410873413086</v>
       </c>
       <c r="F6" s="1">
-        <v>25.260692596435547</v>
+        <v>25.318410873413086</v>
       </c>
       <c r="G6" s="1">
-        <v>24.1107177734375</v>
+        <v>24.168436050415039</v>
       </c>
       <c r="H6" s="1">
         <v>2.2826457023620605</v>
@@ -2243,13 +2249,13 @@
         <v>2.6779658794403076</v>
       </c>
       <c r="J6" s="1">
-        <v>6.9294953346252442</v>
+        <v>5.8691129684448242</v>
       </c>
       <c r="K6" s="1">
         <v>2.0267543792724609</v>
       </c>
       <c r="L6" s="1">
-        <v>8.1054286956787109</v>
+        <v>8.4469757080078125</v>
       </c>
       <c r="M6" s="1">
         <v>0</v>
@@ -2269,13 +2275,13 @@
         <v>26.774463653564453</v>
       </c>
       <c r="E7" s="1">
-        <v>24.274307250976563</v>
+        <v>24.38306999206543</v>
       </c>
       <c r="F7" s="1">
-        <v>24.274307250976563</v>
+        <v>24.38306999206543</v>
       </c>
       <c r="G7" s="1">
-        <v>23.119962692260742</v>
+        <v>23.228727340698242</v>
       </c>
       <c r="H7" s="1">
         <v>2.2826457023620605</v>
@@ -2284,13 +2290,13 @@
         <v>3.0823919773101807</v>
       </c>
       <c r="J7" s="1">
-        <v>10.788318634033203</v>
+        <v>8.3237791061401367</v>
       </c>
       <c r="K7" s="1">
         <v>4.1976490020751953</v>
       </c>
       <c r="L7" s="1">
-        <v>4.1022982597351074</v>
+        <v>4.5807633399963379</v>
       </c>
       <c r="M7" s="1">
         <v>2</v>
@@ -2310,13 +2316,13 @@
         <v>33.739055633544922</v>
       </c>
       <c r="E8" s="1">
-        <v>31.73249626159668</v>
+        <v>31.786628723144531</v>
       </c>
       <c r="F8" s="1">
-        <v>31.73249626159668</v>
+        <v>31.786628723144531</v>
       </c>
       <c r="G8" s="1">
-        <v>30.506839752197266</v>
+        <v>30.560972213745117</v>
       </c>
       <c r="H8" s="1">
         <v>2.4324369430541992</v>
@@ -2331,7 +2337,7 @@
         <v>-1.3978339433670044</v>
       </c>
       <c r="L8" s="1">
-        <v>2.8361277580261231</v>
+        <v>3.0991890430450439</v>
       </c>
       <c r="M8" s="1">
         <v>0</v>
@@ -2351,13 +2357,13 @@
         <v>33.739055633544922</v>
       </c>
       <c r="E9" s="1">
-        <v>29.312572479248047</v>
+        <v>29.427352905273438</v>
       </c>
       <c r="F9" s="1">
-        <v>29.312572479248047</v>
+        <v>29.427352905273438</v>
       </c>
       <c r="G9" s="1">
-        <v>28.086645126342774</v>
+        <v>28.201423645019531</v>
       </c>
       <c r="H9" s="1">
         <v>2.4324369430541992</v>
@@ -2366,13 +2372,13 @@
         <v>3.2127015590667725</v>
       </c>
       <c r="J9" s="1">
-        <v>8.0391464233398438</v>
+        <v>7.053370475769043</v>
       </c>
       <c r="K9" s="1">
         <v>5.0109190940856934</v>
       </c>
       <c r="L9" s="1">
-        <v>-0.2759544849395752</v>
+        <v>0.15603455901145935</v>
       </c>
       <c r="M9" s="1">
         <v>0</v>
@@ -2392,13 +2398,13 @@
         <v>33.739055633544922</v>
       </c>
       <c r="E10" s="1">
-        <v>26.87030029296875</v>
+        <v>27.080663681030273</v>
       </c>
       <c r="F10" s="1">
-        <v>26.87030029296875</v>
+        <v>27.080663681030273</v>
       </c>
       <c r="G10" s="1">
-        <v>25.639717102050781</v>
+        <v>25.850080490112305</v>
       </c>
       <c r="H10" s="1">
         <v>2.4324369430541992</v>
@@ -2407,13 +2413,13 @@
         <v>3.6171276569366455</v>
       </c>
       <c r="J10" s="1">
-        <v>11.396491050720215</v>
+        <v>9.1396102905273438</v>
       </c>
       <c r="K10" s="1">
         <v>10.378209114074707</v>
       </c>
       <c r="L10" s="1">
-        <v>-4.2748856544494629</v>
+        <v>-3.5775794982910156</v>
       </c>
       <c r="M10" s="1">
         <v>2</v>
@@ -2433,13 +2439,13 @@
         <v>20.997871398925781</v>
       </c>
       <c r="E11" s="1">
-        <v>20.007450103759766</v>
+        <v>20.052921295166016</v>
       </c>
       <c r="F11" s="1">
-        <v>20.007450103759766</v>
+        <v>20.052921295166016</v>
       </c>
       <c r="G11" s="1">
-        <v>18.575643539428711</v>
+        <v>18.621114730834961</v>
       </c>
       <c r="H11" s="1">
         <v>4.6891798973083496</v>
@@ -2454,7 +2460,7 @@
         <v>-1.1965206861495972</v>
       </c>
       <c r="L11" s="1">
-        <v>5.2938055992126465</v>
+        <v>5.7105202674865723</v>
       </c>
       <c r="M11" s="1">
         <v>0</v>
@@ -2474,13 +2480,13 @@
         <v>20.997871398925781</v>
       </c>
       <c r="E12" s="1">
-        <v>18.249076843261719</v>
+        <v>18.437797546386719</v>
       </c>
       <c r="F12" s="1">
-        <v>18.249076843261719</v>
+        <v>18.437797546386719</v>
       </c>
       <c r="G12" s="1">
-        <v>16.816951751708984</v>
+        <v>17.005672454833984</v>
       </c>
       <c r="H12" s="1">
         <v>4.6891798973083496</v>
@@ -2489,13 +2495,13 @@
         <v>3.9312069416046143</v>
       </c>
       <c r="J12" s="1">
-        <v>11.531002998352051</v>
+        <v>9.3541927337646484</v>
       </c>
       <c r="K12" s="1">
         <v>4.2892565727233887</v>
       </c>
       <c r="L12" s="1">
-        <v>-1.1211901903152466</v>
+        <v>0.072676762938499451</v>
       </c>
       <c r="M12" s="1">
         <v>0</v>
@@ -2515,13 +2521,13 @@
         <v>20.997871398925781</v>
       </c>
       <c r="E13" s="1">
-        <v>16.181604385375977</v>
+        <v>16.628829956054688</v>
       </c>
       <c r="F13" s="1">
-        <v>16.181604385375977</v>
+        <v>16.628829956054688</v>
       </c>
       <c r="G13" s="1">
-        <v>14.744041442871094</v>
+        <v>15.191267013549805</v>
       </c>
       <c r="H13" s="1">
         <v>4.6891798973083496</v>
@@ -2530,13 +2536,13 @@
         <v>4.3356328010559082</v>
       </c>
       <c r="J13" s="1">
-        <v>18.640840530395508</v>
+        <v>13.726461410522461</v>
       </c>
       <c r="K13" s="1">
         <v>8.8835592269897461</v>
       </c>
       <c r="L13" s="1">
-        <v>-9.3604249954223633</v>
+        <v>-7.0278525352478027</v>
       </c>
       <c r="M13" s="1">
         <v>0</v>
@@ -2556,13 +2562,13 @@
         <v>25.186426162719727</v>
       </c>
       <c r="E14" s="1">
-        <v>24.52734375</v>
+        <v>24.573089599609375</v>
       </c>
       <c r="F14" s="1">
-        <v>24.52734375</v>
+        <v>24.573089599609375</v>
       </c>
       <c r="G14" s="1">
-        <v>23.345138549804688</v>
+        <v>23.39088249206543</v>
       </c>
       <c r="H14" s="1">
         <v>2.0056905746459961</v>
@@ -2577,7 +2583,7 @@
         <v>-0.52895146608352661</v>
       </c>
       <c r="L14" s="1">
-        <v>10.206048965454102</v>
+        <v>10.599246978759766</v>
       </c>
       <c r="M14" s="1">
         <v>0</v>
@@ -2597,13 +2603,13 @@
         <v>25.186426162719727</v>
       </c>
       <c r="E15" s="1">
-        <v>23.7139892578125</v>
+        <v>23.781251907348633</v>
       </c>
       <c r="F15" s="1">
-        <v>23.7139892578125</v>
+        <v>23.781251907348633</v>
       </c>
       <c r="G15" s="1">
-        <v>22.531518936157227</v>
+        <v>22.598781585693359</v>
       </c>
       <c r="H15" s="1">
         <v>2.0056905746459961</v>
@@ -2612,13 +2618,13 @@
         <v>2.89040207862854</v>
       </c>
       <c r="J15" s="1">
-        <v>9.1292171478271484</v>
+        <v>7.7649846076965332</v>
       </c>
       <c r="K15" s="1">
         <v>1.8961714506149292</v>
       </c>
       <c r="L15" s="1">
-        <v>6.2713603973388672</v>
+        <v>6.7154746055603027</v>
       </c>
       <c r="M15" s="1">
         <v>0</v>
@@ -2638,13 +2644,13 @@
         <v>25.186426162719727</v>
       </c>
       <c r="E16" s="1">
-        <v>22.683252334594727</v>
+        <v>22.814777374267578</v>
       </c>
       <c r="F16" s="1">
-        <v>22.683252334594727</v>
+        <v>22.814777374267578</v>
       </c>
       <c r="G16" s="1">
-        <v>21.496292114257813</v>
+        <v>21.627817153930664</v>
       </c>
       <c r="H16" s="1">
         <v>2.0056905746459961</v>
@@ -2653,13 +2659,13 @@
         <v>3.294827938079834</v>
       </c>
       <c r="J16" s="1">
-        <v>14.085872650146484</v>
+        <v>10.934903144836426</v>
       </c>
       <c r="K16" s="1">
         <v>3.9271962642669678</v>
       </c>
       <c r="L16" s="1">
-        <v>1.1666896343231201</v>
+        <v>1.7954444885253906</v>
       </c>
       <c r="M16" s="1">
         <v>0</v>
@@ -2679,13 +2685,13 @@
         <v>21.000280380249024</v>
       </c>
       <c r="E17" s="1">
-        <v>21.391849517822266</v>
+        <v>21.43501091003418</v>
       </c>
       <c r="F17" s="1">
         <v>21.087326049804688</v>
       </c>
       <c r="G17" s="1">
-        <v>20.355043411254883</v>
+        <v>20.398204803466797</v>
       </c>
       <c r="H17" s="1">
         <v>1.8732786178588867</v>
@@ -2700,7 +2706,7 @@
         <v>-0.25997251272201538</v>
       </c>
       <c r="L17" s="1">
-        <v>20.448823928833008</v>
+        <v>20.893764495849609</v>
       </c>
       <c r="M17" s="1">
         <v>0</v>
@@ -2720,13 +2726,13 @@
         <v>21.000280380249024</v>
       </c>
       <c r="E18" s="1">
-        <v>20.995651245117188</v>
+        <v>21.023605346679688</v>
       </c>
       <c r="F18" s="1">
-        <v>20.995651245117188</v>
+        <v>21.023605346679688</v>
       </c>
       <c r="G18" s="1">
-        <v>19.958614349365234</v>
+        <v>19.986568450927734</v>
       </c>
       <c r="H18" s="1">
         <v>1.8732786178588867</v>
@@ -2735,13 +2741,13 @@
         <v>2.4145216941833496</v>
       </c>
       <c r="J18" s="1">
-        <v>7.973358154296875</v>
+        <v>6.6617794036865234</v>
       </c>
       <c r="K18" s="1">
         <v>0.93194276094436646</v>
       </c>
       <c r="L18" s="1">
-        <v>16.672637939453125</v>
+        <v>16.960758209228516</v>
       </c>
       <c r="M18" s="1">
         <v>0</v>
@@ -2761,13 +2767,13 @@
         <v>21.000280380249024</v>
       </c>
       <c r="E19" s="1">
-        <v>20.556858062744141</v>
+        <v>20.588703155517578</v>
       </c>
       <c r="F19" s="1">
-        <v>20.556858062744141</v>
+        <v>20.588703155517578</v>
       </c>
       <c r="G19" s="1">
-        <v>19.515880584716797</v>
+        <v>19.5477294921875</v>
       </c>
       <c r="H19" s="1">
         <v>1.8732786178588867</v>
@@ -2776,13 +2782,13 @@
         <v>2.8189475536346436</v>
       </c>
       <c r="J19" s="1">
-        <v>12.920832633972168</v>
+        <v>9.8408060073852539</v>
       </c>
       <c r="K19" s="1">
         <v>1.930164098739624</v>
       </c>
       <c r="L19" s="1">
-        <v>11.900041580200195</v>
+        <v>12.130273818969727</v>
       </c>
       <c r="M19" s="1">
         <v>0</v>
@@ -2870,22 +2876,22 @@
         <v>15.258353233337402</v>
       </c>
       <c r="E2" s="1">
-        <v>13.888388633728027</v>
+        <v>13.953507423400879</v>
       </c>
       <c r="F2" s="1">
-        <v>8.6847171783447266</v>
+        <v>8.9468879699707031</v>
       </c>
       <c r="G2" s="1">
-        <v>3.8185718059539795</v>
+        <v>4.332122802734375</v>
       </c>
       <c r="H2" s="1">
-        <v>13.888388633728027</v>
+        <v>13.953507423400879</v>
       </c>
       <c r="I2" s="1">
-        <v>8.6847171783447266</v>
+        <v>8.9468879699707031</v>
       </c>
       <c r="J2" s="1">
-        <v>3.8185718059539795</v>
+        <v>4.332122802734375</v>
       </c>
       <c r="K2" s="1">
         <v>4.110689640045166</v>
@@ -2900,10 +2906,10 @@
         <v>10.841164588928223</v>
       </c>
       <c r="O2" s="1">
-        <v>17.671440124511719</v>
+        <v>15.048938751220703</v>
       </c>
       <c r="P2" s="1">
-        <v>26.379657745361328</v>
+        <v>20.47364616394043</v>
       </c>
       <c r="Q2" s="1">
         <v>-6.1849474906921387</v>
@@ -2929,22 +2935,22 @@
         <v>14.531709671020508</v>
       </c>
       <c r="E3" s="1">
-        <v>14.748130798339844</v>
+        <v>14.789926528930664</v>
       </c>
       <c r="F3" s="1">
-        <v>9.4534473419189453</v>
+        <v>9.5582170486450195</v>
       </c>
       <c r="G3" s="1">
-        <v>4.341585636138916</v>
+        <v>4.5139832496643066</v>
       </c>
       <c r="H3" s="1">
         <v>14.441656112670898</v>
       </c>
       <c r="I3" s="1">
-        <v>9.4534473419189453</v>
+        <v>9.5582170486450195</v>
       </c>
       <c r="J3" s="1">
-        <v>4.341585636138916</v>
+        <v>4.5139832496643066</v>
       </c>
       <c r="K3" s="1">
         <v>2.7762997150421143</v>
@@ -2959,10 +2965,10 @@
         <v>0.87802988290786743</v>
       </c>
       <c r="O3" s="1">
-        <v>6.9505338668823242</v>
+        <v>4.6583266258239746</v>
       </c>
       <c r="P3" s="1">
-        <v>15.192225456237793</v>
+        <v>9.8767995834350586</v>
       </c>
       <c r="Q3" s="1">
         <v>-7.7250099182128906</v>
@@ -2985,52 +2991,52 @@
         <v>0</v>
       </c>
       <c r="D4" s="1">
-        <v>16.995023727416992</v>
+        <v>11.067777633666992</v>
       </c>
       <c r="E4" s="1">
-        <v>14.499282836914063</v>
+        <v>10.273059844970703</v>
       </c>
       <c r="F4" s="1">
-        <v>11.541708946228027</v>
+        <v>9.6659345626831055</v>
       </c>
       <c r="G4" s="1">
-        <v>8.3242111206054688</v>
+        <v>8.7613296508789063</v>
       </c>
       <c r="H4" s="1">
-        <v>14.499282836914063</v>
+        <v>10.273059844970703</v>
       </c>
       <c r="I4" s="1">
-        <v>11.541708946228027</v>
+        <v>9.6659345626831055</v>
       </c>
       <c r="J4" s="1">
-        <v>8.3242111206054688</v>
+        <v>8.7613296508789063</v>
       </c>
       <c r="K4" s="1">
-        <v>9.7105236053466797</v>
+        <v>4.0069994926452637</v>
       </c>
       <c r="L4" s="1">
-        <v>107.99939727783203</v>
+        <v>0</v>
       </c>
       <c r="M4" s="1">
         <v>0</v>
       </c>
       <c r="N4" s="1">
-        <v>2.5873517990112305</v>
+        <v>2.3124582767486572</v>
       </c>
       <c r="O4" s="1">
-        <v>16.237209320068359</v>
+        <v>6.5004057884216309</v>
       </c>
       <c r="P4" s="1">
-        <v>32.544410705566406</v>
+        <v>12.252050399780273</v>
       </c>
       <c r="Q4" s="1">
-        <v>-1.1151782274246216</v>
+        <v>0</v>
       </c>
       <c r="R4" s="1">
-        <v>3.9976620674133301</v>
+        <v>0</v>
       </c>
       <c r="S4" s="1">
-        <v>8.279632568359375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -3044,52 +3050,52 @@
         <v>0</v>
       </c>
       <c r="D5" s="1">
-        <v>11.067777633666992</v>
+        <v>16.995023727416992</v>
       </c>
       <c r="E5" s="1">
-        <v>10.247744560241699</v>
+        <v>14.599208831787109</v>
       </c>
       <c r="F5" s="1">
-        <v>9.4956283569335938</v>
+        <v>12.234023094177246</v>
       </c>
       <c r="G5" s="1">
-        <v>8.4508266448974609</v>
+        <v>9.7104988098144531</v>
       </c>
       <c r="H5" s="1">
-        <v>10.247744560241699</v>
+        <v>14.599208831787109</v>
       </c>
       <c r="I5" s="1">
-        <v>9.4956283569335938</v>
+        <v>12.234023094177246</v>
       </c>
       <c r="J5" s="1">
-        <v>8.4508266448974609</v>
+        <v>9.7104988098144531</v>
       </c>
       <c r="K5" s="1">
-        <v>4.0069994926452637</v>
+        <v>9.7105236053466797</v>
       </c>
       <c r="L5" s="1">
-        <v>0</v>
+        <v>107.99939727783203</v>
       </c>
       <c r="M5" s="1">
         <v>0</v>
       </c>
       <c r="N5" s="1">
-        <v>2.3124582767486572</v>
+        <v>2.5873517990112305</v>
       </c>
       <c r="O5" s="1">
-        <v>9.2142171859741211</v>
+        <v>10.777472496032715</v>
       </c>
       <c r="P5" s="1">
-        <v>18.406246185302734</v>
+        <v>20.612627029418945</v>
       </c>
       <c r="Q5" s="1">
-        <v>0</v>
+        <v>-1.1151782274246216</v>
       </c>
       <c r="R5" s="1">
-        <v>0</v>
+        <v>3.9976620674133301</v>
       </c>
       <c r="S5" s="1">
-        <v>0</v>
+        <v>8.279632568359375</v>
       </c>
     </row>
     <row r="6">
@@ -3097,58 +3103,58 @@
         <v>51</v>
       </c>
       <c r="B6" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="1">
         <v>0</v>
       </c>
       <c r="D6" s="1">
-        <v>18.721660614013672</v>
+        <v>23.036062240600586</v>
       </c>
       <c r="E6" s="1">
-        <v>18.567167282104492</v>
+        <v>24.048755645751953</v>
       </c>
       <c r="F6" s="1">
-        <v>16.099763870239258</v>
+        <v>18.155899047851563</v>
       </c>
       <c r="G6" s="1">
-        <v>13.072973251342773</v>
+        <v>13.120973587036133</v>
       </c>
       <c r="H6" s="1">
-        <v>18.48286247253418</v>
+        <v>23.208763122558594</v>
       </c>
       <c r="I6" s="1">
-        <v>16.099763870239258</v>
+        <v>18.155899047851563</v>
       </c>
       <c r="J6" s="1">
-        <v>13.072973251342773</v>
+        <v>13.120973587036133</v>
       </c>
       <c r="K6" s="1">
-        <v>5.2122688293457031</v>
+        <v>0.52955126762390137</v>
       </c>
       <c r="L6" s="1">
-        <v>278.64407348632813</v>
+        <v>557.02593994140625</v>
       </c>
       <c r="M6" s="1">
         <v>0</v>
       </c>
       <c r="N6" s="1">
-        <v>6.6135783195495605</v>
+        <v>1.100072979927063</v>
       </c>
       <c r="O6" s="1">
-        <v>13.194785118103027</v>
+        <v>2.4174280166625977</v>
       </c>
       <c r="P6" s="1">
-        <v>21.753849029541016</v>
+        <v>4.3831706047058106</v>
       </c>
       <c r="Q6" s="1">
-        <v>-2.8772175312042236</v>
+        <v>-5.7517280578613281</v>
       </c>
       <c r="R6" s="1">
-        <v>10.314175605773926</v>
+        <v>20.618646621704102</v>
       </c>
       <c r="S6" s="1">
-        <v>21.361883163452148</v>
+        <v>42.703670501708984</v>
       </c>
     </row>
     <row r="7">
@@ -3162,52 +3168,52 @@
         <v>0</v>
       </c>
       <c r="D7" s="1">
-        <v>23.036062240600586</v>
+        <v>17.446327209472656</v>
       </c>
       <c r="E7" s="1">
-        <v>24.004234313964844</v>
+        <v>14.568453788757324</v>
       </c>
       <c r="F7" s="1">
-        <v>18.185268402099609</v>
+        <v>14.019899368286133</v>
       </c>
       <c r="G7" s="1">
-        <v>13.221207618713379</v>
+        <v>13.375641822814941</v>
       </c>
       <c r="H7" s="1">
-        <v>23.208763122558594</v>
+        <v>14.568453788757324</v>
       </c>
       <c r="I7" s="1">
-        <v>18.185268402099609</v>
+        <v>14.019899368286133</v>
       </c>
       <c r="J7" s="1">
-        <v>13.221207618713379</v>
+        <v>13.375641822814941</v>
       </c>
       <c r="K7" s="1">
-        <v>0.52955126762390137</v>
+        <v>2.846287727355957</v>
       </c>
       <c r="L7" s="1">
-        <v>557.02593994140625</v>
+        <v>0</v>
       </c>
       <c r="M7" s="1">
         <v>0</v>
       </c>
       <c r="N7" s="1">
-        <v>1.100072979927063</v>
+        <v>0</v>
       </c>
       <c r="O7" s="1">
-        <v>2.9496452808380127</v>
+        <v>3.2099995613098145</v>
       </c>
       <c r="P7" s="1">
-        <v>5.8247413635253906</v>
+        <v>7.2772231101989746</v>
       </c>
       <c r="Q7" s="1">
-        <v>-5.7517280578613281</v>
+        <v>0</v>
       </c>
       <c r="R7" s="1">
-        <v>20.618646621704102</v>
+        <v>0</v>
       </c>
       <c r="S7" s="1">
-        <v>42.703670501708984</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3215,58 +3221,58 @@
         <v>53</v>
       </c>
       <c r="B8" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="1">
         <v>0</v>
       </c>
       <c r="D8" s="1">
-        <v>17.446327209472656</v>
+        <v>18.721660614013672</v>
       </c>
       <c r="E8" s="1">
-        <v>14.429388999938965</v>
+        <v>18.6204833984375</v>
       </c>
       <c r="F8" s="1">
-        <v>13.904655456542969</v>
+        <v>16.189268112182617</v>
       </c>
       <c r="G8" s="1">
-        <v>13.278882026672363</v>
+        <v>13.445269584655762</v>
       </c>
       <c r="H8" s="1">
-        <v>14.429388999938965</v>
+        <v>18.48286247253418</v>
       </c>
       <c r="I8" s="1">
-        <v>13.904655456542969</v>
+        <v>16.189268112182617</v>
       </c>
       <c r="J8" s="1">
-        <v>13.278882026672363</v>
+        <v>13.445269584655762</v>
       </c>
       <c r="K8" s="1">
-        <v>2.846287727355957</v>
+        <v>5.2122688293457031</v>
       </c>
       <c r="L8" s="1">
-        <v>0</v>
+        <v>278.64407348632813</v>
       </c>
       <c r="M8" s="1">
         <v>0</v>
       </c>
       <c r="N8" s="1">
-        <v>0</v>
+        <v>6.6135783195495605</v>
       </c>
       <c r="O8" s="1">
-        <v>5.3499994277954102</v>
+        <v>10.562674522399902</v>
       </c>
       <c r="P8" s="1">
-        <v>12.128705024719238</v>
+        <v>15.713345527648926</v>
       </c>
       <c r="Q8" s="1">
-        <v>0</v>
+        <v>-2.8772175312042236</v>
       </c>
       <c r="R8" s="1">
-        <v>0</v>
+        <v>10.314175605773926</v>
       </c>
       <c r="S8" s="1">
-        <v>0</v>
+        <v>21.361883163452148</v>
       </c>
     </row>
     <row r="9">
@@ -3277,55 +3283,55 @@
         <v>3</v>
       </c>
       <c r="C9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="1">
-        <v>20.045049667358399</v>
+        <v>24.320249557495117</v>
       </c>
       <c r="E9" s="1">
-        <v>19.551990509033203</v>
+        <v>23.969804763793945</v>
       </c>
       <c r="F9" s="1">
-        <v>18.191621780395508</v>
+        <v>19.696483612060547</v>
       </c>
       <c r="G9" s="1">
-        <v>15.442683219909668</v>
+        <v>15.744843482971191</v>
       </c>
       <c r="H9" s="1">
-        <v>19.551990509033203</v>
+        <v>23.939676284790039</v>
       </c>
       <c r="I9" s="1">
-        <v>18.191621780395508</v>
+        <v>19.696483612060547</v>
       </c>
       <c r="J9" s="1">
-        <v>15.442683219909668</v>
+        <v>15.744843482971191</v>
       </c>
       <c r="K9" s="1">
-        <v>2.9860866069793701</v>
+        <v>2.0872793197631836</v>
       </c>
       <c r="L9" s="1">
-        <v>68.826248168945313</v>
+        <v>372.96136474609375</v>
       </c>
       <c r="M9" s="1">
         <v>0</v>
       </c>
       <c r="N9" s="1">
-        <v>9.7155628204345703</v>
+        <v>1.9466069936752319</v>
       </c>
       <c r="O9" s="1">
-        <v>20.671564102172852</v>
+        <v>4.3342394828796387</v>
       </c>
       <c r="P9" s="1">
-        <v>34.281124114990234</v>
+        <v>7.2991957664489746</v>
       </c>
       <c r="Q9" s="1">
-        <v>-0.71068477630615234</v>
+        <v>-3.8511176109313965</v>
       </c>
       <c r="R9" s="1">
-        <v>2.5476441383361817</v>
+        <v>13.805386543273926</v>
       </c>
       <c r="S9" s="1">
-        <v>5.2764739990234375</v>
+        <v>28.592596054077149</v>
       </c>
     </row>
     <row r="10">
@@ -3333,58 +3339,58 @@
         <v>55</v>
       </c>
       <c r="B10" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" s="1">
         <v>0</v>
       </c>
       <c r="D10" s="1">
-        <v>24.320249557495117</v>
+        <v>20.894319534301758</v>
       </c>
       <c r="E10" s="1">
-        <v>23.930278778076172</v>
+        <v>20.035505294799805</v>
       </c>
       <c r="F10" s="1">
-        <v>19.647172927856445</v>
+        <v>18.20323371887207</v>
       </c>
       <c r="G10" s="1">
-        <v>15.585298538208008</v>
+        <v>16.038419723510742</v>
       </c>
       <c r="H10" s="1">
-        <v>23.930278778076172</v>
+        <v>20.035505294799805</v>
       </c>
       <c r="I10" s="1">
-        <v>19.647172927856445</v>
+        <v>18.20323371887207</v>
       </c>
       <c r="J10" s="1">
-        <v>15.585298538208008</v>
+        <v>16.038419723510742</v>
       </c>
       <c r="K10" s="1">
-        <v>2.0872793197631836</v>
+        <v>3.036236047744751</v>
       </c>
       <c r="L10" s="1">
-        <v>372.96136474609375</v>
+        <v>164.36265563964844</v>
       </c>
       <c r="M10" s="1">
         <v>0</v>
       </c>
       <c r="N10" s="1">
-        <v>1.9466069936752319</v>
+        <v>0.26833945512771606</v>
       </c>
       <c r="O10" s="1">
-        <v>5.6418848037719727</v>
+        <v>3.311276912689209</v>
       </c>
       <c r="P10" s="1">
-        <v>10.294215202331543</v>
+        <v>7.225557804107666</v>
       </c>
       <c r="Q10" s="1">
-        <v>-3.8511176109313965</v>
+        <v>-1.6971728801727295</v>
       </c>
       <c r="R10" s="1">
-        <v>13.805386543273926</v>
+        <v>6.0839815139770508</v>
       </c>
       <c r="S10" s="1">
-        <v>28.592596054077149</v>
+        <v>12.600648880004883</v>
       </c>
     </row>
     <row r="11">
@@ -3392,58 +3398,58 @@
         <v>56</v>
       </c>
       <c r="B11" s="1">
+        <v>3</v>
+      </c>
+      <c r="C11" s="1">
         <v>1</v>
       </c>
-      <c r="C11" s="1">
-        <v>0</v>
-      </c>
       <c r="D11" s="1">
-        <v>20.894319534301758</v>
+        <v>20.045049667358399</v>
       </c>
       <c r="E11" s="1">
-        <v>20.004240036010742</v>
+        <v>19.632438659667969</v>
       </c>
       <c r="F11" s="1">
-        <v>18.007610321044922</v>
+        <v>18.51762580871582</v>
       </c>
       <c r="G11" s="1">
-        <v>15.638980865478516</v>
+        <v>16.054164886474609</v>
       </c>
       <c r="H11" s="1">
-        <v>20.004240036010742</v>
+        <v>19.632438659667969</v>
       </c>
       <c r="I11" s="1">
-        <v>18.007610321044922</v>
+        <v>18.51762580871582</v>
       </c>
       <c r="J11" s="1">
-        <v>15.638980865478516</v>
+        <v>16.054164886474609</v>
       </c>
       <c r="K11" s="1">
-        <v>3.036236047744751</v>
+        <v>2.9860866069793701</v>
       </c>
       <c r="L11" s="1">
-        <v>164.36265563964844</v>
+        <v>68.826248168945313</v>
       </c>
       <c r="M11" s="1">
         <v>0</v>
       </c>
       <c r="N11" s="1">
-        <v>0.26833945512771606</v>
+        <v>9.7155628204345703</v>
       </c>
       <c r="O11" s="1">
-        <v>5.1909928321838379</v>
+        <v>16.716278076171875</v>
       </c>
       <c r="P11" s="1">
-        <v>11.427026748657227</v>
+        <v>25.319673538208008</v>
       </c>
       <c r="Q11" s="1">
-        <v>-1.6971728801727295</v>
+        <v>-0.71068477630615234</v>
       </c>
       <c r="R11" s="1">
-        <v>6.0839815139770508</v>
+        <v>2.5476441383361817</v>
       </c>
       <c r="S11" s="1">
-        <v>12.600648880004883</v>
+        <v>5.2764739990234375</v>
       </c>
     </row>
     <row r="12">
@@ -3451,58 +3457,58 @@
         <v>57</v>
       </c>
       <c r="B12" s="1">
+        <v>4</v>
+      </c>
+      <c r="C12" s="1">
         <v>1</v>
       </c>
-      <c r="C12" s="1">
-        <v>0</v>
-      </c>
       <c r="D12" s="1">
-        <v>30.1993408203125</v>
+        <v>18.293428421020508</v>
       </c>
       <c r="E12" s="1">
-        <v>22.156579971313477</v>
+        <v>18.047218322753906</v>
       </c>
       <c r="F12" s="1">
-        <v>19.556190490722656</v>
+        <v>17.652900695800781</v>
       </c>
       <c r="G12" s="1">
-        <v>16.95014762878418</v>
+        <v>17.145034790039063</v>
       </c>
       <c r="H12" s="1">
-        <v>22.156579971313477</v>
+        <v>18.047218322753906</v>
       </c>
       <c r="I12" s="1">
-        <v>19.556190490722656</v>
+        <v>17.652900695800781</v>
       </c>
       <c r="J12" s="1">
-        <v>16.95014762878418</v>
+        <v>17.145034790039063</v>
       </c>
       <c r="K12" s="1">
-        <v>2.441215991973877</v>
+        <v>1.9084329605102539</v>
       </c>
       <c r="L12" s="1">
-        <v>104.05338287353516</v>
+        <v>20.314830780029297</v>
       </c>
       <c r="M12" s="1">
         <v>0</v>
       </c>
       <c r="N12" s="1">
-        <v>0</v>
+        <v>3.6911745071411133</v>
       </c>
       <c r="O12" s="1">
-        <v>2.4699621200561523</v>
+        <v>6.7656407356262207</v>
       </c>
       <c r="P12" s="1">
-        <v>5.5606765747070313</v>
+        <v>10.635995864868164</v>
       </c>
       <c r="Q12" s="1">
-        <v>-1.0744326114654541</v>
+        <v>-0.20976652204990387</v>
       </c>
       <c r="R12" s="1">
-        <v>3.851597785949707</v>
+        <v>0.75196552276611328</v>
       </c>
       <c r="S12" s="1">
-        <v>7.9771161079406738</v>
+        <v>1.5574100017547607</v>
       </c>
     </row>
     <row r="13">
@@ -3516,52 +3522,52 @@
         <v>1</v>
       </c>
       <c r="D13" s="1">
-        <v>18.293428421020508</v>
+        <v>17.884822845458984</v>
       </c>
       <c r="E13" s="1">
-        <v>18.007177352905274</v>
+        <v>18.472982406616211</v>
       </c>
       <c r="F13" s="1">
-        <v>17.611238479614258</v>
+        <v>17.983821868896484</v>
       </c>
       <c r="G13" s="1">
-        <v>17.030733108520508</v>
+        <v>17.501615524291992</v>
       </c>
       <c r="H13" s="1">
-        <v>18.007177352905274</v>
+        <v>18.007511138916016</v>
       </c>
       <c r="I13" s="1">
-        <v>17.611238479614258</v>
+        <v>17.958602905273438</v>
       </c>
       <c r="J13" s="1">
-        <v>17.030733108520508</v>
+        <v>17.501615524291992</v>
       </c>
       <c r="K13" s="1">
-        <v>1.9084329605102539</v>
+        <v>0.99057501554489136</v>
       </c>
       <c r="L13" s="1">
-        <v>20.314830780029297</v>
+        <v>53.776096343994141</v>
       </c>
       <c r="M13" s="1">
         <v>0</v>
       </c>
       <c r="N13" s="1">
-        <v>3.6911745071411133</v>
+        <v>2.4085962772369385</v>
       </c>
       <c r="O13" s="1">
-        <v>8.4010066986083984</v>
+        <v>5.2269372940063477</v>
       </c>
       <c r="P13" s="1">
-        <v>14.431048393249512</v>
+        <v>8.8422298431396484</v>
       </c>
       <c r="Q13" s="1">
-        <v>-0.20976652204990387</v>
+        <v>-0.55528020858764648</v>
       </c>
       <c r="R13" s="1">
-        <v>0.75196552276611328</v>
+        <v>1.9905540943145752</v>
       </c>
       <c r="S13" s="1">
-        <v>1.5574100017547607</v>
+        <v>4.1226739883422852</v>
       </c>
     </row>
     <row r="14">
@@ -3569,58 +3575,58 @@
         <v>59</v>
       </c>
       <c r="B14" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="1">
-        <v>17.884822845458984</v>
+        <v>30.1993408203125</v>
       </c>
       <c r="E14" s="1">
-        <v>18.427993774414063</v>
+        <v>22.168155670166016</v>
       </c>
       <c r="F14" s="1">
-        <v>17.966167449951172</v>
+        <v>19.812767028808594</v>
       </c>
       <c r="G14" s="1">
-        <v>17.505853652954102</v>
+        <v>17.515897750854492</v>
       </c>
       <c r="H14" s="1">
-        <v>18.007511138916016</v>
+        <v>22.168155670166016</v>
       </c>
       <c r="I14" s="1">
-        <v>17.953563690185547</v>
+        <v>19.812767028808594</v>
       </c>
       <c r="J14" s="1">
-        <v>17.505853652954102</v>
+        <v>17.515897750854492</v>
       </c>
       <c r="K14" s="1">
-        <v>0.99057501554489136</v>
+        <v>2.441215991973877</v>
       </c>
       <c r="L14" s="1">
-        <v>53.776096343994141</v>
+        <v>104.05338287353516</v>
       </c>
       <c r="M14" s="1">
         <v>0</v>
       </c>
       <c r="N14" s="1">
-        <v>2.4085962772369385</v>
+        <v>0</v>
       </c>
       <c r="O14" s="1">
-        <v>6.6539797782897949</v>
+        <v>1.481977105140686</v>
       </c>
       <c r="P14" s="1">
-        <v>12.218425750732422</v>
+        <v>3.3364059925079346</v>
       </c>
       <c r="Q14" s="1">
-        <v>-0.55528020858764648</v>
+        <v>-1.0744326114654541</v>
       </c>
       <c r="R14" s="1">
-        <v>1.9905540943145752</v>
+        <v>3.851597785949707</v>
       </c>
       <c r="S14" s="1">
-        <v>4.1226739883422852</v>
+        <v>7.9771161079406738</v>
       </c>
     </row>
     <row r="15">
@@ -3637,22 +3643,22 @@
         <v>23.573837280273438</v>
       </c>
       <c r="E15" s="1">
-        <v>22.539394378662109</v>
+        <v>22.581605911254883</v>
       </c>
       <c r="F15" s="1">
-        <v>20.394044876098633</v>
+        <v>20.625648498535156</v>
       </c>
       <c r="G15" s="1">
-        <v>17.554388046264649</v>
+        <v>17.981990814208984</v>
       </c>
       <c r="H15" s="1">
-        <v>22.539394378662109</v>
+        <v>22.581605911254883</v>
       </c>
       <c r="I15" s="1">
-        <v>20.394044876098633</v>
+        <v>20.625648498535156</v>
       </c>
       <c r="J15" s="1">
-        <v>17.554388046264649</v>
+        <v>17.981990814208984</v>
       </c>
       <c r="K15" s="1">
         <v>3.2154037952423096</v>
@@ -3667,10 +3673,10 @@
         <v>1.6507298946380615</v>
       </c>
       <c r="O15" s="1">
-        <v>7.0251946449279785</v>
+        <v>5.0641231536865234</v>
       </c>
       <c r="P15" s="1">
-        <v>13.618130683898926</v>
+        <v>9.2124223709106445</v>
       </c>
       <c r="Q15" s="1">
         <v>-1.8186583518981934</v>
@@ -3696,22 +3702,22 @@
         <v>28.380533218383789</v>
       </c>
       <c r="E16" s="1">
-        <v>28.232702255249024</v>
+        <v>28.277248382568359</v>
       </c>
       <c r="F16" s="1">
-        <v>22.998754501342774</v>
+        <v>23.010080337524414</v>
       </c>
       <c r="G16" s="1">
-        <v>18.456802368164063</v>
+        <v>18.461458206176758</v>
       </c>
       <c r="H16" s="1">
         <v>28.072620391845703</v>
       </c>
       <c r="I16" s="1">
-        <v>22.998754501342774</v>
+        <v>23.010080337524414</v>
       </c>
       <c r="J16" s="1">
-        <v>18.456802368164063</v>
+        <v>18.461458206176758</v>
       </c>
       <c r="K16" s="1">
         <v>0.76714533567428589</v>
@@ -3726,10 +3732,10 @@
         <v>14.127007484436035</v>
       </c>
       <c r="O16" s="1">
-        <v>16.628742218017578</v>
+        <v>15.798462867736816</v>
       </c>
       <c r="P16" s="1">
-        <v>19.909807205200195</v>
+        <v>17.930709838867188</v>
       </c>
       <c r="Q16" s="1">
         <v>-4.1387767791748047</v>
@@ -3755,22 +3761,22 @@
         <v>20.405284881591797</v>
       </c>
       <c r="E17" s="1">
-        <v>20.537343978881836</v>
+        <v>20.588369369506836</v>
       </c>
       <c r="F17" s="1">
-        <v>19.829217910766602</v>
+        <v>19.912443161010742</v>
       </c>
       <c r="G17" s="1">
-        <v>18.793422698974609</v>
+        <v>19.057771682739258</v>
       </c>
       <c r="H17" s="1">
         <v>20.414770126342774</v>
       </c>
       <c r="I17" s="1">
-        <v>19.829217910766602</v>
+        <v>19.912443161010742</v>
       </c>
       <c r="J17" s="1">
-        <v>18.793422698974609</v>
+        <v>19.057771682739258</v>
       </c>
       <c r="K17" s="1">
         <v>1.8116350173950195</v>
@@ -3785,10 +3791,10 @@
         <v>4.443941593170166</v>
       </c>
       <c r="O17" s="1">
-        <v>10.871476173400879</v>
+        <v>8.5933599472045899</v>
       </c>
       <c r="P17" s="1">
-        <v>18.936885833740234</v>
+        <v>13.72999382019043</v>
       </c>
       <c r="Q17" s="1">
         <v>-0.51077693700790405</v>
@@ -3814,22 +3820,22 @@
         <v>23.414220809936524</v>
       </c>
       <c r="E18" s="1">
-        <v>22.591592788696289</v>
+        <v>22.605495452880859</v>
       </c>
       <c r="F18" s="1">
-        <v>20.841276168823242</v>
+        <v>20.910068511962891</v>
       </c>
       <c r="G18" s="1">
-        <v>18.808174133300781</v>
+        <v>19.124574661254883</v>
       </c>
       <c r="H18" s="1">
-        <v>22.591592788696289</v>
+        <v>22.605495452880859</v>
       </c>
       <c r="I18" s="1">
-        <v>20.841276168823242</v>
+        <v>20.910068511962891</v>
       </c>
       <c r="J18" s="1">
-        <v>18.808174133300781</v>
+        <v>19.124574661254883</v>
       </c>
       <c r="K18" s="1">
         <v>2.153038501739502</v>
@@ -3844,10 +3850,10 @@
         <v>0</v>
       </c>
       <c r="O18" s="1">
-        <v>2.7186367511749268</v>
+        <v>1.6311819553375244</v>
       </c>
       <c r="P18" s="1">
-        <v>6.2221164703369141</v>
+        <v>3.7332696914672852</v>
       </c>
       <c r="Q18" s="1">
         <v>-1.3891488313674927</v>
@@ -3873,22 +3879,22 @@
         <v>33.737167358398438</v>
       </c>
       <c r="E19" s="1">
-        <v>31.179271697998047</v>
+        <v>31.302248001098633</v>
       </c>
       <c r="F19" s="1">
-        <v>25.220613479614258</v>
+        <v>26.00886344909668</v>
       </c>
       <c r="G19" s="1">
-        <v>19.41423225402832</v>
+        <v>20.975751876831055</v>
       </c>
       <c r="H19" s="1">
-        <v>31.179271697998047</v>
+        <v>31.302248001098633</v>
       </c>
       <c r="I19" s="1">
-        <v>25.220613479614258</v>
+        <v>26.00886344909668</v>
       </c>
       <c r="J19" s="1">
-        <v>19.41423225402832</v>
+        <v>20.975751876831055</v>
       </c>
       <c r="K19" s="1">
         <v>4.3763270378112793</v>
@@ -3903,10 +3909,10 @@
         <v>0</v>
       </c>
       <c r="O19" s="1">
-        <v>7.950502872467041</v>
+        <v>4.7703018188476563</v>
       </c>
       <c r="P19" s="1">
-        <v>17.337860107421875</v>
+        <v>10.402714729309082</v>
       </c>
       <c r="Q19" s="1">
         <v>-2.3791112899780273</v>
@@ -3932,22 +3938,22 @@
         <v>22.279584884643555</v>
       </c>
       <c r="E20" s="1">
-        <v>21.786508560180664</v>
+        <v>21.832197189331055</v>
       </c>
       <c r="F20" s="1">
-        <v>21.441341400146484</v>
+        <v>21.450376510620117</v>
       </c>
       <c r="G20" s="1">
-        <v>21.124746322631836</v>
+        <v>21.098854064941406</v>
       </c>
       <c r="H20" s="1">
-        <v>21.786508560180664</v>
+        <v>21.832197189331055</v>
       </c>
       <c r="I20" s="1">
-        <v>21.441341400146484</v>
+        <v>21.450376510620117</v>
       </c>
       <c r="J20" s="1">
-        <v>21.124746322631836</v>
+        <v>21.098854064941406</v>
       </c>
       <c r="K20" s="1">
         <v>1.231325626373291</v>
@@ -3962,10 +3968,10 @@
         <v>11.425483703613281</v>
       </c>
       <c r="O20" s="1">
-        <v>14.542804718017578</v>
+        <v>13.490241050720215</v>
       </c>
       <c r="P20" s="1">
-        <v>18.598545074462891</v>
+        <v>16.114065170288086</v>
       </c>
       <c r="Q20" s="1">
         <v>-0.19765809178352356</v>
@@ -3991,22 +3997,22 @@
         <v>21.489063262939453</v>
       </c>
       <c r="E21" s="1">
-        <v>22.169673919677734</v>
+        <v>22.217504501342774</v>
       </c>
       <c r="F21" s="1">
-        <v>21.784017562866211</v>
+        <v>21.818704605102539</v>
       </c>
       <c r="G21" s="1">
-        <v>21.370183944702148</v>
+        <v>21.39973258972168</v>
       </c>
       <c r="H21" s="1">
         <v>21.65791130065918</v>
       </c>
       <c r="I21" s="1">
-        <v>21.607955932617188</v>
+        <v>21.617155075073242</v>
       </c>
       <c r="J21" s="1">
-        <v>21.370183944702148</v>
+        <v>21.39973258972168</v>
       </c>
       <c r="K21" s="1">
         <v>2.8153021335601807</v>
@@ -4021,10 +4027,10 @@
         <v>8.5872840881347656</v>
       </c>
       <c r="O21" s="1">
-        <v>12.385482788085938</v>
+        <v>10.917184829711914</v>
       </c>
       <c r="P21" s="1">
-        <v>17.729238510131836</v>
+        <v>14.303579330444336</v>
       </c>
       <c r="Q21" s="1">
         <v>-0.18233299255371094</v>
@@ -4047,52 +4053,52 @@
         <v>0</v>
       </c>
       <c r="D22" s="1">
-        <v>23.519998550415039</v>
+        <v>23.088916778564453</v>
       </c>
       <c r="E22" s="1">
-        <v>23.195619583129883</v>
+        <v>22.767730712890625</v>
       </c>
       <c r="F22" s="1">
-        <v>22.587013244628906</v>
+        <v>22.384037017822266</v>
       </c>
       <c r="G22" s="1">
-        <v>21.888105392456055</v>
+        <v>22.011739730834961</v>
       </c>
       <c r="H22" s="1">
-        <v>23.195619583129883</v>
+        <v>22.767730712890625</v>
       </c>
       <c r="I22" s="1">
-        <v>22.587013244628906</v>
+        <v>22.384037017822266</v>
       </c>
       <c r="J22" s="1">
-        <v>21.888105392456055</v>
+        <v>22.011739730834961</v>
       </c>
       <c r="K22" s="1">
-        <v>1.8094415664672852</v>
+        <v>1.8331828117370605</v>
       </c>
       <c r="L22" s="1">
-        <v>58.85650634765625</v>
+        <v>18.29620361328125</v>
       </c>
       <c r="M22" s="1">
         <v>0</v>
       </c>
       <c r="N22" s="1">
-        <v>4.2926797866821289</v>
+        <v>0.6298632025718689</v>
       </c>
       <c r="O22" s="1">
-        <v>8.0223407745361328</v>
+        <v>2.4449839591979981</v>
       </c>
       <c r="P22" s="1">
-        <v>12.748421669006348</v>
+        <v>4.8412685394287109</v>
       </c>
       <c r="Q22" s="1">
-        <v>-0.60773938894271851</v>
+        <v>-0.18892258405685425</v>
       </c>
       <c r="R22" s="1">
-        <v>2.1786086559295654</v>
+        <v>0.67724478244781494</v>
       </c>
       <c r="S22" s="1">
-        <v>4.5121569633483887</v>
+        <v>1.4026545286178589</v>
       </c>
     </row>
     <row r="23">
@@ -4106,52 +4112,52 @@
         <v>0</v>
       </c>
       <c r="D23" s="1">
-        <v>23.088916778564453</v>
+        <v>23.519998550415039</v>
       </c>
       <c r="E23" s="1">
-        <v>22.736509323120117</v>
+        <v>23.234500885009766</v>
       </c>
       <c r="F23" s="1">
-        <v>22.355678558349609</v>
+        <v>22.633596420288086</v>
       </c>
       <c r="G23" s="1">
-        <v>21.977024078369141</v>
+        <v>22.022214889526367</v>
       </c>
       <c r="H23" s="1">
-        <v>22.736509323120117</v>
+        <v>23.234500885009766</v>
       </c>
       <c r="I23" s="1">
-        <v>22.355678558349609</v>
+        <v>22.633596420288086</v>
       </c>
       <c r="J23" s="1">
-        <v>21.977024078369141</v>
+        <v>22.022214889526367</v>
       </c>
       <c r="K23" s="1">
-        <v>1.8331828117370605</v>
+        <v>1.8094415664672852</v>
       </c>
       <c r="L23" s="1">
-        <v>18.29620361328125</v>
+        <v>58.85650634765625</v>
       </c>
       <c r="M23" s="1">
         <v>0</v>
       </c>
       <c r="N23" s="1">
-        <v>0.6298632025718689</v>
+        <v>4.2926797866821289</v>
       </c>
       <c r="O23" s="1">
-        <v>3.4057650566101074</v>
+        <v>6.71484375</v>
       </c>
       <c r="P23" s="1">
-        <v>7.1071696281433105</v>
+        <v>9.7364273071289063</v>
       </c>
       <c r="Q23" s="1">
-        <v>-0.18892258405685425</v>
+        <v>-0.60773938894271851</v>
       </c>
       <c r="R23" s="1">
-        <v>0.67724478244781494</v>
+        <v>2.1786086559295654</v>
       </c>
       <c r="S23" s="1">
-        <v>1.4026545286178589</v>
+        <v>4.5121569633483887</v>
       </c>
     </row>
     <row r="24">
@@ -4168,22 +4174,22 @@
         <v>28.985597610473633</v>
       </c>
       <c r="E24" s="1">
-        <v>26.339178085327149</v>
+        <v>26.33201789855957</v>
       </c>
       <c r="F24" s="1">
-        <v>24.357187271118164</v>
+        <v>24.540962219238281</v>
       </c>
       <c r="G24" s="1">
-        <v>22.403219223022461</v>
+        <v>22.828071594238281</v>
       </c>
       <c r="H24" s="1">
-        <v>26.339178085327149</v>
+        <v>26.33201789855957</v>
       </c>
       <c r="I24" s="1">
-        <v>24.357187271118164</v>
+        <v>24.540962219238281</v>
       </c>
       <c r="J24" s="1">
-        <v>22.403219223022461</v>
+        <v>22.828071594238281</v>
       </c>
       <c r="K24" s="1">
         <v>1.4881768226623535</v>
@@ -4198,10 +4204,10 @@
         <v>0</v>
       </c>
       <c r="O24" s="1">
-        <v>1.6049402952194214</v>
+        <v>0.96296417713165283</v>
       </c>
       <c r="P24" s="1">
-        <v>3.6210050582885742</v>
+        <v>2.1726033687591553</v>
       </c>
       <c r="Q24" s="1">
         <v>-0.86902743577957153</v>
@@ -4227,22 +4233,22 @@
         <v>28.494235992431641</v>
       </c>
       <c r="E25" s="1">
-        <v>27.126667022705078</v>
+        <v>27.170236587524414</v>
       </c>
       <c r="F25" s="1">
-        <v>25.271799087524414</v>
+        <v>25.376089096069336</v>
       </c>
       <c r="G25" s="1">
-        <v>22.784492492675781</v>
+        <v>22.920974731445313</v>
       </c>
       <c r="H25" s="1">
-        <v>27.126667022705078</v>
+        <v>27.170236587524414</v>
       </c>
       <c r="I25" s="1">
-        <v>25.271799087524414</v>
+        <v>25.376089096069336</v>
       </c>
       <c r="J25" s="1">
-        <v>22.784492492675781</v>
+        <v>22.920974731445313</v>
       </c>
       <c r="K25" s="1">
         <v>1.3515106439590454</v>
@@ -4257,10 +4263,10 @@
         <v>1.5251953601837158</v>
       </c>
       <c r="O25" s="1">
-        <v>4.7614107131958008</v>
+        <v>3.6281261444091797</v>
       </c>
       <c r="P25" s="1">
-        <v>8.8604898452758789</v>
+        <v>6.2520194053649902</v>
       </c>
       <c r="Q25" s="1">
         <v>-1.5533427000045776</v>
@@ -4286,22 +4292,22 @@
         <v>25.033319473266602</v>
       </c>
       <c r="E26" s="1">
-        <v>25.218048095703125</v>
+        <v>25.246953964233398</v>
       </c>
       <c r="F26" s="1">
-        <v>24.946056365966797</v>
+        <v>24.961872100830078</v>
       </c>
       <c r="G26" s="1">
-        <v>24.690711975097656</v>
+        <v>24.700096130371094</v>
       </c>
       <c r="H26" s="1">
         <v>25.06391716003418</v>
       </c>
       <c r="I26" s="1">
-        <v>24.946056365966797</v>
+        <v>24.961872100830078</v>
       </c>
       <c r="J26" s="1">
-        <v>24.690711975097656</v>
+        <v>24.700096130371094</v>
       </c>
       <c r="K26" s="1">
         <v>1.5383285284042358</v>
@@ -4316,10 +4322,10 @@
         <v>2.0261704921722412</v>
       </c>
       <c r="O26" s="1">
-        <v>4.117067813873291</v>
+        <v>3.4124050140380859</v>
       </c>
       <c r="P26" s="1">
-        <v>6.925590991973877</v>
+        <v>5.2420177459716797</v>
       </c>
       <c r="Q26" s="1">
         <v>-0.11669077724218369</v>
@@ -4342,52 +4348,52 @@
         <v>0</v>
       </c>
       <c r="D27" s="1">
-        <v>27.585422515869141</v>
+        <v>32.023998260498047</v>
       </c>
       <c r="E27" s="1">
-        <v>26.890562057495117</v>
+        <v>30.339357376098633</v>
       </c>
       <c r="F27" s="1">
-        <v>26.163722991943359</v>
+        <v>27.920125961303711</v>
       </c>
       <c r="G27" s="1">
-        <v>24.794157028198242</v>
+        <v>25.27391242980957</v>
       </c>
       <c r="H27" s="1">
-        <v>26.890562057495117</v>
+        <v>30.339357376098633</v>
       </c>
       <c r="I27" s="1">
-        <v>26.163722991943359</v>
+        <v>27.920125961303711</v>
       </c>
       <c r="J27" s="1">
-        <v>24.794157028198242</v>
+        <v>25.27391242980957</v>
       </c>
       <c r="K27" s="1">
-        <v>3.7642781734466553</v>
+        <v>5.4320864677429199</v>
       </c>
       <c r="L27" s="1">
-        <v>8.1391191482543945</v>
+        <v>143.84133911132813</v>
       </c>
       <c r="M27" s="1">
         <v>0</v>
       </c>
       <c r="N27" s="1">
-        <v>9.6269979476928711</v>
+        <v>2.8455393314361572</v>
       </c>
       <c r="O27" s="1">
-        <v>15.784145355224609</v>
+        <v>4.9676198959350586</v>
       </c>
       <c r="P27" s="1">
-        <v>23.488571166992188</v>
+        <v>7.7184958457946777</v>
       </c>
       <c r="Q27" s="1">
-        <v>-0.084042765200138092</v>
+        <v>-1.4852741956710816</v>
       </c>
       <c r="R27" s="1">
-        <v>0.30127432942390442</v>
+        <v>5.3243727684020996</v>
       </c>
       <c r="S27" s="1">
-        <v>0.62397491931915283</v>
+        <v>11.027406692504883</v>
       </c>
     </row>
     <row r="28">
@@ -4401,52 +4407,52 @@
         <v>0</v>
       </c>
       <c r="D28" s="1">
-        <v>32.023998260498047</v>
+        <v>27.585422515869141</v>
       </c>
       <c r="E28" s="1">
-        <v>30.280406951904297</v>
+        <v>26.945394515991211</v>
       </c>
       <c r="F28" s="1">
-        <v>27.773284912109375</v>
+        <v>26.301008224487305</v>
       </c>
       <c r="G28" s="1">
-        <v>25.056312561035156</v>
+        <v>25.325437545776367</v>
       </c>
       <c r="H28" s="1">
-        <v>30.280406951904297</v>
+        <v>26.945394515991211</v>
       </c>
       <c r="I28" s="1">
-        <v>27.773284912109375</v>
+        <v>26.301008224487305</v>
       </c>
       <c r="J28" s="1">
-        <v>25.056312561035156</v>
+        <v>25.325437545776367</v>
       </c>
       <c r="K28" s="1">
-        <v>5.4320864677429199</v>
+        <v>3.7642781734466553</v>
       </c>
       <c r="L28" s="1">
-        <v>143.84133911132813</v>
+        <v>8.1391191482543945</v>
       </c>
       <c r="M28" s="1">
         <v>0</v>
       </c>
       <c r="N28" s="1">
-        <v>2.8455393314361572</v>
+        <v>9.6269979476928711</v>
       </c>
       <c r="O28" s="1">
-        <v>6.3820791244506836</v>
+        <v>13.491902351379395</v>
       </c>
       <c r="P28" s="1">
-        <v>10.969767570495605</v>
+        <v>18.331710815429688</v>
       </c>
       <c r="Q28" s="1">
-        <v>-1.4852741956710816</v>
+        <v>-0.084042765200138092</v>
       </c>
       <c r="R28" s="1">
-        <v>5.3243727684020996</v>
+        <v>0.30127432942390442</v>
       </c>
       <c r="S28" s="1">
-        <v>11.027406692504883</v>
+        <v>0.62397491931915283</v>
       </c>
     </row>
     <row r="29">
@@ -4463,22 +4469,22 @@
         <v>27.39015007019043</v>
       </c>
       <c r="E29" s="1">
-        <v>27.750909805297852</v>
+        <v>27.787363052368164</v>
       </c>
       <c r="F29" s="1">
-        <v>27.436735153198242</v>
+        <v>27.457674026489258</v>
       </c>
       <c r="G29" s="1">
-        <v>27.122634887695313</v>
+        <v>27.136386871337891</v>
       </c>
       <c r="H29" s="1">
         <v>27.465723037719727</v>
       </c>
       <c r="I29" s="1">
-        <v>27.436735153198242</v>
+        <v>27.442955017089844</v>
       </c>
       <c r="J29" s="1">
-        <v>27.122634887695313</v>
+        <v>27.136386871337891</v>
       </c>
       <c r="K29" s="1">
         <v>1.7580658197402954</v>
@@ -4493,10 +4499,10 @@
         <v>1.5793594121932983</v>
       </c>
       <c r="O29" s="1">
-        <v>3.9285428524017334</v>
+        <v>3.1063168048858643</v>
       </c>
       <c r="P29" s="1">
-        <v>7.162083625793457</v>
+        <v>5.2022213935852051</v>
       </c>
       <c r="Q29" s="1">
         <v>-0.092668108642101288</v>
@@ -4522,22 +4528,22 @@
         <v>30.68280029296875</v>
       </c>
       <c r="E30" s="1">
-        <v>28.572349548339844</v>
+        <v>28.622161865234375</v>
       </c>
       <c r="F30" s="1">
-        <v>28.382940292358399</v>
+        <v>28.356170654296875</v>
       </c>
       <c r="G30" s="1">
-        <v>28.022138595581055</v>
+        <v>27.814144134521484</v>
       </c>
       <c r="H30" s="1">
-        <v>28.572349548339844</v>
+        <v>28.622161865234375</v>
       </c>
       <c r="I30" s="1">
-        <v>28.382940292358399</v>
+        <v>28.356170654296875</v>
       </c>
       <c r="J30" s="1">
-        <v>28.022138595581055</v>
+        <v>27.814144134521484</v>
       </c>
       <c r="K30" s="1">
         <v>1.2923356294631958</v>
@@ -4552,10 +4558,10 @@
         <v>11.875863075256348</v>
       </c>
       <c r="O30" s="1">
-        <v>13.526473045349121</v>
+        <v>12.967769622802734</v>
       </c>
       <c r="P30" s="1">
-        <v>15.909316062927246</v>
+        <v>14.525602340698242</v>
       </c>
       <c r="Q30" s="1">
         <v>-0.051728162914514542</v>
@@ -4581,22 +4587,22 @@
         <v>33.137016296386719</v>
       </c>
       <c r="E31" s="1">
-        <v>31.089242935180664</v>
+        <v>31.126087188720703</v>
       </c>
       <c r="F31" s="1">
-        <v>30.448698043823242</v>
+        <v>30.538948059082031</v>
       </c>
       <c r="G31" s="1">
-        <v>29.576528549194336</v>
+        <v>29.761831283569336</v>
       </c>
       <c r="H31" s="1">
-        <v>31.089242935180664</v>
+        <v>31.126087188720703</v>
       </c>
       <c r="I31" s="1">
-        <v>30.448698043823242</v>
+        <v>30.538948059082031</v>
       </c>
       <c r="J31" s="1">
-        <v>29.576528549194336</v>
+        <v>29.761831283569336</v>
       </c>
       <c r="K31" s="1">
         <v>2.8590431213378906</v>
@@ -4611,10 +4617,10 @@
         <v>0</v>
       </c>
       <c r="O31" s="1">
-        <v>2.4342901706695557</v>
+        <v>1.4605740308761597</v>
       </c>
       <c r="P31" s="1">
-        <v>5.5137238502502441</v>
+        <v>3.3082342147827149</v>
       </c>
       <c r="Q31" s="1">
         <v>-0.25040501356124878</v>
@@ -4640,22 +4646,22 @@
         <v>32.963825225830078</v>
       </c>
       <c r="E32" s="1">
-        <v>31.662679672241211</v>
+        <v>31.700702667236328</v>
       </c>
       <c r="F32" s="1">
-        <v>31.331905364990234</v>
+        <v>31.366029739379883</v>
       </c>
       <c r="G32" s="1">
-        <v>31.007537841796875</v>
+        <v>31.068126678466797</v>
       </c>
       <c r="H32" s="1">
-        <v>31.662679672241211</v>
+        <v>31.700702667236328</v>
       </c>
       <c r="I32" s="1">
-        <v>31.331905364990234</v>
+        <v>31.366029739379883</v>
       </c>
       <c r="J32" s="1">
-        <v>31.007537841796875</v>
+        <v>31.068126678466797</v>
       </c>
       <c r="K32" s="1">
         <v>1.812983512878418</v>
@@ -4670,10 +4676,10 @@
         <v>2.8534793853759766</v>
       </c>
       <c r="O32" s="1">
-        <v>5.2173285484313965</v>
+        <v>4.4012646675109863</v>
       </c>
       <c r="P32" s="1">
-        <v>8.256169319152832</v>
+        <v>6.3552460670471192</v>
       </c>
       <c r="Q32" s="1">
         <v>-0.026917701587080956</v>
@@ -4699,22 +4705,22 @@
         <v>40.793071746826172</v>
       </c>
       <c r="E33" s="1">
-        <v>35.467098236083984</v>
+        <v>35.553970336914063</v>
       </c>
       <c r="F33" s="1">
-        <v>33.966518402099609</v>
+        <v>34.119129180908203</v>
       </c>
       <c r="G33" s="1">
-        <v>32.444877624511719</v>
+        <v>32.693763732910156</v>
       </c>
       <c r="H33" s="1">
-        <v>35.467098236083984</v>
+        <v>35.553970336914063</v>
       </c>
       <c r="I33" s="1">
-        <v>33.966518402099609</v>
+        <v>34.119129180908203</v>
       </c>
       <c r="J33" s="1">
-        <v>32.444877624511719</v>
+        <v>32.693763732910156</v>
       </c>
       <c r="K33" s="1">
         <v>2.0582499504089356</v>
@@ -4729,10 +4735,10 @@
         <v>5.1132559776306152</v>
       </c>
       <c r="O33" s="1">
-        <v>7.3252196311950684</v>
+        <v>6.5396246910095215</v>
       </c>
       <c r="P33" s="1">
-        <v>10.090941429138184</v>
+        <v>8.2968120574951172</v>
       </c>
       <c r="Q33" s="1">
         <v>-0.33560475707054138</v>
@@ -4758,22 +4764,22 @@
         <v>36.838943481445313</v>
       </c>
       <c r="E34" s="1">
-        <v>35.453342437744141</v>
+        <v>35.497901916503906</v>
       </c>
       <c r="F34" s="1">
-        <v>34.325752258300781</v>
+        <v>34.394428253173828</v>
       </c>
       <c r="G34" s="1">
-        <v>32.945659637451172</v>
+        <v>33.180706024169922</v>
       </c>
       <c r="H34" s="1">
-        <v>35.453342437744141</v>
+        <v>35.497901916503906</v>
       </c>
       <c r="I34" s="1">
-        <v>34.325752258300781</v>
+        <v>34.394428253173828</v>
       </c>
       <c r="J34" s="1">
-        <v>32.945659637451172</v>
+        <v>33.180706024169922</v>
       </c>
       <c r="K34" s="1">
         <v>3.0391237735748291</v>
@@ -4788,10 +4794,10 @@
         <v>58.534774780273438</v>
       </c>
       <c r="O34" s="1">
-        <v>61.411361694335938</v>
+        <v>60.339527130126953</v>
       </c>
       <c r="P34" s="1">
-        <v>65.033004760742188</v>
+        <v>62.578033447265625</v>
       </c>
       <c r="Q34" s="1">
         <v>-0.67763090133666992</v>
@@ -4817,22 +4823,22 @@
         <v>35.928680419921875</v>
       </c>
       <c r="E35" s="1">
-        <v>34.155609130859375</v>
+        <v>34.195388793945313</v>
       </c>
       <c r="F35" s="1">
-        <v>33.768051147460938</v>
+        <v>33.815982818603516</v>
       </c>
       <c r="G35" s="1">
-        <v>33.252079010009766</v>
+        <v>33.380916595458984</v>
       </c>
       <c r="H35" s="1">
-        <v>34.155609130859375</v>
+        <v>34.195388793945313</v>
       </c>
       <c r="I35" s="1">
-        <v>33.768051147460938</v>
+        <v>33.815982818603516</v>
       </c>
       <c r="J35" s="1">
-        <v>33.252079010009766</v>
+        <v>33.380916595458984</v>
       </c>
       <c r="K35" s="1">
         <v>2.6939806938171387</v>
@@ -4847,10 +4853,10 @@
         <v>1.2021737098693848</v>
       </c>
       <c r="O35" s="1">
-        <v>3.6201558113098145</v>
+        <v>2.7424185276031494</v>
       </c>
       <c r="P35" s="1">
-        <v>6.7551174163818359</v>
+        <v>4.7401785850524902</v>
       </c>
       <c r="Q35" s="1">
         <v>-0.10902998596429825</v>
@@ -4876,22 +4882,22 @@
         <v>39.194725036621094</v>
       </c>
       <c r="E36" s="1">
-        <v>37.019683837890625</v>
+        <v>37.043521881103516</v>
       </c>
       <c r="F36" s="1">
-        <v>36.075977325439453</v>
+        <v>36.075004577636719</v>
       </c>
       <c r="G36" s="1">
-        <v>35.153644561767578</v>
+        <v>35.117691040039063</v>
       </c>
       <c r="H36" s="1">
-        <v>37.019683837890625</v>
+        <v>37.043521881103516</v>
       </c>
       <c r="I36" s="1">
-        <v>36.075977325439453</v>
+        <v>36.075004577636719</v>
       </c>
       <c r="J36" s="1">
-        <v>35.153644561767578</v>
+        <v>35.117691040039063</v>
       </c>
       <c r="K36" s="1">
         <v>0.32150024175643921</v>
@@ -4906,10 +4912,10 @@
         <v>0</v>
       </c>
       <c r="O36" s="1">
-        <v>0.679859459400177</v>
+        <v>0.40791568160057068</v>
       </c>
       <c r="P36" s="1">
-        <v>1.6802687644958496</v>
+        <v>1.008161187171936</v>
       </c>
       <c r="Q36" s="1">
         <v>-0.71462589502334595</v>
@@ -4935,22 +4941,22 @@
         <v>41.467826843261719</v>
       </c>
       <c r="E37" s="1">
-        <v>39.873992919921875</v>
+        <v>39.927154541015625</v>
       </c>
       <c r="F37" s="1">
-        <v>37.760429382324219</v>
+        <v>37.797622680664063</v>
       </c>
       <c r="G37" s="1">
-        <v>35.926563262939453</v>
+        <v>36.001800537109375</v>
       </c>
       <c r="H37" s="1">
-        <v>39.873992919921875</v>
+        <v>39.927154541015625</v>
       </c>
       <c r="I37" s="1">
-        <v>37.760429382324219</v>
+        <v>37.797622680664063</v>
       </c>
       <c r="J37" s="1">
-        <v>35.926563262939453</v>
+        <v>36.001800537109375</v>
       </c>
       <c r="K37" s="1">
         <v>1.9415525197982788</v>
@@ -4965,10 +4971,10 @@
         <v>3.7543389797210693</v>
       </c>
       <c r="O37" s="1">
-        <v>6.1446247100830078</v>
+        <v>5.3080329895019531</v>
       </c>
       <c r="P37" s="1">
-        <v>9.1783218383789063</v>
+        <v>7.2479825019836426</v>
       </c>
       <c r="Q37" s="1">
         <v>-1.0365113019943237</v>
@@ -4991,52 +4997,52 @@
         <v>0</v>
       </c>
       <c r="D38" s="1">
-        <v>47.321636199951172</v>
+        <v>48.211658477783203</v>
       </c>
       <c r="E38" s="1">
-        <v>45.018539428710938</v>
+        <v>44.672458648681641</v>
       </c>
       <c r="F38" s="1">
-        <v>43.642322540283203</v>
+        <v>43.480243682861328</v>
       </c>
       <c r="G38" s="1">
-        <v>42.536151885986328</v>
+        <v>42.231597900390625</v>
       </c>
       <c r="H38" s="1">
-        <v>45.018539428710938</v>
+        <v>44.672458648681641</v>
       </c>
       <c r="I38" s="1">
-        <v>43.642322540283203</v>
+        <v>43.480243682861328</v>
       </c>
       <c r="J38" s="1">
-        <v>42.536151885986328</v>
+        <v>42.231597900390625</v>
       </c>
       <c r="K38" s="1">
-        <v>1.9545148611068726</v>
+        <v>2.3083720207214355</v>
       </c>
       <c r="L38" s="1">
-        <v>57.353202819824219</v>
+        <v>31.862676620483398</v>
       </c>
       <c r="M38" s="1">
         <v>0</v>
       </c>
       <c r="N38" s="1">
-        <v>0</v>
+        <v>3.545093297958374</v>
       </c>
       <c r="O38" s="1">
-        <v>1.1810562610626221</v>
+        <v>4.3755054473876953</v>
       </c>
       <c r="P38" s="1">
-        <v>2.7857098579406738</v>
+        <v>5.755126953125</v>
       </c>
       <c r="Q38" s="1">
-        <v>-0.59221667051315308</v>
+        <v>-0.32900702953338623</v>
       </c>
       <c r="R38" s="1">
-        <v>2.1229629516601563</v>
+        <v>1.1794159412384033</v>
       </c>
       <c r="S38" s="1">
-        <v>4.3969082832336426</v>
+        <v>2.4427101612091065</v>
       </c>
     </row>
     <row r="39">
@@ -5050,52 +5056,52 @@
         <v>0</v>
       </c>
       <c r="D39" s="1">
-        <v>48.211658477783203</v>
+        <v>47.321636199951172</v>
       </c>
       <c r="E39" s="1">
-        <v>44.509128570556641</v>
+        <v>45.056312561035156</v>
       </c>
       <c r="F39" s="1">
-        <v>43.548534393310547</v>
+        <v>43.660480499267578</v>
       </c>
       <c r="G39" s="1">
-        <v>42.564781188964844</v>
+        <v>42.539924621582031</v>
       </c>
       <c r="H39" s="1">
-        <v>44.509128570556641</v>
+        <v>45.056312561035156</v>
       </c>
       <c r="I39" s="1">
-        <v>43.548534393310547</v>
+        <v>43.660480499267578</v>
       </c>
       <c r="J39" s="1">
-        <v>42.564781188964844</v>
+        <v>42.539924621582031</v>
       </c>
       <c r="K39" s="1">
-        <v>2.3083720207214355</v>
+        <v>1.9545148611068726</v>
       </c>
       <c r="L39" s="1">
-        <v>31.862676620483398</v>
+        <v>57.353202819824219</v>
       </c>
       <c r="M39" s="1">
         <v>0</v>
       </c>
       <c r="N39" s="1">
-        <v>3.545093297958374</v>
+        <v>0</v>
       </c>
       <c r="O39" s="1">
-        <v>4.9173016548156738</v>
+        <v>0.70863378047943115</v>
       </c>
       <c r="P39" s="1">
-        <v>7.0847058296203613</v>
+        <v>1.6714258193969727</v>
       </c>
       <c r="Q39" s="1">
-        <v>-0.32900702953338623</v>
+        <v>-0.59221667051315308</v>
       </c>
       <c r="R39" s="1">
-        <v>1.1794159412384033</v>
+        <v>2.1229629516601563</v>
       </c>
       <c r="S39" s="1">
-        <v>2.4427101612091065</v>
+        <v>4.3969082832336426</v>
       </c>
     </row>
     <row r="40">
@@ -5112,22 +5118,22 @@
         <v>50.226909637451172</v>
       </c>
       <c r="E40" s="1">
-        <v>48.685302734375</v>
+        <v>48.705303192138672</v>
       </c>
       <c r="F40" s="1">
-        <v>47.173667907714844</v>
+        <v>47.287216186523438</v>
       </c>
       <c r="G40" s="1">
-        <v>45.731891632080078</v>
+        <v>46.100208282470703</v>
       </c>
       <c r="H40" s="1">
-        <v>48.685302734375</v>
+        <v>48.705303192138672</v>
       </c>
       <c r="I40" s="1">
-        <v>47.173667907714844</v>
+        <v>47.287216186523438</v>
       </c>
       <c r="J40" s="1">
-        <v>45.731891632080078</v>
+        <v>46.100208282470703</v>
       </c>
       <c r="K40" s="1">
         <v>2.9923243522644043</v>
@@ -5142,10 +5148,10 @@
         <v>24.986234664916992</v>
       </c>
       <c r="O40" s="1">
-        <v>27.190309524536133</v>
+        <v>26.380487442016602</v>
       </c>
       <c r="P40" s="1">
-        <v>29.817365646362305</v>
+        <v>28.010160446166992</v>
       </c>
       <c r="Q40" s="1">
         <v>-0.68098533153533936</v>
@@ -5171,22 +5177,22 @@
         <v>53.848400115966797</v>
       </c>
       <c r="E41" s="1">
-        <v>48.631397247314453</v>
+        <v>48.762378692626953</v>
       </c>
       <c r="F41" s="1">
-        <v>47.9991455078125</v>
+        <v>48.045505523681641</v>
       </c>
       <c r="G41" s="1">
-        <v>47.337520599365234</v>
+        <v>47.310131072998047</v>
       </c>
       <c r="H41" s="1">
-        <v>48.631397247314453</v>
+        <v>48.762378692626953</v>
       </c>
       <c r="I41" s="1">
-        <v>47.9991455078125</v>
+        <v>48.045505523681641</v>
       </c>
       <c r="J41" s="1">
-        <v>47.337520599365234</v>
+        <v>47.310131072998047</v>
       </c>
       <c r="K41" s="1">
         <v>1.8385132551193237</v>
@@ -5201,10 +5207,10 @@
         <v>0</v>
       </c>
       <c r="O41" s="1">
-        <v>1.3201804161071777</v>
+        <v>0.79210829734802246</v>
       </c>
       <c r="P41" s="1">
-        <v>3.1080698966979981</v>
+        <v>1.8648418188095093</v>
       </c>
       <c r="Q41" s="1">
         <v>-0.0324648916721344</v>
@@ -5230,22 +5236,22 @@
         <v>58.708145141601563</v>
       </c>
       <c r="E42" s="1">
-        <v>57.504634857177734</v>
+        <v>57.542507171630859</v>
       </c>
       <c r="F42" s="1">
-        <v>56.702167510986328</v>
+        <v>56.709213256835938</v>
       </c>
       <c r="G42" s="1">
-        <v>56.17529296875</v>
+        <v>56.149486541748047</v>
       </c>
       <c r="H42" s="1">
-        <v>57.504634857177734</v>
+        <v>57.542507171630859</v>
       </c>
       <c r="I42" s="1">
-        <v>56.702167510986328</v>
+        <v>56.709213256835938</v>
       </c>
       <c r="J42" s="1">
-        <v>56.17529296875</v>
+        <v>56.149486541748047</v>
       </c>
       <c r="K42" s="1">
         <v>2.3428640365600586</v>
@@ -5260,10 +5266,10 @@
         <v>8.4981727600097656</v>
       </c>
       <c r="O42" s="1">
-        <v>9.4255790710449219</v>
+        <v>9.0965824127197266</v>
       </c>
       <c r="P42" s="1">
-        <v>10.611268997192383</v>
+        <v>9.8502340316772461</v>
       </c>
       <c r="Q42" s="1">
         <v>-0.41630640625953674</v>
@@ -5289,22 +5295,22 @@
         <v>71.537399291992188</v>
       </c>
       <c r="E43" s="1">
-        <v>65.240455627441406</v>
+        <v>65.327873229980469</v>
       </c>
       <c r="F43" s="1">
-        <v>63.065341949462891</v>
+        <v>63.170707702636719</v>
       </c>
       <c r="G43" s="1">
-        <v>61.162994384765625</v>
+        <v>61.3074951171875</v>
       </c>
       <c r="H43" s="1">
-        <v>65.240455627441406</v>
+        <v>65.327873229980469</v>
       </c>
       <c r="I43" s="1">
-        <v>63.065341949462891</v>
+        <v>63.170707702636719</v>
       </c>
       <c r="J43" s="1">
-        <v>61.162994384765625</v>
+        <v>61.3074951171875</v>
       </c>
       <c r="K43" s="1">
         <v>1.9380583763122559</v>
@@ -5319,10 +5325,10 @@
         <v>0</v>
       </c>
       <c r="O43" s="1">
-        <v>0.94468170404434204</v>
+        <v>0.56680899858474732</v>
       </c>
       <c r="P43" s="1">
-        <v>2.1745691299438477</v>
+        <v>1.3047416210174561</v>
       </c>
       <c r="Q43" s="1">
         <v>-0.50616496801376343</v>
@@ -5348,22 +5354,22 @@
         <v>71.927200317382813</v>
       </c>
       <c r="E44" s="1">
-        <v>68.602897644042969</v>
+        <v>68.643959045410156</v>
       </c>
       <c r="F44" s="1">
-        <v>64.81640625</v>
+        <v>64.866615295410156</v>
       </c>
       <c r="G44" s="1">
-        <v>61.522605895996094</v>
+        <v>61.676933288574219</v>
       </c>
       <c r="H44" s="1">
-        <v>68.602897644042969</v>
+        <v>68.643959045410156</v>
       </c>
       <c r="I44" s="1">
-        <v>64.81640625</v>
+        <v>64.866615295410156</v>
       </c>
       <c r="J44" s="1">
-        <v>61.522605895996094</v>
+        <v>61.676933288574219</v>
       </c>
       <c r="K44" s="1">
         <v>1.1138042211532593</v>
@@ -5378,10 +5384,10 @@
         <v>0</v>
       </c>
       <c r="O44" s="1">
-        <v>1.1383930444717407</v>
+        <v>0.68303579092025757</v>
       </c>
       <c r="P44" s="1">
-        <v>2.6293468475341797</v>
+        <v>1.5776081085205078</v>
       </c>
       <c r="Q44" s="1">
         <v>-1.2609143257141113</v>
@@ -5407,22 +5413,22 @@
         <v>66.349037170410156</v>
       </c>
       <c r="E45" s="1">
-        <v>64.582183837890625</v>
+        <v>64.624092102050781</v>
       </c>
       <c r="F45" s="1">
-        <v>64.476692199707031</v>
+        <v>64.470008850097656</v>
       </c>
       <c r="G45" s="1">
-        <v>64.539825439453125</v>
+        <v>64.483314514160156</v>
       </c>
       <c r="H45" s="1">
-        <v>64.582183837890625</v>
+        <v>64.624092102050781</v>
       </c>
       <c r="I45" s="1">
-        <v>64.476692199707031</v>
+        <v>64.470008850097656</v>
       </c>
       <c r="J45" s="1">
-        <v>64.539825439453125</v>
+        <v>64.483314514160156</v>
       </c>
       <c r="K45" s="1">
         <v>1.7335447072982788</v>
@@ -5437,10 +5443,10 @@
         <v>4.5350542068481445</v>
       </c>
       <c r="O45" s="1">
-        <v>5.275667667388916</v>
+        <v>5.0140829086303711</v>
       </c>
       <c r="P45" s="1">
-        <v>6.3042812347412109</v>
+        <v>5.6756038665771484</v>
       </c>
       <c r="Q45" s="1">
         <v>-0.0028829965740442276</v>
@@ -5466,22 +5472,22 @@
         <v>86.785316467285156</v>
       </c>
       <c r="E46" s="1">
-        <v>80.810401916503906</v>
+        <v>80.859710693359375</v>
       </c>
       <c r="F46" s="1">
-        <v>77.793388366699219</v>
+        <v>78.164665222167969</v>
       </c>
       <c r="G46" s="1">
-        <v>74.754150390625</v>
+        <v>75.479133605957031</v>
       </c>
       <c r="H46" s="1">
-        <v>80.810401916503906</v>
+        <v>80.859710693359375</v>
       </c>
       <c r="I46" s="1">
-        <v>77.793388366699219</v>
+        <v>78.164665222167969</v>
       </c>
       <c r="J46" s="1">
-        <v>74.754150390625</v>
+        <v>75.479133605957031</v>
       </c>
       <c r="K46" s="1">
         <v>5.2754936218261719</v>
@@ -5496,10 +5502,10 @@
         <v>0</v>
       </c>
       <c r="O46" s="1">
-        <v>1.8910566568374634</v>
+        <v>1.1346340179443359</v>
       </c>
       <c r="P46" s="1">
-        <v>4.194979190826416</v>
+        <v>2.5169875621795654</v>
       </c>
       <c r="Q46" s="1">
         <v>-0.52598530054092407</v>
@@ -5525,22 +5531,22 @@
         <v>89.858207702636719</v>
       </c>
       <c r="E47" s="1">
-        <v>87.971145629882813</v>
+        <v>88.031982421875</v>
       </c>
       <c r="F47" s="1">
-        <v>83.316246032714844</v>
+        <v>83.644485473632813</v>
       </c>
       <c r="G47" s="1">
-        <v>79.352760314941406</v>
+        <v>79.9896240234375</v>
       </c>
       <c r="H47" s="1">
-        <v>87.971145629882813</v>
+        <v>88.031982421875</v>
       </c>
       <c r="I47" s="1">
-        <v>83.316246032714844</v>
+        <v>83.644485473632813</v>
       </c>
       <c r="J47" s="1">
-        <v>79.352760314941406</v>
+        <v>79.9896240234375</v>
       </c>
       <c r="K47" s="1">
         <v>8.960113525390625</v>
@@ -5555,10 +5561,10 @@
         <v>31.123693466186523</v>
       </c>
       <c r="O47" s="1">
-        <v>34.515571594238281</v>
+        <v>33.191570281982422</v>
       </c>
       <c r="P47" s="1">
-        <v>38.477104187011719</v>
+        <v>35.591495513916016</v>
       </c>
       <c r="Q47" s="1">
         <v>-1.037487268447876</v>
@@ -5634,13 +5640,13 @@
         <v>22.532503128051761</v>
       </c>
       <c r="C2" s="1">
-        <v>22.48326301574707</v>
+        <v>22.527645111083981</v>
       </c>
       <c r="D2" s="1">
         <v>21.33632850646973</v>
       </c>
       <c r="E2" s="1">
-        <v>21.37819862365723</v>
+        <v>21.42258262634277</v>
       </c>
       <c r="F2" s="1">
         <v>2.098418235778809</v>
@@ -5655,7 +5661,7 @@
         <v>-0.45855069879978899</v>
       </c>
       <c r="J2" s="1">
-        <v>15.695722980486099</v>
+        <v>16.113849786571429</v>
       </c>
       <c r="K2" s="1">
         <v>100</v>
@@ -5681,13 +5687,13 @@
         <v>22.532503128051761</v>
       </c>
       <c r="C3" s="1">
-        <v>21.815752029418949</v>
+        <v>21.867099761962891</v>
       </c>
       <c r="D3" s="1">
         <v>21.33632850646973</v>
       </c>
       <c r="E3" s="1">
-        <v>20.710443496704102</v>
+        <v>20.761791229248051</v>
       </c>
       <c r="F3" s="1">
         <v>2.098418235778809</v>
@@ -5696,16 +5702,16 @@
         <v>2.656042337417603</v>
       </c>
       <c r="H3" s="1">
-        <v>8.5026045191464661</v>
+        <v>7.1449146370557051</v>
       </c>
       <c r="I3" s="1">
         <v>1.6438007223960529</v>
       </c>
       <c r="J3" s="1">
-        <v>11.75924173093461</v>
+        <v>12.152605871467211</v>
       </c>
       <c r="K3" s="1">
-        <v>83.799181254205919</v>
+        <v>81.296461938225832</v>
       </c>
       <c r="L3" s="1">
         <v>0</v>
@@ -5728,13 +5734,13 @@
         <v>22.532503128051761</v>
       </c>
       <c r="C4" s="1">
-        <v>21.04714202880859</v>
+        <v>21.13709831237793</v>
       </c>
       <c r="D4" s="1">
         <v>21.33632850646973</v>
       </c>
       <c r="E4" s="1">
-        <v>19.937633514404301</v>
+        <v>20.027591705322269</v>
       </c>
       <c r="F4" s="1">
         <v>2.098418235778809</v>
@@ -5743,16 +5749,16 @@
         <v>3.060468435287476</v>
       </c>
       <c r="H4" s="1">
-        <v>13.484676326366801</v>
+        <v>10.32599401582298</v>
       </c>
       <c r="I4" s="1">
         <v>3.404506446363996</v>
       </c>
       <c r="J4" s="1">
-        <v>6.7365932485337092</v>
+        <v>7.2291114380765036</v>
       </c>
       <c r="K4" s="1">
-        <v>79.84208891468154</v>
+        <v>75.204789834574385</v>
       </c>
       <c r="L4" s="1">
         <v>2</v>
@@ -5773,7 +5779,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5781,7 +5787,7 @@
         <v>113</v>
       </c>
       <c r="B1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2">
@@ -5797,7 +5803,7 @@
         <v>115</v>
       </c>
       <c r="B3" s="1">
-        <v>0.050000000000000003</v>
+        <v>0.029999999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -5845,7 +5851,7 @@
         <v>121</v>
       </c>
       <c r="B9" s="1">
-        <v>0.22</v>
+        <v>0.14499999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -5853,7 +5859,7 @@
         <v>122</v>
       </c>
       <c r="B10" s="1">
-        <v>265</v>
+        <v>0.69399999999999995</v>
       </c>
     </row>
     <row r="11">
@@ -5861,6 +5867,22 @@
         <v>123</v>
       </c>
       <c r="B11" s="1">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" s="1">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>125</v>
+      </c>
+      <c r="B13" s="1">
         <v>4</v>
       </c>
     </row>

--- a/output/fixed/stress_test_summary.xlsx
+++ b/output/fixed/stress_test_summary.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="249" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="253" uniqueCount="131">
   <si>
     <t>qtr</t>
   </si>
@@ -164,117 +164,117 @@
     <t>BINA</t>
   </si>
   <si>
+    <t>MAYA</t>
+  </si>
+  <si>
+    <t>BBKP</t>
+  </si>
+  <si>
     <t>BCIC</t>
   </si>
   <si>
-    <t>MAYA</t>
-  </si>
-  <si>
-    <t>BBKP</t>
+    <t>PNBS</t>
+  </si>
+  <si>
+    <t>BJBR</t>
+  </si>
+  <si>
+    <t>BBTN</t>
+  </si>
+  <si>
+    <t>BBNI</t>
+  </si>
+  <si>
+    <t>BMRI</t>
+  </si>
+  <si>
+    <t>BABP</t>
+  </si>
+  <si>
+    <t>MASB</t>
+  </si>
+  <si>
+    <t>NISP</t>
+  </si>
+  <si>
+    <t>BRIS</t>
+  </si>
+  <si>
+    <t>INPC</t>
+  </si>
+  <si>
+    <t>BSIM</t>
+  </si>
+  <si>
+    <t>BVIC</t>
+  </si>
+  <si>
+    <t>BDMN</t>
+  </si>
+  <si>
+    <t>BNGA</t>
+  </si>
+  <si>
+    <t>BBRI</t>
+  </si>
+  <si>
+    <t>BNII</t>
+  </si>
+  <si>
+    <t>MEGA</t>
   </si>
   <si>
     <t>NOBU</t>
   </si>
   <si>
-    <t>PNBS</t>
-  </si>
-  <si>
-    <t>BJBR</t>
-  </si>
-  <si>
-    <t>BNII</t>
-  </si>
-  <si>
-    <t>BABP</t>
-  </si>
-  <si>
-    <t>BBTN</t>
-  </si>
-  <si>
-    <t>BBNI</t>
-  </si>
-  <si>
-    <t>BMRI</t>
-  </si>
-  <si>
-    <t>INPC</t>
-  </si>
-  <si>
-    <t>BVIC</t>
+    <t>BJTM</t>
+  </si>
+  <si>
+    <t>MCOR</t>
+  </si>
+  <si>
+    <t>BEKS</t>
+  </si>
+  <si>
+    <t>BBCA</t>
   </si>
   <si>
     <t>ARTO</t>
   </si>
   <si>
-    <t>BRIS</t>
-  </si>
-  <si>
-    <t>MASB</t>
-  </si>
-  <si>
-    <t>BEKS</t>
-  </si>
-  <si>
-    <t>BDMN</t>
-  </si>
-  <si>
-    <t>BBRI</t>
-  </si>
-  <si>
-    <t>NISP</t>
-  </si>
-  <si>
-    <t>BNGA</t>
-  </si>
-  <si>
-    <t>BSIM</t>
-  </si>
-  <si>
-    <t>MCOR</t>
-  </si>
-  <si>
-    <t>MEGA</t>
+    <t>BTPN</t>
   </si>
   <si>
     <t>SDRA</t>
   </si>
   <si>
-    <t>BJTM</t>
-  </si>
-  <si>
-    <t>BBCA</t>
-  </si>
-  <si>
-    <t>BTPN</t>
+    <t>BNLI</t>
   </si>
   <si>
     <t>AGRS</t>
   </si>
   <si>
-    <t>BNLI</t>
-  </si>
-  <si>
     <t>AGRO</t>
   </si>
   <si>
+    <t>PNBN</t>
+  </si>
+  <si>
     <t>BBSI</t>
   </si>
   <si>
-    <t>PNBN</t>
-  </si>
-  <si>
     <t>BACA</t>
   </si>
   <si>
     <t>DNAR</t>
   </si>
   <si>
+    <t>BBMD</t>
+  </si>
+  <si>
     <t>BMAS</t>
   </si>
   <si>
-    <t>BBMD</t>
-  </si>
-  <si>
     <t>BBYB</t>
   </si>
   <si>
@@ -284,15 +284,15 @@
     <t>BTPS</t>
   </si>
   <si>
+    <t>BBHI</t>
+  </si>
+  <si>
     <t>BNBA</t>
   </si>
   <si>
     <t>BGTG</t>
   </si>
   <si>
-    <t>BBHI</t>
-  </si>
-  <si>
     <t>BSWD</t>
   </si>
   <si>
@@ -351,6 +351,18 @@
   </si>
   <si>
     <t>credit_share</t>
+  </si>
+  <si>
+    <t>banks_car_below9</t>
+  </si>
+  <si>
+    <t>banks_car_below10</t>
+  </si>
+  <si>
+    <t>banks_car_below11</t>
+  </si>
+  <si>
+    <t>banks_car_below14</t>
   </si>
   <si>
     <t>base_quarter</t>
@@ -562,13 +574,13 @@
         <v>0.21444690227508545</v>
       </c>
       <c r="R2" s="1">
-        <v>0.086249701678752899</v>
+        <v>0.17044071853160858</v>
       </c>
       <c r="S2" s="1">
-        <v>0.086249701678752899</v>
+        <v>0.17044071853160858</v>
       </c>
       <c r="T2" s="1">
-        <v>0.086249701678752899</v>
+        <v>0.17044071853160858</v>
       </c>
     </row>
     <row r="3">
@@ -579,22 +591,22 @@
         <v>46</v>
       </c>
       <c r="C3" s="1">
-        <v>22.498384475708008</v>
+        <v>22.518278121948242</v>
       </c>
       <c r="D3" s="1">
-        <v>22.417062759399414</v>
+        <v>22.348623275756836</v>
       </c>
       <c r="E3" s="1">
-        <v>22.316936492919922</v>
+        <v>22.151773452758789</v>
       </c>
       <c r="F3" s="1">
-        <v>21.326032638549805</v>
+        <v>21.345926284790039</v>
       </c>
       <c r="G3" s="1">
-        <v>21.244945526123047</v>
+        <v>21.176506042480469</v>
       </c>
       <c r="H3" s="1">
-        <v>21.144376754760742</v>
+        <v>20.979213714599609</v>
       </c>
       <c r="I3" s="1">
         <v>2.2504801750183105</v>
@@ -606,13 +618,13 @@
         <v>2.2504801750183105</v>
       </c>
       <c r="L3" s="1">
-        <v>0.48911944031715393</v>
+        <v>0.48890626430511475</v>
       </c>
       <c r="M3" s="1">
-        <v>0.45468792319297791</v>
+        <v>0.45542126893997192</v>
       </c>
       <c r="N3" s="1">
-        <v>0.39158865809440613</v>
+        <v>0.39349496364593506</v>
       </c>
       <c r="O3" s="1">
         <v>0.24474991858005524</v>
@@ -624,13 +636,13 @@
         <v>0.31002038717269897</v>
       </c>
       <c r="R3" s="1">
-        <v>-0.017933163791894913</v>
+        <v>-0.035438284277915955</v>
       </c>
       <c r="S3" s="1">
-        <v>0.061694394797086716</v>
+        <v>0.12191621214151382</v>
       </c>
       <c r="T3" s="1">
-        <v>0.14943104982376099</v>
+        <v>0.29529532790184021</v>
       </c>
     </row>
     <row r="4">
@@ -641,22 +653,22 @@
         <v>46</v>
       </c>
       <c r="C4" s="1">
-        <v>22.469232559204102</v>
+        <v>22.500307083129883</v>
       </c>
       <c r="D4" s="1">
-        <v>22.259685516357422</v>
+        <v>22.095428466796875</v>
       </c>
       <c r="E4" s="1">
-        <v>22.022344589233398</v>
+        <v>21.669698715209961</v>
       </c>
       <c r="F4" s="1">
-        <v>21.32002067565918</v>
+        <v>21.351095199584961</v>
       </c>
       <c r="G4" s="1">
-        <v>21.110710144042969</v>
+        <v>20.946453094482422</v>
       </c>
       <c r="H4" s="1">
-        <v>20.872064590454102</v>
+        <v>20.519418716430664</v>
       </c>
       <c r="I4" s="1">
         <v>2.2543222904205322</v>
@@ -668,13 +680,13 @@
         <v>2.3612267971038818</v>
       </c>
       <c r="L4" s="1">
-        <v>0.4925592839717865</v>
+        <v>0.4924352765083313</v>
       </c>
       <c r="M4" s="1">
-        <v>0.41057136654853821</v>
+        <v>0.41164842247962952</v>
       </c>
       <c r="N4" s="1">
-        <v>0.29879981279373169</v>
+        <v>0.3011833131313324</v>
       </c>
       <c r="O4" s="1">
         <v>0.2353503555059433</v>
@@ -686,13 +698,13 @@
         <v>0.39858812093734741</v>
       </c>
       <c r="R4" s="1">
-        <v>-0.010432972572743893</v>
+        <v>-0.020616920664906502</v>
       </c>
       <c r="S4" s="1">
-        <v>0.087736643850803375</v>
+        <v>0.17337912321090698</v>
       </c>
       <c r="T4" s="1">
-        <v>0.17319515347480774</v>
+        <v>0.34225636720657349</v>
       </c>
     </row>
     <row r="5">
@@ -703,22 +715,22 @@
         <v>46</v>
       </c>
       <c r="C5" s="1">
-        <v>22.496133804321289</v>
+        <v>22.566783905029297</v>
       </c>
       <c r="D5" s="1">
-        <v>22.073032379150391</v>
+        <v>21.815973281860352</v>
       </c>
       <c r="E5" s="1">
-        <v>21.635410308837891</v>
+        <v>21.101951599121094</v>
       </c>
       <c r="F5" s="1">
-        <v>21.369081497192383</v>
+        <v>21.439731597900391</v>
       </c>
       <c r="G5" s="1">
-        <v>20.946313858032227</v>
+        <v>20.68925666809082</v>
       </c>
       <c r="H5" s="1">
-        <v>20.506130218505859</v>
+        <v>19.972671508789063</v>
       </c>
       <c r="I5" s="1">
         <v>2.2808027267456055</v>
@@ -730,13 +742,13 @@
         <v>2.6856958866119385</v>
       </c>
       <c r="L5" s="1">
-        <v>0.52787935733795166</v>
+        <v>0.52744883298873901</v>
       </c>
       <c r="M5" s="1">
-        <v>0.36503401398658752</v>
+        <v>0.36617392301559448</v>
       </c>
       <c r="N5" s="1">
-        <v>0.18356201052665711</v>
+        <v>0.18595214188098908</v>
       </c>
       <c r="O5" s="1">
         <v>0.2173498272895813</v>
@@ -748,13 +760,13 @@
         <v>0.53755128383636475</v>
       </c>
       <c r="R5" s="1">
-        <v>-0.036216519773006439</v>
+        <v>-0.071568593382835388</v>
       </c>
       <c r="S5" s="1">
-        <v>0.086968399584293365</v>
+        <v>0.1718609631061554</v>
       </c>
       <c r="T5" s="1">
-        <v>0.17032821476459503</v>
+        <v>0.33659088611602783</v>
       </c>
     </row>
     <row r="6">
@@ -765,22 +777,22 @@
         <v>46</v>
       </c>
       <c r="C6" s="1">
-        <v>22.527645111083984</v>
+        <v>22.622074127197266</v>
       </c>
       <c r="D6" s="1">
-        <v>21.867099761962891</v>
+        <v>21.529762268066406</v>
       </c>
       <c r="E6" s="1">
-        <v>21.13709831237793</v>
+        <v>20.438739776611328</v>
       </c>
       <c r="F6" s="1">
-        <v>21.422582626342774</v>
+        <v>21.517011642456055</v>
       </c>
       <c r="G6" s="1">
-        <v>20.761791229248047</v>
+        <v>20.42445182800293</v>
       </c>
       <c r="H6" s="1">
-        <v>20.027591705322266</v>
+        <v>19.329233169555664</v>
       </c>
       <c r="I6" s="1">
         <v>2.2517673969268799</v>
@@ -792,13 +804,13 @@
         <v>3.0604684352874756</v>
       </c>
       <c r="L6" s="1">
-        <v>0.54909712076187134</v>
+        <v>0.54882758855819702</v>
       </c>
       <c r="M6" s="1">
-        <v>0.32786744832992554</v>
+        <v>0.32891777157783508</v>
       </c>
       <c r="N6" s="1">
-        <v>0.062386922538280487</v>
+        <v>0.064673960208892822</v>
       </c>
       <c r="O6" s="1">
         <v>0.20698535442352295</v>
@@ -810,13 +822,13 @@
         <v>0.71863949298858643</v>
       </c>
       <c r="R6" s="1">
-        <v>-0.0226777084171772</v>
+        <v>-0.044814124703407288</v>
       </c>
       <c r="S6" s="1">
-        <v>0.077321052551269531</v>
+        <v>0.15279653668403626</v>
       </c>
       <c r="T6" s="1">
-        <v>0.15874394774436951</v>
+        <v>0.31369885802268982</v>
       </c>
     </row>
   </sheetData>
@@ -915,22 +927,22 @@
         <v>5</v>
       </c>
       <c r="D3" s="1">
-        <v>19.512197494506836</v>
+        <v>19.5338134765625</v>
       </c>
       <c r="E3" s="1">
-        <v>19.468423843383789</v>
+        <v>19.39405632019043</v>
       </c>
       <c r="F3" s="1">
-        <v>19.410497665405274</v>
+        <v>19.230369567871094</v>
       </c>
       <c r="G3" s="1">
-        <v>18.374406814575195</v>
+        <v>18.396024703979492</v>
       </c>
       <c r="H3" s="1">
-        <v>18.330860137939453</v>
+        <v>18.256492614746094</v>
       </c>
       <c r="I3" s="1">
-        <v>18.272504806518555</v>
+        <v>18.092376708984375</v>
       </c>
       <c r="J3" s="1">
         <v>2.1769814491271973</v>
@@ -953,22 +965,22 @@
         <v>5</v>
       </c>
       <c r="D4" s="1">
-        <v>19.584991455078125</v>
+        <v>19.618757247924805</v>
       </c>
       <c r="E4" s="1">
-        <v>19.458097457885742</v>
+        <v>19.279438018798828</v>
       </c>
       <c r="F4" s="1">
-        <v>19.300325393676758</v>
+        <v>18.914844512939453</v>
       </c>
       <c r="G4" s="1">
-        <v>18.469655990600586</v>
+        <v>18.503423690795898</v>
       </c>
       <c r="H4" s="1">
-        <v>18.342994689941406</v>
+        <v>18.164333343505859</v>
       </c>
       <c r="I4" s="1">
-        <v>18.183956146240234</v>
+        <v>17.79847526550293</v>
       </c>
       <c r="J4" s="1">
         <v>2.208909273147583</v>
@@ -991,22 +1003,22 @@
         <v>5</v>
       </c>
       <c r="D5" s="1">
-        <v>19.700643539428711</v>
+        <v>19.777414321899414</v>
       </c>
       <c r="E5" s="1">
-        <v>19.417373657226563</v>
+        <v>19.137338638305664</v>
       </c>
       <c r="F5" s="1">
-        <v>19.096343994140625</v>
+        <v>18.512580871582031</v>
       </c>
       <c r="G5" s="1">
-        <v>18.606815338134766</v>
+        <v>18.683588027954102</v>
       </c>
       <c r="H5" s="1">
-        <v>18.323871612548828</v>
+        <v>18.04383659362793</v>
       </c>
       <c r="I5" s="1">
-        <v>18.000354766845703</v>
+        <v>17.416591644287109</v>
       </c>
       <c r="J5" s="1">
         <v>2.254328727722168</v>
@@ -1029,22 +1041,22 @@
         <v>5</v>
       </c>
       <c r="D6" s="1">
-        <v>19.827547073364258</v>
+        <v>19.930156707763672</v>
       </c>
       <c r="E6" s="1">
-        <v>19.349361419677734</v>
+        <v>18.981443405151367</v>
       </c>
       <c r="F6" s="1">
-        <v>18.769155502319336</v>
+        <v>18.00425910949707</v>
       </c>
       <c r="G6" s="1">
-        <v>18.755060195922852</v>
+        <v>18.857669830322266</v>
       </c>
       <c r="H6" s="1">
-        <v>18.276636123657227</v>
+        <v>17.908718109130859</v>
       </c>
       <c r="I6" s="1">
-        <v>17.692358016967773</v>
+        <v>16.927459716796875</v>
       </c>
       <c r="J6" s="1">
         <v>2.2380642890930176</v>
@@ -1105,22 +1117,22 @@
         <v>41</v>
       </c>
       <c r="D8" s="1">
-        <v>26.591842651367188</v>
+        <v>26.609373092651367</v>
       </c>
       <c r="E8" s="1">
-        <v>26.459049224853516</v>
+        <v>26.398736953735352</v>
       </c>
       <c r="F8" s="1">
-        <v>26.301076889038086</v>
+        <v>26.156427383422852</v>
       </c>
       <c r="G8" s="1">
-        <v>25.372116088867188</v>
+        <v>25.389646530151367</v>
       </c>
       <c r="H8" s="1">
-        <v>25.239564895629883</v>
+        <v>25.179254531860352</v>
       </c>
       <c r="I8" s="1">
-        <v>25.081132888793945</v>
+        <v>24.936483383178711</v>
       </c>
       <c r="J8" s="1">
         <v>2.3680710792541504</v>
@@ -1143,22 +1155,22 @@
         <v>41</v>
       </c>
       <c r="D9" s="1">
-        <v>26.422945022583008</v>
+        <v>26.450328826904297</v>
       </c>
       <c r="E9" s="1">
-        <v>26.100095748901367</v>
+        <v>25.955581665039063</v>
       </c>
       <c r="F9" s="1">
-        <v>25.753681182861328</v>
+        <v>25.446044921875</v>
       </c>
       <c r="G9" s="1">
-        <v>25.227291107177734</v>
+        <v>25.254674911499024</v>
       </c>
       <c r="H9" s="1">
-        <v>24.904687881469727</v>
+        <v>24.760173797607422</v>
       </c>
       <c r="I9" s="1">
-        <v>24.556917190551758</v>
+        <v>24.24928092956543</v>
       </c>
       <c r="J9" s="1">
         <v>2.3269786834716797</v>
@@ -1181,22 +1193,22 @@
         <v>41</v>
       </c>
       <c r="D10" s="1">
-        <v>26.328184127807617</v>
+        <v>26.390443801879883</v>
       </c>
       <c r="E10" s="1">
-        <v>25.713403701782227</v>
+        <v>25.487838745117188</v>
       </c>
       <c r="F10" s="1">
-        <v>25.115957260131836</v>
+        <v>24.651453018188477</v>
       </c>
       <c r="G10" s="1">
-        <v>25.155586242675781</v>
+        <v>25.21784782409668</v>
       </c>
       <c r="H10" s="1">
-        <v>24.541152954101563</v>
+        <v>24.315587997436524</v>
       </c>
       <c r="I10" s="1">
-        <v>23.941041946411133</v>
+        <v>23.476537704467773</v>
       </c>
       <c r="J10" s="1">
         <v>2.3231587409973145</v>
@@ -1219,22 +1231,22 @@
         <v>41</v>
       </c>
       <c r="D11" s="1">
-        <v>26.228933334350586</v>
+        <v>26.312149047851563</v>
       </c>
       <c r="E11" s="1">
-        <v>25.318410873413086</v>
+        <v>25.022989273071289</v>
       </c>
       <c r="F11" s="1">
-        <v>24.38306999206543</v>
+        <v>23.775920867919922</v>
       </c>
       <c r="G11" s="1">
-        <v>25.079212188720703</v>
+        <v>25.16242790222168</v>
       </c>
       <c r="H11" s="1">
-        <v>24.168436050415039</v>
+        <v>23.873014450073242</v>
       </c>
       <c r="I11" s="1">
-        <v>23.228727340698242</v>
+        <v>22.621576309204102</v>
       </c>
       <c r="J11" s="1">
         <v>2.273690938949585</v>
@@ -1295,22 +1307,22 @@
         <v>24</v>
       </c>
       <c r="D13" s="1">
-        <v>33.182823181152344</v>
+        <v>33.139156341552734</v>
       </c>
       <c r="E13" s="1">
-        <v>32.778701782226563</v>
+        <v>32.928916931152344</v>
       </c>
       <c r="F13" s="1">
-        <v>32.309421539306641</v>
+        <v>32.687999725341797</v>
       </c>
       <c r="G13" s="1">
-        <v>31.882535934448242</v>
+        <v>31.838871002197266</v>
       </c>
       <c r="H13" s="1">
-        <v>31.478673934936524</v>
+        <v>31.628889083862305</v>
       </c>
       <c r="I13" s="1">
-        <v>31.008905410766602</v>
+        <v>31.387481689453125</v>
       </c>
       <c r="J13" s="1">
         <v>2.6759073734283447</v>
@@ -1333,22 +1345,22 @@
         <v>24</v>
       </c>
       <c r="D14" s="1">
-        <v>32.614086151123047</v>
+        <v>32.545879364013672</v>
       </c>
       <c r="E14" s="1">
-        <v>31.67633056640625</v>
+        <v>32.041072845458984</v>
       </c>
       <c r="F14" s="1">
-        <v>30.678815841674805</v>
+        <v>31.508712768554688</v>
       </c>
       <c r="G14" s="1">
-        <v>31.339462280273438</v>
+        <v>31.271257400512695</v>
       </c>
       <c r="H14" s="1">
-        <v>30.401969909667969</v>
+        <v>30.766712188720703</v>
       </c>
       <c r="I14" s="1">
-        <v>29.403009414672852</v>
+        <v>30.232906341552734</v>
       </c>
       <c r="J14" s="1">
         <v>2.7413887977600098</v>
@@ -1371,22 +1383,22 @@
         <v>24</v>
       </c>
       <c r="D15" s="1">
-        <v>32.220645904541016</v>
+        <v>32.065574645996094</v>
       </c>
       <c r="E15" s="1">
-        <v>30.542661666870117</v>
+        <v>31.124122619628906</v>
       </c>
       <c r="F15" s="1">
-        <v>28.926494598388672</v>
+        <v>30.1973876953125</v>
       </c>
       <c r="G15" s="1">
-        <v>30.970600128173828</v>
+        <v>30.815530776977539</v>
       </c>
       <c r="H15" s="1">
-        <v>29.292987823486328</v>
+        <v>29.874448776245117</v>
       </c>
       <c r="I15" s="1">
-        <v>27.673978805541992</v>
+        <v>28.944873809814453</v>
       </c>
       <c r="J15" s="1">
         <v>2.8094339370727539</v>
@@ -1409,22 +1421,22 @@
         <v>24</v>
       </c>
       <c r="D16" s="1">
-        <v>31.786628723144531</v>
+        <v>31.579368591308594</v>
       </c>
       <c r="E16" s="1">
-        <v>29.427352905273438</v>
+        <v>30.200901031494141</v>
       </c>
       <c r="F16" s="1">
-        <v>27.080663681030273</v>
+        <v>28.761171340942383</v>
       </c>
       <c r="G16" s="1">
-        <v>30.560972213745117</v>
+        <v>30.35371208190918</v>
       </c>
       <c r="H16" s="1">
-        <v>28.201423645019531</v>
+        <v>28.974971771240234</v>
       </c>
       <c r="I16" s="1">
-        <v>25.850080490112305</v>
+        <v>27.530588150024414</v>
       </c>
       <c r="J16" s="1">
         <v>2.8084266185760498</v>
@@ -1485,22 +1497,22 @@
         <v>8</v>
       </c>
       <c r="D18" s="1">
-        <v>20.652599334716797</v>
+        <v>20.645727157592774</v>
       </c>
       <c r="E18" s="1">
-        <v>20.409036636352539</v>
+        <v>20.432682037353516</v>
       </c>
       <c r="F18" s="1">
-        <v>20.094171524047852</v>
+        <v>20.15144157409668</v>
       </c>
       <c r="G18" s="1">
-        <v>19.133609771728516</v>
+        <v>19.126737594604492</v>
       </c>
       <c r="H18" s="1">
-        <v>18.890350341796875</v>
+        <v>18.913995742797852</v>
       </c>
       <c r="I18" s="1">
-        <v>18.574911117553711</v>
+        <v>18.632181167602539</v>
       </c>
       <c r="J18" s="1">
         <v>4.3011026382446289</v>
@@ -1523,22 +1535,22 @@
         <v>8</v>
       </c>
       <c r="D19" s="1">
-        <v>20.388845443725586</v>
+        <v>20.378108978271484</v>
       </c>
       <c r="E19" s="1">
-        <v>19.795322418212891</v>
+        <v>19.852127075195313</v>
       </c>
       <c r="F19" s="1">
-        <v>19.117879867553711</v>
+        <v>19.240440368652344</v>
       </c>
       <c r="G19" s="1">
-        <v>18.899835586547852</v>
+        <v>18.88909912109375</v>
       </c>
       <c r="H19" s="1">
-        <v>18.306619644165039</v>
+        <v>18.363424301147461</v>
       </c>
       <c r="I19" s="1">
-        <v>17.627487182617188</v>
+        <v>17.75004768371582</v>
       </c>
       <c r="J19" s="1">
         <v>3.9407155513763428</v>
@@ -1561,22 +1573,22 @@
         <v>8</v>
       </c>
       <c r="D20" s="1">
-        <v>20.228128433227539</v>
+        <v>20.203720092773438</v>
       </c>
       <c r="E20" s="1">
-        <v>19.126827239990234</v>
+        <v>19.215862274169922</v>
       </c>
       <c r="F20" s="1">
-        <v>17.967748641967773</v>
+        <v>18.153350830078125</v>
       </c>
       <c r="G20" s="1">
-        <v>18.767831802368164</v>
+        <v>18.743423461914063</v>
       </c>
       <c r="H20" s="1">
-        <v>17.666963577270508</v>
+        <v>17.755998611450195</v>
       </c>
       <c r="I20" s="1">
-        <v>16.504566192626953</v>
+        <v>16.690168380737305</v>
       </c>
       <c r="J20" s="1">
         <v>3.7215871810913086</v>
@@ -1599,22 +1611,22 @@
         <v>8</v>
       </c>
       <c r="D21" s="1">
-        <v>20.052921295166016</v>
+        <v>20.020298004150391</v>
       </c>
       <c r="E21" s="1">
-        <v>18.437797546386719</v>
+        <v>18.554775238037109</v>
       </c>
       <c r="F21" s="1">
-        <v>16.628829956054688</v>
+        <v>16.872024536132813</v>
       </c>
       <c r="G21" s="1">
-        <v>18.621114730834961</v>
+        <v>18.588491439819336</v>
       </c>
       <c r="H21" s="1">
-        <v>17.005672454833984</v>
+        <v>17.122650146484375</v>
       </c>
       <c r="I21" s="1">
-        <v>15.191267013549805</v>
+        <v>15.434459686279297</v>
       </c>
       <c r="J21" s="1">
         <v>3.5269320011138916</v>
@@ -1675,22 +1687,22 @@
         <v>10</v>
       </c>
       <c r="D23" s="1">
-        <v>24.995981216430664</v>
+        <v>25.030181884765625</v>
       </c>
       <c r="E23" s="1">
-        <v>24.892892837524414</v>
+        <v>24.775230407714844</v>
       </c>
       <c r="F23" s="1">
-        <v>24.772912979125977</v>
+        <v>24.487918853759766</v>
       </c>
       <c r="G23" s="1">
-        <v>23.741788864135742</v>
+        <v>23.775991439819336</v>
       </c>
       <c r="H23" s="1">
-        <v>23.638952255249024</v>
+        <v>23.52128791809082</v>
       </c>
       <c r="I23" s="1">
-        <v>23.518499374389648</v>
+        <v>23.233505249023438</v>
       </c>
       <c r="J23" s="1">
         <v>2.2920432090759277</v>
@@ -1713,22 +1725,22 @@
         <v>10</v>
       </c>
       <c r="D24" s="1">
-        <v>24.806625366210938</v>
+        <v>24.860050201416016</v>
       </c>
       <c r="E24" s="1">
-        <v>24.548187255859375</v>
+        <v>24.26551628112793</v>
       </c>
       <c r="F24" s="1">
-        <v>24.252639770507813</v>
+        <v>23.642744064331055</v>
       </c>
       <c r="G24" s="1">
-        <v>23.577186584472656</v>
+        <v>23.630611419677734</v>
       </c>
       <c r="H24" s="1">
-        <v>23.319002151489258</v>
+        <v>23.036331176757813</v>
       </c>
       <c r="I24" s="1">
-        <v>23.022062301635742</v>
+        <v>22.412164688110352</v>
       </c>
       <c r="J24" s="1">
         <v>2.3864409923553467</v>
@@ -1751,22 +1763,22 @@
         <v>10</v>
       </c>
       <c r="D25" s="1">
-        <v>24.687498092651367</v>
+        <v>24.808965682983398</v>
       </c>
       <c r="E25" s="1">
-        <v>24.177635192871094</v>
+        <v>23.734575271606445</v>
       </c>
       <c r="F25" s="1">
-        <v>23.611125946044922</v>
+        <v>22.687515258789063</v>
       </c>
       <c r="G25" s="1">
-        <v>23.481767654418945</v>
+        <v>23.603235244750977</v>
       </c>
       <c r="H25" s="1">
-        <v>22.972263336181641</v>
+        <v>22.529201507568359</v>
       </c>
       <c r="I25" s="1">
-        <v>22.403013229370117</v>
+        <v>21.479400634765625</v>
       </c>
       <c r="J25" s="1">
         <v>2.4739854335784912</v>
@@ -1789,22 +1801,22 @@
         <v>10</v>
       </c>
       <c r="D26" s="1">
-        <v>24.573089599609375</v>
+        <v>24.735437393188477</v>
       </c>
       <c r="E26" s="1">
-        <v>23.781251907348633</v>
+        <v>23.199142456054688</v>
       </c>
       <c r="F26" s="1">
-        <v>22.814777374267578</v>
+        <v>21.604581832885742</v>
       </c>
       <c r="G26" s="1">
-        <v>23.39088249206543</v>
+        <v>23.553230285644531</v>
       </c>
       <c r="H26" s="1">
-        <v>22.598781585693359</v>
+        <v>22.016672134399414</v>
       </c>
       <c r="I26" s="1">
-        <v>21.627817153930664</v>
+        <v>20.417621612548828</v>
       </c>
       <c r="J26" s="1">
         <v>2.4861268997192383</v>
@@ -1865,22 +1877,22 @@
         <v>4</v>
       </c>
       <c r="D28" s="1">
-        <v>21.087326049804688</v>
+        <v>21.108558654785156</v>
       </c>
       <c r="E28" s="1">
-        <v>21.050283432006836</v>
+        <v>20.97723388671875</v>
       </c>
       <c r="F28" s="1">
-        <v>21.001811981201172</v>
+        <v>20.824878692626953</v>
       </c>
       <c r="G28" s="1">
-        <v>19.987386703491211</v>
+        <v>20.008621215820313</v>
       </c>
       <c r="H28" s="1">
-        <v>19.950565338134766</v>
+        <v>19.87751579284668</v>
       </c>
       <c r="I28" s="1">
-        <v>19.901678085327149</v>
+        <v>19.724742889404297</v>
       </c>
       <c r="J28" s="1">
         <v>2.0186150074005127</v>
@@ -1903,22 +1915,22 @@
         <v>4</v>
       </c>
       <c r="D29" s="1">
-        <v>21.174322128295898</v>
+        <v>21.207489013671875</v>
       </c>
       <c r="E29" s="1">
-        <v>21.06635856628418</v>
+        <v>20.890867233276367</v>
       </c>
       <c r="F29" s="1">
-        <v>20.94157600402832</v>
+        <v>20.562932968139648</v>
       </c>
       <c r="G29" s="1">
-        <v>20.096092224121094</v>
+        <v>20.12925910949707</v>
       </c>
       <c r="H29" s="1">
-        <v>19.988351821899414</v>
+        <v>19.812860488891602</v>
       </c>
       <c r="I29" s="1">
-        <v>19.862346649169922</v>
+        <v>19.48370361328125</v>
       </c>
       <c r="J29" s="1">
         <v>2.0179219245910645</v>
@@ -1941,22 +1953,22 @@
         <v>4</v>
       </c>
       <c r="D30" s="1">
-        <v>21.300020217895508</v>
+        <v>21.375431060791016</v>
       </c>
       <c r="E30" s="1">
-        <v>21.054529190063477</v>
+        <v>20.779462814331055</v>
       </c>
       <c r="F30" s="1">
-        <v>20.809549331665039</v>
+        <v>20.236141204833984</v>
       </c>
       <c r="G30" s="1">
-        <v>20.242584228515625</v>
+        <v>20.3179931640625</v>
       </c>
       <c r="H30" s="1">
-        <v>19.997406005859375</v>
+        <v>19.722339630126953</v>
       </c>
       <c r="I30" s="1">
-        <v>19.750022888183594</v>
+        <v>19.176614761352539</v>
       </c>
       <c r="J30" s="1">
         <v>2.041344165802002</v>
@@ -1979,22 +1991,22 @@
         <v>4</v>
       </c>
       <c r="D31" s="1">
-        <v>21.43501091003418</v>
+        <v>21.535800933837891</v>
       </c>
       <c r="E31" s="1">
-        <v>21.023605346679688</v>
+        <v>20.662214279174805</v>
       </c>
       <c r="F31" s="1">
-        <v>20.588703155517578</v>
+        <v>19.837373733520508</v>
       </c>
       <c r="G31" s="1">
-        <v>20.398204803466797</v>
+        <v>20.498994827270508</v>
       </c>
       <c r="H31" s="1">
-        <v>19.986568450927734</v>
+        <v>19.625177383422852</v>
       </c>
       <c r="I31" s="1">
-        <v>19.5477294921875</v>
+        <v>18.796398162841797</v>
       </c>
       <c r="J31" s="1">
         <v>2.0102465152740479</v>
@@ -2070,13 +2082,13 @@
         <v>19.437982559204102</v>
       </c>
       <c r="E2" s="1">
-        <v>19.827547073364258</v>
+        <v>19.930156707763672</v>
       </c>
       <c r="F2" s="1">
-        <v>19.512197494506836</v>
+        <v>19.5338134765625</v>
       </c>
       <c r="G2" s="1">
-        <v>18.755060195922852</v>
+        <v>18.857669830322266</v>
       </c>
       <c r="H2" s="1">
         <v>1.9832693338394165</v>
@@ -2088,7 +2100,7 @@
         <v>5.4604249000549317</v>
       </c>
       <c r="K2" s="1">
-        <v>-0.351205974817276</v>
+        <v>-0.92261844873428345</v>
       </c>
       <c r="L2" s="1">
         <v>20.727863311767578</v>
@@ -2111,13 +2123,13 @@
         <v>19.437982559204102</v>
       </c>
       <c r="E3" s="1">
-        <v>19.349361419677734</v>
+        <v>18.981443405151367</v>
       </c>
       <c r="F3" s="1">
-        <v>19.349361419677734</v>
+        <v>18.981443405151367</v>
       </c>
       <c r="G3" s="1">
-        <v>18.276636123657227</v>
+        <v>17.908718109130859</v>
       </c>
       <c r="H3" s="1">
         <v>1.9832693338394165</v>
@@ -2129,7 +2141,7 @@
         <v>8.4268894195556641</v>
       </c>
       <c r="K3" s="1">
-        <v>1.2589941024780274</v>
+        <v>3.3073787689208984</v>
       </c>
       <c r="L3" s="1">
         <v>15.876166343688965</v>
@@ -2152,13 +2164,13 @@
         <v>19.437982559204102</v>
       </c>
       <c r="E4" s="1">
-        <v>18.769155502319336</v>
+        <v>18.00425910949707</v>
       </c>
       <c r="F4" s="1">
-        <v>18.769155502319336</v>
+        <v>18.00425910949707</v>
       </c>
       <c r="G4" s="1">
-        <v>17.692358016967773</v>
+        <v>16.927459716796875</v>
       </c>
       <c r="H4" s="1">
         <v>1.9832693338394165</v>
@@ -2170,7 +2182,7 @@
         <v>12.337897300720215</v>
       </c>
       <c r="K4" s="1">
-        <v>2.6075263023376465</v>
+        <v>6.8499741554260254</v>
       </c>
       <c r="L4" s="1">
         <v>9.8902740478515625</v>
@@ -2193,13 +2205,13 @@
         <v>26.774463653564453</v>
       </c>
       <c r="E5" s="1">
-        <v>26.228933334350586</v>
+        <v>26.312149047851563</v>
       </c>
       <c r="F5" s="1">
-        <v>26.228933334350586</v>
+        <v>26.312149047851563</v>
       </c>
       <c r="G5" s="1">
-        <v>25.079212188720703</v>
+        <v>25.16242790222168</v>
       </c>
       <c r="H5" s="1">
         <v>2.2826457023620605</v>
@@ -2211,10 +2223,10 @@
         <v>3.9928374290466309</v>
       </c>
       <c r="K5" s="1">
-        <v>-0.56537854671478272</v>
+        <v>-0.88977342844009399</v>
       </c>
       <c r="L5" s="1">
-        <v>11.522054672241211</v>
+        <v>11.505799293518066</v>
       </c>
       <c r="M5" s="1">
         <v>0</v>
@@ -2234,13 +2246,13 @@
         <v>26.774463653564453</v>
       </c>
       <c r="E6" s="1">
-        <v>25.318410873413086</v>
+        <v>25.022989273071289</v>
       </c>
       <c r="F6" s="1">
-        <v>25.318410873413086</v>
+        <v>25.022989273071289</v>
       </c>
       <c r="G6" s="1">
-        <v>24.168436050415039</v>
+        <v>23.873014450073242</v>
       </c>
       <c r="H6" s="1">
         <v>2.2826457023620605</v>
@@ -2252,10 +2264,10 @@
         <v>5.8691129684448242</v>
       </c>
       <c r="K6" s="1">
-        <v>2.0267543792724609</v>
+        <v>3.1896369457244873</v>
       </c>
       <c r="L6" s="1">
-        <v>8.4469757080078125</v>
+        <v>8.509552001953125</v>
       </c>
       <c r="M6" s="1">
         <v>0</v>
@@ -2275,13 +2287,13 @@
         <v>26.774463653564453</v>
       </c>
       <c r="E7" s="1">
-        <v>24.38306999206543</v>
+        <v>23.775920867919922</v>
       </c>
       <c r="F7" s="1">
-        <v>24.38306999206543</v>
+        <v>23.775920867919922</v>
       </c>
       <c r="G7" s="1">
-        <v>23.228727340698242</v>
+        <v>22.621576309204102</v>
       </c>
       <c r="H7" s="1">
         <v>2.2826457023620605</v>
@@ -2293,13 +2305,13 @@
         <v>8.3237791061401367</v>
       </c>
       <c r="K7" s="1">
-        <v>4.1976490020751953</v>
+        <v>6.6061167716979981</v>
       </c>
       <c r="L7" s="1">
-        <v>4.5807633399963379</v>
+        <v>4.7205715179443359</v>
       </c>
       <c r="M7" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -2316,13 +2328,13 @@
         <v>33.739055633544922</v>
       </c>
       <c r="E8" s="1">
-        <v>31.786628723144531</v>
+        <v>31.579368591308594</v>
       </c>
       <c r="F8" s="1">
-        <v>31.786628723144531</v>
+        <v>31.579368591308594</v>
       </c>
       <c r="G8" s="1">
-        <v>30.560972213745117</v>
+        <v>30.35371208190918</v>
       </c>
       <c r="H8" s="1">
         <v>2.4324369430541992</v>
@@ -2334,10 +2346,10 @@
         <v>5.4335556030273438</v>
       </c>
       <c r="K8" s="1">
-        <v>-1.3978339433670044</v>
+        <v>-0.64549577236175537</v>
       </c>
       <c r="L8" s="1">
-        <v>3.0991890430450439</v>
+        <v>2.9803662300109863</v>
       </c>
       <c r="M8" s="1">
         <v>0</v>
@@ -2357,13 +2369,13 @@
         <v>33.739055633544922</v>
       </c>
       <c r="E9" s="1">
-        <v>29.427352905273438</v>
+        <v>30.200901031494141</v>
       </c>
       <c r="F9" s="1">
-        <v>29.427352905273438</v>
+        <v>30.200901031494141</v>
       </c>
       <c r="G9" s="1">
-        <v>28.201423645019531</v>
+        <v>28.974971771240234</v>
       </c>
       <c r="H9" s="1">
         <v>2.4324369430541992</v>
@@ -2375,10 +2387,10 @@
         <v>7.053370475769043</v>
       </c>
       <c r="K9" s="1">
-        <v>5.0109190940856934</v>
+        <v>2.3139567375183105</v>
       </c>
       <c r="L9" s="1">
-        <v>0.15603455901145935</v>
+        <v>0.61715596914291382</v>
       </c>
       <c r="M9" s="1">
         <v>0</v>
@@ -2398,13 +2410,13 @@
         <v>33.739055633544922</v>
       </c>
       <c r="E10" s="1">
-        <v>27.080663681030273</v>
+        <v>28.761171340942383</v>
       </c>
       <c r="F10" s="1">
-        <v>27.080663681030273</v>
+        <v>28.761171340942383</v>
       </c>
       <c r="G10" s="1">
-        <v>25.850080490112305</v>
+        <v>27.530588150024414</v>
       </c>
       <c r="H10" s="1">
         <v>2.4324369430541992</v>
@@ -2416,13 +2428,13 @@
         <v>9.1396102905273438</v>
       </c>
       <c r="K10" s="1">
-        <v>10.378209114074707</v>
+        <v>4.7924790382385254</v>
       </c>
       <c r="L10" s="1">
-        <v>-3.5775794982910156</v>
+        <v>-2.5392048358917236</v>
       </c>
       <c r="M10" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -2439,13 +2451,13 @@
         <v>20.997871398925781</v>
       </c>
       <c r="E11" s="1">
-        <v>20.052921295166016</v>
+        <v>20.020298004150391</v>
       </c>
       <c r="F11" s="1">
-        <v>20.052921295166016</v>
+        <v>20.020298004150391</v>
       </c>
       <c r="G11" s="1">
-        <v>18.621114730834961</v>
+        <v>18.588491439819336</v>
       </c>
       <c r="H11" s="1">
         <v>4.6891798973083496</v>
@@ -2457,10 +2469,10 @@
         <v>5.9410257339477539</v>
       </c>
       <c r="K11" s="1">
-        <v>-1.1965206861495972</v>
+        <v>-1.0172096490859985</v>
       </c>
       <c r="L11" s="1">
-        <v>5.7105202674865723</v>
+        <v>5.6962862014770508</v>
       </c>
       <c r="M11" s="1">
         <v>0</v>
@@ -2480,13 +2492,13 @@
         <v>20.997871398925781</v>
       </c>
       <c r="E12" s="1">
-        <v>18.437797546386719</v>
+        <v>18.554775238037109</v>
       </c>
       <c r="F12" s="1">
-        <v>18.437797546386719</v>
+        <v>18.554775238037109</v>
       </c>
       <c r="G12" s="1">
-        <v>17.005672454833984</v>
+        <v>17.122650146484375</v>
       </c>
       <c r="H12" s="1">
         <v>4.6891798973083496</v>
@@ -2498,10 +2510,10 @@
         <v>9.3541927337646484</v>
       </c>
       <c r="K12" s="1">
-        <v>4.2892565727233887</v>
+        <v>3.6464669704437256</v>
       </c>
       <c r="L12" s="1">
-        <v>0.072676762938499451</v>
+        <v>0.12370235472917557</v>
       </c>
       <c r="M12" s="1">
         <v>0</v>
@@ -2521,13 +2533,13 @@
         <v>20.997871398925781</v>
       </c>
       <c r="E13" s="1">
-        <v>16.628829956054688</v>
+        <v>16.872024536132813</v>
       </c>
       <c r="F13" s="1">
-        <v>16.628829956054688</v>
+        <v>16.872024536132813</v>
       </c>
       <c r="G13" s="1">
-        <v>15.191267013549805</v>
+        <v>15.434459686279297</v>
       </c>
       <c r="H13" s="1">
         <v>4.6891798973083496</v>
@@ -2539,10 +2551,10 @@
         <v>13.726461410522461</v>
       </c>
       <c r="K13" s="1">
-        <v>8.8835592269897461</v>
+        <v>7.5522656440734863</v>
       </c>
       <c r="L13" s="1">
-        <v>-7.0278525352478027</v>
+        <v>-6.9221720695495605</v>
       </c>
       <c r="M13" s="1">
         <v>0</v>
@@ -2562,13 +2574,13 @@
         <v>25.186426162719727</v>
       </c>
       <c r="E14" s="1">
-        <v>24.573089599609375</v>
+        <v>24.735437393188477</v>
       </c>
       <c r="F14" s="1">
-        <v>24.573089599609375</v>
+        <v>24.735437393188477</v>
       </c>
       <c r="G14" s="1">
-        <v>23.39088249206543</v>
+        <v>23.553230285644531</v>
       </c>
       <c r="H14" s="1">
         <v>2.0056905746459961</v>
@@ -2580,7 +2592,7 @@
         <v>5.2559685707092285</v>
       </c>
       <c r="K14" s="1">
-        <v>-0.52895146608352661</v>
+        <v>-1.2266808748245239</v>
       </c>
       <c r="L14" s="1">
         <v>10.599246978759766</v>
@@ -2603,13 +2615,13 @@
         <v>25.186426162719727</v>
       </c>
       <c r="E15" s="1">
-        <v>23.781251907348633</v>
+        <v>23.199142456054688</v>
       </c>
       <c r="F15" s="1">
-        <v>23.781251907348633</v>
+        <v>23.199142456054688</v>
       </c>
       <c r="G15" s="1">
-        <v>22.598781585693359</v>
+        <v>22.016672134399414</v>
       </c>
       <c r="H15" s="1">
         <v>2.0056905746459961</v>
@@ -2621,7 +2633,7 @@
         <v>7.7649846076965332</v>
       </c>
       <c r="K15" s="1">
-        <v>1.8961714506149292</v>
+        <v>4.397374153137207</v>
       </c>
       <c r="L15" s="1">
         <v>6.7154746055603027</v>
@@ -2644,13 +2656,13 @@
         <v>25.186426162719727</v>
       </c>
       <c r="E16" s="1">
-        <v>22.814777374267578</v>
+        <v>21.604581832885742</v>
       </c>
       <c r="F16" s="1">
-        <v>22.814777374267578</v>
+        <v>21.604581832885742</v>
       </c>
       <c r="G16" s="1">
-        <v>21.627817153930664</v>
+        <v>20.417621612548828</v>
       </c>
       <c r="H16" s="1">
         <v>2.0056905746459961</v>
@@ -2662,7 +2674,7 @@
         <v>10.934903144836426</v>
       </c>
       <c r="K16" s="1">
-        <v>3.9271962642669678</v>
+        <v>9.1074838638305664</v>
       </c>
       <c r="L16" s="1">
         <v>1.7954444885253906</v>
@@ -2685,13 +2697,13 @@
         <v>21.000280380249024</v>
       </c>
       <c r="E17" s="1">
-        <v>21.43501091003418</v>
+        <v>21.535800933837891</v>
       </c>
       <c r="F17" s="1">
-        <v>21.087326049804688</v>
+        <v>21.108558654785156</v>
       </c>
       <c r="G17" s="1">
-        <v>20.398204803466797</v>
+        <v>20.498994827270508</v>
       </c>
       <c r="H17" s="1">
         <v>1.8732786178588867</v>
@@ -2703,7 +2715,7 @@
         <v>4.298314094543457</v>
       </c>
       <c r="K17" s="1">
-        <v>-0.25997251272201538</v>
+        <v>-0.77949464321136475</v>
       </c>
       <c r="L17" s="1">
         <v>20.893764495849609</v>
@@ -2726,13 +2738,13 @@
         <v>21.000280380249024</v>
       </c>
       <c r="E18" s="1">
-        <v>21.023605346679688</v>
+        <v>20.662214279174805</v>
       </c>
       <c r="F18" s="1">
-        <v>21.023605346679688</v>
+        <v>20.662214279174805</v>
       </c>
       <c r="G18" s="1">
-        <v>19.986568450927734</v>
+        <v>19.625177383422852</v>
       </c>
       <c r="H18" s="1">
         <v>1.8732786178588867</v>
@@ -2744,7 +2756,7 @@
         <v>6.6617794036865234</v>
       </c>
       <c r="K18" s="1">
-        <v>0.93194276094436646</v>
+        <v>2.7943122386932373</v>
       </c>
       <c r="L18" s="1">
         <v>16.960758209228516</v>
@@ -2767,13 +2779,13 @@
         <v>21.000280380249024</v>
       </c>
       <c r="E19" s="1">
-        <v>20.588703155517578</v>
+        <v>19.837373733520508</v>
       </c>
       <c r="F19" s="1">
-        <v>20.588703155517578</v>
+        <v>19.837373733520508</v>
       </c>
       <c r="G19" s="1">
-        <v>19.5477294921875</v>
+        <v>18.796398162841797</v>
       </c>
       <c r="H19" s="1">
         <v>1.8732786178588867</v>
@@ -2785,7 +2797,7 @@
         <v>9.8408060073852539</v>
       </c>
       <c r="K19" s="1">
-        <v>1.930164098739624</v>
+        <v>5.7873525619506836</v>
       </c>
       <c r="L19" s="1">
         <v>12.130273818969727</v>
@@ -2876,28 +2888,28 @@
         <v>15.258353233337402</v>
       </c>
       <c r="E2" s="1">
-        <v>13.953507423400879</v>
+        <v>13.660133361816406</v>
       </c>
       <c r="F2" s="1">
-        <v>8.9468879699707031</v>
+        <v>9.9988040924072266</v>
       </c>
       <c r="G2" s="1">
-        <v>4.332122802734375</v>
+        <v>6.5190367698669434</v>
       </c>
       <c r="H2" s="1">
-        <v>13.953507423400879</v>
+        <v>13.660133361816406</v>
       </c>
       <c r="I2" s="1">
-        <v>8.9468879699707031</v>
+        <v>9.9988040924072266</v>
       </c>
       <c r="J2" s="1">
-        <v>4.332122802734375</v>
+        <v>6.5190367698669434</v>
       </c>
       <c r="K2" s="1">
         <v>4.110689640045166</v>
       </c>
       <c r="L2" s="1">
-        <v>598.98114013671875</v>
+        <v>397.42337036132813</v>
       </c>
       <c r="M2" s="1">
         <v>0</v>
@@ -2912,13 +2924,13 @@
         <v>20.47364616394043</v>
       </c>
       <c r="Q2" s="1">
-        <v>-6.1849474906921387</v>
+        <v>-4.1037063598632813</v>
       </c>
       <c r="R2" s="1">
-        <v>22.171640396118164</v>
+        <v>14.710862159729004</v>
       </c>
       <c r="S2" s="1">
-        <v>45.920097351074219</v>
+        <v>30.467941284179688</v>
       </c>
     </row>
     <row r="3">
@@ -2926,58 +2938,58 @@
         <v>48</v>
       </c>
       <c r="B3" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="1">
         <v>0</v>
       </c>
       <c r="D3" s="1">
-        <v>14.531709671020508</v>
+        <v>11.067777633666992</v>
       </c>
       <c r="E3" s="1">
-        <v>14.789926528930664</v>
+        <v>10.294058799743652</v>
       </c>
       <c r="F3" s="1">
-        <v>9.5582170486450195</v>
+        <v>9.5906448364257813</v>
       </c>
       <c r="G3" s="1">
-        <v>4.5139832496643066</v>
+        <v>8.6048049926757813</v>
       </c>
       <c r="H3" s="1">
-        <v>14.441656112670898</v>
+        <v>10.294058799743652</v>
       </c>
       <c r="I3" s="1">
-        <v>9.5582170486450195</v>
+        <v>9.5906448364257813</v>
       </c>
       <c r="J3" s="1">
-        <v>4.5139832496643066</v>
+        <v>8.6048049926757813</v>
       </c>
       <c r="K3" s="1">
-        <v>2.7762997150421143</v>
+        <v>4.0069994926452637</v>
       </c>
       <c r="L3" s="1">
-        <v>748.1282958984375</v>
+        <v>19.888339996337891</v>
       </c>
       <c r="M3" s="1">
         <v>0</v>
       </c>
       <c r="N3" s="1">
-        <v>0.87802988290786743</v>
+        <v>2.3124582767486572</v>
       </c>
       <c r="O3" s="1">
-        <v>4.6583266258239746</v>
+        <v>6.5004057884216309</v>
       </c>
       <c r="P3" s="1">
-        <v>9.8767995834350586</v>
+        <v>12.252050399780273</v>
       </c>
       <c r="Q3" s="1">
-        <v>-7.7250099182128906</v>
+        <v>-0.20536266267299652</v>
       </c>
       <c r="R3" s="1">
-        <v>27.692415237426758</v>
+        <v>0.73617881536483765</v>
       </c>
       <c r="S3" s="1">
-        <v>57.354278564453125</v>
+        <v>1.5247136354446411</v>
       </c>
     </row>
     <row r="4">
@@ -2991,52 +3003,52 @@
         <v>0</v>
       </c>
       <c r="D4" s="1">
-        <v>11.067777633666992</v>
+        <v>16.995023727416992</v>
       </c>
       <c r="E4" s="1">
-        <v>10.273059844970703</v>
+        <v>14.599208831787109</v>
       </c>
       <c r="F4" s="1">
-        <v>9.6659345626831055</v>
+        <v>12.234023094177246</v>
       </c>
       <c r="G4" s="1">
-        <v>8.7613296508789063</v>
+        <v>9.7104988098144531</v>
       </c>
       <c r="H4" s="1">
-        <v>10.273059844970703</v>
+        <v>14.599208831787109</v>
       </c>
       <c r="I4" s="1">
-        <v>9.6659345626831055</v>
+        <v>12.234023094177246</v>
       </c>
       <c r="J4" s="1">
-        <v>8.7613296508789063</v>
+        <v>9.7104988098144531</v>
       </c>
       <c r="K4" s="1">
-        <v>4.0069994926452637</v>
+        <v>9.7105236053466797</v>
       </c>
       <c r="L4" s="1">
-        <v>0</v>
+        <v>107.99939727783203</v>
       </c>
       <c r="M4" s="1">
         <v>0</v>
       </c>
       <c r="N4" s="1">
-        <v>2.3124582767486572</v>
+        <v>2.5873517990112305</v>
       </c>
       <c r="O4" s="1">
-        <v>6.5004057884216309</v>
+        <v>10.777472496032715</v>
       </c>
       <c r="P4" s="1">
-        <v>12.252050399780273</v>
+        <v>20.612627029418945</v>
       </c>
       <c r="Q4" s="1">
-        <v>0</v>
+        <v>-1.1151782274246216</v>
       </c>
       <c r="R4" s="1">
-        <v>0</v>
+        <v>3.9976620674133301</v>
       </c>
       <c r="S4" s="1">
-        <v>0</v>
+        <v>8.279632568359375</v>
       </c>
     </row>
     <row r="5">
@@ -3044,58 +3056,58 @@
         <v>50</v>
       </c>
       <c r="B5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="1">
         <v>0</v>
       </c>
       <c r="D5" s="1">
-        <v>16.995023727416992</v>
+        <v>14.531709671020508</v>
       </c>
       <c r="E5" s="1">
-        <v>14.599208831787109</v>
+        <v>13.839043617248535</v>
       </c>
       <c r="F5" s="1">
-        <v>12.234023094177246</v>
+        <v>12.967679023742676</v>
       </c>
       <c r="G5" s="1">
-        <v>9.7104988098144531</v>
+        <v>11.602200508117676</v>
       </c>
       <c r="H5" s="1">
-        <v>14.599208831787109</v>
+        <v>13.839043617248535</v>
       </c>
       <c r="I5" s="1">
-        <v>12.234023094177246</v>
+        <v>12.967679023742676</v>
       </c>
       <c r="J5" s="1">
-        <v>9.7104988098144531</v>
+        <v>11.602200508117676</v>
       </c>
       <c r="K5" s="1">
-        <v>9.7105236053466797</v>
+        <v>2.7762997150421143</v>
       </c>
       <c r="L5" s="1">
-        <v>107.99939727783203</v>
+        <v>62.173713684082031</v>
       </c>
       <c r="M5" s="1">
         <v>0</v>
       </c>
       <c r="N5" s="1">
-        <v>2.5873517990112305</v>
+        <v>0.87802988290786743</v>
       </c>
       <c r="O5" s="1">
-        <v>10.777472496032715</v>
+        <v>4.6583266258239746</v>
       </c>
       <c r="P5" s="1">
-        <v>20.612627029418945</v>
+        <v>9.8767995834350586</v>
       </c>
       <c r="Q5" s="1">
-        <v>-1.1151782274246216</v>
+        <v>-0.64199221134185791</v>
       </c>
       <c r="R5" s="1">
-        <v>3.9976620674133301</v>
+        <v>2.3013970851898193</v>
       </c>
       <c r="S5" s="1">
-        <v>8.279632568359375</v>
+        <v>4.7664666175842285</v>
       </c>
     </row>
     <row r="6">
@@ -3109,52 +3121,52 @@
         <v>0</v>
       </c>
       <c r="D6" s="1">
-        <v>23.036062240600586</v>
+        <v>17.446327209472656</v>
       </c>
       <c r="E6" s="1">
-        <v>24.048755645751953</v>
+        <v>14.707612991333008</v>
       </c>
       <c r="F6" s="1">
-        <v>18.155899047851563</v>
+        <v>13.520934104919434</v>
       </c>
       <c r="G6" s="1">
-        <v>13.120973587036133</v>
+        <v>12.338296890258789</v>
       </c>
       <c r="H6" s="1">
-        <v>23.208763122558594</v>
+        <v>14.707612991333008</v>
       </c>
       <c r="I6" s="1">
-        <v>18.155899047851563</v>
+        <v>13.520934104919434</v>
       </c>
       <c r="J6" s="1">
-        <v>13.120973587036133</v>
+        <v>12.338296890258789</v>
       </c>
       <c r="K6" s="1">
-        <v>0.52955126762390137</v>
+        <v>2.846287727355957</v>
       </c>
       <c r="L6" s="1">
-        <v>557.02593994140625</v>
+        <v>83.617057800292969</v>
       </c>
       <c r="M6" s="1">
         <v>0</v>
       </c>
       <c r="N6" s="1">
-        <v>1.100072979927063</v>
+        <v>0</v>
       </c>
       <c r="O6" s="1">
-        <v>2.4174280166625977</v>
+        <v>3.2099995613098145</v>
       </c>
       <c r="P6" s="1">
-        <v>4.3831706047058106</v>
+        <v>7.2772231101989746</v>
       </c>
       <c r="Q6" s="1">
-        <v>-5.7517280578613281</v>
+        <v>-0.8634113073348999</v>
       </c>
       <c r="R6" s="1">
-        <v>20.618646621704102</v>
+        <v>3.0951347351074219</v>
       </c>
       <c r="S6" s="1">
-        <v>42.703670501708984</v>
+        <v>6.4103927612304688</v>
       </c>
     </row>
     <row r="7">
@@ -3162,58 +3174,58 @@
         <v>52</v>
       </c>
       <c r="B7" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="1">
         <v>0</v>
       </c>
       <c r="D7" s="1">
-        <v>17.446327209472656</v>
+        <v>18.721660614013672</v>
       </c>
       <c r="E7" s="1">
-        <v>14.568453788757324</v>
+        <v>18.569673538208008</v>
       </c>
       <c r="F7" s="1">
-        <v>14.019899368286133</v>
+        <v>16.371454238891602</v>
       </c>
       <c r="G7" s="1">
-        <v>13.375641822814941</v>
+        <v>13.824036598205566</v>
       </c>
       <c r="H7" s="1">
-        <v>14.568453788757324</v>
+        <v>18.466142654418945</v>
       </c>
       <c r="I7" s="1">
-        <v>14.019899368286133</v>
+        <v>16.371454238891602</v>
       </c>
       <c r="J7" s="1">
-        <v>13.375641822814941</v>
+        <v>13.824036598205566</v>
       </c>
       <c r="K7" s="1">
-        <v>2.846287727355957</v>
+        <v>5.2122688293457031</v>
       </c>
       <c r="L7" s="1">
-        <v>0</v>
+        <v>250.19287109375</v>
       </c>
       <c r="M7" s="1">
         <v>0</v>
       </c>
       <c r="N7" s="1">
-        <v>0</v>
+        <v>6.6135783195495605</v>
       </c>
       <c r="O7" s="1">
-        <v>3.2099995613098145</v>
+        <v>10.562674522399902</v>
       </c>
       <c r="P7" s="1">
-        <v>7.2772231101989746</v>
+        <v>15.713345527648926</v>
       </c>
       <c r="Q7" s="1">
-        <v>0</v>
+        <v>-2.5834367275238037</v>
       </c>
       <c r="R7" s="1">
-        <v>0</v>
+        <v>9.2610368728637695</v>
       </c>
       <c r="S7" s="1">
-        <v>0</v>
+        <v>19.180709838867188</v>
       </c>
     </row>
     <row r="8">
@@ -3221,58 +3233,58 @@
         <v>53</v>
       </c>
       <c r="B8" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="1">
-        <v>18.721660614013672</v>
+        <v>20.045049667358399</v>
       </c>
       <c r="E8" s="1">
-        <v>18.6204833984375</v>
+        <v>19.758615493774414</v>
       </c>
       <c r="F8" s="1">
-        <v>16.189268112182617</v>
+        <v>18.065219879150391</v>
       </c>
       <c r="G8" s="1">
-        <v>13.445269584655762</v>
+        <v>15.11362361907959</v>
       </c>
       <c r="H8" s="1">
-        <v>18.48286247253418</v>
+        <v>19.758615493774414</v>
       </c>
       <c r="I8" s="1">
-        <v>16.189268112182617</v>
+        <v>18.065219879150391</v>
       </c>
       <c r="J8" s="1">
-        <v>13.445269584655762</v>
+        <v>15.11362361907959</v>
       </c>
       <c r="K8" s="1">
-        <v>5.2122688293457031</v>
+        <v>2.9860866069793701</v>
       </c>
       <c r="L8" s="1">
-        <v>278.64407348632813</v>
+        <v>134.81123352050781</v>
       </c>
       <c r="M8" s="1">
         <v>0</v>
       </c>
       <c r="N8" s="1">
-        <v>6.6135783195495605</v>
+        <v>9.7155628204345703</v>
       </c>
       <c r="O8" s="1">
-        <v>10.562674522399902</v>
+        <v>16.716278076171875</v>
       </c>
       <c r="P8" s="1">
-        <v>15.713345527648926</v>
+        <v>25.319673538208008</v>
       </c>
       <c r="Q8" s="1">
-        <v>-2.8772175312042236</v>
+        <v>-1.3920310735702515</v>
       </c>
       <c r="R8" s="1">
-        <v>10.314175605773926</v>
+        <v>4.9901175498962402</v>
       </c>
       <c r="S8" s="1">
-        <v>21.361883163452148</v>
+        <v>10.335126876831055</v>
       </c>
     </row>
     <row r="9">
@@ -3280,58 +3292,58 @@
         <v>54</v>
       </c>
       <c r="B9" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="1">
-        <v>24.320249557495117</v>
+        <v>18.293428421020508</v>
       </c>
       <c r="E9" s="1">
-        <v>23.969804763793945</v>
+        <v>18.193994522094727</v>
       </c>
       <c r="F9" s="1">
-        <v>19.696483612060547</v>
+        <v>17.126621246337891</v>
       </c>
       <c r="G9" s="1">
-        <v>15.744843482971191</v>
+        <v>16.0509033203125</v>
       </c>
       <c r="H9" s="1">
-        <v>23.939676284790039</v>
+        <v>18.167383193969727</v>
       </c>
       <c r="I9" s="1">
-        <v>19.696483612060547</v>
+        <v>17.126621246337891</v>
       </c>
       <c r="J9" s="1">
-        <v>15.744843482971191</v>
+        <v>16.0509033203125</v>
       </c>
       <c r="K9" s="1">
-        <v>2.0872793197631836</v>
+        <v>1.9084329605102539</v>
       </c>
       <c r="L9" s="1">
-        <v>372.96136474609375</v>
+        <v>104.42517852783203</v>
       </c>
       <c r="M9" s="1">
         <v>0</v>
       </c>
       <c r="N9" s="1">
-        <v>1.9466069936752319</v>
+        <v>3.6911745071411133</v>
       </c>
       <c r="O9" s="1">
-        <v>4.3342394828796387</v>
+        <v>6.7656407356262207</v>
       </c>
       <c r="P9" s="1">
-        <v>7.2991957664489746</v>
+        <v>10.635995864868164</v>
       </c>
       <c r="Q9" s="1">
-        <v>-3.8511176109313965</v>
+        <v>-1.0782716274261475</v>
       </c>
       <c r="R9" s="1">
-        <v>13.805386543273926</v>
+        <v>3.8653600215911865</v>
       </c>
       <c r="S9" s="1">
-        <v>28.592596054077149</v>
+        <v>8.005620002746582</v>
       </c>
     </row>
     <row r="10">
@@ -3339,58 +3351,58 @@
         <v>55</v>
       </c>
       <c r="B10" s="1">
+        <v>4</v>
+      </c>
+      <c r="C10" s="1">
         <v>1</v>
       </c>
-      <c r="C10" s="1">
-        <v>0</v>
-      </c>
       <c r="D10" s="1">
-        <v>20.894319534301758</v>
+        <v>17.884822845458984</v>
       </c>
       <c r="E10" s="1">
-        <v>20.035505294799805</v>
+        <v>18.550848007202148</v>
       </c>
       <c r="F10" s="1">
-        <v>18.20323371887207</v>
+        <v>17.704624176025391</v>
       </c>
       <c r="G10" s="1">
-        <v>16.038419723510742</v>
+        <v>16.921169281005859</v>
       </c>
       <c r="H10" s="1">
-        <v>20.035505294799805</v>
+        <v>18.02391242980957</v>
       </c>
       <c r="I10" s="1">
-        <v>18.20323371887207</v>
+        <v>17.704624176025391</v>
       </c>
       <c r="J10" s="1">
-        <v>16.038419723510742</v>
+        <v>16.921169281005859</v>
       </c>
       <c r="K10" s="1">
-        <v>3.036236047744751</v>
+        <v>0.99057501554489136</v>
       </c>
       <c r="L10" s="1">
-        <v>164.36265563964844</v>
+        <v>99.417144775390625</v>
       </c>
       <c r="M10" s="1">
         <v>0</v>
       </c>
       <c r="N10" s="1">
-        <v>0.26833945512771606</v>
+        <v>2.4085962772369385</v>
       </c>
       <c r="O10" s="1">
-        <v>3.311276912689209</v>
+        <v>5.2269372940063477</v>
       </c>
       <c r="P10" s="1">
-        <v>7.225557804107666</v>
+        <v>8.8422298431396484</v>
       </c>
       <c r="Q10" s="1">
-        <v>-1.6971728801727295</v>
+        <v>-1.0265597105026245</v>
       </c>
       <c r="R10" s="1">
-        <v>6.0839815139770508</v>
+        <v>3.6799843311309815</v>
       </c>
       <c r="S10" s="1">
-        <v>12.600648880004883</v>
+        <v>7.6216850280761719</v>
       </c>
     </row>
     <row r="11">
@@ -3398,58 +3410,58 @@
         <v>56</v>
       </c>
       <c r="B11" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="1">
-        <v>20.045049667358399</v>
+        <v>20.894319534301758</v>
       </c>
       <c r="E11" s="1">
-        <v>19.632438659667969</v>
+        <v>19.894077301025391</v>
       </c>
       <c r="F11" s="1">
-        <v>18.51762580871582</v>
+        <v>18.710332870483398</v>
       </c>
       <c r="G11" s="1">
-        <v>16.054164886474609</v>
+        <v>17.092670440673828</v>
       </c>
       <c r="H11" s="1">
-        <v>19.632438659667969</v>
+        <v>19.894077301025391</v>
       </c>
       <c r="I11" s="1">
-        <v>18.51762580871582</v>
+        <v>18.710332870483398</v>
       </c>
       <c r="J11" s="1">
-        <v>16.054164886474609</v>
+        <v>17.092670440673828</v>
       </c>
       <c r="K11" s="1">
-        <v>2.9860866069793701</v>
+        <v>3.036236047744751</v>
       </c>
       <c r="L11" s="1">
-        <v>68.826248168945313</v>
+        <v>93.40631103515625</v>
       </c>
       <c r="M11" s="1">
         <v>0</v>
       </c>
       <c r="N11" s="1">
-        <v>9.7155628204345703</v>
+        <v>0.26833945512771606</v>
       </c>
       <c r="O11" s="1">
-        <v>16.716278076171875</v>
+        <v>3.311276912689209</v>
       </c>
       <c r="P11" s="1">
-        <v>25.319673538208008</v>
+        <v>7.225557804107666</v>
       </c>
       <c r="Q11" s="1">
-        <v>-0.71068477630615234</v>
+        <v>-0.96449315547943115</v>
       </c>
       <c r="R11" s="1">
-        <v>2.5476441383361817</v>
+        <v>3.4574902057647705</v>
       </c>
       <c r="S11" s="1">
-        <v>5.2764739990234375</v>
+        <v>7.1608729362487793</v>
       </c>
     </row>
     <row r="12">
@@ -3457,58 +3469,58 @@
         <v>57</v>
       </c>
       <c r="B12" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="1">
-        <v>18.293428421020508</v>
+        <v>23.414220809936524</v>
       </c>
       <c r="E12" s="1">
-        <v>18.047218322753906</v>
+        <v>22.750297546386719</v>
       </c>
       <c r="F12" s="1">
-        <v>17.652900695800781</v>
+        <v>20.390876770019531</v>
       </c>
       <c r="G12" s="1">
-        <v>17.145034790039063</v>
+        <v>18.045185089111328</v>
       </c>
       <c r="H12" s="1">
-        <v>18.047218322753906</v>
+        <v>22.750297546386719</v>
       </c>
       <c r="I12" s="1">
-        <v>17.652900695800781</v>
+        <v>20.390876770019531</v>
       </c>
       <c r="J12" s="1">
-        <v>17.145034790039063</v>
+        <v>18.045185089111328</v>
       </c>
       <c r="K12" s="1">
-        <v>1.9084329605102539</v>
+        <v>2.153038501739502</v>
       </c>
       <c r="L12" s="1">
-        <v>20.314830780029297</v>
+        <v>199.36177062988281</v>
       </c>
       <c r="M12" s="1">
         <v>0</v>
       </c>
       <c r="N12" s="1">
-        <v>3.6911745071411133</v>
+        <v>0</v>
       </c>
       <c r="O12" s="1">
-        <v>6.7656407356262207</v>
+        <v>1.6311819553375244</v>
       </c>
       <c r="P12" s="1">
-        <v>10.635995864868164</v>
+        <v>3.7332696914672852</v>
       </c>
       <c r="Q12" s="1">
-        <v>-0.20976652204990387</v>
+        <v>-2.0585658550262451</v>
       </c>
       <c r="R12" s="1">
-        <v>0.75196552276611328</v>
+        <v>7.3794941902160645</v>
       </c>
       <c r="S12" s="1">
-        <v>1.5574100017547607</v>
+        <v>15.283807754516602</v>
       </c>
     </row>
     <row r="13">
@@ -3516,58 +3528,58 @@
         <v>58</v>
       </c>
       <c r="B13" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="1">
-        <v>17.884822845458984</v>
+        <v>23.088916778564453</v>
       </c>
       <c r="E13" s="1">
-        <v>18.472982406616211</v>
+        <v>23.290472030639648</v>
       </c>
       <c r="F13" s="1">
-        <v>17.983821868896484</v>
+        <v>20.509708404541016</v>
       </c>
       <c r="G13" s="1">
-        <v>17.501615524291992</v>
+        <v>18.115036010742188</v>
       </c>
       <c r="H13" s="1">
-        <v>18.007511138916016</v>
+        <v>23.050949096679688</v>
       </c>
       <c r="I13" s="1">
-        <v>17.958602905273438</v>
+        <v>20.509708404541016</v>
       </c>
       <c r="J13" s="1">
-        <v>17.501615524291992</v>
+        <v>18.115036010742188</v>
       </c>
       <c r="K13" s="1">
-        <v>0.99057501554489136</v>
+        <v>1.8331828117370605</v>
       </c>
       <c r="L13" s="1">
-        <v>53.776096343994141</v>
+        <v>255.63514709472656</v>
       </c>
       <c r="M13" s="1">
         <v>0</v>
       </c>
       <c r="N13" s="1">
-        <v>2.4085962772369385</v>
+        <v>0.6298632025718689</v>
       </c>
       <c r="O13" s="1">
-        <v>5.2269372940063477</v>
+        <v>2.4449839591979981</v>
       </c>
       <c r="P13" s="1">
-        <v>8.8422298431396484</v>
+        <v>4.8412685394287109</v>
       </c>
       <c r="Q13" s="1">
-        <v>-0.55528020858764648</v>
+        <v>-2.6396324634552002</v>
       </c>
       <c r="R13" s="1">
-        <v>1.9905540943145752</v>
+        <v>9.4624862670898438</v>
       </c>
       <c r="S13" s="1">
-        <v>4.1226739883422852</v>
+        <v>19.597934722900391</v>
       </c>
     </row>
     <row r="14">
@@ -3575,58 +3587,58 @@
         <v>59</v>
       </c>
       <c r="B14" s="1">
+        <v>3</v>
+      </c>
+      <c r="C14" s="1">
         <v>1</v>
       </c>
-      <c r="C14" s="1">
-        <v>0</v>
-      </c>
       <c r="D14" s="1">
-        <v>30.1993408203125</v>
+        <v>20.405284881591797</v>
       </c>
       <c r="E14" s="1">
-        <v>22.168155670166016</v>
+        <v>20.669912338256836</v>
       </c>
       <c r="F14" s="1">
-        <v>19.812767028808594</v>
+        <v>19.620058059692383</v>
       </c>
       <c r="G14" s="1">
-        <v>17.515897750854492</v>
+        <v>18.449911117553711</v>
       </c>
       <c r="H14" s="1">
-        <v>22.168155670166016</v>
+        <v>20.431947708129883</v>
       </c>
       <c r="I14" s="1">
-        <v>19.812767028808594</v>
+        <v>19.620058059692383</v>
       </c>
       <c r="J14" s="1">
-        <v>17.515897750854492</v>
+        <v>18.449911117553711</v>
       </c>
       <c r="K14" s="1">
-        <v>2.441215991973877</v>
+        <v>1.8116350173950195</v>
       </c>
       <c r="L14" s="1">
-        <v>104.05338287353516</v>
+        <v>91.358657836914063</v>
       </c>
       <c r="M14" s="1">
         <v>0</v>
       </c>
       <c r="N14" s="1">
-        <v>0</v>
+        <v>4.443941593170166</v>
       </c>
       <c r="O14" s="1">
-        <v>1.481977105140686</v>
+        <v>8.5933599472045899</v>
       </c>
       <c r="P14" s="1">
-        <v>3.3364059925079346</v>
+        <v>13.72999382019043</v>
       </c>
       <c r="Q14" s="1">
-        <v>-1.0744326114654541</v>
+        <v>-0.94334948062896729</v>
       </c>
       <c r="R14" s="1">
-        <v>3.851597785949707</v>
+        <v>3.381695032119751</v>
       </c>
       <c r="S14" s="1">
-        <v>7.9771161079406738</v>
+        <v>7.0038914680480957</v>
       </c>
     </row>
     <row r="15">
@@ -3640,52 +3652,52 @@
         <v>0</v>
       </c>
       <c r="D15" s="1">
-        <v>23.573837280273438</v>
+        <v>30.1993408203125</v>
       </c>
       <c r="E15" s="1">
-        <v>22.581605911254883</v>
+        <v>21.983280181884766</v>
       </c>
       <c r="F15" s="1">
-        <v>20.625648498535156</v>
+        <v>20.475656509399414</v>
       </c>
       <c r="G15" s="1">
-        <v>17.981990814208984</v>
+        <v>18.894035339355469</v>
       </c>
       <c r="H15" s="1">
-        <v>22.581605911254883</v>
+        <v>21.983280181884766</v>
       </c>
       <c r="I15" s="1">
-        <v>20.625648498535156</v>
+        <v>20.475656509399414</v>
       </c>
       <c r="J15" s="1">
-        <v>17.981990814208984</v>
+        <v>18.894035339355469</v>
       </c>
       <c r="K15" s="1">
-        <v>3.2154037952423096</v>
+        <v>2.441215991973877</v>
       </c>
       <c r="L15" s="1">
-        <v>176.12789916992188</v>
+        <v>39.877792358398438</v>
       </c>
       <c r="M15" s="1">
         <v>0</v>
       </c>
       <c r="N15" s="1">
-        <v>1.6507298946380615</v>
+        <v>0</v>
       </c>
       <c r="O15" s="1">
-        <v>5.0641231536865234</v>
+        <v>1.481977105140686</v>
       </c>
       <c r="P15" s="1">
-        <v>9.2124223709106445</v>
+        <v>3.3364059925079346</v>
       </c>
       <c r="Q15" s="1">
-        <v>-1.8186583518981934</v>
+        <v>-0.41176936030387878</v>
       </c>
       <c r="R15" s="1">
-        <v>6.5194787979125977</v>
+        <v>1.4761000871658325</v>
       </c>
       <c r="S15" s="1">
-        <v>13.502614974975586</v>
+        <v>3.0571784973144531</v>
       </c>
     </row>
     <row r="16">
@@ -3699,52 +3711,52 @@
         <v>0</v>
       </c>
       <c r="D16" s="1">
-        <v>28.380533218383789</v>
+        <v>28.985597610473633</v>
       </c>
       <c r="E16" s="1">
-        <v>28.277248382568359</v>
+        <v>26.783292770385742</v>
       </c>
       <c r="F16" s="1">
-        <v>23.010080337524414</v>
+        <v>22.922908782958984</v>
       </c>
       <c r="G16" s="1">
-        <v>18.461458206176758</v>
+        <v>19.464162826538086</v>
       </c>
       <c r="H16" s="1">
-        <v>28.072620391845703</v>
+        <v>26.783292770385742</v>
       </c>
       <c r="I16" s="1">
-        <v>23.010080337524414</v>
+        <v>22.922908782958984</v>
       </c>
       <c r="J16" s="1">
-        <v>18.461458206176758</v>
+        <v>19.464162826538086</v>
       </c>
       <c r="K16" s="1">
-        <v>0.76714533567428589</v>
+        <v>1.4881768226623535</v>
       </c>
       <c r="L16" s="1">
-        <v>400.8197021484375</v>
+        <v>247.36726379394531</v>
       </c>
       <c r="M16" s="1">
         <v>0</v>
       </c>
       <c r="N16" s="1">
-        <v>14.127007484436035</v>
+        <v>0</v>
       </c>
       <c r="O16" s="1">
-        <v>15.798462867736816</v>
+        <v>0.96296417713165283</v>
       </c>
       <c r="P16" s="1">
-        <v>17.930709838867188</v>
+        <v>2.1726033687591553</v>
       </c>
       <c r="Q16" s="1">
-        <v>-4.1387767791748047</v>
+        <v>-2.55426025390625</v>
       </c>
       <c r="R16" s="1">
-        <v>14.836581230163574</v>
+        <v>9.1564464569091797</v>
       </c>
       <c r="S16" s="1">
-        <v>30.72831916809082</v>
+        <v>18.964090347290039</v>
       </c>
     </row>
     <row r="17">
@@ -3752,58 +3764,58 @@
         <v>62</v>
       </c>
       <c r="B17" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="1">
-        <v>20.405284881591797</v>
+        <v>23.573837280273438</v>
       </c>
       <c r="E17" s="1">
-        <v>20.588369369506836</v>
+        <v>22.423791885375977</v>
       </c>
       <c r="F17" s="1">
-        <v>19.912443161010742</v>
+        <v>21.440399169921875</v>
       </c>
       <c r="G17" s="1">
-        <v>19.057771682739258</v>
+        <v>19.968385696411133</v>
       </c>
       <c r="H17" s="1">
-        <v>20.414770126342774</v>
+        <v>22.423791885375977</v>
       </c>
       <c r="I17" s="1">
-        <v>19.912443161010742</v>
+        <v>21.440399169921875</v>
       </c>
       <c r="J17" s="1">
-        <v>19.057771682739258</v>
+        <v>19.968385696411133</v>
       </c>
       <c r="K17" s="1">
-        <v>1.8116350173950195</v>
+        <v>3.2154037952423096</v>
       </c>
       <c r="L17" s="1">
-        <v>49.466175079345703</v>
+        <v>52.231098175048828</v>
       </c>
       <c r="M17" s="1">
         <v>0</v>
       </c>
       <c r="N17" s="1">
-        <v>4.443941593170166</v>
+        <v>1.6507298946380615</v>
       </c>
       <c r="O17" s="1">
-        <v>8.5933599472045899</v>
+        <v>5.0641231536865234</v>
       </c>
       <c r="P17" s="1">
-        <v>13.72999382019043</v>
+        <v>9.2124223709106445</v>
       </c>
       <c r="Q17" s="1">
-        <v>-0.51077693700790405</v>
+        <v>-0.53932696580886841</v>
       </c>
       <c r="R17" s="1">
-        <v>1.8310197591781616</v>
+        <v>1.9333652257919312</v>
       </c>
       <c r="S17" s="1">
-        <v>3.7922592163085938</v>
+        <v>4.0042281150817871</v>
       </c>
     </row>
     <row r="18">
@@ -3811,58 +3823,58 @@
         <v>63</v>
       </c>
       <c r="B18" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" s="1">
         <v>0</v>
       </c>
       <c r="D18" s="1">
-        <v>23.414220809936524</v>
+        <v>22.279584884643555</v>
       </c>
       <c r="E18" s="1">
-        <v>22.605495452880859</v>
+        <v>21.953798294067383</v>
       </c>
       <c r="F18" s="1">
-        <v>20.910068511962891</v>
+        <v>21.014358520507813</v>
       </c>
       <c r="G18" s="1">
-        <v>19.124574661254883</v>
+        <v>20.192378997802734</v>
       </c>
       <c r="H18" s="1">
-        <v>22.605495452880859</v>
+        <v>21.953798294067383</v>
       </c>
       <c r="I18" s="1">
-        <v>20.910068511962891</v>
+        <v>21.014358520507813</v>
       </c>
       <c r="J18" s="1">
-        <v>19.124574661254883</v>
+        <v>20.192378997802734</v>
       </c>
       <c r="K18" s="1">
-        <v>2.153038501739502</v>
+        <v>1.231325626373291</v>
       </c>
       <c r="L18" s="1">
-        <v>134.53208923339844</v>
+        <v>76.359031677246094</v>
       </c>
       <c r="M18" s="1">
         <v>0</v>
       </c>
       <c r="N18" s="1">
-        <v>0</v>
+        <v>11.425483703613281</v>
       </c>
       <c r="O18" s="1">
-        <v>1.6311819553375244</v>
+        <v>13.490241050720215</v>
       </c>
       <c r="P18" s="1">
-        <v>3.7332696914672852</v>
+        <v>16.114065170288086</v>
       </c>
       <c r="Q18" s="1">
-        <v>-1.3891488313674927</v>
+        <v>-0.78846675157546997</v>
       </c>
       <c r="R18" s="1">
-        <v>4.9797854423522949</v>
+        <v>2.8264749050140381</v>
       </c>
       <c r="S18" s="1">
-        <v>10.313726425170898</v>
+        <v>5.8539657592773438</v>
       </c>
     </row>
     <row r="19">
@@ -3870,58 +3882,58 @@
         <v>64</v>
       </c>
       <c r="B19" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19" s="1">
         <v>0</v>
       </c>
       <c r="D19" s="1">
-        <v>33.737167358398438</v>
+        <v>23.519998550415039</v>
       </c>
       <c r="E19" s="1">
-        <v>31.302248001098633</v>
+        <v>23.419235229492188</v>
       </c>
       <c r="F19" s="1">
-        <v>26.00886344909668</v>
+        <v>21.971221923828125</v>
       </c>
       <c r="G19" s="1">
-        <v>20.975751876831055</v>
+        <v>20.645145416259766</v>
       </c>
       <c r="H19" s="1">
-        <v>31.302248001098633</v>
+        <v>23.373727798461914</v>
       </c>
       <c r="I19" s="1">
-        <v>26.00886344909668</v>
+        <v>21.971221923828125</v>
       </c>
       <c r="J19" s="1">
-        <v>20.975751876831055</v>
+        <v>20.645145416259766</v>
       </c>
       <c r="K19" s="1">
-        <v>4.3763270378112793</v>
+        <v>1.8094415664672852</v>
       </c>
       <c r="L19" s="1">
-        <v>230.40496826171875</v>
+        <v>141.19319152832031</v>
       </c>
       <c r="M19" s="1">
         <v>0</v>
       </c>
       <c r="N19" s="1">
-        <v>0</v>
+        <v>4.2926797866821289</v>
       </c>
       <c r="O19" s="1">
-        <v>4.7703018188476563</v>
+        <v>6.71484375</v>
       </c>
       <c r="P19" s="1">
-        <v>10.402714729309082</v>
+        <v>9.7364273071289063</v>
       </c>
       <c r="Q19" s="1">
-        <v>-2.3791112899780273</v>
+        <v>-1.4579299688339233</v>
       </c>
       <c r="R19" s="1">
-        <v>8.5285768508911133</v>
+        <v>5.2263503074645996</v>
       </c>
       <c r="S19" s="1">
-        <v>17.663694381713867</v>
+        <v>10.824390411376953</v>
       </c>
     </row>
     <row r="20">
@@ -3929,58 +3941,58 @@
         <v>65</v>
       </c>
       <c r="B20" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" s="1">
-        <v>22.279584884643555</v>
+        <v>21.489063262939453</v>
       </c>
       <c r="E20" s="1">
-        <v>21.832197189331055</v>
+        <v>22.31791877746582</v>
       </c>
       <c r="F20" s="1">
-        <v>21.450376510620117</v>
+        <v>21.458662033081055</v>
       </c>
       <c r="G20" s="1">
-        <v>21.098854064941406</v>
+        <v>20.651205062866211</v>
       </c>
       <c r="H20" s="1">
-        <v>21.832197189331055</v>
+        <v>21.679065704345703</v>
       </c>
       <c r="I20" s="1">
-        <v>21.450376510620117</v>
+        <v>21.458662033081055</v>
       </c>
       <c r="J20" s="1">
-        <v>21.098854064941406</v>
+        <v>20.651205062866211</v>
       </c>
       <c r="K20" s="1">
-        <v>1.231325626373291</v>
+        <v>2.8153021335601807</v>
       </c>
       <c r="L20" s="1">
-        <v>19.142190933227539</v>
+        <v>66.6431884765625</v>
       </c>
       <c r="M20" s="1">
         <v>0</v>
       </c>
       <c r="N20" s="1">
-        <v>11.425483703613281</v>
+        <v>8.5872840881347656</v>
       </c>
       <c r="O20" s="1">
-        <v>13.490241050720215</v>
+        <v>10.917184829711914</v>
       </c>
       <c r="P20" s="1">
-        <v>16.114065170288086</v>
+        <v>14.303579330444336</v>
       </c>
       <c r="Q20" s="1">
-        <v>-0.19765809178352356</v>
+        <v>-0.68814295530319214</v>
       </c>
       <c r="R20" s="1">
-        <v>0.70855957269668579</v>
+        <v>2.4668374061584473</v>
       </c>
       <c r="S20" s="1">
-        <v>1.4675110578536987</v>
+        <v>5.1091127395629883</v>
       </c>
     </row>
     <row r="21">
@@ -3988,58 +4000,58 @@
         <v>66</v>
       </c>
       <c r="B21" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" s="1">
-        <v>21.489063262939453</v>
+        <v>24.320249557495117</v>
       </c>
       <c r="E21" s="1">
-        <v>22.217504501342774</v>
+        <v>23.302276611328125</v>
       </c>
       <c r="F21" s="1">
-        <v>21.818704605102539</v>
+        <v>22.089944839477539</v>
       </c>
       <c r="G21" s="1">
-        <v>21.39973258972168</v>
+        <v>20.72081184387207</v>
       </c>
       <c r="H21" s="1">
-        <v>21.65791130065918</v>
+        <v>23.302276611328125</v>
       </c>
       <c r="I21" s="1">
-        <v>21.617155075073242</v>
+        <v>22.089944839477539</v>
       </c>
       <c r="J21" s="1">
-        <v>21.39973258972168</v>
+        <v>20.72081184387207</v>
       </c>
       <c r="K21" s="1">
-        <v>2.8153021335601807</v>
+        <v>2.0872793197631836</v>
       </c>
       <c r="L21" s="1">
-        <v>17.658035278320313</v>
+        <v>85.23150634765625</v>
       </c>
       <c r="M21" s="1">
         <v>0</v>
       </c>
       <c r="N21" s="1">
-        <v>8.5872840881347656</v>
+        <v>1.9466069936752319</v>
       </c>
       <c r="O21" s="1">
-        <v>10.917184829711914</v>
+        <v>4.3342394828796387</v>
       </c>
       <c r="P21" s="1">
-        <v>14.303579330444336</v>
+        <v>7.2991957664489746</v>
       </c>
       <c r="Q21" s="1">
-        <v>-0.18233299255371094</v>
+        <v>-0.88008189201354981</v>
       </c>
       <c r="R21" s="1">
-        <v>0.65362268686294556</v>
+        <v>3.1548945903778076</v>
       </c>
       <c r="S21" s="1">
-        <v>1.3537302017211914</v>
+        <v>6.5341615676879883</v>
       </c>
     </row>
     <row r="22">
@@ -4053,52 +4065,52 @@
         <v>0</v>
       </c>
       <c r="D22" s="1">
-        <v>23.088916778564453</v>
+        <v>25.033319473266602</v>
       </c>
       <c r="E22" s="1">
-        <v>22.767730712890625</v>
+        <v>25.766880035400391</v>
       </c>
       <c r="F22" s="1">
-        <v>22.384037017822266</v>
+        <v>23.097631454467773</v>
       </c>
       <c r="G22" s="1">
-        <v>22.011739730834961</v>
+        <v>20.824373245239258</v>
       </c>
       <c r="H22" s="1">
-        <v>22.767730712890625</v>
+        <v>25.173452377319336</v>
       </c>
       <c r="I22" s="1">
-        <v>22.384037017822266</v>
+        <v>23.097631454467773</v>
       </c>
       <c r="J22" s="1">
-        <v>22.011739730834961</v>
+        <v>20.824373245239258</v>
       </c>
       <c r="K22" s="1">
-        <v>1.8331828117370605</v>
+        <v>1.5383285284042358</v>
       </c>
       <c r="L22" s="1">
-        <v>18.29620361328125</v>
+        <v>229.02645874023438</v>
       </c>
       <c r="M22" s="1">
         <v>0</v>
       </c>
       <c r="N22" s="1">
-        <v>0.6298632025718689</v>
+        <v>2.0261704921722412</v>
       </c>
       <c r="O22" s="1">
-        <v>2.4449839591979981</v>
+        <v>3.4124050140380859</v>
       </c>
       <c r="P22" s="1">
-        <v>4.8412685394287109</v>
+        <v>5.2420177459716797</v>
       </c>
       <c r="Q22" s="1">
-        <v>-0.18892258405685425</v>
+        <v>-2.3648772239685059</v>
       </c>
       <c r="R22" s="1">
-        <v>0.67724478244781494</v>
+        <v>8.4775495529174805</v>
       </c>
       <c r="S22" s="1">
-        <v>1.4026545286178589</v>
+        <v>17.558013916015625</v>
       </c>
     </row>
     <row r="23">
@@ -4106,58 +4118,58 @@
         <v>68</v>
       </c>
       <c r="B23" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C23" s="1">
         <v>0</v>
       </c>
       <c r="D23" s="1">
-        <v>23.519998550415039</v>
+        <v>23.036062240600586</v>
       </c>
       <c r="E23" s="1">
-        <v>23.234500885009766</v>
+        <v>22.870183944702148</v>
       </c>
       <c r="F23" s="1">
-        <v>22.633596420288086</v>
+        <v>22.381757736206055</v>
       </c>
       <c r="G23" s="1">
-        <v>22.022214889526367</v>
+        <v>21.906463623046875</v>
       </c>
       <c r="H23" s="1">
-        <v>23.234500885009766</v>
+        <v>22.870183944702148</v>
       </c>
       <c r="I23" s="1">
-        <v>22.633596420288086</v>
+        <v>22.381757736206055</v>
       </c>
       <c r="J23" s="1">
-        <v>22.022214889526367</v>
+        <v>21.906463623046875</v>
       </c>
       <c r="K23" s="1">
-        <v>1.8094415664672852</v>
+        <v>0.52955126762390137</v>
       </c>
       <c r="L23" s="1">
-        <v>58.85650634765625</v>
+        <v>20.694961547851563</v>
       </c>
       <c r="M23" s="1">
         <v>0</v>
       </c>
       <c r="N23" s="1">
-        <v>4.2926797866821289</v>
+        <v>1.100072979927063</v>
       </c>
       <c r="O23" s="1">
-        <v>6.71484375</v>
+        <v>2.4174280166625977</v>
       </c>
       <c r="P23" s="1">
-        <v>9.7364273071289063</v>
+        <v>4.3831706047058106</v>
       </c>
       <c r="Q23" s="1">
-        <v>-0.60773938894271851</v>
+        <v>-0.21369165182113648</v>
       </c>
       <c r="R23" s="1">
-        <v>2.1786086559295654</v>
+        <v>0.7660362720489502</v>
       </c>
       <c r="S23" s="1">
-        <v>4.5121569633483887</v>
+        <v>1.5865522623062134</v>
       </c>
     </row>
     <row r="24">
@@ -4171,52 +4183,52 @@
         <v>0</v>
       </c>
       <c r="D24" s="1">
-        <v>28.985597610473633</v>
+        <v>27.585422515869141</v>
       </c>
       <c r="E24" s="1">
-        <v>26.33201789855957</v>
+        <v>27.094945907592774</v>
       </c>
       <c r="F24" s="1">
-        <v>24.540962219238281</v>
+        <v>25.764791488647461</v>
       </c>
       <c r="G24" s="1">
-        <v>22.828071594238281</v>
+        <v>24.210647583007813</v>
       </c>
       <c r="H24" s="1">
-        <v>26.33201789855957</v>
+        <v>27.094945907592774</v>
       </c>
       <c r="I24" s="1">
-        <v>24.540962219238281</v>
+        <v>25.764791488647461</v>
       </c>
       <c r="J24" s="1">
-        <v>22.828071594238281</v>
+        <v>24.210647583007813</v>
       </c>
       <c r="K24" s="1">
-        <v>1.4881768226623535</v>
+        <v>3.7642781734466553</v>
       </c>
       <c r="L24" s="1">
-        <v>84.160934448242188</v>
+        <v>64.9705810546875</v>
       </c>
       <c r="M24" s="1">
         <v>0</v>
       </c>
       <c r="N24" s="1">
-        <v>0</v>
+        <v>9.6269979476928711</v>
       </c>
       <c r="O24" s="1">
-        <v>0.96296417713165283</v>
+        <v>13.491902351379395</v>
       </c>
       <c r="P24" s="1">
-        <v>2.1726033687591553</v>
+        <v>18.331710815429688</v>
       </c>
       <c r="Q24" s="1">
-        <v>-0.86902743577957153</v>
+        <v>-0.67087197303771973</v>
       </c>
       <c r="R24" s="1">
-        <v>3.115267276763916</v>
+        <v>2.4049246311187744</v>
       </c>
       <c r="S24" s="1">
-        <v>6.4520883560180664</v>
+        <v>4.9808840751647949</v>
       </c>
     </row>
     <row r="25">
@@ -4233,28 +4245,28 @@
         <v>28.494235992431641</v>
       </c>
       <c r="E25" s="1">
-        <v>27.170236587524414</v>
+        <v>27.069841384887695</v>
       </c>
       <c r="F25" s="1">
-        <v>25.376089096069336</v>
+        <v>25.903257369995117</v>
       </c>
       <c r="G25" s="1">
-        <v>22.920974731445313</v>
+        <v>24.469926834106445</v>
       </c>
       <c r="H25" s="1">
-        <v>27.170236587524414</v>
+        <v>27.069841384887695</v>
       </c>
       <c r="I25" s="1">
-        <v>25.376089096069336</v>
+        <v>25.903257369995117</v>
       </c>
       <c r="J25" s="1">
-        <v>22.920974731445313</v>
+        <v>24.469926834106445</v>
       </c>
       <c r="K25" s="1">
         <v>1.3515106439590454</v>
       </c>
       <c r="L25" s="1">
-        <v>150.43344116210938</v>
+        <v>67.617576599121094</v>
       </c>
       <c r="M25" s="1">
         <v>0</v>
@@ -4269,13 +4281,13 @@
         <v>6.2520194053649902</v>
       </c>
       <c r="Q25" s="1">
-        <v>-1.5533427000045776</v>
+        <v>-0.69820433855056763</v>
       </c>
       <c r="R25" s="1">
-        <v>5.5683836936950684</v>
+        <v>2.5029053688049316</v>
       </c>
       <c r="S25" s="1">
-        <v>11.532782554626465</v>
+        <v>5.1838130950927734</v>
       </c>
     </row>
     <row r="26">
@@ -4283,58 +4295,58 @@
         <v>71</v>
       </c>
       <c r="B26" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C26" s="1">
         <v>0</v>
       </c>
       <c r="D26" s="1">
-        <v>25.033319473266602</v>
+        <v>33.737167358398438</v>
       </c>
       <c r="E26" s="1">
-        <v>25.246953964233398</v>
+        <v>30.714231491088867</v>
       </c>
       <c r="F26" s="1">
-        <v>24.961872100830078</v>
+        <v>28.117233276367188</v>
       </c>
       <c r="G26" s="1">
-        <v>24.700096130371094</v>
+        <v>25.359024047851563</v>
       </c>
       <c r="H26" s="1">
-        <v>25.06391716003418</v>
+        <v>30.714231491088867</v>
       </c>
       <c r="I26" s="1">
-        <v>24.961872100830078</v>
+        <v>28.117233276367188</v>
       </c>
       <c r="J26" s="1">
-        <v>24.700096130371094</v>
+        <v>25.359024047851563</v>
       </c>
       <c r="K26" s="1">
-        <v>1.5383285284042358</v>
+        <v>4.3763270378112793</v>
       </c>
       <c r="L26" s="1">
-        <v>11.300914764404297</v>
+        <v>47.693958282470703</v>
       </c>
       <c r="M26" s="1">
         <v>0</v>
       </c>
       <c r="N26" s="1">
-        <v>2.0261704921722412</v>
+        <v>0</v>
       </c>
       <c r="O26" s="1">
-        <v>3.4124050140380859</v>
+        <v>4.7703018188476563</v>
       </c>
       <c r="P26" s="1">
-        <v>5.2420177459716797</v>
+        <v>10.402714729309082</v>
       </c>
       <c r="Q26" s="1">
-        <v>-0.11669077724218369</v>
+        <v>-0.49247738718986511</v>
       </c>
       <c r="R26" s="1">
-        <v>0.41831004619598389</v>
+        <v>1.7654204368591309</v>
       </c>
       <c r="S26" s="1">
-        <v>0.86636990308761597</v>
+        <v>3.6563949584960938</v>
       </c>
     </row>
     <row r="27">
@@ -4342,58 +4354,58 @@
         <v>72</v>
       </c>
       <c r="B27" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C27" s="1">
         <v>0</v>
       </c>
       <c r="D27" s="1">
-        <v>32.023998260498047</v>
+        <v>27.39015007019043</v>
       </c>
       <c r="E27" s="1">
-        <v>30.339357376098633</v>
+        <v>27.880903244018555</v>
       </c>
       <c r="F27" s="1">
-        <v>27.920125961303711</v>
+        <v>27.122276306152344</v>
       </c>
       <c r="G27" s="1">
-        <v>25.27391242980957</v>
+        <v>26.439104080200195</v>
       </c>
       <c r="H27" s="1">
-        <v>30.339357376098633</v>
+        <v>27.485429763793945</v>
       </c>
       <c r="I27" s="1">
-        <v>27.920125961303711</v>
+        <v>27.122276306152344</v>
       </c>
       <c r="J27" s="1">
-        <v>25.27391242980957</v>
+        <v>26.439104080200195</v>
       </c>
       <c r="K27" s="1">
-        <v>5.4320864677429199</v>
+        <v>1.7580658197402954</v>
       </c>
       <c r="L27" s="1">
-        <v>143.84133911132813</v>
+        <v>44.7750244140625</v>
       </c>
       <c r="M27" s="1">
         <v>0</v>
       </c>
       <c r="N27" s="1">
-        <v>2.8455393314361572</v>
+        <v>1.5793594121932983</v>
       </c>
       <c r="O27" s="1">
-        <v>4.9676198959350586</v>
+        <v>3.1063168048858643</v>
       </c>
       <c r="P27" s="1">
-        <v>7.7184958457946777</v>
+        <v>5.2022213935852051</v>
       </c>
       <c r="Q27" s="1">
-        <v>-1.4852741956710816</v>
+        <v>-0.46233710646629333</v>
       </c>
       <c r="R27" s="1">
-        <v>5.3243727684020996</v>
+        <v>1.6573742628097534</v>
       </c>
       <c r="S27" s="1">
-        <v>11.027406692504883</v>
+        <v>3.4326186180114746</v>
       </c>
     </row>
     <row r="28">
@@ -4407,52 +4419,52 @@
         <v>0</v>
       </c>
       <c r="D28" s="1">
-        <v>27.585422515869141</v>
+        <v>28.380533218383789</v>
       </c>
       <c r="E28" s="1">
-        <v>26.945394515991211</v>
+        <v>27.192106246948242</v>
       </c>
       <c r="F28" s="1">
-        <v>26.301008224487305</v>
+        <v>26.900918960571289</v>
       </c>
       <c r="G28" s="1">
-        <v>25.325437545776367</v>
+        <v>26.550449371337891</v>
       </c>
       <c r="H28" s="1">
-        <v>26.945394515991211</v>
+        <v>27.192106246948242</v>
       </c>
       <c r="I28" s="1">
-        <v>26.301008224487305</v>
+        <v>26.900918960571289</v>
       </c>
       <c r="J28" s="1">
-        <v>25.325437545776367</v>
+        <v>26.550449371337891</v>
       </c>
       <c r="K28" s="1">
-        <v>3.7642781734466553</v>
+        <v>0.76714533567428589</v>
       </c>
       <c r="L28" s="1">
-        <v>8.1391191482543945</v>
+        <v>0</v>
       </c>
       <c r="M28" s="1">
         <v>0</v>
       </c>
       <c r="N28" s="1">
-        <v>9.6269979476928711</v>
+        <v>14.127007484436035</v>
       </c>
       <c r="O28" s="1">
-        <v>13.491902351379395</v>
+        <v>15.798462867736816</v>
       </c>
       <c r="P28" s="1">
-        <v>18.331710815429688</v>
+        <v>17.930709838867188</v>
       </c>
       <c r="Q28" s="1">
-        <v>-0.084042765200138092</v>
+        <v>0</v>
       </c>
       <c r="R28" s="1">
-        <v>0.30127432942390442</v>
+        <v>0</v>
       </c>
       <c r="S28" s="1">
-        <v>0.62397491931915283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -4460,58 +4472,58 @@
         <v>74</v>
       </c>
       <c r="B29" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C29" s="1">
         <v>0</v>
       </c>
       <c r="D29" s="1">
-        <v>27.39015007019043</v>
+        <v>30.68280029296875</v>
       </c>
       <c r="E29" s="1">
-        <v>27.787363052368164</v>
+        <v>28.721988677978516</v>
       </c>
       <c r="F29" s="1">
-        <v>27.457674026489258</v>
+        <v>27.998226165771484</v>
       </c>
       <c r="G29" s="1">
-        <v>27.136386871337891</v>
+        <v>27.069978713989258</v>
       </c>
       <c r="H29" s="1">
-        <v>27.465723037719727</v>
+        <v>28.721988677978516</v>
       </c>
       <c r="I29" s="1">
-        <v>27.442955017089844</v>
+        <v>27.998226165771484</v>
       </c>
       <c r="J29" s="1">
-        <v>27.136386871337891</v>
+        <v>27.069978713989258</v>
       </c>
       <c r="K29" s="1">
-        <v>1.7580658197402954</v>
+        <v>1.2923356294631958</v>
       </c>
       <c r="L29" s="1">
-        <v>8.9744405746459961</v>
+        <v>39.117073059082031</v>
       </c>
       <c r="M29" s="1">
         <v>0</v>
       </c>
       <c r="N29" s="1">
-        <v>1.5793594121932983</v>
+        <v>11.875863075256348</v>
       </c>
       <c r="O29" s="1">
-        <v>3.1063168048858643</v>
+        <v>12.967769622802734</v>
       </c>
       <c r="P29" s="1">
-        <v>5.2022213935852051</v>
+        <v>14.525602340698242</v>
       </c>
       <c r="Q29" s="1">
-        <v>-0.092668108642101288</v>
+        <v>-0.40391433238983154</v>
       </c>
       <c r="R29" s="1">
-        <v>0.33219426870346069</v>
+        <v>1.4479418992996216</v>
       </c>
       <c r="S29" s="1">
-        <v>0.68801367282867432</v>
+        <v>2.9988594055175781</v>
       </c>
     </row>
     <row r="30">
@@ -4519,58 +4531,58 @@
         <v>75</v>
       </c>
       <c r="B30" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C30" s="1">
         <v>0</v>
       </c>
       <c r="D30" s="1">
-        <v>30.68280029296875</v>
+        <v>32.023998260498047</v>
       </c>
       <c r="E30" s="1">
-        <v>28.622161865234375</v>
+        <v>29.989042282104492</v>
       </c>
       <c r="F30" s="1">
-        <v>28.356170654296875</v>
+        <v>29.176193237304688</v>
       </c>
       <c r="G30" s="1">
-        <v>27.814144134521484</v>
+        <v>27.885251998901367</v>
       </c>
       <c r="H30" s="1">
-        <v>28.622161865234375</v>
+        <v>29.989042282104492</v>
       </c>
       <c r="I30" s="1">
-        <v>28.356170654296875</v>
+        <v>29.176193237304688</v>
       </c>
       <c r="J30" s="1">
-        <v>27.814144134521484</v>
+        <v>27.885251998901367</v>
       </c>
       <c r="K30" s="1">
-        <v>1.2923356294631958</v>
+        <v>5.4320864677429199</v>
       </c>
       <c r="L30" s="1">
-        <v>5.0096120834350586</v>
+        <v>29.167816162109375</v>
       </c>
       <c r="M30" s="1">
         <v>0</v>
       </c>
       <c r="N30" s="1">
-        <v>11.875863075256348</v>
+        <v>2.8455393314361572</v>
       </c>
       <c r="O30" s="1">
-        <v>12.967769622802734</v>
+        <v>4.9676198959350586</v>
       </c>
       <c r="P30" s="1">
-        <v>14.525602340698242</v>
+        <v>7.7184958457946777</v>
       </c>
       <c r="Q30" s="1">
-        <v>-0.051728162914514542</v>
+        <v>-0.30118048191070557</v>
       </c>
       <c r="R30" s="1">
-        <v>0.1854337751865387</v>
+        <v>1.0796641111373901</v>
       </c>
       <c r="S30" s="1">
-        <v>0.38405537605285645</v>
+        <v>2.2361123561859131</v>
       </c>
     </row>
     <row r="31">
@@ -4578,58 +4590,58 @@
         <v>76</v>
       </c>
       <c r="B31" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C31" s="1">
         <v>0</v>
       </c>
       <c r="D31" s="1">
-        <v>33.137016296386719</v>
+        <v>32.963825225830078</v>
       </c>
       <c r="E31" s="1">
-        <v>31.126087188720703</v>
+        <v>32.059024810791016</v>
       </c>
       <c r="F31" s="1">
-        <v>30.538948059082031</v>
+        <v>30.081253051757813</v>
       </c>
       <c r="G31" s="1">
-        <v>29.761831283569336</v>
+        <v>28.3970947265625</v>
       </c>
       <c r="H31" s="1">
-        <v>31.126087188720703</v>
+        <v>32.059024810791016</v>
       </c>
       <c r="I31" s="1">
-        <v>30.538948059082031</v>
+        <v>30.081253051757813</v>
       </c>
       <c r="J31" s="1">
-        <v>29.761831283569336</v>
+        <v>28.3970947265625</v>
       </c>
       <c r="K31" s="1">
-        <v>2.8590431213378906</v>
+        <v>1.812983512878418</v>
       </c>
       <c r="L31" s="1">
-        <v>24.250465393066406</v>
+        <v>116.55748748779297</v>
       </c>
       <c r="M31" s="1">
         <v>0</v>
       </c>
       <c r="N31" s="1">
-        <v>0</v>
+        <v>2.8534793853759766</v>
       </c>
       <c r="O31" s="1">
-        <v>1.4605740308761597</v>
+        <v>4.4012646675109863</v>
       </c>
       <c r="P31" s="1">
-        <v>3.3082342147827149</v>
+        <v>6.3552460670471192</v>
       </c>
       <c r="Q31" s="1">
-        <v>-0.25040501356124878</v>
+        <v>-1.2035470008850098</v>
       </c>
       <c r="R31" s="1">
-        <v>0.89764535427093506</v>
+        <v>4.3144440650939942</v>
       </c>
       <c r="S31" s="1">
-        <v>1.8591302633285523</v>
+        <v>8.9357261657714844</v>
       </c>
     </row>
     <row r="32">
@@ -4637,58 +4649,58 @@
         <v>77</v>
       </c>
       <c r="B32" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32" s="1">
         <v>0</v>
       </c>
       <c r="D32" s="1">
-        <v>32.963825225830078</v>
+        <v>33.137016296386719</v>
       </c>
       <c r="E32" s="1">
-        <v>31.700702667236328</v>
+        <v>31.111860275268555</v>
       </c>
       <c r="F32" s="1">
-        <v>31.366029739379883</v>
+        <v>30.58995246887207</v>
       </c>
       <c r="G32" s="1">
-        <v>31.068126678466797</v>
+        <v>29.867862701416016</v>
       </c>
       <c r="H32" s="1">
-        <v>31.700702667236328</v>
+        <v>31.111860275268555</v>
       </c>
       <c r="I32" s="1">
-        <v>31.366029739379883</v>
+        <v>30.58995246887207</v>
       </c>
       <c r="J32" s="1">
-        <v>31.068126678466797</v>
+        <v>29.867862701416016</v>
       </c>
       <c r="K32" s="1">
-        <v>1.812983512878418</v>
+        <v>2.8590431213378906</v>
       </c>
       <c r="L32" s="1">
-        <v>2.6068441867828369</v>
+        <v>19.750577926635742</v>
       </c>
       <c r="M32" s="1">
         <v>0</v>
       </c>
       <c r="N32" s="1">
-        <v>2.8534793853759766</v>
+        <v>0</v>
       </c>
       <c r="O32" s="1">
-        <v>4.4012646675109863</v>
+        <v>1.4605740308761597</v>
       </c>
       <c r="P32" s="1">
-        <v>6.3552460670471192</v>
+        <v>3.3082342147827149</v>
       </c>
       <c r="Q32" s="1">
-        <v>-0.026917701587080956</v>
+        <v>-0.20394015312194824</v>
       </c>
       <c r="R32" s="1">
-        <v>0.096493877470493317</v>
+        <v>0.7310793399810791</v>
       </c>
       <c r="S32" s="1">
-        <v>0.19985027611255646</v>
+        <v>1.5141520500183105</v>
       </c>
     </row>
     <row r="33">
@@ -4705,28 +4717,28 @@
         <v>40.793071746826172</v>
       </c>
       <c r="E33" s="1">
-        <v>35.553970336914063</v>
+        <v>35.801841735839844</v>
       </c>
       <c r="F33" s="1">
-        <v>34.119129180908203</v>
+        <v>33.230339050292969</v>
       </c>
       <c r="G33" s="1">
-        <v>32.693763732910156</v>
+        <v>30.845993041992188</v>
       </c>
       <c r="H33" s="1">
-        <v>35.553970336914063</v>
+        <v>35.801841735839844</v>
       </c>
       <c r="I33" s="1">
-        <v>34.119129180908203</v>
+        <v>33.230339050292969</v>
       </c>
       <c r="J33" s="1">
-        <v>32.693763732910156</v>
+        <v>30.845993041992188</v>
       </c>
       <c r="K33" s="1">
         <v>2.0582499504089356</v>
       </c>
       <c r="L33" s="1">
-        <v>32.501632690429688</v>
+        <v>96.201278686523438</v>
       </c>
       <c r="M33" s="1">
         <v>0</v>
@@ -4741,13 +4753,13 @@
         <v>8.2968120574951172</v>
       </c>
       <c r="Q33" s="1">
-        <v>-0.33560475707054138</v>
+        <v>-0.99335330724716187</v>
       </c>
       <c r="R33" s="1">
-        <v>1.2030673027038574</v>
+        <v>3.5609474182128906</v>
       </c>
       <c r="S33" s="1">
-        <v>2.4916951656341553</v>
+        <v>7.3751444816589355</v>
       </c>
     </row>
     <row r="34">
@@ -4755,58 +4767,58 @@
         <v>79</v>
       </c>
       <c r="B34" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C34" s="1">
         <v>0</v>
       </c>
       <c r="D34" s="1">
-        <v>36.838943481445313</v>
+        <v>35.928680419921875</v>
       </c>
       <c r="E34" s="1">
-        <v>35.497901916503906</v>
+        <v>34.437847137451172</v>
       </c>
       <c r="F34" s="1">
-        <v>34.394428253173828</v>
+        <v>32.946636199951172</v>
       </c>
       <c r="G34" s="1">
-        <v>33.180706024169922</v>
+        <v>31.573554992675781</v>
       </c>
       <c r="H34" s="1">
-        <v>35.497901916503906</v>
+        <v>34.437847137451172</v>
       </c>
       <c r="I34" s="1">
-        <v>34.394428253173828</v>
+        <v>32.946636199951172</v>
       </c>
       <c r="J34" s="1">
-        <v>33.180706024169922</v>
+        <v>31.573554992675781</v>
       </c>
       <c r="K34" s="1">
-        <v>3.0391237735748291</v>
+        <v>2.6939806938171387</v>
       </c>
       <c r="L34" s="1">
-        <v>65.625144958496094</v>
+        <v>81.301338195800781</v>
       </c>
       <c r="M34" s="1">
         <v>0</v>
       </c>
       <c r="N34" s="1">
-        <v>58.534774780273438</v>
+        <v>1.2021737098693848</v>
       </c>
       <c r="O34" s="1">
-        <v>60.339527130126953</v>
+        <v>2.7424185276031494</v>
       </c>
       <c r="P34" s="1">
-        <v>62.578033447265625</v>
+        <v>4.7401785850524902</v>
       </c>
       <c r="Q34" s="1">
-        <v>-0.67763090133666992</v>
+        <v>-0.83949977159500122</v>
       </c>
       <c r="R34" s="1">
-        <v>2.4291539192199707</v>
+        <v>3.0094175338745117</v>
       </c>
       <c r="S34" s="1">
-        <v>5.0310659408569336</v>
+        <v>6.2328600883483887</v>
       </c>
     </row>
     <row r="35">
@@ -4814,58 +4826,58 @@
         <v>80</v>
       </c>
       <c r="B35" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C35" s="1">
         <v>0</v>
       </c>
       <c r="D35" s="1">
-        <v>35.928680419921875</v>
+        <v>36.838943481445313</v>
       </c>
       <c r="E35" s="1">
-        <v>34.195388793945313</v>
+        <v>35.337623596191406</v>
       </c>
       <c r="F35" s="1">
-        <v>33.815982818603516</v>
+        <v>34.9691162109375</v>
       </c>
       <c r="G35" s="1">
-        <v>33.380916595458984</v>
+        <v>34.542106628417969</v>
       </c>
       <c r="H35" s="1">
-        <v>34.195388793945313</v>
+        <v>35.337623596191406</v>
       </c>
       <c r="I35" s="1">
-        <v>33.815982818603516</v>
+        <v>34.9691162109375</v>
       </c>
       <c r="J35" s="1">
-        <v>33.380916595458984</v>
+        <v>34.542106628417969</v>
       </c>
       <c r="K35" s="1">
-        <v>2.6939806938171387</v>
+        <v>3.0391237735748291</v>
       </c>
       <c r="L35" s="1">
-        <v>10.559006690979004</v>
+        <v>0</v>
       </c>
       <c r="M35" s="1">
         <v>0</v>
       </c>
       <c r="N35" s="1">
-        <v>1.2021737098693848</v>
+        <v>58.534774780273438</v>
       </c>
       <c r="O35" s="1">
-        <v>2.7424185276031494</v>
+        <v>60.339527130126953</v>
       </c>
       <c r="P35" s="1">
-        <v>4.7401785850524902</v>
+        <v>62.578033447265625</v>
       </c>
       <c r="Q35" s="1">
-        <v>-0.10902998596429825</v>
+        <v>0</v>
       </c>
       <c r="R35" s="1">
-        <v>0.39084795117378235</v>
+        <v>0</v>
       </c>
       <c r="S35" s="1">
-        <v>0.80949240922927857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -4882,28 +4894,28 @@
         <v>39.194725036621094</v>
       </c>
       <c r="E36" s="1">
-        <v>37.043521881103516</v>
+        <v>37.104454040527344</v>
       </c>
       <c r="F36" s="1">
-        <v>36.075004577636719</v>
+        <v>35.856513977050781</v>
       </c>
       <c r="G36" s="1">
-        <v>35.117691040039063</v>
+        <v>34.860889434814453</v>
       </c>
       <c r="H36" s="1">
-        <v>37.043521881103516</v>
+        <v>37.104454040527344</v>
       </c>
       <c r="I36" s="1">
-        <v>36.075004577636719</v>
+        <v>35.856513977050781</v>
       </c>
       <c r="J36" s="1">
-        <v>35.117691040039063</v>
+        <v>34.860889434814453</v>
       </c>
       <c r="K36" s="1">
         <v>0.32150024175643921</v>
       </c>
       <c r="L36" s="1">
-        <v>69.207923889160156</v>
+        <v>65.7987060546875</v>
       </c>
       <c r="M36" s="1">
         <v>0</v>
@@ -4918,13 +4930,13 @@
         <v>1.008161187171936</v>
       </c>
       <c r="Q36" s="1">
-        <v>-0.71462589502334595</v>
+        <v>-0.67942309379577637</v>
       </c>
       <c r="R36" s="1">
-        <v>2.561772346496582</v>
+        <v>2.4355783462524414</v>
       </c>
       <c r="S36" s="1">
-        <v>5.3057351112365723</v>
+        <v>5.0443720817565918</v>
       </c>
     </row>
     <row r="37">
@@ -4941,28 +4953,28 @@
         <v>41.467826843261719</v>
       </c>
       <c r="E37" s="1">
-        <v>39.927154541015625</v>
+        <v>39.547966003417969</v>
       </c>
       <c r="F37" s="1">
-        <v>37.797622680664063</v>
+        <v>39.157230377197266</v>
       </c>
       <c r="G37" s="1">
-        <v>36.001800537109375</v>
+        <v>38.828407287597656</v>
       </c>
       <c r="H37" s="1">
-        <v>39.927154541015625</v>
+        <v>39.547966003417969</v>
       </c>
       <c r="I37" s="1">
-        <v>37.797622680664063</v>
+        <v>39.157230377197266</v>
       </c>
       <c r="J37" s="1">
-        <v>36.001800537109375</v>
+        <v>38.828407287597656</v>
       </c>
       <c r="K37" s="1">
         <v>1.9415525197982788</v>
       </c>
       <c r="L37" s="1">
-        <v>100.38091278076172</v>
+        <v>4.5227675437927246</v>
       </c>
       <c r="M37" s="1">
         <v>0</v>
@@ -4977,13 +4989,13 @@
         <v>7.2479825019836426</v>
       </c>
       <c r="Q37" s="1">
-        <v>-1.0365113019943237</v>
+        <v>-0.046701107174158096</v>
       </c>
       <c r="R37" s="1">
-        <v>3.7156591415405274</v>
+        <v>0.16741292178630829</v>
       </c>
       <c r="S37" s="1">
-        <v>7.6955704689025879</v>
+        <v>0.34673202037811279</v>
       </c>
     </row>
     <row r="38">
@@ -4997,52 +5009,52 @@
         <v>0</v>
       </c>
       <c r="D38" s="1">
-        <v>48.211658477783203</v>
+        <v>47.321636199951172</v>
       </c>
       <c r="E38" s="1">
-        <v>44.672458648681641</v>
+        <v>45.120143890380859</v>
       </c>
       <c r="F38" s="1">
-        <v>43.480243682861328</v>
+        <v>43.431587219238281</v>
       </c>
       <c r="G38" s="1">
-        <v>42.231597900390625</v>
+        <v>42.064064025878906</v>
       </c>
       <c r="H38" s="1">
-        <v>44.672458648681641</v>
+        <v>45.120143890380859</v>
       </c>
       <c r="I38" s="1">
-        <v>43.480243682861328</v>
+        <v>43.431587219238281</v>
       </c>
       <c r="J38" s="1">
-        <v>42.231597900390625</v>
+        <v>42.064064025878906</v>
       </c>
       <c r="K38" s="1">
-        <v>2.3083720207214355</v>
+        <v>1.9545148611068726</v>
       </c>
       <c r="L38" s="1">
-        <v>31.862676620483398</v>
+        <v>71.494659423828125</v>
       </c>
       <c r="M38" s="1">
         <v>0</v>
       </c>
       <c r="N38" s="1">
-        <v>3.545093297958374</v>
+        <v>0</v>
       </c>
       <c r="O38" s="1">
-        <v>4.3755054473876953</v>
+        <v>0.70863378047943115</v>
       </c>
       <c r="P38" s="1">
-        <v>5.755126953125</v>
+        <v>1.6714258193969727</v>
       </c>
       <c r="Q38" s="1">
-        <v>-0.32900702953338623</v>
+        <v>-0.73823827505111694</v>
       </c>
       <c r="R38" s="1">
-        <v>1.1794159412384033</v>
+        <v>2.6464176177978516</v>
       </c>
       <c r="S38" s="1">
-        <v>2.4427101612091065</v>
+        <v>5.4810447692871094</v>
       </c>
     </row>
     <row r="39">
@@ -5056,52 +5068,52 @@
         <v>0</v>
       </c>
       <c r="D39" s="1">
-        <v>47.321636199951172</v>
+        <v>48.211658477783203</v>
       </c>
       <c r="E39" s="1">
-        <v>45.056312561035156</v>
+        <v>44.655899047851563</v>
       </c>
       <c r="F39" s="1">
-        <v>43.660480499267578</v>
+        <v>43.539646148681641</v>
       </c>
       <c r="G39" s="1">
-        <v>42.539924621582031</v>
+        <v>42.355094909667969</v>
       </c>
       <c r="H39" s="1">
-        <v>45.056312561035156</v>
+        <v>44.655899047851563</v>
       </c>
       <c r="I39" s="1">
-        <v>43.660480499267578</v>
+        <v>43.539646148681641</v>
       </c>
       <c r="J39" s="1">
-        <v>42.539924621582031</v>
+        <v>42.355094909667969</v>
       </c>
       <c r="K39" s="1">
-        <v>1.9545148611068726</v>
+        <v>2.3083720207214355</v>
       </c>
       <c r="L39" s="1">
-        <v>57.353202819824219</v>
+        <v>28.260345458984375</v>
       </c>
       <c r="M39" s="1">
         <v>0</v>
       </c>
       <c r="N39" s="1">
-        <v>0</v>
+        <v>3.545093297958374</v>
       </c>
       <c r="O39" s="1">
-        <v>0.70863378047943115</v>
+        <v>4.3755054473876953</v>
       </c>
       <c r="P39" s="1">
-        <v>1.6714258193969727</v>
+        <v>5.755126953125</v>
       </c>
       <c r="Q39" s="1">
-        <v>-0.59221667051315308</v>
+        <v>-0.29181015491485596</v>
       </c>
       <c r="R39" s="1">
-        <v>2.1229629516601563</v>
+        <v>1.0460735559463501</v>
       </c>
       <c r="S39" s="1">
-        <v>4.3969082832336426</v>
+        <v>2.1665422916412354</v>
       </c>
     </row>
     <row r="40">
@@ -5118,28 +5130,28 @@
         <v>50.226909637451172</v>
       </c>
       <c r="E40" s="1">
-        <v>48.705303192138672</v>
+        <v>48.955039978027344</v>
       </c>
       <c r="F40" s="1">
-        <v>47.287216186523438</v>
+        <v>46.391777038574219</v>
       </c>
       <c r="G40" s="1">
-        <v>46.100208282470703</v>
+        <v>44.238613128662109</v>
       </c>
       <c r="H40" s="1">
-        <v>48.705303192138672</v>
+        <v>48.955039978027344</v>
       </c>
       <c r="I40" s="1">
-        <v>47.287216186523438</v>
+        <v>46.391777038574219</v>
       </c>
       <c r="J40" s="1">
-        <v>46.100208282470703</v>
+        <v>44.238613128662109</v>
       </c>
       <c r="K40" s="1">
         <v>2.9923243522644043</v>
       </c>
       <c r="L40" s="1">
-        <v>65.950004577636719</v>
+        <v>97.957611083984375</v>
       </c>
       <c r="M40" s="1">
         <v>0</v>
@@ -5154,13 +5166,13 @@
         <v>28.010160446166992</v>
       </c>
       <c r="Q40" s="1">
-        <v>-0.68098533153533936</v>
+        <v>-1.0114889144897461</v>
       </c>
       <c r="R40" s="1">
-        <v>2.4411787986755371</v>
+        <v>3.6259593963623047</v>
       </c>
       <c r="S40" s="1">
-        <v>5.0559706687927246</v>
+        <v>7.5097918510437012</v>
       </c>
     </row>
     <row r="41">
@@ -5177,28 +5189,28 @@
         <v>53.848400115966797</v>
       </c>
       <c r="E41" s="1">
-        <v>48.762378692626953</v>
+        <v>48.939346313476563</v>
       </c>
       <c r="F41" s="1">
-        <v>48.045505523681641</v>
+        <v>47.410991668701172</v>
       </c>
       <c r="G41" s="1">
-        <v>47.310131072998047</v>
+        <v>45.990985870361328</v>
       </c>
       <c r="H41" s="1">
-        <v>48.762378692626953</v>
+        <v>48.939346313476563</v>
       </c>
       <c r="I41" s="1">
-        <v>48.045505523681641</v>
+        <v>47.410991668701172</v>
       </c>
       <c r="J41" s="1">
-        <v>47.310131072998047</v>
+        <v>45.990985870361328</v>
       </c>
       <c r="K41" s="1">
         <v>1.8385132551193237</v>
       </c>
       <c r="L41" s="1">
-        <v>3.1440615653991699</v>
+        <v>37.594581604003906</v>
       </c>
       <c r="M41" s="1">
         <v>0</v>
@@ -5213,13 +5225,13 @@
         <v>1.8648418188095093</v>
       </c>
       <c r="Q41" s="1">
-        <v>-0.0324648916721344</v>
+        <v>-0.38819345831871033</v>
       </c>
       <c r="R41" s="1">
-        <v>0.11637930572032928</v>
+        <v>1.3915858268737793</v>
       </c>
       <c r="S41" s="1">
-        <v>0.24103538691997528</v>
+        <v>2.8821396827697754</v>
       </c>
     </row>
     <row r="42">
@@ -5236,28 +5248,28 @@
         <v>58.708145141601563</v>
       </c>
       <c r="E42" s="1">
-        <v>57.542507171630859</v>
+        <v>57.405815124511719</v>
       </c>
       <c r="F42" s="1">
-        <v>56.709213256835938</v>
+        <v>57.199329376220703</v>
       </c>
       <c r="G42" s="1">
-        <v>56.149486541748047</v>
+        <v>57.168418884277344</v>
       </c>
       <c r="H42" s="1">
-        <v>57.542507171630859</v>
+        <v>57.405815124511719</v>
       </c>
       <c r="I42" s="1">
-        <v>56.709213256835938</v>
+        <v>57.199329376220703</v>
       </c>
       <c r="J42" s="1">
-        <v>56.149486541748047</v>
+        <v>57.168418884277344</v>
       </c>
       <c r="K42" s="1">
         <v>2.3428640365600586</v>
       </c>
       <c r="L42" s="1">
-        <v>40.317180633544922</v>
+        <v>4.9435420036315918</v>
       </c>
       <c r="M42" s="1">
         <v>0</v>
@@ -5272,13 +5284,13 @@
         <v>9.8502340316772461</v>
       </c>
       <c r="Q42" s="1">
-        <v>-0.41630640625953674</v>
+        <v>-0.051045931875705719</v>
       </c>
       <c r="R42" s="1">
-        <v>1.4923642873764038</v>
+        <v>0.18298813700675964</v>
       </c>
       <c r="S42" s="1">
-        <v>3.0908637046813965</v>
+        <v>0.37899017333984375</v>
       </c>
     </row>
     <row r="43">
@@ -5292,52 +5304,52 @@
         <v>0</v>
       </c>
       <c r="D43" s="1">
-        <v>71.537399291992188</v>
+        <v>66.349037170410156</v>
       </c>
       <c r="E43" s="1">
-        <v>65.327873229980469</v>
+        <v>64.881248474121094</v>
       </c>
       <c r="F43" s="1">
-        <v>63.170707702636719</v>
+        <v>63.547927856445313</v>
       </c>
       <c r="G43" s="1">
-        <v>61.3074951171875</v>
+        <v>62.566314697265625</v>
       </c>
       <c r="H43" s="1">
-        <v>65.327873229980469</v>
+        <v>64.881248474121094</v>
       </c>
       <c r="I43" s="1">
-        <v>63.170707702636719</v>
+        <v>63.547927856445313</v>
       </c>
       <c r="J43" s="1">
-        <v>61.3074951171875</v>
+        <v>62.566314697265625</v>
       </c>
       <c r="K43" s="1">
-        <v>1.9380583763122559</v>
+        <v>1.7335447072982788</v>
       </c>
       <c r="L43" s="1">
-        <v>49.01953125</v>
+        <v>40.910678863525391</v>
       </c>
       <c r="M43" s="1">
         <v>0</v>
       </c>
       <c r="N43" s="1">
-        <v>0</v>
+        <v>4.5350542068481445</v>
       </c>
       <c r="O43" s="1">
-        <v>0.56680899858474732</v>
+        <v>5.0140829086303711</v>
       </c>
       <c r="P43" s="1">
-        <v>1.3047416210174561</v>
+        <v>5.6756038665771484</v>
       </c>
       <c r="Q43" s="1">
-        <v>-0.50616496801376343</v>
+        <v>-0.42243471741676331</v>
       </c>
       <c r="R43" s="1">
-        <v>1.8144869804382324</v>
+        <v>1.5143332481384277</v>
       </c>
       <c r="S43" s="1">
-        <v>3.7580180168151855</v>
+        <v>3.1363637447357178</v>
       </c>
     </row>
     <row r="44">
@@ -5351,31 +5363,31 @@
         <v>0</v>
       </c>
       <c r="D44" s="1">
-        <v>71.927200317382813</v>
+        <v>71.537399291992188</v>
       </c>
       <c r="E44" s="1">
-        <v>68.643959045410156</v>
+        <v>64.993354797363281</v>
       </c>
       <c r="F44" s="1">
-        <v>64.866615295410156</v>
+        <v>64.370140075683594</v>
       </c>
       <c r="G44" s="1">
-        <v>61.676933288574219</v>
+        <v>63.801094055175781</v>
       </c>
       <c r="H44" s="1">
-        <v>68.643959045410156</v>
+        <v>64.993354797363281</v>
       </c>
       <c r="I44" s="1">
-        <v>64.866615295410156</v>
+        <v>64.370140075683594</v>
       </c>
       <c r="J44" s="1">
-        <v>61.676933288574219</v>
+        <v>63.801094055175781</v>
       </c>
       <c r="K44" s="1">
-        <v>1.1138042211532593</v>
+        <v>1.9380583763122559</v>
       </c>
       <c r="L44" s="1">
-        <v>122.11321258544922</v>
+        <v>0</v>
       </c>
       <c r="M44" s="1">
         <v>0</v>
@@ -5384,19 +5396,19 @@
         <v>0</v>
       </c>
       <c r="O44" s="1">
-        <v>0.68303579092025757</v>
+        <v>0.56680899858474732</v>
       </c>
       <c r="P44" s="1">
-        <v>1.5776081085205078</v>
+        <v>1.3047416210174561</v>
       </c>
       <c r="Q44" s="1">
-        <v>-1.2609143257141113</v>
+        <v>0</v>
       </c>
       <c r="R44" s="1">
-        <v>4.5200934410095215</v>
+        <v>0</v>
       </c>
       <c r="S44" s="1">
-        <v>9.3616495132446289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -5410,52 +5422,52 @@
         <v>0</v>
       </c>
       <c r="D45" s="1">
-        <v>66.349037170410156</v>
+        <v>71.927200317382813</v>
       </c>
       <c r="E45" s="1">
-        <v>64.624092102050781</v>
+        <v>68.230331420898438</v>
       </c>
       <c r="F45" s="1">
-        <v>64.470008850097656</v>
+        <v>66.349678039550781</v>
       </c>
       <c r="G45" s="1">
-        <v>64.483314514160156</v>
+        <v>64.760208129882813</v>
       </c>
       <c r="H45" s="1">
-        <v>64.624092102050781</v>
+        <v>68.230331420898438</v>
       </c>
       <c r="I45" s="1">
-        <v>64.470008850097656</v>
+        <v>66.349678039550781</v>
       </c>
       <c r="J45" s="1">
-        <v>64.483314514160156</v>
+        <v>64.760208129882813</v>
       </c>
       <c r="K45" s="1">
-        <v>1.7335447072982788</v>
+        <v>1.1138042211532593</v>
       </c>
       <c r="L45" s="1">
-        <v>0.27920371294021606</v>
+        <v>61.830154418945313</v>
       </c>
       <c r="M45" s="1">
         <v>0</v>
       </c>
       <c r="N45" s="1">
-        <v>4.5350542068481445</v>
+        <v>0</v>
       </c>
       <c r="O45" s="1">
-        <v>5.0140829086303711</v>
+        <v>0.68303579092025757</v>
       </c>
       <c r="P45" s="1">
-        <v>5.6756038665771484</v>
+        <v>1.5776081085205078</v>
       </c>
       <c r="Q45" s="1">
-        <v>-0.0028829965740442276</v>
+        <v>-0.63844466209411621</v>
       </c>
       <c r="R45" s="1">
-        <v>0.010334892198443413</v>
+        <v>2.2886800765991211</v>
       </c>
       <c r="S45" s="1">
-        <v>0.02140478789806366</v>
+        <v>4.7401280403137207</v>
       </c>
     </row>
     <row r="46">
@@ -5472,28 +5484,28 @@
         <v>86.785316467285156</v>
       </c>
       <c r="E46" s="1">
-        <v>80.859710693359375</v>
+        <v>80.438003540039063</v>
       </c>
       <c r="F46" s="1">
-        <v>78.164665222167969</v>
+        <v>79.676734924316406</v>
       </c>
       <c r="G46" s="1">
-        <v>75.479133605957031</v>
+        <v>78.622695922851563</v>
       </c>
       <c r="H46" s="1">
-        <v>80.859710693359375</v>
+        <v>80.438003540039063</v>
       </c>
       <c r="I46" s="1">
-        <v>78.164665222167969</v>
+        <v>79.676734924316406</v>
       </c>
       <c r="J46" s="1">
-        <v>75.479133605957031</v>
+        <v>78.622695922851563</v>
       </c>
       <c r="K46" s="1">
         <v>5.2754936218261719</v>
       </c>
       <c r="L46" s="1">
-        <v>50.939029693603516</v>
+        <v>0</v>
       </c>
       <c r="M46" s="1">
         <v>0</v>
@@ -5508,13 +5520,13 @@
         <v>2.5169875621795654</v>
       </c>
       <c r="Q46" s="1">
-        <v>-0.52598530054092407</v>
+        <v>0</v>
       </c>
       <c r="R46" s="1">
-        <v>1.8855386972427368</v>
+        <v>0</v>
       </c>
       <c r="S46" s="1">
-        <v>3.9051744937896729</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -5531,28 +5543,28 @@
         <v>89.858207702636719</v>
       </c>
       <c r="E47" s="1">
-        <v>88.031982421875</v>
+        <v>87.537544250488281</v>
       </c>
       <c r="F47" s="1">
-        <v>83.644485473632813</v>
+        <v>85.417304992675781</v>
       </c>
       <c r="G47" s="1">
-        <v>79.9896240234375</v>
+        <v>83.675285339355469</v>
       </c>
       <c r="H47" s="1">
-        <v>88.031982421875</v>
+        <v>87.537544250488281</v>
       </c>
       <c r="I47" s="1">
-        <v>83.644485473632813</v>
+        <v>85.417304992675781</v>
       </c>
       <c r="J47" s="1">
-        <v>79.9896240234375</v>
+        <v>83.675285339355469</v>
       </c>
       <c r="K47" s="1">
         <v>8.960113525390625</v>
       </c>
       <c r="L47" s="1">
-        <v>100.47543334960938</v>
+        <v>42.794353485107422</v>
       </c>
       <c r="M47" s="1">
         <v>0</v>
@@ -5567,13 +5579,13 @@
         <v>35.591495513916016</v>
       </c>
       <c r="Q47" s="1">
-        <v>-1.037487268447876</v>
+        <v>-0.44188514351844788</v>
       </c>
       <c r="R47" s="1">
-        <v>3.7191579341888428</v>
+        <v>1.584058403968811</v>
       </c>
       <c r="S47" s="1">
-        <v>7.7028179168701172</v>
+        <v>3.2807731628417969</v>
       </c>
     </row>
   </sheetData>
@@ -5582,7 +5594,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5629,6 +5641,18 @@
         <v>112</v>
       </c>
       <c r="O1" t="s">
+        <v>113</v>
+      </c>
+      <c r="P1" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>115</v>
+      </c>
+      <c r="R1" t="s">
+        <v>116</v>
+      </c>
+      <c r="S1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -5640,13 +5664,13 @@
         <v>22.532503128051761</v>
       </c>
       <c r="C2" s="1">
-        <v>22.527645111083981</v>
+        <v>22.622074127197269</v>
       </c>
       <c r="D2" s="1">
         <v>21.33632850646973</v>
       </c>
       <c r="E2" s="1">
-        <v>21.42258262634277</v>
+        <v>21.517011642456051</v>
       </c>
       <c r="F2" s="1">
         <v>2.098418235778809</v>
@@ -5658,10 +5682,10 @@
         <v>4.7248601695613051</v>
       </c>
       <c r="I2" s="1">
-        <v>-0.45855069879978899</v>
+        <v>-0.90615629968353872</v>
       </c>
       <c r="J2" s="1">
-        <v>16.113849786571429</v>
+        <v>16.105702802192902</v>
       </c>
       <c r="K2" s="1">
         <v>100</v>
@@ -5669,13 +5693,25 @@
       <c r="L2" s="1">
         <v>0</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="1">
+        <v>0</v>
+      </c>
+      <c r="N2" s="1">
+        <v>0</v>
+      </c>
+      <c r="O2" s="1">
         <v>1</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R2" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="1">
+      <c r="S2" s="1">
         <v>46</v>
       </c>
     </row>
@@ -5687,13 +5723,13 @@
         <v>22.532503128051761</v>
       </c>
       <c r="C3" s="1">
-        <v>21.867099761962891</v>
+        <v>21.52976226806641</v>
       </c>
       <c r="D3" s="1">
         <v>21.33632850646973</v>
       </c>
       <c r="E3" s="1">
-        <v>20.761791229248051</v>
+        <v>20.42445182800293</v>
       </c>
       <c r="F3" s="1">
         <v>2.098418235778809</v>
@@ -5705,24 +5741,36 @@
         <v>7.1449146370557051</v>
       </c>
       <c r="I3" s="1">
-        <v>1.6438007223960529</v>
+        <v>3.2483657953797951</v>
       </c>
       <c r="J3" s="1">
-        <v>12.152605871467211</v>
+        <v>12.18396943111795</v>
       </c>
       <c r="K3" s="1">
-        <v>81.296461938225832</v>
+        <v>68.745519602817154</v>
       </c>
       <c r="L3" s="1">
         <v>0</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="1">
+        <v>2</v>
+      </c>
+      <c r="O3" s="1">
+        <v>2</v>
+      </c>
+      <c r="P3" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q3" t="s">
         <v>1</v>
       </c>
-      <c r="N3" t="s">
+      <c r="R3" t="s">
         <v>5</v>
       </c>
-      <c r="O3" s="1">
+      <c r="S3" s="1">
         <v>46</v>
       </c>
     </row>
@@ -5734,13 +5782,13 @@
         <v>22.532503128051761</v>
       </c>
       <c r="C4" s="1">
-        <v>21.13709831237793</v>
+        <v>20.438739776611332</v>
       </c>
       <c r="D4" s="1">
         <v>21.33632850646973</v>
       </c>
       <c r="E4" s="1">
-        <v>20.027591705322269</v>
+        <v>19.329233169555661</v>
       </c>
       <c r="F4" s="1">
         <v>2.098418235778809</v>
@@ -5752,24 +5800,36 @@
         <v>10.32599401582298</v>
       </c>
       <c r="I4" s="1">
-        <v>3.404506446363996</v>
+        <v>6.727751261922184</v>
       </c>
       <c r="J4" s="1">
-        <v>7.2291114380765036</v>
+        <v>7.2991843483800274</v>
       </c>
       <c r="K4" s="1">
-        <v>75.204789834574385</v>
+        <v>60.549714139909305</v>
       </c>
       <c r="L4" s="1">
+        <v>1</v>
+      </c>
+      <c r="M4" s="1">
         <v>2</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" s="1">
+        <v>3</v>
+      </c>
+      <c r="O4" s="1">
+        <v>3</v>
+      </c>
+      <c r="P4" s="1">
+        <v>6</v>
+      </c>
+      <c r="Q4" t="s">
         <v>1</v>
       </c>
-      <c r="N4" t="s">
+      <c r="R4" t="s">
         <v>5</v>
       </c>
-      <c r="O4" s="1">
+      <c r="S4" s="1">
         <v>46</v>
       </c>
     </row>
@@ -5784,15 +5844,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B2" s="1">
         <v>0.5</v>
@@ -5800,7 +5860,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B3" s="1">
         <v>0.029999999999999999</v>
@@ -5808,7 +5868,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B4" s="1">
         <v>0.18894011085868601</v>
@@ -5816,7 +5876,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B5" s="1">
         <v>0.1172495384343593</v>
@@ -5824,7 +5884,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B6" s="1">
         <v>0.36201603544677707</v>
@@ -5832,7 +5892,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B7" s="1">
         <v>5</v>
@@ -5840,7 +5900,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B8" s="1">
         <v>-0.42899999999999999</v>
@@ -5848,7 +5908,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B9" s="1">
         <v>0.14499999999999999</v>
@@ -5856,7 +5916,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B10" s="1">
         <v>0.69399999999999995</v>
@@ -5864,7 +5924,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B11" s="1">
         <v>0.22</v>
@@ -5872,7 +5932,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B12" s="1">
         <v>265</v>
@@ -5880,7 +5940,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B13" s="1">
         <v>4</v>
